--- a/LED_characterisation.xlsx
+++ b/LED_characterisation.xlsx
@@ -289,7 +289,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="124">
+  <cellXfs count="134">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -570,6 +570,32 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="23" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="18" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="23" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="18" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="18" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="18" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3037,7 +3063,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U16"/>
+  <dimension ref="A1:V16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3055,19 +3081,20 @@
     <col width="12" customWidth="1" min="17" max="18"/>
     <col width="46" customWidth="1" min="19" max="19"/>
     <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TEST A - Bench comparison at 4 m, 0 deg   (run 3, 0.2 mm wall)</t>
+          <t>TEST A - Bench comparison at 4 m, 0 deg   (run 4: reprinted caps, 4.5 s cure, blackout)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Blue on yellow = fill in.  Black = calculated.  Peak 200-230 is the controlled variable. RUN 3 FOCUS DIFFERS FROM RUN 2: the rig was rebuilt and the lens is sharper, so exposure, area and fill are NOT comparable across runs (same total flux, packed into 26% fewer pixels). Within run 3 everything is comparable. All diffused rows here are 0.2 mm wall; 0.4 and 0.5 mm are on G_Diffuser.</t>
+          <t>Blue on yellow = fill in.  Black = calculated.  Peak targeted 205-215. BLEND GATE IS NOW fill &gt;= 0.70, not 0.85: across 16 builds sigma improves with fill only up to ~0.65-0.70 and is flat above it (0.018-0.026 for every build, all four LEDs, against 10-15% repeatability). Above the knee you pay exposure for blending that buys no precision. Caps reprinted 4.5s cure, no supports, post-cured together. Focus locked, blackout, 4 m.</t>
         </is>
       </c>
     </row>
@@ -3193,6 +3220,12 @@
 (centre/rim)</t>
         </is>
       </c>
+      <c r="V3" s="8" t="inlineStr">
+        <is>
+          <t>Lobe
+(0=circular)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="9" t="inlineStr">
@@ -3240,7 +3273,7 @@
         <v>1.03</v>
       </c>
       <c r="O4" s="10">
-        <f>IF(OR(M4="",N4="",U4=""),"",IF(AND(M4=1,N4&gt;=0.9,N4&lt;=1.1,U4&gt;=0.85),"pass","FAIL"))</f>
+        <f>IF(OR(M4="",N4="",U4=""),"",IF(AND(M4=1,N4&gt;=0.9,N4&lt;=1.1,U4&gt;=0.70),"pass","FAIL"))</f>
         <v/>
       </c>
       <c r="P4" s="55" t="n">
@@ -3263,6 +3296,7 @@
         </is>
       </c>
       <c r="U4" s="13" t="n"/>
+      <c r="V4" s="124" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="15" t="inlineStr">
@@ -3297,7 +3331,7 @@
       <c r="M5" s="19" t="n"/>
       <c r="N5" s="21" t="n"/>
       <c r="O5" s="16">
-        <f>IF(OR(M5="",N5="",U5=""),"",IF(AND(M5=1,N5&gt;=0.9,N5&lt;=1.1,U5&gt;=0.85),"pass","FAIL"))</f>
+        <f>IF(OR(M5="",N5="",U5=""),"",IF(AND(M5=1,N5&gt;=0.9,N5&lt;=1.1,U5&gt;=0.70),"pass","FAIL"))</f>
         <v/>
       </c>
       <c r="P5" s="59" t="n"/>
@@ -3312,6 +3346,7 @@
       </c>
       <c r="T5" s="117" t="inlineStr"/>
       <c r="U5" s="21" t="n"/>
+      <c r="V5" s="39" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="25" t="inlineStr">
@@ -3346,7 +3381,7 @@
       <c r="M6" s="29" t="n"/>
       <c r="N6" s="31" t="n"/>
       <c r="O6" s="26">
-        <f>IF(OR(M6="",N6="",U6=""),"",IF(AND(M6=1,N6&gt;=0.9,N6&lt;=1.1,U6&gt;=0.85),"pass","FAIL"))</f>
+        <f>IF(OR(M6="",N6="",U6=""),"",IF(AND(M6=1,N6&gt;=0.9,N6&lt;=1.1,U6&gt;=0.70),"pass","FAIL"))</f>
         <v/>
       </c>
       <c r="P6" s="63" t="n"/>
@@ -3361,6 +3396,7 @@
       </c>
       <c r="T6" s="118" t="inlineStr"/>
       <c r="U6" s="31" t="n"/>
+      <c r="V6" s="41" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="25" t="inlineStr">
@@ -3395,7 +3431,7 @@
       <c r="M7" s="29" t="n"/>
       <c r="N7" s="31" t="n"/>
       <c r="O7" s="26">
-        <f>IF(OR(M7="",N7="",U7=""),"",IF(AND(M7=1,N7&gt;=0.9,N7&lt;=1.1,U7&gt;=0.85),"pass","FAIL"))</f>
+        <f>IF(OR(M7="",N7="",U7=""),"",IF(AND(M7=1,N7&gt;=0.9,N7&lt;=1.1,U7&gt;=0.70),"pass","FAIL"))</f>
         <v/>
       </c>
       <c r="P7" s="63" t="n"/>
@@ -3410,6 +3446,7 @@
       </c>
       <c r="T7" s="118" t="inlineStr"/>
       <c r="U7" s="31" t="n"/>
+      <c r="V7" s="41" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="25" t="inlineStr">
@@ -3444,7 +3481,7 @@
       <c r="M8" s="29" t="n"/>
       <c r="N8" s="31" t="n"/>
       <c r="O8" s="26">
-        <f>IF(OR(M8="",N8="",U8=""),"",IF(AND(M8=1,N8&gt;=0.9,N8&lt;=1.1,U8&gt;=0.85),"pass","FAIL"))</f>
+        <f>IF(OR(M8="",N8="",U8=""),"",IF(AND(M8=1,N8&gt;=0.9,N8&lt;=1.1,U8&gt;=0.70),"pass","FAIL"))</f>
         <v/>
       </c>
       <c r="P8" s="63" t="n"/>
@@ -3459,6 +3496,7 @@
       </c>
       <c r="T8" s="118" t="inlineStr"/>
       <c r="U8" s="31" t="n"/>
+      <c r="V8" s="41" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
@@ -3480,24 +3518,44 @@
       <c r="E9" s="57" t="n">
         <v>78.8</v>
       </c>
-      <c r="F9" s="19" t="n"/>
-      <c r="G9" s="19" t="n"/>
-      <c r="H9" s="58" t="n"/>
-      <c r="I9" s="19" t="n"/>
+      <c r="F9" s="19" t="n">
+        <v>215</v>
+      </c>
+      <c r="G9" s="19" t="n">
+        <v>213.6</v>
+      </c>
+      <c r="H9" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="19" t="n">
+        <v>0</v>
+      </c>
       <c r="J9" s="17">
         <f>IF(OR(F9="",G9="",G9=0),"",IF(H9&gt;0,"reduce light",ROUND(F9*210/G9/21.3,0)*21.3))</f>
         <v/>
       </c>
-      <c r="K9" s="19" t="n"/>
-      <c r="L9" s="19" t="n"/>
-      <c r="M9" s="19" t="n"/>
-      <c r="N9" s="21" t="n"/>
+      <c r="K9" s="19" t="n">
+        <v>437</v>
+      </c>
+      <c r="L9" s="19" t="n">
+        <v>658</v>
+      </c>
+      <c r="M9" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" s="21" t="n">
+        <v>1.04</v>
+      </c>
       <c r="O9" s="16">
-        <f>IF(OR(M9="",N9="",U9=""),"",IF(AND(M9=1,N9&gt;=0.9,N9&lt;=1.1,U9&gt;=0.85),"pass","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="P9" s="59" t="n"/>
-      <c r="Q9" s="59" t="n"/>
+        <f>IF(OR(M9="",N9="",U9=""),"",IF(AND(M9=1,N9&gt;=0.9,N9&lt;=1.1,U9&gt;=0.70),"pass","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="P9" s="59" t="n">
+        <v>0.0347</v>
+      </c>
+      <c r="Q9" s="59" t="n">
+        <v>0.0405</v>
+      </c>
       <c r="R9" s="60">
         <f>IF(OR(P9="",Q9=""),"",SQRT(0.5*(P9^2+Q9^2)))</f>
         <v/>
@@ -3506,8 +3564,17 @@
         <f>IF(OR(P9="",Q9="",P9=0),"",Q9/P9)</f>
         <v/>
       </c>
-      <c r="T9" s="117" t="inlineStr"/>
-      <c r="U9" s="21" t="n"/>
+      <c r="T9" s="117" t="inlineStr">
+        <is>
+          <t>cap 1. Worst blend of the study: fill 0.53 AND lobe 0.120 - the only build where the four LEDs are still azimuthally distinct (everything else 0.057-0.082). Also the shortest exposure (215 us = 0.3 px smear) and the worst sigma (0.0377).  flux 434, blend FAIL</t>
+        </is>
+      </c>
+      <c r="U9" s="21" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="V9" s="39" t="n">
+        <v>0.12</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="25" t="inlineStr">
@@ -3529,24 +3596,44 @@
       <c r="E10" s="53" t="n">
         <v>38.2</v>
       </c>
-      <c r="F10" s="29" t="n"/>
-      <c r="G10" s="29" t="n"/>
-      <c r="H10" s="62" t="n"/>
-      <c r="I10" s="29" t="n"/>
+      <c r="F10" s="29" t="n">
+        <v>2282</v>
+      </c>
+      <c r="G10" s="29" t="n">
+        <v>208.7</v>
+      </c>
+      <c r="H10" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="29" t="n">
+        <v>0</v>
+      </c>
       <c r="J10" s="27">
         <f>IF(OR(F10="",G10="",G10=0),"",IF(H10&gt;0,"reduce light",ROUND(F10*210/G10/21.3,0)*21.3))</f>
         <v/>
       </c>
-      <c r="K10" s="29" t="n"/>
-      <c r="L10" s="29" t="n"/>
-      <c r="M10" s="29" t="n"/>
-      <c r="N10" s="31" t="n"/>
+      <c r="K10" s="29" t="n">
+        <v>774</v>
+      </c>
+      <c r="L10" s="29" t="n">
+        <v>866</v>
+      </c>
+      <c r="M10" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" s="31" t="n">
+        <v>1.03</v>
+      </c>
       <c r="O10" s="26">
-        <f>IF(OR(M10="",N10="",U10=""),"",IF(AND(M10=1,N10&gt;=0.9,N10&lt;=1.1,U10&gt;=0.85),"pass","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="P10" s="63" t="n"/>
-      <c r="Q10" s="63" t="n"/>
+        <f>IF(OR(M10="",N10="",U10=""),"",IF(AND(M10=1,N10&gt;=0.9,N10&lt;=1.1,U10&gt;=0.70),"pass","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="P10" s="63" t="n">
+        <v>0.0188</v>
+      </c>
+      <c r="Q10" s="63" t="n">
+        <v>0.0211</v>
+      </c>
       <c r="R10" s="64">
         <f>IF(OR(P10="",Q10=""),"",SQRT(0.5*(P10^2+Q10^2)))</f>
         <v/>
@@ -3555,8 +3642,17 @@
         <f>IF(OR(P10="",Q10="",P10=0),"",Q10/P10)</f>
         <v/>
       </c>
-      <c r="T10" s="118" t="inlineStr"/>
-      <c r="U10" s="31" t="n"/>
+      <c r="T10" s="118" t="inlineStr">
+        <is>
+          <t>cap 1. Lobe 0.057 is the lowest of the study - confirms all four LEDs survived the reversed connection. Intermediate on every axis, as beam angle predicts.  flux 71, blend FAIL</t>
+        </is>
+      </c>
+      <c r="U10" s="31" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="V10" s="41" t="n">
+        <v>0.057</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="25" t="inlineStr">
@@ -3578,24 +3674,44 @@
       <c r="E11" s="53" t="n">
         <v>21.7</v>
       </c>
-      <c r="F11" s="29" t="n"/>
-      <c r="G11" s="29" t="n"/>
-      <c r="H11" s="62" t="n"/>
-      <c r="I11" s="29" t="n"/>
+      <c r="F11" s="29" t="n">
+        <v>5967</v>
+      </c>
+      <c r="G11" s="29" t="n">
+        <v>205.1</v>
+      </c>
+      <c r="H11" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="29" t="n">
+        <v>0</v>
+      </c>
       <c r="J11" s="27">
         <f>IF(OR(F11="",G11="",G11=0),"",IF(H11&gt;0,"reduce light",ROUND(F11*210/G11/21.3,0)*21.3))</f>
         <v/>
       </c>
-      <c r="K11" s="29" t="n"/>
-      <c r="L11" s="29" t="n"/>
-      <c r="M11" s="29" t="n"/>
-      <c r="N11" s="31" t="n"/>
+      <c r="K11" s="29" t="n">
+        <v>816</v>
+      </c>
+      <c r="L11" s="29" t="n">
+        <v>921</v>
+      </c>
+      <c r="M11" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" s="31" t="n">
+        <v>1.01</v>
+      </c>
       <c r="O11" s="26">
-        <f>IF(OR(M11="",N11="",U11=""),"",IF(AND(M11=1,N11&gt;=0.9,N11&lt;=1.1,U11&gt;=0.85),"pass","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="P11" s="63" t="n"/>
-      <c r="Q11" s="63" t="n"/>
+        <f>IF(OR(M11="",N11="",U11=""),"",IF(AND(M11=1,N11&gt;=0.9,N11&lt;=1.1,U11&gt;=0.70),"pass","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="P11" s="63" t="n">
+        <v>0.0177</v>
+      </c>
+      <c r="Q11" s="63" t="n">
+        <v>0.032</v>
+      </c>
       <c r="R11" s="64">
         <f>IF(OR(P11="",Q11=""),"",SQRT(0.5*(P11^2+Q11^2)))</f>
         <v/>
@@ -3604,8 +3720,17 @@
         <f>IF(OR(P11="",Q11="",P11=0),"",Q11/P11)</f>
         <v/>
       </c>
-      <c r="T11" s="118" t="inlineStr"/>
-      <c r="U11" s="31" t="n"/>
+      <c r="T11" s="118" t="inlineStr">
+        <is>
+          <t>cap 1. Fills FAR better than Kingbright (0.82 vs 0.59-0.67) and the rim is nearly circular (lobe 0.065). Confirms beam angle dominates over shell geometry. Cost: 5967 us.  flux 28, blend FAIL</t>
+        </is>
+      </c>
+      <c r="U11" s="31" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="V11" s="41" t="n">
+        <v>0.065</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="25" t="inlineStr">
@@ -3628,10 +3753,10 @@
         <v>38.2</v>
       </c>
       <c r="F12" s="29" t="n">
-        <v>790</v>
+        <v>539</v>
       </c>
       <c r="G12" s="29" t="n">
-        <v>208.1</v>
+        <v>212.7</v>
       </c>
       <c r="H12" s="62" t="n">
         <v>0</v>
@@ -3644,26 +3769,26 @@
         <v/>
       </c>
       <c r="K12" s="29" t="n">
-        <v>506</v>
+        <v>603</v>
       </c>
       <c r="L12" s="29" t="n">
-        <v>676</v>
+        <v>729</v>
       </c>
       <c r="M12" s="29" t="n">
         <v>1</v>
       </c>
       <c r="N12" s="31" t="n">
-        <v>0.96</v>
+        <v>1.03</v>
       </c>
       <c r="O12" s="26">
-        <f>IF(OR(M12="",N12="",U12=""),"",IF(AND(M12=1,N12&gt;=0.9,N12&lt;=1.1,U12&gt;=0.85),"pass","FAIL"))</f>
+        <f>IF(OR(M12="",N12="",U12=""),"",IF(AND(M12=1,N12&gt;=0.9,N12&lt;=1.1,U12&gt;=0.70),"pass","FAIL"))</f>
         <v/>
       </c>
       <c r="P12" s="63" t="n">
+        <v>0.0233</v>
+      </c>
+      <c r="Q12" s="63" t="n">
         <v>0.0263</v>
-      </c>
-      <c r="Q12" s="63" t="n">
-        <v>0.0267</v>
       </c>
       <c r="R12" s="64">
         <f>IF(OR(P12="",Q12=""),"",SQRT(0.5*(P12^2+Q12^2)))</f>
@@ -3675,11 +3800,14 @@
       </c>
       <c r="T12" s="118" t="inlineStr">
         <is>
-          <t>Run 3 baseline for the 0.4/0.5 ladder.  peak 208.1 (max 222), sat 0, blend FAIL, sig_v/sig_u 1.02</t>
+          <t>cap 1, re-seat #2 (first fit: 557us area638 fill0.59 sigma0.0270). Repeats to 5% area, 0.01 fill, 8% sigma - the new no-support post-cured caps are twice as repeatable as the old ones (was 16% on sigma). Lobe 0.082 vs XL 0.059: azimuthally blended, so this is an ANNULUS not four lobes.  flux 238, blend FAIL</t>
         </is>
       </c>
       <c r="U12" s="31" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
+      </c>
+      <c r="V12" s="41" t="n">
+        <v>0.082</v>
       </c>
     </row>
     <row r="13">
@@ -3702,24 +3830,44 @@
       <c r="E13" s="57" t="n">
         <v>78.8</v>
       </c>
-      <c r="F13" s="19" t="n"/>
-      <c r="G13" s="19" t="n"/>
-      <c r="H13" s="58" t="n"/>
-      <c r="I13" s="19" t="n"/>
+      <c r="F13" s="19" t="n">
+        <v>503</v>
+      </c>
+      <c r="G13" s="19" t="n">
+        <v>211</v>
+      </c>
+      <c r="H13" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="19" t="n">
+        <v>0</v>
+      </c>
       <c r="J13" s="17">
         <f>IF(OR(F13="",G13="",G13=0),"",IF(H13&gt;0,"reduce light",ROUND(F13*210/G13/21.3,0)*21.3))</f>
         <v/>
       </c>
-      <c r="K13" s="19" t="n"/>
-      <c r="L13" s="19" t="n"/>
-      <c r="M13" s="19" t="n"/>
-      <c r="N13" s="21" t="n"/>
+      <c r="K13" s="19" t="n">
+        <v>718</v>
+      </c>
+      <c r="L13" s="19" t="n">
+        <v>811</v>
+      </c>
+      <c r="M13" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" s="21" t="n">
+        <v>1.02</v>
+      </c>
       <c r="O13" s="16">
-        <f>IF(OR(M13="",N13="",U13=""),"",IF(AND(M13=1,N13&gt;=0.9,N13&lt;=1.1,U13&gt;=0.85),"pass","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="P13" s="59" t="n"/>
-      <c r="Q13" s="59" t="n"/>
+        <f>IF(OR(M13="",N13="",U13=""),"",IF(AND(M13=1,N13&gt;=0.9,N13&lt;=1.1,U13&gt;=0.70),"pass","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="P13" s="59" t="n">
+        <v>0.0206</v>
+      </c>
+      <c r="Q13" s="59" t="n">
+        <v>0.0246</v>
+      </c>
       <c r="R13" s="60">
         <f>IF(OR(P13="",Q13=""),"",SQRT(0.5*(P13^2+Q13^2)))</f>
         <v/>
@@ -3728,8 +3876,17 @@
         <f>IF(OR(P13="",Q13="",P13=0),"",Q13/P13)</f>
         <v/>
       </c>
-      <c r="T13" s="117" t="inlineStr"/>
-      <c r="U13" s="21" t="n"/>
+      <c r="T13" s="117" t="inlineStr">
+        <is>
+          <t>cap 1. Biggest single improvement in the study: diameter gives +0.18 fill (0.53-&gt;0.71), lobe 0.120-&gt;0.067, sigma 40% better. Sigma now EQUALS Everlight 25/0.2 (0.0227 vs 0.0228) at 7x less smear (0.65 vs 4.5 px) - fails the fill gate but may win on the tracking criterion.  flux 301, blend FAIL</t>
+        </is>
+      </c>
+      <c r="U13" s="21" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="V13" s="39" t="n">
+        <v>0.067</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="25" t="inlineStr">
@@ -3751,24 +3908,44 @@
       <c r="E14" s="53" t="n">
         <v>38.2</v>
       </c>
-      <c r="F14" s="29" t="n"/>
-      <c r="G14" s="29" t="n"/>
-      <c r="H14" s="62" t="n"/>
-      <c r="I14" s="29" t="n"/>
+      <c r="F14" s="29" t="n">
+        <v>3469</v>
+      </c>
+      <c r="G14" s="29" t="n">
+        <v>211.6</v>
+      </c>
+      <c r="H14" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="29" t="n">
+        <v>0</v>
+      </c>
       <c r="J14" s="27">
         <f>IF(OR(F14="",G14="",G14=0),"",IF(H14&gt;0,"reduce light",ROUND(F14*210/G14/21.3,0)*21.3))</f>
         <v/>
       </c>
-      <c r="K14" s="29" t="n"/>
-      <c r="L14" s="29" t="n"/>
-      <c r="M14" s="29" t="n"/>
-      <c r="N14" s="31" t="n"/>
+      <c r="K14" s="29" t="n">
+        <v>883</v>
+      </c>
+      <c r="L14" s="29" t="n">
+        <v>997</v>
+      </c>
+      <c r="M14" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" s="31" t="n">
+        <v>1.03</v>
+      </c>
       <c r="O14" s="26">
-        <f>IF(OR(M14="",N14="",U14=""),"",IF(AND(M14=1,N14&gt;=0.9,N14&lt;=1.1,U14&gt;=0.85),"pass","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="P14" s="63" t="n"/>
-      <c r="Q14" s="63" t="n"/>
+        <f>IF(OR(M14="",N14="",U14=""),"",IF(AND(M14=1,N14&gt;=0.9,N14&lt;=1.1,U14&gt;=0.70),"pass","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="P14" s="63" t="n">
+        <v>0.0158</v>
+      </c>
+      <c r="Q14" s="63" t="n">
+        <v>0.0281</v>
+      </c>
       <c r="R14" s="64">
         <f>IF(OR(P14="",Q14=""),"",SQRT(0.5*(P14^2+Q14^2)))</f>
         <v/>
@@ -3777,8 +3954,17 @@
         <f>IF(OR(P14="",Q14="",P14=0),"",Q14/P14)</f>
         <v/>
       </c>
-      <c r="T14" s="118" t="inlineStr"/>
-      <c r="U14" s="31" t="n"/>
+      <c r="T14" s="118" t="inlineStr">
+        <is>
+          <t>cap 1. PASSES THE BLEND GATE at 0.92, and at 3469 us that is 2.4x less smear than XL 25/0.2 needs for fill 1.00. Diameter is again the strong lever: fill 0.77 -&gt; 0.92 for only 1.52x exposure.  flux 54, blend pass</t>
+        </is>
+      </c>
+      <c r="U14" s="31" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="V14" s="41" t="n">
+        <v>0.064</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="25" t="inlineStr">
@@ -3800,24 +3986,44 @@
       <c r="E15" s="53" t="n">
         <v>21.7</v>
       </c>
-      <c r="F15" s="29" t="n"/>
-      <c r="G15" s="29" t="n"/>
-      <c r="H15" s="62" t="n"/>
-      <c r="I15" s="29" t="n"/>
+      <c r="F15" s="29" t="n">
+        <v>8196</v>
+      </c>
+      <c r="G15" s="29" t="n">
+        <v>215</v>
+      </c>
+      <c r="H15" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="29" t="n">
+        <v>0</v>
+      </c>
       <c r="J15" s="27">
         <f>IF(OR(F15="",G15="",G15=0),"",IF(H15&gt;0,"reduce light",ROUND(F15*210/G15/21.3,0)*21.3))</f>
         <v/>
       </c>
-      <c r="K15" s="29" t="n"/>
-      <c r="L15" s="29" t="n"/>
-      <c r="M15" s="29" t="n"/>
-      <c r="N15" s="31" t="n"/>
+      <c r="K15" s="29" t="n">
+        <v>954</v>
+      </c>
+      <c r="L15" s="29" t="n">
+        <v>1069</v>
+      </c>
+      <c r="M15" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="N15" s="31" t="n">
+        <v>1.02</v>
+      </c>
       <c r="O15" s="26">
-        <f>IF(OR(M15="",N15="",U15=""),"",IF(AND(M15=1,N15&gt;=0.9,N15&lt;=1.1,U15&gt;=0.85),"pass","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="P15" s="63" t="n"/>
-      <c r="Q15" s="63" t="n"/>
+        <f>IF(OR(M15="",N15="",U15=""),"",IF(AND(M15=1,N15&gt;=0.9,N15&lt;=1.1,U15&gt;=0.70),"pass","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="P15" s="63" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="Q15" s="63" t="n">
+        <v>0.021</v>
+      </c>
       <c r="R15" s="64">
         <f>IF(OR(P15="",Q15=""),"",SQRT(0.5*(P15^2+Q15^2)))</f>
         <v/>
@@ -3826,8 +4032,17 @@
         <f>IF(OR(P15="",Q15="",P15=0),"",Q15/P15)</f>
         <v/>
       </c>
-      <c r="T15" s="118" t="inlineStr"/>
-      <c r="U15" s="31" t="n"/>
+      <c r="T15" s="118" t="inlineStr">
+        <is>
+          <t>cap 1. BEST BUILD OF THE STUDY on optics: fill 1.00 (centre as bright as rim), lobe 0.059, largest area 954, lowest sigma 0.0186. For XL diameter is the strong lever (fill 0.82-&gt;1.00) and thickness the weak one (0.82-&gt;0.85).  flux 25, blend pass</t>
+        </is>
+      </c>
+      <c r="U15" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="V15" s="41" t="n">
+        <v>0.059</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="25" t="inlineStr">
@@ -3850,10 +4065,10 @@
         <v>38.2</v>
       </c>
       <c r="F16" s="29" t="n">
-        <v>790</v>
+        <v>1114</v>
       </c>
       <c r="G16" s="29" t="n">
-        <v>213.7</v>
+        <v>213.5</v>
       </c>
       <c r="H16" s="62" t="n">
         <v>0</v>
@@ -3866,26 +4081,26 @@
         <v/>
       </c>
       <c r="K16" s="29" t="n">
-        <v>603</v>
+        <v>692</v>
       </c>
       <c r="L16" s="29" t="n">
-        <v>685</v>
+        <v>778</v>
       </c>
       <c r="M16" s="29" t="n">
         <v>1</v>
       </c>
       <c r="N16" s="31" t="n">
-        <v>0.99</v>
+        <v>1.03</v>
       </c>
       <c r="O16" s="26">
-        <f>IF(OR(M16="",N16="",U16=""),"",IF(AND(M16=1,N16&gt;=0.9,N16&lt;=1.1,U16&gt;=0.85),"pass","FAIL"))</f>
+        <f>IF(OR(M16="",N16="",U16=""),"",IF(AND(M16=1,N16&gt;=0.9,N16&lt;=1.1,U16&gt;=0.70),"pass","FAIL"))</f>
         <v/>
       </c>
       <c r="P16" s="63" t="n">
-        <v>0.0257</v>
+        <v>0.0186</v>
       </c>
       <c r="Q16" s="63" t="n">
-        <v>0.0272</v>
+        <v>0.027</v>
       </c>
       <c r="R16" s="64">
         <f>IF(OR(P16="",Q16=""),"",SQRT(0.5*(P16^2+Q16^2)))</f>
@@ -3897,11 +4112,14 @@
       </c>
       <c r="T16" s="118" t="inlineStr">
         <is>
-          <t>RE-SEAT CONTROL of the same cap. First fit: 808us peak202 area611 fill0.67 sigma0.0227. Area and fill reproduce to 1-2%; sigma moved 16%. Real build uncertainty on sigma is ~16%, not the 3% measured without re-seating.  peak 213.7 (max 233), sat 0, blend FAIL, sig_v/sig_u 1.06</t>
+          <t>cap 1, re-seat #2 (first: 1132us area702 fill0.66 sigma0.0221). Repeats to 1% area, 0.00 fill, 5% sigma.  flux 133, blend FAIL</t>
         </is>
       </c>
       <c r="U16" s="31" t="n">
         <v>0.66</v>
+      </c>
+      <c r="V16" s="41" t="n">
+        <v>0.07099999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -6083,3150 +6301,1042 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K107"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <dimension ref="A1:R27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="6"/>
-    <col width="12" customWidth="1" min="7" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="34" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="7" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="9" customWidth="1" min="16" max="16"/>
+    <col width="9" customWidth="1" min="17" max="17"/>
+    <col width="34" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>TEST B - Angular response (off-axis) and roll (centroid bias)</t>
+    <row r="1">
+      <c r="A1" s="65" t="inlineStr">
+        <is>
+          <t>TEST B - Isotropy: head-on (0 deg) vs upright (90 deg)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
-        <is>
-          <t>Blue on yellow = fill in.  Black = calculated.  Each diffused marker holds FOUR LEDs in series off 9 V; 'bare (ref)' is a single LED, kept as a reference and never ranked.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A2" s="66" t="inlineStr">
+        <is>
+          <t>The LEDs sit on a flat PCB, so 0 deg looks down the emission axis and 90 deg views it from the side - the extreme of beam angle. A spherical diffuser should make the marker look the SAME from both. The 90/0 ratios are the test: near 1.00 = isotropic. Add 45 deg ONLY if 0 and 90 diverge. 25 mm builds only; marker is moved, camera is NOT - rotating the camera changes framing, background and focus distance all at once.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="77" t="inlineStr">
         <is>
           <t>LED Type</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="C3" s="8" t="inlineStr">
-        <is>
-          <t>Sample</t>
-        </is>
-      </c>
-      <c r="D3" s="8" t="inlineStr">
+      <c r="B4" s="77" t="inlineStr">
+        <is>
+          <t>Wall
+(mm)</t>
+        </is>
+      </c>
+      <c r="C4" s="77" t="inlineStr">
         <is>
           <t>Angle
 (deg)</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="D4" s="77" t="inlineStr">
         <is>
           <t>Exposure
 (us)</t>
         </is>
       </c>
-      <c r="F3" s="8" t="inlineStr">
-        <is>
-          <t>Peak
-(0-255)</t>
-        </is>
-      </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="E4" s="77" t="inlineStr">
+        <is>
+          <t>Peak</t>
+        </is>
+      </c>
+      <c r="F4" s="77" t="inlineStr">
         <is>
           <t>Sensor area
 (px)</t>
         </is>
       </c>
-      <c r="H3" s="8" t="inlineStr">
+      <c r="G4" s="77" t="inlineStr">
+        <is>
+          <t>npix</t>
+        </is>
+      </c>
+      <c r="H4" s="77" t="inlineStr">
         <is>
           <t>blobs</t>
         </is>
       </c>
-      <c r="I3" s="8" t="inlineStr">
-        <is>
-          <t>Area vs 0 deg</t>
-        </is>
-      </c>
-      <c r="J3" s="8" t="inlineStr">
-        <is>
-          <t>Peak vs 0 deg</t>
-        </is>
-      </c>
-      <c r="K3" s="8" t="inlineStr">
+      <c r="I4" s="77" t="inlineStr">
+        <is>
+          <t>w/h</t>
+        </is>
+      </c>
+      <c r="J4" s="77" t="inlineStr">
+        <is>
+          <t>Fill</t>
+        </is>
+      </c>
+      <c r="K4" s="77" t="inlineStr">
+        <is>
+          <t>Lobe</t>
+        </is>
+      </c>
+      <c r="L4" s="77" t="inlineStr">
+        <is>
+          <t>sigma_u
+(px)</t>
+        </is>
+      </c>
+      <c r="M4" s="77" t="inlineStr">
+        <is>
+          <t>sigma_v
+(px)</t>
+        </is>
+      </c>
+      <c r="N4" s="77" t="inlineStr">
+        <is>
+          <t>sigma_RMS
+(px)</t>
+        </is>
+      </c>
+      <c r="O4" s="77" t="inlineStr">
+        <is>
+          <t>Exposure
+90/0</t>
+        </is>
+      </c>
+      <c r="P4" s="77" t="inlineStr">
+        <is>
+          <t>Area
+90/0</t>
+        </is>
+      </c>
+      <c r="Q4" s="77" t="inlineStr">
+        <is>
+          <t>Fill
+90/0</t>
+        </is>
+      </c>
+      <c r="R4" s="77" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="128" t="inlineStr">
         <is>
           <t>Vishay</t>
         </is>
       </c>
-      <c r="B4" s="16" t="inlineStr">
-        <is>
-          <t>bare (ref)</t>
-        </is>
-      </c>
-      <c r="C4" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" s="17" t="n">
+      <c r="B5" s="101" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C5" s="100" t="n">
         <v>0</v>
       </c>
-      <c r="E4" s="19" t="n"/>
-      <c r="F4" s="19" t="n"/>
-      <c r="G4" s="19" t="n"/>
-      <c r="H4" s="19" t="n"/>
-      <c r="I4" s="67">
-        <f>IF(OR(G4="",G$4=""),"",G4/G$4)</f>
-        <v/>
-      </c>
-      <c r="J4" s="67">
-        <f>IF(OR(F4="",F$4=""),"",F4/F$4)</f>
-        <v/>
-      </c>
-      <c r="K4" s="24" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="25" t="inlineStr">
+      <c r="D5" s="129" t="n">
+        <v>485</v>
+      </c>
+      <c r="E5" s="129" t="n">
+        <v>211.1</v>
+      </c>
+      <c r="F5" s="129" t="n">
+        <v>703</v>
+      </c>
+      <c r="G5" s="129" t="n">
+        <v>794</v>
+      </c>
+      <c r="H5" s="129" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="130" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" s="130" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K5" s="131" t="n">
+        <v>0.08400000000000001</v>
+      </c>
+      <c r="L5" s="132" t="n">
+        <v>0.0251</v>
+      </c>
+      <c r="M5" s="132" t="n">
+        <v>0.0336</v>
+      </c>
+      <c r="N5" s="107">
+        <f>IF(OR(L5="",M5=""),"",SQRT(0.5*(L5^2+M5^2)))</f>
+        <v/>
+      </c>
+      <c r="O5" s="108" t="n"/>
+      <c r="P5" s="108" t="n"/>
+      <c r="Q5" s="108" t="n"/>
+      <c r="R5" s="110" t="inlineStr">
+        <is>
+          <t>cap 1, head-on baseline for the thin-wall Vishay.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="133" t="inlineStr">
         <is>
           <t>Vishay</t>
         </is>
       </c>
-      <c r="B5" s="26" t="inlineStr">
-        <is>
-          <t>bare (ref)</t>
-        </is>
-      </c>
-      <c r="C5" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" s="27" t="n">
-        <v>15</v>
-      </c>
-      <c r="E5" s="29" t="n"/>
-      <c r="F5" s="29" t="n"/>
-      <c r="G5" s="29" t="n"/>
-      <c r="H5" s="29" t="n"/>
-      <c r="I5" s="68">
-        <f>IF(OR(G5="",G$4=""),"",G5/G$4)</f>
-        <v/>
-      </c>
-      <c r="J5" s="68">
-        <f>IF(OR(F5="",F$4=""),"",F5/F$4)</f>
-        <v/>
-      </c>
-      <c r="K5" s="34" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="25" t="inlineStr">
+      <c r="B6" s="86" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C6" s="85" t="n">
+        <v>90</v>
+      </c>
+      <c r="D6" s="74" t="n">
+        <v>6183</v>
+      </c>
+      <c r="E6" s="74" t="n">
+        <v>204.5</v>
+      </c>
+      <c r="F6" s="74" t="n">
+        <v>1018</v>
+      </c>
+      <c r="G6" s="74" t="n">
+        <v>1129</v>
+      </c>
+      <c r="H6" s="74" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="79" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="J6" s="79" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="K6" s="126" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="L6" s="83" t="n">
+        <v>0.0193</v>
+      </c>
+      <c r="M6" s="83" t="n">
+        <v>0.0167</v>
+      </c>
+      <c r="N6" s="84">
+        <f>IF(OR(L6="",M6=""),"",SQRT(0.5*(L6^2+M6^2)))</f>
+        <v/>
+      </c>
+      <c r="O6" s="75">
+        <f>IF(OR(D6="",D5=""),"",D6/D5)</f>
+        <v/>
+      </c>
+      <c r="P6" s="75">
+        <f>IF(OR(F6="",F5=""),"",F6/F5)</f>
+        <v/>
+      </c>
+      <c r="Q6" s="75">
+        <f>IF(OR(J6="",J5=""),"",J6/J5)</f>
+        <v/>
+      </c>
+      <c r="R6" s="81" t="inlineStr">
+        <is>
+          <t>12.7x anisotropy - WORSE than the 0.4mm wall's 8.8x, as predicted. Thickness buys isotropy (31% less anisotropic) even though it barely moved fill or sigma at 25 mm. That is a new and better reason to prefer the thicker shell.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="133" t="inlineStr">
         <is>
           <t>Vishay</t>
         </is>
       </c>
-      <c r="B6" s="26" t="inlineStr">
-        <is>
-          <t>bare (ref)</t>
-        </is>
-      </c>
-      <c r="C6" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" s="27" t="n">
-        <v>30</v>
-      </c>
-      <c r="E6" s="29" t="n"/>
-      <c r="F6" s="29" t="n"/>
-      <c r="G6" s="29" t="n"/>
-      <c r="H6" s="29" t="n"/>
-      <c r="I6" s="68">
-        <f>IF(OR(G6="",G$4=""),"",G6/G$4)</f>
-        <v/>
-      </c>
-      <c r="J6" s="68">
-        <f>IF(OR(F6="",F$4=""),"",F6/F$4)</f>
-        <v/>
-      </c>
-      <c r="K6" s="34" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="25" t="inlineStr">
+      <c r="B7" s="86" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C7" s="85" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="74" t="n">
+        <v>557</v>
+      </c>
+      <c r="E7" s="74" t="n">
+        <v>203.5</v>
+      </c>
+      <c r="F7" s="74" t="n">
+        <v>742</v>
+      </c>
+      <c r="G7" s="74" t="n">
+        <v>838</v>
+      </c>
+      <c r="H7" s="74" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="79" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="J7" s="79" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="K7" s="126" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="L7" s="83" t="n">
+        <v>0.0248</v>
+      </c>
+      <c r="M7" s="83" t="n">
+        <v>0.0219</v>
+      </c>
+      <c r="N7" s="84">
+        <f>IF(OR(L7="",M7=""),"",SQRT(0.5*(L7^2+M7^2)))</f>
+        <v/>
+      </c>
+      <c r="O7" s="75" t="n"/>
+      <c r="P7" s="75" t="n"/>
+      <c r="Q7" s="75" t="n"/>
+      <c r="R7" s="81" t="inlineStr">
+        <is>
+          <t>cap 1, head-on baseline. Consistent with the 4-cap mean (602us, area 751, fill 0.74, sigma 0.0240) - all inside the measured spread.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="133" t="inlineStr">
         <is>
           <t>Vishay</t>
         </is>
       </c>
-      <c r="B7" s="26" t="inlineStr">
-        <is>
-          <t>bare (ref)</t>
-        </is>
-      </c>
-      <c r="C7" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" s="27" t="n">
-        <v>45</v>
-      </c>
-      <c r="E7" s="29" t="n"/>
-      <c r="F7" s="29" t="n"/>
-      <c r="G7" s="29" t="n"/>
-      <c r="H7" s="29" t="n"/>
-      <c r="I7" s="68">
-        <f>IF(OR(G7="",G$4=""),"",G7/G$4)</f>
-        <v/>
-      </c>
-      <c r="J7" s="68">
-        <f>IF(OR(F7="",F$4=""),"",F7/F$4)</f>
-        <v/>
-      </c>
-      <c r="K7" s="34" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="25" t="inlineStr">
-        <is>
-          <t>Vishay</t>
-        </is>
-      </c>
-      <c r="B8" s="26" t="inlineStr">
-        <is>
-          <t>bare (ref)</t>
-        </is>
-      </c>
-      <c r="C8" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" s="27" t="n">
-        <v>60</v>
-      </c>
-      <c r="E8" s="29" t="n"/>
-      <c r="F8" s="29" t="n"/>
-      <c r="G8" s="29" t="n"/>
-      <c r="H8" s="29" t="n"/>
-      <c r="I8" s="68">
-        <f>IF(OR(G8="",G$4=""),"",G8/G$4)</f>
-        <v/>
-      </c>
-      <c r="J8" s="68">
-        <f>IF(OR(F8="",F$4=""),"",F8/F$4)</f>
-        <v/>
-      </c>
-      <c r="K8" s="34" t="n"/>
+      <c r="B8" s="86" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C8" s="85" t="n">
+        <v>90</v>
+      </c>
+      <c r="D8" s="74" t="n">
+        <v>4925</v>
+      </c>
+      <c r="E8" s="74" t="n">
+        <v>199.7</v>
+      </c>
+      <c r="F8" s="74" t="n">
+        <v>978</v>
+      </c>
+      <c r="G8" s="74" t="n">
+        <v>1097</v>
+      </c>
+      <c r="H8" s="74" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="79" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="J8" s="79" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K8" s="126" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="L8" s="83" t="n">
+        <v>0.0198</v>
+      </c>
+      <c r="M8" s="83" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="N8" s="84">
+        <f>IF(OR(L8="",M8=""),"",SQRT(0.5*(L8^2+M8^2)))</f>
+        <v/>
+      </c>
+      <c r="O8" s="75">
+        <f>IF(OR(D8="",D7=""),"",D8/D7)</f>
+        <v/>
+      </c>
+      <c r="P8" s="75">
+        <f>IF(OR(F8="",F7=""),"",F8/F7)</f>
+        <v/>
+      </c>
+      <c r="Q8" s="75">
+        <f>IF(OR(J8="",J7=""),"",J8/J7)</f>
+        <v/>
+      </c>
+      <c r="R8" s="81" t="inlineStr">
+        <is>
+          <t>8.8x MORE EXPOSURE than head-on. Optically better from the side (fill 0.73-&gt;1.02, area +32%, sigma 0.0234-&gt;0.0185) because you see the shell wall lit at grazing incidence rather than the LEDs' direct beams - but 8.8x exceeds the ~3x dynamic range between THRESH_LO and saturation, so no fixed exposure covers both views.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="25" t="inlineStr">
+      <c r="A9" s="128" t="inlineStr">
+        <is>
+          <t>Kingbright</t>
+        </is>
+      </c>
+      <c r="B9" s="101" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C9" s="100" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="129" t="n">
+        <v>952</v>
+      </c>
+      <c r="E9" s="129" t="n">
+        <v>213.5</v>
+      </c>
+      <c r="F9" s="129" t="n">
+        <v>676</v>
+      </c>
+      <c r="G9" s="129" t="n">
+        <v>762</v>
+      </c>
+      <c r="H9" s="129" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="130" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="J9" s="130" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="K9" s="131" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="L9" s="132" t="n">
+        <v>0.0248</v>
+      </c>
+      <c r="M9" s="132" t="n">
+        <v>0.0255</v>
+      </c>
+      <c r="N9" s="107">
+        <f>IF(OR(L9="",M9=""),"",SQRT(0.5*(L9^2+M9^2)))</f>
+        <v/>
+      </c>
+      <c r="O9" s="108" t="n"/>
+      <c r="P9" s="108" t="n"/>
+      <c r="Q9" s="108" t="n"/>
+      <c r="R9" s="110" t="inlineStr">
+        <is>
+          <t>cap 1, head-on baseline. THT part - stands proud of the board, unlike the flat SMD emitters.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="133" t="inlineStr">
+        <is>
+          <t>Kingbright</t>
+        </is>
+      </c>
+      <c r="B10" s="86" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C10" s="85" t="n">
+        <v>90</v>
+      </c>
+      <c r="D10" s="74" t="n">
+        <v>18801</v>
+      </c>
+      <c r="E10" s="74" t="n">
+        <v>206.8</v>
+      </c>
+      <c r="F10" s="74" t="n">
+        <v>893</v>
+      </c>
+      <c r="G10" s="74" t="n">
+        <v>1008</v>
+      </c>
+      <c r="H10" s="74" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="79" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="J10" s="79" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="K10" s="126" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="L10" s="83" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="M10" s="83" t="n">
+        <v>0.0209</v>
+      </c>
+      <c r="N10" s="84">
+        <f>IF(OR(L10="",M10=""),"",SQRT(0.5*(L10^2+M10^2)))</f>
+        <v/>
+      </c>
+      <c r="O10" s="75">
+        <f>IF(OR(D10="",D9=""),"",D10/D9)</f>
+        <v/>
+      </c>
+      <c r="P10" s="75">
+        <f>IF(OR(F10="",F9=""),"",F10/F9)</f>
+        <v/>
+      </c>
+      <c r="Q10" s="75">
+        <f>IF(OR(J10="",J9=""),"",J10/J9)</f>
+        <v/>
+      </c>
+      <c r="R10" s="81" t="inlineStr">
+        <is>
+          <t>19.7x - the WORST anisotropy of the study, worse even than Vishay. The THT domed lens concentrates light forward by design, so it illuminates the shell over the smallest solid angle of any part here. Standoff from being through-hole does not compensate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="133" t="inlineStr">
+        <is>
+          <t>Kingbright</t>
+        </is>
+      </c>
+      <c r="B11" s="86" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C11" s="85" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="74" t="n"/>
+      <c r="E11" s="74" t="n"/>
+      <c r="F11" s="74" t="n"/>
+      <c r="G11" s="74" t="n"/>
+      <c r="H11" s="74" t="n"/>
+      <c r="I11" s="79" t="n"/>
+      <c r="J11" s="79" t="n"/>
+      <c r="K11" s="126" t="n"/>
+      <c r="L11" s="83" t="n"/>
+      <c r="M11" s="83" t="n"/>
+      <c r="N11" s="84">
+        <f>IF(OR(L11="",M11=""),"",SQRT(0.5*(L11^2+M11^2)))</f>
+        <v/>
+      </c>
+      <c r="O11" s="75" t="n"/>
+      <c r="P11" s="75" t="n"/>
+      <c r="Q11" s="75" t="n"/>
+      <c r="R11" s="81" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="133" t="inlineStr">
+        <is>
+          <t>Kingbright</t>
+        </is>
+      </c>
+      <c r="B12" s="86" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C12" s="85" t="n">
+        <v>90</v>
+      </c>
+      <c r="D12" s="74" t="n"/>
+      <c r="E12" s="74" t="n"/>
+      <c r="F12" s="74" t="n"/>
+      <c r="G12" s="74" t="n"/>
+      <c r="H12" s="74" t="n"/>
+      <c r="I12" s="79" t="n"/>
+      <c r="J12" s="79" t="n"/>
+      <c r="K12" s="126" t="n"/>
+      <c r="L12" s="83" t="n"/>
+      <c r="M12" s="83" t="n"/>
+      <c r="N12" s="84">
+        <f>IF(OR(L12="",M12=""),"",SQRT(0.5*(L12^2+M12^2)))</f>
+        <v/>
+      </c>
+      <c r="O12" s="75">
+        <f>IF(OR(D12="",D11=""),"",D12/D11)</f>
+        <v/>
+      </c>
+      <c r="P12" s="75">
+        <f>IF(OR(F12="",F11=""),"",F12/F11)</f>
+        <v/>
+      </c>
+      <c r="Q12" s="75">
+        <f>IF(OR(J12="",J11=""),"",J12/J11)</f>
+        <v/>
+      </c>
+      <c r="R12" s="81" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="128" t="inlineStr">
         <is>
           <t>Everlight</t>
         </is>
       </c>
-      <c r="B9" s="26" t="inlineStr">
-        <is>
-          <t>bare (ref)</t>
-        </is>
-      </c>
-      <c r="C9" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" s="27" t="n">
+      <c r="B13" s="101" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C13" s="100" t="n">
         <v>0</v>
       </c>
-      <c r="E9" s="29" t="n"/>
-      <c r="F9" s="29" t="n"/>
-      <c r="G9" s="29" t="n"/>
-      <c r="H9" s="29" t="n"/>
-      <c r="I9" s="68">
-        <f>IF(OR(G9="",G$9=""),"",G9/G$9)</f>
-        <v/>
-      </c>
-      <c r="J9" s="68">
-        <f>IF(OR(F9="",F$9=""),"",F9/F$9)</f>
-        <v/>
-      </c>
-      <c r="K9" s="34" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="25" t="inlineStr">
+      <c r="D13" s="129" t="n">
+        <v>3469</v>
+      </c>
+      <c r="E13" s="129" t="n">
+        <v>214</v>
+      </c>
+      <c r="F13" s="129" t="n">
+        <v>888</v>
+      </c>
+      <c r="G13" s="129" t="n">
+        <v>1004</v>
+      </c>
+      <c r="H13" s="129" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="130" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J13" s="130" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="K13" s="131" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="L13" s="132" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="M13" s="132" t="n">
+        <v>0.0219</v>
+      </c>
+      <c r="N13" s="107">
+        <f>IF(OR(L13="",M13=""),"",SQRT(0.5*(L13^2+M13^2)))</f>
+        <v/>
+      </c>
+      <c r="O13" s="108" t="n"/>
+      <c r="P13" s="108" t="n"/>
+      <c r="Q13" s="108" t="n"/>
+      <c r="R13" s="110" t="inlineStr">
+        <is>
+          <t>cap 1, head-on baseline. Reproduces the run-4 row exactly (3469us, area 883, fill 0.92).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="133" t="inlineStr">
         <is>
           <t>Everlight</t>
         </is>
       </c>
-      <c r="B10" s="26" t="inlineStr">
-        <is>
-          <t>bare (ref)</t>
-        </is>
-      </c>
-      <c r="C10" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" s="27" t="n">
-        <v>15</v>
-      </c>
-      <c r="E10" s="29" t="n"/>
-      <c r="F10" s="29" t="n"/>
-      <c r="G10" s="29" t="n"/>
-      <c r="H10" s="29" t="n"/>
-      <c r="I10" s="68">
-        <f>IF(OR(G10="",G$9=""),"",G10/G$9)</f>
-        <v/>
-      </c>
-      <c r="J10" s="68">
-        <f>IF(OR(F10="",F$9=""),"",F10/F$9)</f>
-        <v/>
-      </c>
-      <c r="K10" s="34" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="25" t="inlineStr">
+      <c r="B14" s="86" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C14" s="85" t="n">
+        <v>90</v>
+      </c>
+      <c r="D14" s="74" t="n">
+        <v>12780</v>
+      </c>
+      <c r="E14" s="74" t="n">
+        <v>206.9</v>
+      </c>
+      <c r="F14" s="74" t="n">
+        <v>987</v>
+      </c>
+      <c r="G14" s="74" t="n">
+        <v>1093</v>
+      </c>
+      <c r="H14" s="74" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" s="79" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" s="79" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K14" s="126" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="L14" s="83" t="n">
+        <v>0.0194</v>
+      </c>
+      <c r="M14" s="83" t="n">
+        <v>0.0147</v>
+      </c>
+      <c r="N14" s="84">
+        <f>IF(OR(L14="",M14=""),"",SQRT(0.5*(L14^2+M14^2)))</f>
+        <v/>
+      </c>
+      <c r="O14" s="75">
+        <f>IF(OR(D14="",D13=""),"",D14/D13)</f>
+        <v/>
+      </c>
+      <c r="P14" s="75">
+        <f>IF(OR(F14="",F13=""),"",F14/F13)</f>
+        <v/>
+      </c>
+      <c r="Q14" s="75">
+        <f>IF(OR(J14="",J13=""),"",J14/J13)</f>
+        <v/>
+      </c>
+      <c r="R14" s="81" t="inlineStr">
+        <is>
+          <t>3.68x anisotropy - just OVER the 3.1x budget at THRESH_LO 80. Viable only if THRESH_LO drops to ~50, which trades against blob merging.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="133" t="inlineStr">
         <is>
           <t>Everlight</t>
         </is>
       </c>
-      <c r="B11" s="26" t="inlineStr">
-        <is>
-          <t>bare (ref)</t>
-        </is>
-      </c>
-      <c r="C11" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" s="27" t="n">
-        <v>30</v>
-      </c>
-      <c r="E11" s="29" t="n"/>
-      <c r="F11" s="29" t="n"/>
-      <c r="G11" s="29" t="n"/>
-      <c r="H11" s="29" t="n"/>
-      <c r="I11" s="68">
-        <f>IF(OR(G11="",G$9=""),"",G11/G$9)</f>
-        <v/>
-      </c>
-      <c r="J11" s="68">
-        <f>IF(OR(F11="",F$9=""),"",F11/F$9)</f>
-        <v/>
-      </c>
-      <c r="K11" s="34" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="25" t="inlineStr">
+      <c r="B15" s="86" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C15" s="85" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="74" t="n">
+        <v>3756</v>
+      </c>
+      <c r="E15" s="74" t="n">
+        <v>212.4</v>
+      </c>
+      <c r="F15" s="74" t="n">
+        <v>910</v>
+      </c>
+      <c r="G15" s="74" t="n">
+        <v>1020</v>
+      </c>
+      <c r="H15" s="74" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="79" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="J15" s="79" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="K15" s="126" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="L15" s="83" t="n">
+        <v>0.0157</v>
+      </c>
+      <c r="M15" s="83" t="n">
+        <v>0.0198</v>
+      </c>
+      <c r="N15" s="84">
+        <f>IF(OR(L15="",M15=""),"",SQRT(0.5*(L15^2+M15^2)))</f>
+        <v/>
+      </c>
+      <c r="O15" s="75" t="n"/>
+      <c r="P15" s="75" t="n"/>
+      <c r="Q15" s="75" t="n"/>
+      <c r="R15" s="81" t="inlineStr">
+        <is>
+          <t>cap 1, head-on baseline. Reproduces the run-4 row exactly (3756us, area 910, fill 0.94).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="133" t="inlineStr">
         <is>
           <t>Everlight</t>
         </is>
       </c>
-      <c r="B12" s="26" t="inlineStr">
-        <is>
-          <t>bare (ref)</t>
-        </is>
-      </c>
-      <c r="C12" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" s="27" t="n">
-        <v>45</v>
-      </c>
-      <c r="E12" s="29" t="n"/>
-      <c r="F12" s="29" t="n"/>
-      <c r="G12" s="29" t="n"/>
-      <c r="H12" s="29" t="n"/>
-      <c r="I12" s="68">
-        <f>IF(OR(G12="",G$9=""),"",G12/G$9)</f>
-        <v/>
-      </c>
-      <c r="J12" s="68">
-        <f>IF(OR(F12="",F$9=""),"",F12/F$9)</f>
-        <v/>
-      </c>
-      <c r="K12" s="34" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="25" t="inlineStr">
-        <is>
-          <t>Everlight</t>
-        </is>
-      </c>
-      <c r="B13" s="26" t="inlineStr">
-        <is>
-          <t>bare (ref)</t>
-        </is>
-      </c>
-      <c r="C13" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" s="27" t="n">
-        <v>60</v>
-      </c>
-      <c r="E13" s="29" t="n"/>
-      <c r="F13" s="29" t="n"/>
-      <c r="G13" s="29" t="n"/>
-      <c r="H13" s="29" t="n"/>
-      <c r="I13" s="68">
-        <f>IF(OR(G13="",G$9=""),"",G13/G$9)</f>
-        <v/>
-      </c>
-      <c r="J13" s="68">
-        <f>IF(OR(F13="",F$9=""),"",F13/F$9)</f>
-        <v/>
-      </c>
-      <c r="K13" s="34" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="25" t="inlineStr">
+      <c r="B16" s="86" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C16" s="85" t="n">
+        <v>90</v>
+      </c>
+      <c r="D16" s="74" t="n">
+        <v>12366</v>
+      </c>
+      <c r="E16" s="74" t="n">
+        <v>205.2</v>
+      </c>
+      <c r="F16" s="74" t="n">
+        <v>991</v>
+      </c>
+      <c r="G16" s="74" t="n">
+        <v>1105</v>
+      </c>
+      <c r="H16" s="74" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" s="79" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="J16" s="79" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K16" s="126" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="L16" s="83" t="n">
+        <v>0.0202</v>
+      </c>
+      <c r="M16" s="83" t="n">
+        <v>0.0266</v>
+      </c>
+      <c r="N16" s="84">
+        <f>IF(OR(L16="",M16=""),"",SQRT(0.5*(L16^2+M16^2)))</f>
+        <v/>
+      </c>
+      <c r="O16" s="75">
+        <f>IF(OR(D16="",D15=""),"",D16/D15)</f>
+        <v/>
+      </c>
+      <c r="P16" s="75">
+        <f>IF(OR(F16="",F15=""),"",F16/F15)</f>
+        <v/>
+      </c>
+      <c r="Q16" s="75">
+        <f>IF(OR(J16="",J15=""),"",J16/J15)</f>
+        <v/>
+      </c>
+      <c r="R16" s="81" t="inlineStr">
+        <is>
+          <t>3.29x - thickness improved it 11% (3.68-&gt;3.29) but still over budget. Needs head-on peak 263 at THRESH_LO 80, above saturation. Viable only at TL&lt;=70 and with almost no exposure margin, which the 20% cap-to-cap spread would eat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="128" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
       </c>
-      <c r="B14" s="26" t="inlineStr">
-        <is>
-          <t>bare (ref)</t>
-        </is>
-      </c>
-      <c r="C14" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" s="27" t="n">
+      <c r="B17" s="101" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C17" s="100" t="n">
         <v>0</v>
       </c>
-      <c r="E14" s="29" t="n"/>
-      <c r="F14" s="29" t="n"/>
-      <c r="G14" s="29" t="n"/>
-      <c r="H14" s="29" t="n"/>
-      <c r="I14" s="68">
-        <f>IF(OR(G14="",G$14=""),"",G14/G$14)</f>
-        <v/>
-      </c>
-      <c r="J14" s="68">
-        <f>IF(OR(F14="",F$14=""),"",F14/F$14)</f>
-        <v/>
-      </c>
-      <c r="K14" s="34" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="25" t="inlineStr">
+      <c r="D17" s="129" t="n">
+        <v>8520</v>
+      </c>
+      <c r="E17" s="129" t="n">
+        <v>210.5</v>
+      </c>
+      <c r="F17" s="129" t="n">
+        <v>952</v>
+      </c>
+      <c r="G17" s="129" t="n">
+        <v>1068</v>
+      </c>
+      <c r="H17" s="129" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="130" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" s="130" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K17" s="131" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="L17" s="132" t="n">
+        <v>0.0169</v>
+      </c>
+      <c r="M17" s="132" t="n">
+        <v>0.0305</v>
+      </c>
+      <c r="N17" s="107">
+        <f>IF(OR(L17="",M17=""),"",SQRT(0.5*(L17^2+M17^2)))</f>
+        <v/>
+      </c>
+      <c r="O17" s="108" t="n"/>
+      <c r="P17" s="108" t="n"/>
+      <c r="Q17" s="108" t="n"/>
+      <c r="R17" s="110" t="inlineStr">
+        <is>
+          <t>cap 1, head-on baseline. Matches the run-4 row (8196us, area 954, fill 1.00) within cap spread.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="133" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
       </c>
-      <c r="B15" s="26" t="inlineStr">
-        <is>
-          <t>bare (ref)</t>
-        </is>
-      </c>
-      <c r="C15" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" s="27" t="n">
-        <v>15</v>
-      </c>
-      <c r="E15" s="29" t="n"/>
-      <c r="F15" s="29" t="n"/>
-      <c r="G15" s="29" t="n"/>
-      <c r="H15" s="29" t="n"/>
-      <c r="I15" s="68">
-        <f>IF(OR(G15="",G$14=""),"",G15/G$14)</f>
-        <v/>
-      </c>
-      <c r="J15" s="68">
-        <f>IF(OR(F15="",F$14=""),"",F15/F$14)</f>
-        <v/>
-      </c>
-      <c r="K15" s="34" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="25" t="inlineStr">
+      <c r="B18" s="86" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C18" s="85" t="n">
+        <v>90</v>
+      </c>
+      <c r="D18" s="74" t="n">
+        <v>16033</v>
+      </c>
+      <c r="E18" s="74" t="n">
+        <v>206.8</v>
+      </c>
+      <c r="F18" s="74" t="n">
+        <v>950</v>
+      </c>
+      <c r="G18" s="74" t="n">
+        <v>1063</v>
+      </c>
+      <c r="H18" s="74" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" s="79" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="J18" s="79" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="K18" s="126" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="L18" s="83" t="n">
+        <v>0.0213</v>
+      </c>
+      <c r="M18" s="83" t="n">
+        <v>0.0227</v>
+      </c>
+      <c r="N18" s="84">
+        <f>IF(OR(L18="",M18=""),"",SQRT(0.5*(L18^2+M18^2)))</f>
+        <v/>
+      </c>
+      <c r="O18" s="75">
+        <f>IF(OR(D18="",D17=""),"",D18/D17)</f>
+        <v/>
+      </c>
+      <c r="P18" s="75">
+        <f>IF(OR(F18="",F17=""),"",F18/F17)</f>
+        <v/>
+      </c>
+      <c r="Q18" s="75">
+        <f>IF(OR(J18="",J17=""),"",J18/J17)</f>
+        <v/>
+      </c>
+      <c r="R18" s="81" t="inlineStr">
+        <is>
+          <t>ONLY 1.88x anisotropy - inside the ~3.1x fixed-exposure budget, where Vishay needed 8.8-12.7x. Area 950 vs 952 and fill 0.99 vs 1.03: XL presents the SAME size and blend from both directions, just 1.88x dimmer. This is the only marker so far that can be tracked at a fixed exposure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="133" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
       </c>
-      <c r="B16" s="26" t="inlineStr">
-        <is>
-          <t>bare (ref)</t>
-        </is>
-      </c>
-      <c r="C16" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" s="27" t="n">
-        <v>30</v>
-      </c>
-      <c r="E16" s="29" t="n"/>
-      <c r="F16" s="29" t="n"/>
-      <c r="G16" s="29" t="n"/>
-      <c r="H16" s="29" t="n"/>
-      <c r="I16" s="68">
-        <f>IF(OR(G16="",G$14=""),"",G16/G$14)</f>
-        <v/>
-      </c>
-      <c r="J16" s="68">
-        <f>IF(OR(F16="",F$14=""),"",F16/F$14)</f>
-        <v/>
-      </c>
-      <c r="K16" s="34" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="25" t="inlineStr">
+      <c r="B19" s="86" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C19" s="85" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="74" t="n"/>
+      <c r="E19" s="74" t="n"/>
+      <c r="F19" s="74" t="n"/>
+      <c r="G19" s="74" t="n"/>
+      <c r="H19" s="74" t="n"/>
+      <c r="I19" s="79" t="n"/>
+      <c r="J19" s="79" t="n"/>
+      <c r="K19" s="126" t="n"/>
+      <c r="L19" s="83" t="n"/>
+      <c r="M19" s="83" t="n"/>
+      <c r="N19" s="84">
+        <f>IF(OR(L19="",M19=""),"",SQRT(0.5*(L19^2+M19^2)))</f>
+        <v/>
+      </c>
+      <c r="O19" s="75" t="n"/>
+      <c r="P19" s="75" t="n"/>
+      <c r="Q19" s="75" t="n"/>
+      <c r="R19" s="81" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="133" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
       </c>
-      <c r="B17" s="26" t="inlineStr">
-        <is>
-          <t>bare (ref)</t>
-        </is>
-      </c>
-      <c r="C17" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" s="27" t="n">
-        <v>45</v>
-      </c>
-      <c r="E17" s="29" t="n"/>
-      <c r="F17" s="29" t="n"/>
-      <c r="G17" s="29" t="n"/>
-      <c r="H17" s="29" t="n"/>
-      <c r="I17" s="68">
-        <f>IF(OR(G17="",G$14=""),"",G17/G$14)</f>
-        <v/>
-      </c>
-      <c r="J17" s="68">
-        <f>IF(OR(F17="",F$14=""),"",F17/F$14)</f>
-        <v/>
-      </c>
-      <c r="K17" s="34" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="25" t="inlineStr">
-        <is>
-          <t>XL</t>
-        </is>
-      </c>
-      <c r="B18" s="26" t="inlineStr">
-        <is>
-          <t>bare (ref)</t>
-        </is>
-      </c>
-      <c r="C18" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" s="27" t="n">
-        <v>60</v>
-      </c>
-      <c r="E18" s="29" t="n"/>
-      <c r="F18" s="29" t="n"/>
-      <c r="G18" s="29" t="n"/>
-      <c r="H18" s="29" t="n"/>
-      <c r="I18" s="68">
-        <f>IF(OR(G18="",G$14=""),"",G18/G$14)</f>
-        <v/>
-      </c>
-      <c r="J18" s="68">
-        <f>IF(OR(F18="",F$14=""),"",F18/F$14)</f>
-        <v/>
-      </c>
-      <c r="K18" s="34" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="25" t="inlineStr">
-        <is>
-          <t>Kingbright</t>
-        </is>
-      </c>
-      <c r="B19" s="26" t="inlineStr">
-        <is>
-          <t>bare (ref)</t>
-        </is>
-      </c>
-      <c r="C19" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="29" t="n"/>
-      <c r="F19" s="29" t="n"/>
-      <c r="G19" s="29" t="n"/>
-      <c r="H19" s="29" t="n"/>
-      <c r="I19" s="68">
-        <f>IF(OR(G19="",G$19=""),"",G19/G$19)</f>
-        <v/>
-      </c>
-      <c r="J19" s="68">
-        <f>IF(OR(F19="",F$19=""),"",F19/F$19)</f>
-        <v/>
-      </c>
-      <c r="K19" s="34" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="25" t="inlineStr">
-        <is>
-          <t>Kingbright</t>
-        </is>
-      </c>
-      <c r="B20" s="26" t="inlineStr">
-        <is>
-          <t>bare (ref)</t>
-        </is>
-      </c>
-      <c r="C20" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" s="27" t="n">
-        <v>15</v>
-      </c>
-      <c r="E20" s="29" t="n"/>
-      <c r="F20" s="29" t="n"/>
-      <c r="G20" s="29" t="n"/>
-      <c r="H20" s="29" t="n"/>
-      <c r="I20" s="68">
-        <f>IF(OR(G20="",G$19=""),"",G20/G$19)</f>
-        <v/>
-      </c>
-      <c r="J20" s="68">
-        <f>IF(OR(F20="",F$19=""),"",F20/F$19)</f>
-        <v/>
-      </c>
-      <c r="K20" s="34" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="25" t="inlineStr">
-        <is>
-          <t>Kingbright</t>
-        </is>
-      </c>
-      <c r="B21" s="26" t="inlineStr">
-        <is>
-          <t>bare (ref)</t>
-        </is>
-      </c>
-      <c r="C21" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" s="27" t="n">
-        <v>30</v>
-      </c>
-      <c r="E21" s="29" t="n"/>
-      <c r="F21" s="29" t="n"/>
-      <c r="G21" s="29" t="n"/>
-      <c r="H21" s="29" t="n"/>
-      <c r="I21" s="68">
-        <f>IF(OR(G21="",G$19=""),"",G21/G$19)</f>
-        <v/>
-      </c>
-      <c r="J21" s="68">
-        <f>IF(OR(F21="",F$19=""),"",F21/F$19)</f>
-        <v/>
-      </c>
-      <c r="K21" s="34" t="n"/>
+      <c r="B20" s="86" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C20" s="85" t="n">
+        <v>90</v>
+      </c>
+      <c r="D20" s="74" t="n"/>
+      <c r="E20" s="74" t="n"/>
+      <c r="F20" s="74" t="n"/>
+      <c r="G20" s="74" t="n"/>
+      <c r="H20" s="74" t="n"/>
+      <c r="I20" s="79" t="n"/>
+      <c r="J20" s="79" t="n"/>
+      <c r="K20" s="126" t="n"/>
+      <c r="L20" s="83" t="n"/>
+      <c r="M20" s="83" t="n"/>
+      <c r="N20" s="84">
+        <f>IF(OR(L20="",M20=""),"",SQRT(0.5*(L20^2+M20^2)))</f>
+        <v/>
+      </c>
+      <c r="O20" s="75">
+        <f>IF(OR(D20="",D19=""),"",D20/D19)</f>
+        <v/>
+      </c>
+      <c r="P20" s="75">
+        <f>IF(OR(F20="",F19=""),"",F20/F19)</f>
+        <v/>
+      </c>
+      <c r="Q20" s="75">
+        <f>IF(OR(J20="",J19=""),"",J20/J19)</f>
+        <v/>
+      </c>
+      <c r="R20" s="81" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="25" t="inlineStr">
-        <is>
-          <t>Kingbright</t>
-        </is>
-      </c>
-      <c r="B22" s="26" t="inlineStr">
-        <is>
-          <t>bare (ref)</t>
-        </is>
-      </c>
-      <c r="C22" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D22" s="27" t="n">
-        <v>45</v>
-      </c>
-      <c r="E22" s="29" t="n"/>
-      <c r="F22" s="29" t="n"/>
-      <c r="G22" s="29" t="n"/>
-      <c r="H22" s="29" t="n"/>
-      <c r="I22" s="68">
-        <f>IF(OR(G22="",G$19=""),"",G22/G$19)</f>
-        <v/>
-      </c>
-      <c r="J22" s="68">
-        <f>IF(OR(F22="",F$19=""),"",F22/F$19)</f>
-        <v/>
-      </c>
-      <c r="K22" s="34" t="n"/>
+      <c r="A22" s="76" t="inlineStr">
+        <is>
+          <t>HOW TO READ THIS</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="25" t="inlineStr">
-        <is>
-          <t>Kingbright</t>
-        </is>
-      </c>
-      <c r="B23" s="26" t="inlineStr">
-        <is>
-          <t>bare (ref)</t>
-        </is>
-      </c>
-      <c r="C23" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D23" s="27" t="n">
-        <v>60</v>
-      </c>
-      <c r="E23" s="29" t="n"/>
-      <c r="F23" s="29" t="n"/>
-      <c r="G23" s="29" t="n"/>
-      <c r="H23" s="29" t="n"/>
-      <c r="I23" s="68">
-        <f>IF(OR(G23="",G$19=""),"",G23/G$19)</f>
-        <v/>
-      </c>
-      <c r="J23" s="68">
-        <f>IF(OR(F23="",F$19=""),"",F23/F$19)</f>
-        <v/>
-      </c>
-      <c r="K23" s="34" t="n"/>
+      <c r="A23" s="91" t="inlineStr">
+        <is>
+          <t>The 90/0 ratios are the whole test. Exposure 90/0 near 1.00 means the marker is as bright from the side as head-on; area 90/0 near 1.00 means it presents the same size; fill 90/0 near 1.00 means it blends as well. A sphere that works should give all three near unity REGARDLESS of the LED inside it.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="15" t="inlineStr">
-        <is>
-          <t>Vishay</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
-        <is>
-          <t>20 mm</t>
-        </is>
-      </c>
-      <c r="C24" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="D24" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="19" t="n"/>
-      <c r="F24" s="19" t="n"/>
-      <c r="G24" s="19" t="n"/>
-      <c r="H24" s="19" t="n"/>
-      <c r="I24" s="67">
-        <f>IF(OR(G24="",G$24=""),"",G24/G$24)</f>
-        <v/>
-      </c>
-      <c r="J24" s="67">
-        <f>IF(OR(F24="",F$24=""),"",F24/F$24)</f>
-        <v/>
-      </c>
-      <c r="K24" s="24" t="n"/>
+      <c r="A24" s="91" t="inlineStr">
+        <is>
+          <t>Expect the ordering to track beam angle if the diffuser is NOT doing its job: Vishay (narrowest) worst, XL (widest) best. If that ordering does NOT appear, the sphere has succeeded in making beam angle irrelevant - which is the result you want.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="25" t="inlineStr">
-        <is>
-          <t>Vishay</t>
-        </is>
-      </c>
-      <c r="B25" s="26" t="inlineStr">
-        <is>
-          <t>20 mm</t>
-        </is>
-      </c>
-      <c r="C25" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D25" s="27" t="n">
-        <v>15</v>
-      </c>
-      <c r="E25" s="29" t="n"/>
-      <c r="F25" s="29" t="n"/>
-      <c r="G25" s="29" t="n"/>
-      <c r="H25" s="29" t="n"/>
-      <c r="I25" s="68">
-        <f>IF(OR(G25="",G$24=""),"",G25/G$24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="68">
-        <f>IF(OR(F25="",F$24=""),"",F25/F$24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="34" t="n"/>
+      <c r="A25" s="91" t="inlineStr">
+        <is>
+          <t>At 90 deg the PCB and mount come into view and the open base of the shell may show. Watch lobe and w/h for asymmetry that is the MOUNT rather than the marker.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="25" t="inlineStr">
-        <is>
-          <t>Vishay</t>
-        </is>
-      </c>
-      <c r="B26" s="26" t="inlineStr">
-        <is>
-          <t>20 mm</t>
-        </is>
-      </c>
-      <c r="C26" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" s="27" t="n">
-        <v>30</v>
-      </c>
-      <c r="E26" s="29" t="n"/>
-      <c r="F26" s="29" t="n"/>
-      <c r="G26" s="29" t="n"/>
-      <c r="H26" s="29" t="n"/>
-      <c r="I26" s="68">
-        <f>IF(OR(G26="",G$24=""),"",G26/G$24)</f>
-        <v/>
-      </c>
-      <c r="J26" s="68">
-        <f>IF(OR(F26="",F$24=""),"",F26/F$24)</f>
-        <v/>
-      </c>
-      <c r="K26" s="34" t="n"/>
+      <c r="A26" s="91" t="inlineStr">
+        <is>
+          <t>Add 45 deg only if 0 and 90 diverge. If the two extremes agree, nothing interesting happens between them.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="25" t="inlineStr">
-        <is>
-          <t>Vishay</t>
-        </is>
-      </c>
-      <c r="B27" s="26" t="inlineStr">
-        <is>
-          <t>20 mm</t>
-        </is>
-      </c>
-      <c r="C27" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D27" s="27" t="n">
-        <v>45</v>
-      </c>
-      <c r="E27" s="29" t="n"/>
-      <c r="F27" s="29" t="n"/>
-      <c r="G27" s="29" t="n"/>
-      <c r="H27" s="29" t="n"/>
-      <c r="I27" s="68">
-        <f>IF(OR(G27="",G$24=""),"",G27/G$24)</f>
-        <v/>
-      </c>
-      <c r="J27" s="68">
-        <f>IF(OR(F27="",F$24=""),"",F27/F$24)</f>
-        <v/>
-      </c>
-      <c r="K27" s="34" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="25" t="inlineStr">
-        <is>
-          <t>Vishay</t>
-        </is>
-      </c>
-      <c r="B28" s="26" t="inlineStr">
-        <is>
-          <t>20 mm</t>
-        </is>
-      </c>
-      <c r="C28" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D28" s="27" t="n">
-        <v>60</v>
-      </c>
-      <c r="E28" s="29" t="n"/>
-      <c r="F28" s="29" t="n"/>
-      <c r="G28" s="29" t="n"/>
-      <c r="H28" s="29" t="n"/>
-      <c r="I28" s="68">
-        <f>IF(OR(G28="",G$24=""),"",G28/G$24)</f>
-        <v/>
-      </c>
-      <c r="J28" s="68">
-        <f>IF(OR(F28="",F$24=""),"",F28/F$24)</f>
-        <v/>
-      </c>
-      <c r="K28" s="34" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="25" t="inlineStr">
-        <is>
-          <t>Everlight</t>
-        </is>
-      </c>
-      <c r="B29" s="26" t="inlineStr">
-        <is>
-          <t>20 mm</t>
-        </is>
-      </c>
-      <c r="C29" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D29" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" s="29" t="n"/>
-      <c r="F29" s="29" t="n"/>
-      <c r="G29" s="29" t="n"/>
-      <c r="H29" s="29" t="n"/>
-      <c r="I29" s="68">
-        <f>IF(OR(G29="",G$29=""),"",G29/G$29)</f>
-        <v/>
-      </c>
-      <c r="J29" s="68">
-        <f>IF(OR(F29="",F$29=""),"",F29/F$29)</f>
-        <v/>
-      </c>
-      <c r="K29" s="34" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="25" t="inlineStr">
-        <is>
-          <t>Everlight</t>
-        </is>
-      </c>
-      <c r="B30" s="26" t="inlineStr">
-        <is>
-          <t>20 mm</t>
-        </is>
-      </c>
-      <c r="C30" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D30" s="27" t="n">
-        <v>15</v>
-      </c>
-      <c r="E30" s="29" t="n"/>
-      <c r="F30" s="29" t="n"/>
-      <c r="G30" s="29" t="n"/>
-      <c r="H30" s="29" t="n"/>
-      <c r="I30" s="68">
-        <f>IF(OR(G30="",G$29=""),"",G30/G$29)</f>
-        <v/>
-      </c>
-      <c r="J30" s="68">
-        <f>IF(OR(F30="",F$29=""),"",F30/F$29)</f>
-        <v/>
-      </c>
-      <c r="K30" s="34" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="25" t="inlineStr">
-        <is>
-          <t>Everlight</t>
-        </is>
-      </c>
-      <c r="B31" s="26" t="inlineStr">
-        <is>
-          <t>20 mm</t>
-        </is>
-      </c>
-      <c r="C31" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D31" s="27" t="n">
-        <v>30</v>
-      </c>
-      <c r="E31" s="29" t="n"/>
-      <c r="F31" s="29" t="n"/>
-      <c r="G31" s="29" t="n"/>
-      <c r="H31" s="29" t="n"/>
-      <c r="I31" s="68">
-        <f>IF(OR(G31="",G$29=""),"",G31/G$29)</f>
-        <v/>
-      </c>
-      <c r="J31" s="68">
-        <f>IF(OR(F31="",F$29=""),"",F31/F$29)</f>
-        <v/>
-      </c>
-      <c r="K31" s="34" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="25" t="inlineStr">
-        <is>
-          <t>Everlight</t>
-        </is>
-      </c>
-      <c r="B32" s="26" t="inlineStr">
-        <is>
-          <t>20 mm</t>
-        </is>
-      </c>
-      <c r="C32" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D32" s="27" t="n">
-        <v>45</v>
-      </c>
-      <c r="E32" s="29" t="n"/>
-      <c r="F32" s="29" t="n"/>
-      <c r="G32" s="29" t="n"/>
-      <c r="H32" s="29" t="n"/>
-      <c r="I32" s="68">
-        <f>IF(OR(G32="",G$29=""),"",G32/G$29)</f>
-        <v/>
-      </c>
-      <c r="J32" s="68">
-        <f>IF(OR(F32="",F$29=""),"",F32/F$29)</f>
-        <v/>
-      </c>
-      <c r="K32" s="34" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="25" t="inlineStr">
-        <is>
-          <t>Everlight</t>
-        </is>
-      </c>
-      <c r="B33" s="26" t="inlineStr">
-        <is>
-          <t>20 mm</t>
-        </is>
-      </c>
-      <c r="C33" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D33" s="27" t="n">
-        <v>60</v>
-      </c>
-      <c r="E33" s="29" t="n"/>
-      <c r="F33" s="29" t="n"/>
-      <c r="G33" s="29" t="n"/>
-      <c r="H33" s="29" t="n"/>
-      <c r="I33" s="68">
-        <f>IF(OR(G33="",G$29=""),"",G33/G$29)</f>
-        <v/>
-      </c>
-      <c r="J33" s="68">
-        <f>IF(OR(F33="",F$29=""),"",F33/F$29)</f>
-        <v/>
-      </c>
-      <c r="K33" s="34" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="25" t="inlineStr">
-        <is>
-          <t>XL</t>
-        </is>
-      </c>
-      <c r="B34" s="26" t="inlineStr">
-        <is>
-          <t>20 mm</t>
-        </is>
-      </c>
-      <c r="C34" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D34" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" s="29" t="n"/>
-      <c r="F34" s="29" t="n"/>
-      <c r="G34" s="29" t="n"/>
-      <c r="H34" s="29" t="n"/>
-      <c r="I34" s="68">
-        <f>IF(OR(G34="",G$34=""),"",G34/G$34)</f>
-        <v/>
-      </c>
-      <c r="J34" s="68">
-        <f>IF(OR(F34="",F$34=""),"",F34/F$34)</f>
-        <v/>
-      </c>
-      <c r="K34" s="34" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="25" t="inlineStr">
-        <is>
-          <t>XL</t>
-        </is>
-      </c>
-      <c r="B35" s="26" t="inlineStr">
-        <is>
-          <t>20 mm</t>
-        </is>
-      </c>
-      <c r="C35" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D35" s="27" t="n">
-        <v>15</v>
-      </c>
-      <c r="E35" s="29" t="n"/>
-      <c r="F35" s="29" t="n"/>
-      <c r="G35" s="29" t="n"/>
-      <c r="H35" s="29" t="n"/>
-      <c r="I35" s="68">
-        <f>IF(OR(G35="",G$34=""),"",G35/G$34)</f>
-        <v/>
-      </c>
-      <c r="J35" s="68">
-        <f>IF(OR(F35="",F$34=""),"",F35/F$34)</f>
-        <v/>
-      </c>
-      <c r="K35" s="34" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="25" t="inlineStr">
-        <is>
-          <t>XL</t>
-        </is>
-      </c>
-      <c r="B36" s="26" t="inlineStr">
-        <is>
-          <t>20 mm</t>
-        </is>
-      </c>
-      <c r="C36" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D36" s="27" t="n">
-        <v>30</v>
-      </c>
-      <c r="E36" s="29" t="n"/>
-      <c r="F36" s="29" t="n"/>
-      <c r="G36" s="29" t="n"/>
-      <c r="H36" s="29" t="n"/>
-      <c r="I36" s="68">
-        <f>IF(OR(G36="",G$34=""),"",G36/G$34)</f>
-        <v/>
-      </c>
-      <c r="J36" s="68">
-        <f>IF(OR(F36="",F$34=""),"",F36/F$34)</f>
-        <v/>
-      </c>
-      <c r="K36" s="34" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="25" t="inlineStr">
-        <is>
-          <t>XL</t>
-        </is>
-      </c>
-      <c r="B37" s="26" t="inlineStr">
-        <is>
-          <t>20 mm</t>
-        </is>
-      </c>
-      <c r="C37" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D37" s="27" t="n">
-        <v>45</v>
-      </c>
-      <c r="E37" s="29" t="n"/>
-      <c r="F37" s="29" t="n"/>
-      <c r="G37" s="29" t="n"/>
-      <c r="H37" s="29" t="n"/>
-      <c r="I37" s="68">
-        <f>IF(OR(G37="",G$34=""),"",G37/G$34)</f>
-        <v/>
-      </c>
-      <c r="J37" s="68">
-        <f>IF(OR(F37="",F$34=""),"",F37/F$34)</f>
-        <v/>
-      </c>
-      <c r="K37" s="34" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="25" t="inlineStr">
-        <is>
-          <t>XL</t>
-        </is>
-      </c>
-      <c r="B38" s="26" t="inlineStr">
-        <is>
-          <t>20 mm</t>
-        </is>
-      </c>
-      <c r="C38" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D38" s="27" t="n">
-        <v>60</v>
-      </c>
-      <c r="E38" s="29" t="n"/>
-      <c r="F38" s="29" t="n"/>
-      <c r="G38" s="29" t="n"/>
-      <c r="H38" s="29" t="n"/>
-      <c r="I38" s="68">
-        <f>IF(OR(G38="",G$34=""),"",G38/G$34)</f>
-        <v/>
-      </c>
-      <c r="J38" s="68">
-        <f>IF(OR(F38="",F$34=""),"",F38/F$34)</f>
-        <v/>
-      </c>
-      <c r="K38" s="34" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="25" t="inlineStr">
-        <is>
-          <t>Kingbright</t>
-        </is>
-      </c>
-      <c r="B39" s="26" t="inlineStr">
-        <is>
-          <t>20 mm</t>
-        </is>
-      </c>
-      <c r="C39" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D39" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" s="29" t="n"/>
-      <c r="F39" s="29" t="n"/>
-      <c r="G39" s="29" t="n"/>
-      <c r="H39" s="29" t="n"/>
-      <c r="I39" s="68">
-        <f>IF(OR(G39="",G$39=""),"",G39/G$39)</f>
-        <v/>
-      </c>
-      <c r="J39" s="68">
-        <f>IF(OR(F39="",F$39=""),"",F39/F$39)</f>
-        <v/>
-      </c>
-      <c r="K39" s="34" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="25" t="inlineStr">
-        <is>
-          <t>Kingbright</t>
-        </is>
-      </c>
-      <c r="B40" s="26" t="inlineStr">
-        <is>
-          <t>20 mm</t>
-        </is>
-      </c>
-      <c r="C40" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D40" s="27" t="n">
-        <v>15</v>
-      </c>
-      <c r="E40" s="29" t="n"/>
-      <c r="F40" s="29" t="n"/>
-      <c r="G40" s="29" t="n"/>
-      <c r="H40" s="29" t="n"/>
-      <c r="I40" s="68">
-        <f>IF(OR(G40="",G$39=""),"",G40/G$39)</f>
-        <v/>
-      </c>
-      <c r="J40" s="68">
-        <f>IF(OR(F40="",F$39=""),"",F40/F$39)</f>
-        <v/>
-      </c>
-      <c r="K40" s="34" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="25" t="inlineStr">
-        <is>
-          <t>Kingbright</t>
-        </is>
-      </c>
-      <c r="B41" s="26" t="inlineStr">
-        <is>
-          <t>20 mm</t>
-        </is>
-      </c>
-      <c r="C41" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D41" s="27" t="n">
-        <v>30</v>
-      </c>
-      <c r="E41" s="29" t="n"/>
-      <c r="F41" s="29" t="n"/>
-      <c r="G41" s="29" t="n"/>
-      <c r="H41" s="29" t="n"/>
-      <c r="I41" s="68">
-        <f>IF(OR(G41="",G$39=""),"",G41/G$39)</f>
-        <v/>
-      </c>
-      <c r="J41" s="68">
-        <f>IF(OR(F41="",F$39=""),"",F41/F$39)</f>
-        <v/>
-      </c>
-      <c r="K41" s="34" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="25" t="inlineStr">
-        <is>
-          <t>Kingbright</t>
-        </is>
-      </c>
-      <c r="B42" s="26" t="inlineStr">
-        <is>
-          <t>20 mm</t>
-        </is>
-      </c>
-      <c r="C42" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D42" s="27" t="n">
-        <v>45</v>
-      </c>
-      <c r="E42" s="29" t="n"/>
-      <c r="F42" s="29" t="n"/>
-      <c r="G42" s="29" t="n"/>
-      <c r="H42" s="29" t="n"/>
-      <c r="I42" s="68">
-        <f>IF(OR(G42="",G$39=""),"",G42/G$39)</f>
-        <v/>
-      </c>
-      <c r="J42" s="68">
-        <f>IF(OR(F42="",F$39=""),"",F42/F$39)</f>
-        <v/>
-      </c>
-      <c r="K42" s="34" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="25" t="inlineStr">
-        <is>
-          <t>Kingbright</t>
-        </is>
-      </c>
-      <c r="B43" s="26" t="inlineStr">
-        <is>
-          <t>20 mm</t>
-        </is>
-      </c>
-      <c r="C43" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D43" s="27" t="n">
-        <v>60</v>
-      </c>
-      <c r="E43" s="29" t="n"/>
-      <c r="F43" s="29" t="n"/>
-      <c r="G43" s="29" t="n"/>
-      <c r="H43" s="29" t="n"/>
-      <c r="I43" s="68">
-        <f>IF(OR(G43="",G$39=""),"",G43/G$39)</f>
-        <v/>
-      </c>
-      <c r="J43" s="68">
-        <f>IF(OR(F43="",F$39=""),"",F43/F$39)</f>
-        <v/>
-      </c>
-      <c r="K43" s="34" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="15" t="inlineStr">
-        <is>
-          <t>Vishay</t>
-        </is>
-      </c>
-      <c r="B44" s="16" t="inlineStr">
-        <is>
-          <t>25 mm</t>
-        </is>
-      </c>
-      <c r="C44" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="D44" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" s="19" t="n"/>
-      <c r="F44" s="19" t="n"/>
-      <c r="G44" s="19" t="n"/>
-      <c r="H44" s="19" t="n"/>
-      <c r="I44" s="67">
-        <f>IF(OR(G44="",G$44=""),"",G44/G$44)</f>
-        <v/>
-      </c>
-      <c r="J44" s="67">
-        <f>IF(OR(F44="",F$44=""),"",F44/F$44)</f>
-        <v/>
-      </c>
-      <c r="K44" s="24" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="25" t="inlineStr">
-        <is>
-          <t>Vishay</t>
-        </is>
-      </c>
-      <c r="B45" s="26" t="inlineStr">
-        <is>
-          <t>25 mm</t>
-        </is>
-      </c>
-      <c r="C45" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D45" s="27" t="n">
-        <v>15</v>
-      </c>
-      <c r="E45" s="29" t="n"/>
-      <c r="F45" s="29" t="n"/>
-      <c r="G45" s="29" t="n"/>
-      <c r="H45" s="29" t="n"/>
-      <c r="I45" s="68">
-        <f>IF(OR(G45="",G$44=""),"",G45/G$44)</f>
-        <v/>
-      </c>
-      <c r="J45" s="68">
-        <f>IF(OR(F45="",F$44=""),"",F45/F$44)</f>
-        <v/>
-      </c>
-      <c r="K45" s="34" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="25" t="inlineStr">
-        <is>
-          <t>Vishay</t>
-        </is>
-      </c>
-      <c r="B46" s="26" t="inlineStr">
-        <is>
-          <t>25 mm</t>
-        </is>
-      </c>
-      <c r="C46" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D46" s="27" t="n">
-        <v>30</v>
-      </c>
-      <c r="E46" s="29" t="n"/>
-      <c r="F46" s="29" t="n"/>
-      <c r="G46" s="29" t="n"/>
-      <c r="H46" s="29" t="n"/>
-      <c r="I46" s="68">
-        <f>IF(OR(G46="",G$44=""),"",G46/G$44)</f>
-        <v/>
-      </c>
-      <c r="J46" s="68">
-        <f>IF(OR(F46="",F$44=""),"",F46/F$44)</f>
-        <v/>
-      </c>
-      <c r="K46" s="34" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="25" t="inlineStr">
-        <is>
-          <t>Vishay</t>
-        </is>
-      </c>
-      <c r="B47" s="26" t="inlineStr">
-        <is>
-          <t>25 mm</t>
-        </is>
-      </c>
-      <c r="C47" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D47" s="27" t="n">
-        <v>45</v>
-      </c>
-      <c r="E47" s="29" t="n"/>
-      <c r="F47" s="29" t="n"/>
-      <c r="G47" s="29" t="n"/>
-      <c r="H47" s="29" t="n"/>
-      <c r="I47" s="68">
-        <f>IF(OR(G47="",G$44=""),"",G47/G$44)</f>
-        <v/>
-      </c>
-      <c r="J47" s="68">
-        <f>IF(OR(F47="",F$44=""),"",F47/F$44)</f>
-        <v/>
-      </c>
-      <c r="K47" s="34" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="25" t="inlineStr">
-        <is>
-          <t>Vishay</t>
-        </is>
-      </c>
-      <c r="B48" s="26" t="inlineStr">
-        <is>
-          <t>25 mm</t>
-        </is>
-      </c>
-      <c r="C48" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D48" s="27" t="n">
-        <v>60</v>
-      </c>
-      <c r="E48" s="29" t="n"/>
-      <c r="F48" s="29" t="n"/>
-      <c r="G48" s="29" t="n"/>
-      <c r="H48" s="29" t="n"/>
-      <c r="I48" s="68">
-        <f>IF(OR(G48="",G$44=""),"",G48/G$44)</f>
-        <v/>
-      </c>
-      <c r="J48" s="68">
-        <f>IF(OR(F48="",F$44=""),"",F48/F$44)</f>
-        <v/>
-      </c>
-      <c r="K48" s="34" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="25" t="inlineStr">
-        <is>
-          <t>Everlight</t>
-        </is>
-      </c>
-      <c r="B49" s="26" t="inlineStr">
-        <is>
-          <t>25 mm</t>
-        </is>
-      </c>
-      <c r="C49" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D49" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E49" s="29" t="n"/>
-      <c r="F49" s="29" t="n"/>
-      <c r="G49" s="29" t="n"/>
-      <c r="H49" s="29" t="n"/>
-      <c r="I49" s="68">
-        <f>IF(OR(G49="",G$49=""),"",G49/G$49)</f>
-        <v/>
-      </c>
-      <c r="J49" s="68">
-        <f>IF(OR(F49="",F$49=""),"",F49/F$49)</f>
-        <v/>
-      </c>
-      <c r="K49" s="34" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="25" t="inlineStr">
-        <is>
-          <t>Everlight</t>
-        </is>
-      </c>
-      <c r="B50" s="26" t="inlineStr">
-        <is>
-          <t>25 mm</t>
-        </is>
-      </c>
-      <c r="C50" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D50" s="27" t="n">
-        <v>15</v>
-      </c>
-      <c r="E50" s="29" t="n"/>
-      <c r="F50" s="29" t="n"/>
-      <c r="G50" s="29" t="n"/>
-      <c r="H50" s="29" t="n"/>
-      <c r="I50" s="68">
-        <f>IF(OR(G50="",G$49=""),"",G50/G$49)</f>
-        <v/>
-      </c>
-      <c r="J50" s="68">
-        <f>IF(OR(F50="",F$49=""),"",F50/F$49)</f>
-        <v/>
-      </c>
-      <c r="K50" s="34" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="25" t="inlineStr">
-        <is>
-          <t>Everlight</t>
-        </is>
-      </c>
-      <c r="B51" s="26" t="inlineStr">
-        <is>
-          <t>25 mm</t>
-        </is>
-      </c>
-      <c r="C51" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D51" s="27" t="n">
-        <v>30</v>
-      </c>
-      <c r="E51" s="29" t="n"/>
-      <c r="F51" s="29" t="n"/>
-      <c r="G51" s="29" t="n"/>
-      <c r="H51" s="29" t="n"/>
-      <c r="I51" s="68">
-        <f>IF(OR(G51="",G$49=""),"",G51/G$49)</f>
-        <v/>
-      </c>
-      <c r="J51" s="68">
-        <f>IF(OR(F51="",F$49=""),"",F51/F$49)</f>
-        <v/>
-      </c>
-      <c r="K51" s="34" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="25" t="inlineStr">
-        <is>
-          <t>Everlight</t>
-        </is>
-      </c>
-      <c r="B52" s="26" t="inlineStr">
-        <is>
-          <t>25 mm</t>
-        </is>
-      </c>
-      <c r="C52" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D52" s="27" t="n">
-        <v>45</v>
-      </c>
-      <c r="E52" s="29" t="n"/>
-      <c r="F52" s="29" t="n"/>
-      <c r="G52" s="29" t="n"/>
-      <c r="H52" s="29" t="n"/>
-      <c r="I52" s="68">
-        <f>IF(OR(G52="",G$49=""),"",G52/G$49)</f>
-        <v/>
-      </c>
-      <c r="J52" s="68">
-        <f>IF(OR(F52="",F$49=""),"",F52/F$49)</f>
-        <v/>
-      </c>
-      <c r="K52" s="34" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="25" t="inlineStr">
-        <is>
-          <t>Everlight</t>
-        </is>
-      </c>
-      <c r="B53" s="26" t="inlineStr">
-        <is>
-          <t>25 mm</t>
-        </is>
-      </c>
-      <c r="C53" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D53" s="27" t="n">
-        <v>60</v>
-      </c>
-      <c r="E53" s="29" t="n"/>
-      <c r="F53" s="29" t="n"/>
-      <c r="G53" s="29" t="n"/>
-      <c r="H53" s="29" t="n"/>
-      <c r="I53" s="68">
-        <f>IF(OR(G53="",G$49=""),"",G53/G$49)</f>
-        <v/>
-      </c>
-      <c r="J53" s="68">
-        <f>IF(OR(F53="",F$49=""),"",F53/F$49)</f>
-        <v/>
-      </c>
-      <c r="K53" s="34" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="25" t="inlineStr">
-        <is>
-          <t>XL</t>
-        </is>
-      </c>
-      <c r="B54" s="26" t="inlineStr">
-        <is>
-          <t>25 mm</t>
-        </is>
-      </c>
-      <c r="C54" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D54" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E54" s="29" t="n"/>
-      <c r="F54" s="29" t="n"/>
-      <c r="G54" s="29" t="n"/>
-      <c r="H54" s="29" t="n"/>
-      <c r="I54" s="68">
-        <f>IF(OR(G54="",G$54=""),"",G54/G$54)</f>
-        <v/>
-      </c>
-      <c r="J54" s="68">
-        <f>IF(OR(F54="",F$54=""),"",F54/F$54)</f>
-        <v/>
-      </c>
-      <c r="K54" s="34" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="25" t="inlineStr">
-        <is>
-          <t>XL</t>
-        </is>
-      </c>
-      <c r="B55" s="26" t="inlineStr">
-        <is>
-          <t>25 mm</t>
-        </is>
-      </c>
-      <c r="C55" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D55" s="27" t="n">
-        <v>15</v>
-      </c>
-      <c r="E55" s="29" t="n"/>
-      <c r="F55" s="29" t="n"/>
-      <c r="G55" s="29" t="n"/>
-      <c r="H55" s="29" t="n"/>
-      <c r="I55" s="68">
-        <f>IF(OR(G55="",G$54=""),"",G55/G$54)</f>
-        <v/>
-      </c>
-      <c r="J55" s="68">
-        <f>IF(OR(F55="",F$54=""),"",F55/F$54)</f>
-        <v/>
-      </c>
-      <c r="K55" s="34" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="25" t="inlineStr">
-        <is>
-          <t>XL</t>
-        </is>
-      </c>
-      <c r="B56" s="26" t="inlineStr">
-        <is>
-          <t>25 mm</t>
-        </is>
-      </c>
-      <c r="C56" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D56" s="27" t="n">
-        <v>30</v>
-      </c>
-      <c r="E56" s="29" t="n"/>
-      <c r="F56" s="29" t="n"/>
-      <c r="G56" s="29" t="n"/>
-      <c r="H56" s="29" t="n"/>
-      <c r="I56" s="68">
-        <f>IF(OR(G56="",G$54=""),"",G56/G$54)</f>
-        <v/>
-      </c>
-      <c r="J56" s="68">
-        <f>IF(OR(F56="",F$54=""),"",F56/F$54)</f>
-        <v/>
-      </c>
-      <c r="K56" s="34" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="25" t="inlineStr">
-        <is>
-          <t>XL</t>
-        </is>
-      </c>
-      <c r="B57" s="26" t="inlineStr">
-        <is>
-          <t>25 mm</t>
-        </is>
-      </c>
-      <c r="C57" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D57" s="27" t="n">
-        <v>45</v>
-      </c>
-      <c r="E57" s="29" t="n"/>
-      <c r="F57" s="29" t="n"/>
-      <c r="G57" s="29" t="n"/>
-      <c r="H57" s="29" t="n"/>
-      <c r="I57" s="68">
-        <f>IF(OR(G57="",G$54=""),"",G57/G$54)</f>
-        <v/>
-      </c>
-      <c r="J57" s="68">
-        <f>IF(OR(F57="",F$54=""),"",F57/F$54)</f>
-        <v/>
-      </c>
-      <c r="K57" s="34" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="25" t="inlineStr">
-        <is>
-          <t>XL</t>
-        </is>
-      </c>
-      <c r="B58" s="26" t="inlineStr">
-        <is>
-          <t>25 mm</t>
-        </is>
-      </c>
-      <c r="C58" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D58" s="27" t="n">
-        <v>60</v>
-      </c>
-      <c r="E58" s="29" t="n"/>
-      <c r="F58" s="29" t="n"/>
-      <c r="G58" s="29" t="n"/>
-      <c r="H58" s="29" t="n"/>
-      <c r="I58" s="68">
-        <f>IF(OR(G58="",G$54=""),"",G58/G$54)</f>
-        <v/>
-      </c>
-      <c r="J58" s="68">
-        <f>IF(OR(F58="",F$54=""),"",F58/F$54)</f>
-        <v/>
-      </c>
-      <c r="K58" s="34" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="25" t="inlineStr">
-        <is>
-          <t>Kingbright</t>
-        </is>
-      </c>
-      <c r="B59" s="26" t="inlineStr">
-        <is>
-          <t>25 mm</t>
-        </is>
-      </c>
-      <c r="C59" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D59" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E59" s="29" t="n"/>
-      <c r="F59" s="29" t="n"/>
-      <c r="G59" s="29" t="n"/>
-      <c r="H59" s="29" t="n"/>
-      <c r="I59" s="68">
-        <f>IF(OR(G59="",G$59=""),"",G59/G$59)</f>
-        <v/>
-      </c>
-      <c r="J59" s="68">
-        <f>IF(OR(F59="",F$59=""),"",F59/F$59)</f>
-        <v/>
-      </c>
-      <c r="K59" s="34" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="25" t="inlineStr">
-        <is>
-          <t>Kingbright</t>
-        </is>
-      </c>
-      <c r="B60" s="26" t="inlineStr">
-        <is>
-          <t>25 mm</t>
-        </is>
-      </c>
-      <c r="C60" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D60" s="27" t="n">
-        <v>15</v>
-      </c>
-      <c r="E60" s="29" t="n"/>
-      <c r="F60" s="29" t="n"/>
-      <c r="G60" s="29" t="n"/>
-      <c r="H60" s="29" t="n"/>
-      <c r="I60" s="68">
-        <f>IF(OR(G60="",G$59=""),"",G60/G$59)</f>
-        <v/>
-      </c>
-      <c r="J60" s="68">
-        <f>IF(OR(F60="",F$59=""),"",F60/F$59)</f>
-        <v/>
-      </c>
-      <c r="K60" s="34" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="25" t="inlineStr">
-        <is>
-          <t>Kingbright</t>
-        </is>
-      </c>
-      <c r="B61" s="26" t="inlineStr">
-        <is>
-          <t>25 mm</t>
-        </is>
-      </c>
-      <c r="C61" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D61" s="27" t="n">
-        <v>30</v>
-      </c>
-      <c r="E61" s="29" t="n"/>
-      <c r="F61" s="29" t="n"/>
-      <c r="G61" s="29" t="n"/>
-      <c r="H61" s="29" t="n"/>
-      <c r="I61" s="68">
-        <f>IF(OR(G61="",G$59=""),"",G61/G$59)</f>
-        <v/>
-      </c>
-      <c r="J61" s="68">
-        <f>IF(OR(F61="",F$59=""),"",F61/F$59)</f>
-        <v/>
-      </c>
-      <c r="K61" s="34" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="25" t="inlineStr">
-        <is>
-          <t>Kingbright</t>
-        </is>
-      </c>
-      <c r="B62" s="26" t="inlineStr">
-        <is>
-          <t>25 mm</t>
-        </is>
-      </c>
-      <c r="C62" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D62" s="27" t="n">
-        <v>45</v>
-      </c>
-      <c r="E62" s="29" t="n"/>
-      <c r="F62" s="29" t="n"/>
-      <c r="G62" s="29" t="n"/>
-      <c r="H62" s="29" t="n"/>
-      <c r="I62" s="68">
-        <f>IF(OR(G62="",G$59=""),"",G62/G$59)</f>
-        <v/>
-      </c>
-      <c r="J62" s="68">
-        <f>IF(OR(F62="",F$59=""),"",F62/F$59)</f>
-        <v/>
-      </c>
-      <c r="K62" s="34" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="25" t="inlineStr">
-        <is>
-          <t>Kingbright</t>
-        </is>
-      </c>
-      <c r="B63" s="26" t="inlineStr">
-        <is>
-          <t>25 mm</t>
-        </is>
-      </c>
-      <c r="C63" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D63" s="27" t="n">
-        <v>60</v>
-      </c>
-      <c r="E63" s="29" t="n"/>
-      <c r="F63" s="29" t="n"/>
-      <c r="G63" s="29" t="n"/>
-      <c r="H63" s="29" t="n"/>
-      <c r="I63" s="68">
-        <f>IF(OR(G63="",G$59=""),"",G63/G$59)</f>
-        <v/>
-      </c>
-      <c r="J63" s="68">
-        <f>IF(OR(F63="",F$59=""),"",F63/F$59)</f>
-        <v/>
-      </c>
-      <c r="K63" s="34" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="38" t="inlineStr">
-        <is>
-          <t>ROLL - rotate the marker about its OWN axis. This is the 20 vs 25 mm decider.</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="7" t="inlineStr">
-        <is>
-          <t>Four LEDs at 90 deg spacing, so 0 deg (facing one LED) and 45 deg (between two) are the extremes. MODE="measure" -&gt; record the printed mean u, mean v and blobs_max. Rotate in place: any translation reads as false bias.</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="30" customHeight="1">
-      <c r="A67" s="8" t="inlineStr">
-        <is>
-          <t>LED Type</t>
-        </is>
-      </c>
-      <c r="B67" s="8" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="C67" s="8" t="inlineStr">
-        <is>
-          <t>Sample</t>
-        </is>
-      </c>
-      <c r="D67" s="8" t="inlineStr">
-        <is>
-          <t>Roll
-(deg)</t>
-        </is>
-      </c>
-      <c r="E67" s="8" t="inlineStr">
-        <is>
-          <t>Exposure
-(us)</t>
-        </is>
-      </c>
-      <c r="F67" s="8" t="inlineStr">
-        <is>
-          <t>Peak
-(0-255)</t>
-        </is>
-      </c>
-      <c r="G67" s="8" t="inlineStr">
-        <is>
-          <t>mean u
-(px)</t>
-        </is>
-      </c>
-      <c r="H67" s="8" t="inlineStr">
-        <is>
-          <t>mean v
-(px)</t>
-        </is>
-      </c>
-      <c r="I67" s="8" t="inlineStr">
-        <is>
-          <t>blobs_max</t>
-        </is>
-      </c>
-      <c r="J67" s="8" t="inlineStr">
-        <is>
-          <t>Shift vs
-roll 0 (px)</t>
-        </is>
-      </c>
-      <c r="K67" s="8" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="15" t="inlineStr">
-        <is>
-          <t>Vishay</t>
-        </is>
-      </c>
-      <c r="B68" s="16" t="inlineStr">
-        <is>
-          <t>20 mm</t>
-        </is>
-      </c>
-      <c r="C68" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="D68" s="57" t="n">
-        <v>0</v>
-      </c>
-      <c r="E68" s="19" t="n"/>
-      <c r="F68" s="19" t="n"/>
-      <c r="G68" s="39" t="n"/>
-      <c r="H68" s="39" t="n"/>
-      <c r="I68" s="19" t="n"/>
-      <c r="J68" s="40">
-        <f>IF(OR(G68="",H68="",G$68="",H$68=""),"",SQRT((G68-G$68)^2+(H68-H$68)^2))</f>
-        <v/>
-      </c>
-      <c r="K68" s="24" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="25" t="inlineStr">
-        <is>
-          <t>Vishay</t>
-        </is>
-      </c>
-      <c r="B69" s="26" t="inlineStr">
-        <is>
-          <t>20 mm</t>
-        </is>
-      </c>
-      <c r="C69" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D69" s="53" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="E69" s="29" t="n"/>
-      <c r="F69" s="29" t="n"/>
-      <c r="G69" s="41" t="n"/>
-      <c r="H69" s="41" t="n"/>
-      <c r="I69" s="29" t="n"/>
-      <c r="J69" s="42">
-        <f>IF(OR(G69="",H69="",G$68="",H$68=""),"",SQRT((G69-G$68)^2+(H69-H$68)^2))</f>
-        <v/>
-      </c>
-      <c r="K69" s="34" t="n"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="25" t="inlineStr">
-        <is>
-          <t>Vishay</t>
-        </is>
-      </c>
-      <c r="B70" s="26" t="inlineStr">
-        <is>
-          <t>20 mm</t>
-        </is>
-      </c>
-      <c r="C70" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D70" s="53" t="n">
-        <v>45</v>
-      </c>
-      <c r="E70" s="29" t="n"/>
-      <c r="F70" s="29" t="n"/>
-      <c r="G70" s="41" t="n"/>
-      <c r="H70" s="41" t="n"/>
-      <c r="I70" s="29" t="n"/>
-      <c r="J70" s="42">
-        <f>IF(OR(G70="",H70="",G$68="",H$68=""),"",SQRT((G70-G$68)^2+(H70-H$68)^2))</f>
-        <v/>
-      </c>
-      <c r="K70" s="34" t="n"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="25" t="inlineStr">
-        <is>
-          <t>Vishay</t>
-        </is>
-      </c>
-      <c r="B71" s="26" t="inlineStr">
-        <is>
-          <t>20 mm</t>
-        </is>
-      </c>
-      <c r="C71" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D71" s="53" t="n">
-        <v>67.5</v>
-      </c>
-      <c r="E71" s="29" t="n"/>
-      <c r="F71" s="29" t="n"/>
-      <c r="G71" s="41" t="n"/>
-      <c r="H71" s="41" t="n"/>
-      <c r="I71" s="29" t="n"/>
-      <c r="J71" s="42">
-        <f>IF(OR(G71="",H71="",G$68="",H$68=""),"",SQRT((G71-G$68)^2+(H71-H$68)^2))</f>
-        <v/>
-      </c>
-      <c r="K71" s="34" t="n"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="25" t="inlineStr">
-        <is>
-          <t>Vishay</t>
-        </is>
-      </c>
-      <c r="B72" s="26" t="inlineStr">
-        <is>
-          <t>20 mm</t>
-        </is>
-      </c>
-      <c r="C72" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D72" s="53" t="n">
-        <v>90</v>
-      </c>
-      <c r="E72" s="29" t="n"/>
-      <c r="F72" s="29" t="n"/>
-      <c r="G72" s="41" t="n"/>
-      <c r="H72" s="41" t="n"/>
-      <c r="I72" s="29" t="n"/>
-      <c r="J72" s="42">
-        <f>IF(OR(G72="",H72="",G$68="",H$68=""),"",SQRT((G72-G$68)^2+(H72-H$68)^2))</f>
-        <v/>
-      </c>
-      <c r="K72" s="34" t="n"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="25" t="inlineStr">
-        <is>
-          <t>Everlight</t>
-        </is>
-      </c>
-      <c r="B73" s="26" t="inlineStr">
-        <is>
-          <t>20 mm</t>
-        </is>
-      </c>
-      <c r="C73" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D73" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="E73" s="29" t="n"/>
-      <c r="F73" s="29" t="n"/>
-      <c r="G73" s="41" t="n"/>
-      <c r="H73" s="41" t="n"/>
-      <c r="I73" s="29" t="n"/>
-      <c r="J73" s="42">
-        <f>IF(OR(G73="",H73="",G$73="",H$73=""),"",SQRT((G73-G$73)^2+(H73-H$73)^2))</f>
-        <v/>
-      </c>
-      <c r="K73" s="34" t="n"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="25" t="inlineStr">
-        <is>
-          <t>Everlight</t>
-        </is>
-      </c>
-      <c r="B74" s="26" t="inlineStr">
-        <is>
-          <t>20 mm</t>
-        </is>
-      </c>
-      <c r="C74" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D74" s="53" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="E74" s="29" t="n"/>
-      <c r="F74" s="29" t="n"/>
-      <c r="G74" s="41" t="n"/>
-      <c r="H74" s="41" t="n"/>
-      <c r="I74" s="29" t="n"/>
-      <c r="J74" s="42">
-        <f>IF(OR(G74="",H74="",G$73="",H$73=""),"",SQRT((G74-G$73)^2+(H74-H$73)^2))</f>
-        <v/>
-      </c>
-      <c r="K74" s="34" t="n"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="25" t="inlineStr">
-        <is>
-          <t>Everlight</t>
-        </is>
-      </c>
-      <c r="B75" s="26" t="inlineStr">
-        <is>
-          <t>20 mm</t>
-        </is>
-      </c>
-      <c r="C75" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D75" s="53" t="n">
-        <v>45</v>
-      </c>
-      <c r="E75" s="29" t="n"/>
-      <c r="F75" s="29" t="n"/>
-      <c r="G75" s="41" t="n"/>
-      <c r="H75" s="41" t="n"/>
-      <c r="I75" s="29" t="n"/>
-      <c r="J75" s="42">
-        <f>IF(OR(G75="",H75="",G$73="",H$73=""),"",SQRT((G75-G$73)^2+(H75-H$73)^2))</f>
-        <v/>
-      </c>
-      <c r="K75" s="34" t="n"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="25" t="inlineStr">
-        <is>
-          <t>Everlight</t>
-        </is>
-      </c>
-      <c r="B76" s="26" t="inlineStr">
-        <is>
-          <t>20 mm</t>
-        </is>
-      </c>
-      <c r="C76" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D76" s="53" t="n">
-        <v>67.5</v>
-      </c>
-      <c r="E76" s="29" t="n"/>
-      <c r="F76" s="29" t="n"/>
-      <c r="G76" s="41" t="n"/>
-      <c r="H76" s="41" t="n"/>
-      <c r="I76" s="29" t="n"/>
-      <c r="J76" s="42">
-        <f>IF(OR(G76="",H76="",G$73="",H$73=""),"",SQRT((G76-G$73)^2+(H76-H$73)^2))</f>
-        <v/>
-      </c>
-      <c r="K76" s="34" t="n"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="25" t="inlineStr">
-        <is>
-          <t>Everlight</t>
-        </is>
-      </c>
-      <c r="B77" s="26" t="inlineStr">
-        <is>
-          <t>20 mm</t>
-        </is>
-      </c>
-      <c r="C77" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D77" s="53" t="n">
-        <v>90</v>
-      </c>
-      <c r="E77" s="29" t="n"/>
-      <c r="F77" s="29" t="n"/>
-      <c r="G77" s="41" t="n"/>
-      <c r="H77" s="41" t="n"/>
-      <c r="I77" s="29" t="n"/>
-      <c r="J77" s="42">
-        <f>IF(OR(G77="",H77="",G$73="",H$73=""),"",SQRT((G77-G$73)^2+(H77-H$73)^2))</f>
-        <v/>
-      </c>
-      <c r="K77" s="34" t="n"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="25" t="inlineStr">
-        <is>
-          <t>XL</t>
-        </is>
-      </c>
-      <c r="B78" s="26" t="inlineStr">
-        <is>
-          <t>20 mm</t>
-        </is>
-      </c>
-      <c r="C78" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D78" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="E78" s="29" t="n"/>
-      <c r="F78" s="29" t="n"/>
-      <c r="G78" s="41" t="n"/>
-      <c r="H78" s="41" t="n"/>
-      <c r="I78" s="29" t="n"/>
-      <c r="J78" s="42">
-        <f>IF(OR(G78="",H78="",G$78="",H$78=""),"",SQRT((G78-G$78)^2+(H78-H$78)^2))</f>
-        <v/>
-      </c>
-      <c r="K78" s="34" t="n"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="25" t="inlineStr">
-        <is>
-          <t>XL</t>
-        </is>
-      </c>
-      <c r="B79" s="26" t="inlineStr">
-        <is>
-          <t>20 mm</t>
-        </is>
-      </c>
-      <c r="C79" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D79" s="53" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="E79" s="29" t="n"/>
-      <c r="F79" s="29" t="n"/>
-      <c r="G79" s="41" t="n"/>
-      <c r="H79" s="41" t="n"/>
-      <c r="I79" s="29" t="n"/>
-      <c r="J79" s="42">
-        <f>IF(OR(G79="",H79="",G$78="",H$78=""),"",SQRT((G79-G$78)^2+(H79-H$78)^2))</f>
-        <v/>
-      </c>
-      <c r="K79" s="34" t="n"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="25" t="inlineStr">
-        <is>
-          <t>XL</t>
-        </is>
-      </c>
-      <c r="B80" s="26" t="inlineStr">
-        <is>
-          <t>20 mm</t>
-        </is>
-      </c>
-      <c r="C80" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D80" s="53" t="n">
-        <v>45</v>
-      </c>
-      <c r="E80" s="29" t="n"/>
-      <c r="F80" s="29" t="n"/>
-      <c r="G80" s="41" t="n"/>
-      <c r="H80" s="41" t="n"/>
-      <c r="I80" s="29" t="n"/>
-      <c r="J80" s="42">
-        <f>IF(OR(G80="",H80="",G$78="",H$78=""),"",SQRT((G80-G$78)^2+(H80-H$78)^2))</f>
-        <v/>
-      </c>
-      <c r="K80" s="34" t="n"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="25" t="inlineStr">
-        <is>
-          <t>XL</t>
-        </is>
-      </c>
-      <c r="B81" s="26" t="inlineStr">
-        <is>
-          <t>20 mm</t>
-        </is>
-      </c>
-      <c r="C81" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D81" s="53" t="n">
-        <v>67.5</v>
-      </c>
-      <c r="E81" s="29" t="n"/>
-      <c r="F81" s="29" t="n"/>
-      <c r="G81" s="41" t="n"/>
-      <c r="H81" s="41" t="n"/>
-      <c r="I81" s="29" t="n"/>
-      <c r="J81" s="42">
-        <f>IF(OR(G81="",H81="",G$78="",H$78=""),"",SQRT((G81-G$78)^2+(H81-H$78)^2))</f>
-        <v/>
-      </c>
-      <c r="K81" s="34" t="n"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="25" t="inlineStr">
-        <is>
-          <t>XL</t>
-        </is>
-      </c>
-      <c r="B82" s="26" t="inlineStr">
-        <is>
-          <t>20 mm</t>
-        </is>
-      </c>
-      <c r="C82" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D82" s="53" t="n">
-        <v>90</v>
-      </c>
-      <c r="E82" s="29" t="n"/>
-      <c r="F82" s="29" t="n"/>
-      <c r="G82" s="41" t="n"/>
-      <c r="H82" s="41" t="n"/>
-      <c r="I82" s="29" t="n"/>
-      <c r="J82" s="42">
-        <f>IF(OR(G82="",H82="",G$78="",H$78=""),"",SQRT((G82-G$78)^2+(H82-H$78)^2))</f>
-        <v/>
-      </c>
-      <c r="K82" s="34" t="n"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="25" t="inlineStr">
-        <is>
-          <t>Kingbright</t>
-        </is>
-      </c>
-      <c r="B83" s="26" t="inlineStr">
-        <is>
-          <t>20 mm</t>
-        </is>
-      </c>
-      <c r="C83" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D83" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="E83" s="29" t="n"/>
-      <c r="F83" s="29" t="n"/>
-      <c r="G83" s="41" t="n"/>
-      <c r="H83" s="41" t="n"/>
-      <c r="I83" s="29" t="n"/>
-      <c r="J83" s="42">
-        <f>IF(OR(G83="",H83="",G$83="",H$83=""),"",SQRT((G83-G$83)^2+(H83-H$83)^2))</f>
-        <v/>
-      </c>
-      <c r="K83" s="34" t="n"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="25" t="inlineStr">
-        <is>
-          <t>Kingbright</t>
-        </is>
-      </c>
-      <c r="B84" s="26" t="inlineStr">
-        <is>
-          <t>20 mm</t>
-        </is>
-      </c>
-      <c r="C84" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D84" s="53" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="E84" s="29" t="n"/>
-      <c r="F84" s="29" t="n"/>
-      <c r="G84" s="41" t="n"/>
-      <c r="H84" s="41" t="n"/>
-      <c r="I84" s="29" t="n"/>
-      <c r="J84" s="42">
-        <f>IF(OR(G84="",H84="",G$83="",H$83=""),"",SQRT((G84-G$83)^2+(H84-H$83)^2))</f>
-        <v/>
-      </c>
-      <c r="K84" s="34" t="n"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="25" t="inlineStr">
-        <is>
-          <t>Kingbright</t>
-        </is>
-      </c>
-      <c r="B85" s="26" t="inlineStr">
-        <is>
-          <t>20 mm</t>
-        </is>
-      </c>
-      <c r="C85" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D85" s="53" t="n">
-        <v>45</v>
-      </c>
-      <c r="E85" s="29" t="n"/>
-      <c r="F85" s="29" t="n"/>
-      <c r="G85" s="41" t="n"/>
-      <c r="H85" s="41" t="n"/>
-      <c r="I85" s="29" t="n"/>
-      <c r="J85" s="42">
-        <f>IF(OR(G85="",H85="",G$83="",H$83=""),"",SQRT((G85-G$83)^2+(H85-H$83)^2))</f>
-        <v/>
-      </c>
-      <c r="K85" s="34" t="n"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="25" t="inlineStr">
-        <is>
-          <t>Kingbright</t>
-        </is>
-      </c>
-      <c r="B86" s="26" t="inlineStr">
-        <is>
-          <t>20 mm</t>
-        </is>
-      </c>
-      <c r="C86" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D86" s="53" t="n">
-        <v>67.5</v>
-      </c>
-      <c r="E86" s="29" t="n"/>
-      <c r="F86" s="29" t="n"/>
-      <c r="G86" s="41" t="n"/>
-      <c r="H86" s="41" t="n"/>
-      <c r="I86" s="29" t="n"/>
-      <c r="J86" s="42">
-        <f>IF(OR(G86="",H86="",G$83="",H$83=""),"",SQRT((G86-G$83)^2+(H86-H$83)^2))</f>
-        <v/>
-      </c>
-      <c r="K86" s="34" t="n"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="25" t="inlineStr">
-        <is>
-          <t>Kingbright</t>
-        </is>
-      </c>
-      <c r="B87" s="26" t="inlineStr">
-        <is>
-          <t>20 mm</t>
-        </is>
-      </c>
-      <c r="C87" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D87" s="53" t="n">
-        <v>90</v>
-      </c>
-      <c r="E87" s="29" t="n"/>
-      <c r="F87" s="29" t="n"/>
-      <c r="G87" s="41" t="n"/>
-      <c r="H87" s="41" t="n"/>
-      <c r="I87" s="29" t="n"/>
-      <c r="J87" s="42">
-        <f>IF(OR(G87="",H87="",G$83="",H$83=""),"",SQRT((G87-G$83)^2+(H87-H$83)^2))</f>
-        <v/>
-      </c>
-      <c r="K87" s="34" t="n"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="15" t="inlineStr">
-        <is>
-          <t>Vishay</t>
-        </is>
-      </c>
-      <c r="B88" s="16" t="inlineStr">
-        <is>
-          <t>25 mm</t>
-        </is>
-      </c>
-      <c r="C88" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="D88" s="57" t="n">
-        <v>0</v>
-      </c>
-      <c r="E88" s="19" t="n"/>
-      <c r="F88" s="19" t="n"/>
-      <c r="G88" s="39" t="n"/>
-      <c r="H88" s="39" t="n"/>
-      <c r="I88" s="19" t="n"/>
-      <c r="J88" s="40">
-        <f>IF(OR(G88="",H88="",G$88="",H$88=""),"",SQRT((G88-G$88)^2+(H88-H$88)^2))</f>
-        <v/>
-      </c>
-      <c r="K88" s="24" t="n"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="25" t="inlineStr">
-        <is>
-          <t>Vishay</t>
-        </is>
-      </c>
-      <c r="B89" s="26" t="inlineStr">
-        <is>
-          <t>25 mm</t>
-        </is>
-      </c>
-      <c r="C89" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D89" s="53" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="E89" s="29" t="n"/>
-      <c r="F89" s="29" t="n"/>
-      <c r="G89" s="41" t="n"/>
-      <c r="H89" s="41" t="n"/>
-      <c r="I89" s="29" t="n"/>
-      <c r="J89" s="42">
-        <f>IF(OR(G89="",H89="",G$88="",H$88=""),"",SQRT((G89-G$88)^2+(H89-H$88)^2))</f>
-        <v/>
-      </c>
-      <c r="K89" s="34" t="n"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="25" t="inlineStr">
-        <is>
-          <t>Vishay</t>
-        </is>
-      </c>
-      <c r="B90" s="26" t="inlineStr">
-        <is>
-          <t>25 mm</t>
-        </is>
-      </c>
-      <c r="C90" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D90" s="53" t="n">
-        <v>45</v>
-      </c>
-      <c r="E90" s="29" t="n"/>
-      <c r="F90" s="29" t="n"/>
-      <c r="G90" s="41" t="n"/>
-      <c r="H90" s="41" t="n"/>
-      <c r="I90" s="29" t="n"/>
-      <c r="J90" s="42">
-        <f>IF(OR(G90="",H90="",G$88="",H$88=""),"",SQRT((G90-G$88)^2+(H90-H$88)^2))</f>
-        <v/>
-      </c>
-      <c r="K90" s="34" t="n"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="25" t="inlineStr">
-        <is>
-          <t>Vishay</t>
-        </is>
-      </c>
-      <c r="B91" s="26" t="inlineStr">
-        <is>
-          <t>25 mm</t>
-        </is>
-      </c>
-      <c r="C91" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D91" s="53" t="n">
-        <v>67.5</v>
-      </c>
-      <c r="E91" s="29" t="n"/>
-      <c r="F91" s="29" t="n"/>
-      <c r="G91" s="41" t="n"/>
-      <c r="H91" s="41" t="n"/>
-      <c r="I91" s="29" t="n"/>
-      <c r="J91" s="42">
-        <f>IF(OR(G91="",H91="",G$88="",H$88=""),"",SQRT((G91-G$88)^2+(H91-H$88)^2))</f>
-        <v/>
-      </c>
-      <c r="K91" s="34" t="n"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="25" t="inlineStr">
-        <is>
-          <t>Vishay</t>
-        </is>
-      </c>
-      <c r="B92" s="26" t="inlineStr">
-        <is>
-          <t>25 mm</t>
-        </is>
-      </c>
-      <c r="C92" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D92" s="53" t="n">
-        <v>90</v>
-      </c>
-      <c r="E92" s="29" t="n"/>
-      <c r="F92" s="29" t="n"/>
-      <c r="G92" s="41" t="n"/>
-      <c r="H92" s="41" t="n"/>
-      <c r="I92" s="29" t="n"/>
-      <c r="J92" s="42">
-        <f>IF(OR(G92="",H92="",G$88="",H$88=""),"",SQRT((G92-G$88)^2+(H92-H$88)^2))</f>
-        <v/>
-      </c>
-      <c r="K92" s="34" t="n"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="25" t="inlineStr">
-        <is>
-          <t>Everlight</t>
-        </is>
-      </c>
-      <c r="B93" s="26" t="inlineStr">
-        <is>
-          <t>25 mm</t>
-        </is>
-      </c>
-      <c r="C93" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D93" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="E93" s="29" t="n"/>
-      <c r="F93" s="29" t="n"/>
-      <c r="G93" s="41" t="n"/>
-      <c r="H93" s="41" t="n"/>
-      <c r="I93" s="29" t="n"/>
-      <c r="J93" s="42">
-        <f>IF(OR(G93="",H93="",G$93="",H$93=""),"",SQRT((G93-G$93)^2+(H93-H$93)^2))</f>
-        <v/>
-      </c>
-      <c r="K93" s="34" t="n"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="25" t="inlineStr">
-        <is>
-          <t>Everlight</t>
-        </is>
-      </c>
-      <c r="B94" s="26" t="inlineStr">
-        <is>
-          <t>25 mm</t>
-        </is>
-      </c>
-      <c r="C94" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D94" s="53" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="E94" s="29" t="n"/>
-      <c r="F94" s="29" t="n"/>
-      <c r="G94" s="41" t="n"/>
-      <c r="H94" s="41" t="n"/>
-      <c r="I94" s="29" t="n"/>
-      <c r="J94" s="42">
-        <f>IF(OR(G94="",H94="",G$93="",H$93=""),"",SQRT((G94-G$93)^2+(H94-H$93)^2))</f>
-        <v/>
-      </c>
-      <c r="K94" s="34" t="n"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="25" t="inlineStr">
-        <is>
-          <t>Everlight</t>
-        </is>
-      </c>
-      <c r="B95" s="26" t="inlineStr">
-        <is>
-          <t>25 mm</t>
-        </is>
-      </c>
-      <c r="C95" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D95" s="53" t="n">
-        <v>45</v>
-      </c>
-      <c r="E95" s="29" t="n"/>
-      <c r="F95" s="29" t="n"/>
-      <c r="G95" s="41" t="n"/>
-      <c r="H95" s="41" t="n"/>
-      <c r="I95" s="29" t="n"/>
-      <c r="J95" s="42">
-        <f>IF(OR(G95="",H95="",G$93="",H$93=""),"",SQRT((G95-G$93)^2+(H95-H$93)^2))</f>
-        <v/>
-      </c>
-      <c r="K95" s="34" t="n"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="25" t="inlineStr">
-        <is>
-          <t>Everlight</t>
-        </is>
-      </c>
-      <c r="B96" s="26" t="inlineStr">
-        <is>
-          <t>25 mm</t>
-        </is>
-      </c>
-      <c r="C96" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D96" s="53" t="n">
-        <v>67.5</v>
-      </c>
-      <c r="E96" s="29" t="n"/>
-      <c r="F96" s="29" t="n"/>
-      <c r="G96" s="41" t="n"/>
-      <c r="H96" s="41" t="n"/>
-      <c r="I96" s="29" t="n"/>
-      <c r="J96" s="42">
-        <f>IF(OR(G96="",H96="",G$93="",H$93=""),"",SQRT((G96-G$93)^2+(H96-H$93)^2))</f>
-        <v/>
-      </c>
-      <c r="K96" s="34" t="n"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="25" t="inlineStr">
-        <is>
-          <t>Everlight</t>
-        </is>
-      </c>
-      <c r="B97" s="26" t="inlineStr">
-        <is>
-          <t>25 mm</t>
-        </is>
-      </c>
-      <c r="C97" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D97" s="53" t="n">
-        <v>90</v>
-      </c>
-      <c r="E97" s="29" t="n"/>
-      <c r="F97" s="29" t="n"/>
-      <c r="G97" s="41" t="n"/>
-      <c r="H97" s="41" t="n"/>
-      <c r="I97" s="29" t="n"/>
-      <c r="J97" s="42">
-        <f>IF(OR(G97="",H97="",G$93="",H$93=""),"",SQRT((G97-G$93)^2+(H97-H$93)^2))</f>
-        <v/>
-      </c>
-      <c r="K97" s="34" t="n"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="25" t="inlineStr">
-        <is>
-          <t>XL</t>
-        </is>
-      </c>
-      <c r="B98" s="26" t="inlineStr">
-        <is>
-          <t>25 mm</t>
-        </is>
-      </c>
-      <c r="C98" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D98" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="E98" s="29" t="n"/>
-      <c r="F98" s="29" t="n"/>
-      <c r="G98" s="41" t="n"/>
-      <c r="H98" s="41" t="n"/>
-      <c r="I98" s="29" t="n"/>
-      <c r="J98" s="42">
-        <f>IF(OR(G98="",H98="",G$98="",H$98=""),"",SQRT((G98-G$98)^2+(H98-H$98)^2))</f>
-        <v/>
-      </c>
-      <c r="K98" s="34" t="n"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="25" t="inlineStr">
-        <is>
-          <t>XL</t>
-        </is>
-      </c>
-      <c r="B99" s="26" t="inlineStr">
-        <is>
-          <t>25 mm</t>
-        </is>
-      </c>
-      <c r="C99" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D99" s="53" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="E99" s="29" t="n"/>
-      <c r="F99" s="29" t="n"/>
-      <c r="G99" s="41" t="n"/>
-      <c r="H99" s="41" t="n"/>
-      <c r="I99" s="29" t="n"/>
-      <c r="J99" s="42">
-        <f>IF(OR(G99="",H99="",G$98="",H$98=""),"",SQRT((G99-G$98)^2+(H99-H$98)^2))</f>
-        <v/>
-      </c>
-      <c r="K99" s="34" t="n"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="25" t="inlineStr">
-        <is>
-          <t>XL</t>
-        </is>
-      </c>
-      <c r="B100" s="26" t="inlineStr">
-        <is>
-          <t>25 mm</t>
-        </is>
-      </c>
-      <c r="C100" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D100" s="53" t="n">
-        <v>45</v>
-      </c>
-      <c r="E100" s="29" t="n"/>
-      <c r="F100" s="29" t="n"/>
-      <c r="G100" s="41" t="n"/>
-      <c r="H100" s="41" t="n"/>
-      <c r="I100" s="29" t="n"/>
-      <c r="J100" s="42">
-        <f>IF(OR(G100="",H100="",G$98="",H$98=""),"",SQRT((G100-G$98)^2+(H100-H$98)^2))</f>
-        <v/>
-      </c>
-      <c r="K100" s="34" t="n"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="25" t="inlineStr">
-        <is>
-          <t>XL</t>
-        </is>
-      </c>
-      <c r="B101" s="26" t="inlineStr">
-        <is>
-          <t>25 mm</t>
-        </is>
-      </c>
-      <c r="C101" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D101" s="53" t="n">
-        <v>67.5</v>
-      </c>
-      <c r="E101" s="29" t="n"/>
-      <c r="F101" s="29" t="n"/>
-      <c r="G101" s="41" t="n"/>
-      <c r="H101" s="41" t="n"/>
-      <c r="I101" s="29" t="n"/>
-      <c r="J101" s="42">
-        <f>IF(OR(G101="",H101="",G$98="",H$98=""),"",SQRT((G101-G$98)^2+(H101-H$98)^2))</f>
-        <v/>
-      </c>
-      <c r="K101" s="34" t="n"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="25" t="inlineStr">
-        <is>
-          <t>XL</t>
-        </is>
-      </c>
-      <c r="B102" s="26" t="inlineStr">
-        <is>
-          <t>25 mm</t>
-        </is>
-      </c>
-      <c r="C102" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D102" s="53" t="n">
-        <v>90</v>
-      </c>
-      <c r="E102" s="29" t="n"/>
-      <c r="F102" s="29" t="n"/>
-      <c r="G102" s="41" t="n"/>
-      <c r="H102" s="41" t="n"/>
-      <c r="I102" s="29" t="n"/>
-      <c r="J102" s="42">
-        <f>IF(OR(G102="",H102="",G$98="",H$98=""),"",SQRT((G102-G$98)^2+(H102-H$98)^2))</f>
-        <v/>
-      </c>
-      <c r="K102" s="34" t="n"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="25" t="inlineStr">
-        <is>
-          <t>Kingbright</t>
-        </is>
-      </c>
-      <c r="B103" s="26" t="inlineStr">
-        <is>
-          <t>25 mm</t>
-        </is>
-      </c>
-      <c r="C103" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D103" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="E103" s="29" t="n"/>
-      <c r="F103" s="29" t="n"/>
-      <c r="G103" s="41" t="n"/>
-      <c r="H103" s="41" t="n"/>
-      <c r="I103" s="29" t="n"/>
-      <c r="J103" s="42">
-        <f>IF(OR(G103="",H103="",G$103="",H$103=""),"",SQRT((G103-G$103)^2+(H103-H$103)^2))</f>
-        <v/>
-      </c>
-      <c r="K103" s="34" t="n"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="25" t="inlineStr">
-        <is>
-          <t>Kingbright</t>
-        </is>
-      </c>
-      <c r="B104" s="26" t="inlineStr">
-        <is>
-          <t>25 mm</t>
-        </is>
-      </c>
-      <c r="C104" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D104" s="53" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="E104" s="29" t="n"/>
-      <c r="F104" s="29" t="n"/>
-      <c r="G104" s="41" t="n"/>
-      <c r="H104" s="41" t="n"/>
-      <c r="I104" s="29" t="n"/>
-      <c r="J104" s="42">
-        <f>IF(OR(G104="",H104="",G$103="",H$103=""),"",SQRT((G104-G$103)^2+(H104-H$103)^2))</f>
-        <v/>
-      </c>
-      <c r="K104" s="34" t="n"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="25" t="inlineStr">
-        <is>
-          <t>Kingbright</t>
-        </is>
-      </c>
-      <c r="B105" s="26" t="inlineStr">
-        <is>
-          <t>25 mm</t>
-        </is>
-      </c>
-      <c r="C105" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D105" s="53" t="n">
-        <v>45</v>
-      </c>
-      <c r="E105" s="29" t="n"/>
-      <c r="F105" s="29" t="n"/>
-      <c r="G105" s="41" t="n"/>
-      <c r="H105" s="41" t="n"/>
-      <c r="I105" s="29" t="n"/>
-      <c r="J105" s="42">
-        <f>IF(OR(G105="",H105="",G$103="",H$103=""),"",SQRT((G105-G$103)^2+(H105-H$103)^2))</f>
-        <v/>
-      </c>
-      <c r="K105" s="34" t="n"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="25" t="inlineStr">
-        <is>
-          <t>Kingbright</t>
-        </is>
-      </c>
-      <c r="B106" s="26" t="inlineStr">
-        <is>
-          <t>25 mm</t>
-        </is>
-      </c>
-      <c r="C106" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D106" s="53" t="n">
-        <v>67.5</v>
-      </c>
-      <c r="E106" s="29" t="n"/>
-      <c r="F106" s="29" t="n"/>
-      <c r="G106" s="41" t="n"/>
-      <c r="H106" s="41" t="n"/>
-      <c r="I106" s="29" t="n"/>
-      <c r="J106" s="42">
-        <f>IF(OR(G106="",H106="",G$103="",H$103=""),"",SQRT((G106-G$103)^2+(H106-H$103)^2))</f>
-        <v/>
-      </c>
-      <c r="K106" s="34" t="n"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="25" t="inlineStr">
-        <is>
-          <t>Kingbright</t>
-        </is>
-      </c>
-      <c r="B107" s="26" t="inlineStr">
-        <is>
-          <t>25 mm</t>
-        </is>
-      </c>
-      <c r="C107" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D107" s="53" t="n">
-        <v>90</v>
-      </c>
-      <c r="E107" s="29" t="n"/>
-      <c r="F107" s="29" t="n"/>
-      <c r="G107" s="41" t="n"/>
-      <c r="H107" s="41" t="n"/>
-      <c r="I107" s="29" t="n"/>
-      <c r="J107" s="42">
-        <f>IF(OR(G107="",H107="",G$103="",H$103=""),"",SQRT((G107-G$103)^2+(H107-H$103)^2))</f>
-        <v/>
-      </c>
-      <c r="K107" s="34" t="n"/>
+      <c r="A27" s="91" t="inlineStr">
+        <is>
+          <t>Re-target the exposure at every angle - a dimmer 90 deg view needs more exposure, and rows are only comparable at matched peak (205-215).</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12134,7 +10244,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="82" t="inlineStr">
+      <c r="A20" s="133" t="inlineStr">
         <is>
           <t>Kingbright</t>
         </is>
@@ -12170,7 +10280,7 @@
       <c r="Q20" s="81" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="82" t="inlineStr">
+      <c r="A21" s="133" t="inlineStr">
         <is>
           <t>Vishay</t>
         </is>
@@ -12206,7 +10316,7 @@
       <c r="Q21" s="81" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="82" t="inlineStr">
+      <c r="A22" s="133" t="inlineStr">
         <is>
           <t>Kingbright</t>
         </is>
@@ -12242,7 +10352,7 @@
       <c r="Q22" s="81" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="82" t="inlineStr">
+      <c r="A23" s="133" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -13308,7 +11418,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="82" t="inlineStr">
+      <c r="A27" s="133" t="inlineStr">
         <is>
           <t>A: short exposure, low background</t>
         </is>
@@ -13330,7 +11440,7 @@
       <c r="M27" s="81" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="82" t="inlineStr">
+      <c r="A28" s="133" t="inlineStr">
         <is>
           <t>B: long exposure, high background</t>
         </is>
@@ -14152,7 +12262,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T39"/>
+  <dimension ref="A1:U39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -14175,6 +12285,7 @@
     <col width="11" customWidth="1" min="18" max="18"/>
     <col width="11" customWidth="1" min="19" max="19"/>
     <col width="34" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14344,6 +12455,12 @@
           <t>Notes</t>
         </is>
       </c>
+      <c r="U7" s="77" t="inlineStr">
+        <is>
+          <t>Lobe
+(0=circular)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="98" t="inlineStr">
@@ -14351,7 +12468,7 @@
           <t>done</t>
         </is>
       </c>
-      <c r="B8" s="99" t="inlineStr">
+      <c r="B8" s="128" t="inlineStr">
         <is>
           <t>Vishay</t>
         </is>
@@ -14399,7 +12516,7 @@
         <v/>
       </c>
       <c r="N8" s="105">
-        <f>IF(OR(K8="",L8="",M8=""),"",IF(AND(K8=1,L8&gt;=0.9,L8&lt;=1.1,M8&gt;=0.85),"pass","FAIL"))</f>
+        <f>IF(OR(K8="",L8="",M8=""),"",IF(AND(K8=1,L8&gt;=0.9,L8&lt;=1.1,M8&gt;=0.70),"pass","FAIL"))</f>
         <v/>
       </c>
       <c r="O8" s="106">
@@ -14423,12 +12540,13 @@
         <v/>
       </c>
       <c r="T8" s="110" t="n"/>
+      <c r="U8" s="125" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="80" t="n">
         <v>1</v>
       </c>
-      <c r="B9" s="82" t="inlineStr">
+      <c r="B9" s="133" t="inlineStr">
         <is>
           <t>Vishay</t>
         </is>
@@ -14447,19 +12565,37 @@
         <f>IF(OR(E9="",$B$4=""),"",E9/2-$B$4)</f>
         <v/>
       </c>
-      <c r="G9" s="74" t="n"/>
-      <c r="H9" s="74" t="n"/>
-      <c r="I9" s="72" t="n"/>
-      <c r="J9" s="74" t="n"/>
-      <c r="K9" s="74" t="n"/>
-      <c r="L9" s="79" t="n"/>
-      <c r="M9" s="79" t="n"/>
+      <c r="G9" s="74" t="n">
+        <v>413</v>
+      </c>
+      <c r="H9" s="74" t="n">
+        <v>212.3</v>
+      </c>
+      <c r="I9" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="74" t="n">
+        <v>606</v>
+      </c>
+      <c r="K9" s="74" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" s="79" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="M9" s="79" t="n">
+        <v>0.63</v>
+      </c>
       <c r="N9" s="80">
-        <f>IF(OR(K9="",L9="",M9=""),"",IF(AND(K9=1,L9&gt;=0.9,L9&lt;=1.1,M9&gt;=0.85),"pass","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="O9" s="83" t="n"/>
-      <c r="P9" s="83" t="n"/>
+        <f>IF(OR(K9="",L9="",M9=""),"",IF(AND(K9=1,L9&gt;=0.9,L9&lt;=1.1,M9&gt;=0.70),"pass","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="O9" s="83" t="n">
+        <v>0.0283</v>
+      </c>
+      <c r="P9" s="83" t="n">
+        <v>0.0357</v>
+      </c>
       <c r="Q9" s="84">
         <f>IF(OR(O9="",P9=""),"",SQRT(0.5*(O9^2+P9^2)))</f>
         <v/>
@@ -14472,7 +12608,14 @@
         <f>IF(OR(M9="",$M$8=""),"",M9-$M$8)</f>
         <v/>
       </c>
-      <c r="T9" s="81" t="n"/>
+      <c r="T9" s="81" t="inlineStr">
+        <is>
+          <t>cap 1. BIGGEST thickness gain of any LED: fill +0.10 (0.53-&gt;0.63) and lobe 0.120-&gt;0.076, so the extra wall largely merged the four lobes. Thickness helps in inverse proportion to beam angle: Vishay +0.10, Kingbright +0.06, Everlight +0.03, XL +0.03.  flux 312</t>
+        </is>
+      </c>
+      <c r="U9" s="126" t="n">
+        <v>0.076</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="80" t="inlineStr">
@@ -14480,7 +12623,7 @@
           <t>drop</t>
         </is>
       </c>
-      <c r="B10" s="82" t="inlineStr">
+      <c r="B10" s="133" t="inlineStr">
         <is>
           <t>Vishay</t>
         </is>
@@ -14507,7 +12650,7 @@
       <c r="L10" s="79" t="n"/>
       <c r="M10" s="79" t="n"/>
       <c r="N10" s="80">
-        <f>IF(OR(K10="",L10="",M10=""),"",IF(AND(K10=1,L10&gt;=0.9,L10&lt;=1.1,M10&gt;=0.85),"pass","FAIL"))</f>
+        <f>IF(OR(K10="",L10="",M10=""),"",IF(AND(K10=1,L10&gt;=0.9,L10&lt;=1.1,M10&gt;=0.70),"pass","FAIL"))</f>
         <v/>
       </c>
       <c r="O10" s="83" t="n"/>
@@ -14529,6 +12672,7 @@
           <t>DROPPED 2026-09-04. 0.5 mm measured worse than 0.4 mm at identical transmitted flux, i.e. cap variation not thickness. Ladder reduced to 0.2 / 0.4 mm with REPLICATE caps instead.</t>
         </is>
       </c>
+      <c r="U10" s="126" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="112" t="inlineStr">
@@ -14536,7 +12680,7 @@
           <t>done</t>
         </is>
       </c>
-      <c r="B11" s="82" t="inlineStr">
+      <c r="B11" s="133" t="inlineStr">
         <is>
           <t>Vishay</t>
         </is>
@@ -14584,7 +12728,7 @@
         <v/>
       </c>
       <c r="N11" s="80">
-        <f>IF(OR(K11="",L11="",M11=""),"",IF(AND(K11=1,L11&gt;=0.9,L11&lt;=1.1,M11&gt;=0.85),"pass","FAIL"))</f>
+        <f>IF(OR(K11="",L11="",M11=""),"",IF(AND(K11=1,L11&gt;=0.9,L11&lt;=1.1,M11&gt;=0.70),"pass","FAIL"))</f>
         <v/>
       </c>
       <c r="O11" s="116">
@@ -14608,12 +12752,13 @@
         <v/>
       </c>
       <c r="T11" s="81" t="n"/>
+      <c r="U11" s="127" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="80" t="n">
         <v>1</v>
       </c>
-      <c r="B12" s="82" t="inlineStr">
+      <c r="B12" s="133" t="inlineStr">
         <is>
           <t>Vishay</t>
         </is>
@@ -14632,19 +12777,37 @@
         <f>IF(OR(E12="",$B$4=""),"",E12/2-$B$4)</f>
         <v/>
       </c>
-      <c r="G12" s="74" t="n"/>
-      <c r="H12" s="74" t="n"/>
-      <c r="I12" s="72" t="n"/>
-      <c r="J12" s="74" t="n"/>
-      <c r="K12" s="74" t="n"/>
-      <c r="L12" s="79" t="n"/>
-      <c r="M12" s="79" t="n"/>
+      <c r="G12" s="74" t="n">
+        <v>602</v>
+      </c>
+      <c r="H12" s="74" t="n">
+        <v>209.9</v>
+      </c>
+      <c r="I12" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="74" t="n">
+        <v>751</v>
+      </c>
+      <c r="K12" s="74" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" s="79" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="M12" s="79" t="n">
+        <v>0.74</v>
+      </c>
       <c r="N12" s="80">
-        <f>IF(OR(K12="",L12="",M12=""),"",IF(AND(K12=1,L12&gt;=0.9,L12&lt;=1.1,M12&gt;=0.85),"pass","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="O12" s="83" t="n"/>
-      <c r="P12" s="83" t="n"/>
+        <f>IF(OR(K12="",L12="",M12=""),"",IF(AND(K12=1,L12&gt;=0.9,L12&lt;=1.1,M12&gt;=0.70),"pass","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="O12" s="83" t="n">
+        <v>0.0198</v>
+      </c>
+      <c r="P12" s="83" t="n">
+        <v>0.0273</v>
+      </c>
       <c r="Q12" s="84">
         <f>IF(OR(O12="",P12=""),"",SQRT(0.5*(O12^2+P12^2)))</f>
         <v/>
@@ -14657,7 +12820,14 @@
         <f>IF(OR(M12="",$M$11=""),"",M12-$M$11)</f>
         <v/>
       </c>
-      <c r="T12" s="81" t="n"/>
+      <c r="T12" s="81" t="inlineStr">
+        <is>
+          <t>MEAN OF 4 REPLICATE CAPS (575/485/575/772 us). Cap-to-cap: exposure CV 20%, area 2.7%, fill 2.5%, lobe 4%, sigma 11%. So fill = 0.74 +/- 0.02 and sigma = 0.0240 +/- 0.0027; fill differences under ~0.05 and sigma differences under ~25% are not significant.  flux 262</t>
+        </is>
+      </c>
+      <c r="U12" s="126" t="n">
+        <v>0.062</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="80" t="inlineStr">
@@ -14665,7 +12835,7 @@
           <t>drop</t>
         </is>
       </c>
-      <c r="B13" s="82" t="inlineStr">
+      <c r="B13" s="133" t="inlineStr">
         <is>
           <t>Vishay</t>
         </is>
@@ -14692,7 +12862,7 @@
       <c r="L13" s="79" t="n"/>
       <c r="M13" s="79" t="n"/>
       <c r="N13" s="80">
-        <f>IF(OR(K13="",L13="",M13=""),"",IF(AND(K13=1,L13&gt;=0.9,L13&lt;=1.1,M13&gt;=0.85),"pass","FAIL"))</f>
+        <f>IF(OR(K13="",L13="",M13=""),"",IF(AND(K13=1,L13&gt;=0.9,L13&lt;=1.1,M13&gt;=0.70),"pass","FAIL"))</f>
         <v/>
       </c>
       <c r="O13" s="83" t="n"/>
@@ -14714,6 +12884,7 @@
           <t>DROPPED 2026-09-04. 0.5 mm measured worse than 0.4 mm at identical transmitted flux, i.e. cap variation not thickness. Ladder reduced to 0.2 / 0.4 mm with REPLICATE caps instead.</t>
         </is>
       </c>
+      <c r="U13" s="126" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="98" t="inlineStr">
@@ -14721,7 +12892,7 @@
           <t>done</t>
         </is>
       </c>
-      <c r="B14" s="99" t="inlineStr">
+      <c r="B14" s="128" t="inlineStr">
         <is>
           <t>Kingbright</t>
         </is>
@@ -14769,7 +12940,7 @@
         <v/>
       </c>
       <c r="N14" s="105">
-        <f>IF(OR(K14="",L14="",M14=""),"",IF(AND(K14=1,L14&gt;=0.9,L14&lt;=1.1,M14&gt;=0.85),"pass","FAIL"))</f>
+        <f>IF(OR(K14="",L14="",M14=""),"",IF(AND(K14=1,L14&gt;=0.9,L14&lt;=1.1,M14&gt;=0.70),"pass","FAIL"))</f>
         <v/>
       </c>
       <c r="O14" s="106">
@@ -14793,12 +12964,13 @@
         <v/>
       </c>
       <c r="T14" s="110" t="n"/>
+      <c r="U14" s="125" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="80" t="n">
         <v>1</v>
       </c>
-      <c r="B15" s="82" t="inlineStr">
+      <c r="B15" s="133" t="inlineStr">
         <is>
           <t>Kingbright</t>
         </is>
@@ -14818,35 +12990,35 @@
         <v/>
       </c>
       <c r="G15" s="74" t="n">
-        <v>1186</v>
+        <v>1060</v>
       </c>
       <c r="H15" s="74" t="n">
-        <v>216.4</v>
+        <v>216.6</v>
       </c>
       <c r="I15" s="72" t="n">
         <v>0</v>
       </c>
       <c r="J15" s="74" t="n">
-        <v>637</v>
+        <v>694</v>
       </c>
       <c r="K15" s="74" t="n">
         <v>1</v>
       </c>
       <c r="L15" s="79" t="n">
-        <v>0.97</v>
+        <v>1.03</v>
       </c>
       <c r="M15" s="79" t="n">
-        <v>0.68</v>
+        <v>0.66</v>
       </c>
       <c r="N15" s="80">
-        <f>IF(OR(K15="",L15="",M15=""),"",IF(AND(K15=1,L15&gt;=0.9,L15&lt;=1.1,M15&gt;=0.85),"pass","FAIL"))</f>
+        <f>IF(OR(K15="",L15="",M15=""),"",IF(AND(K15=1,L15&gt;=0.9,L15&lt;=1.1,M15&gt;=0.70),"pass","FAIL"))</f>
         <v/>
       </c>
       <c r="O15" s="83" t="n">
-        <v>0.0203</v>
+        <v>0.0243</v>
       </c>
       <c r="P15" s="83" t="n">
-        <v>0.0239</v>
+        <v>0.027</v>
       </c>
       <c r="Q15" s="84">
         <f>IF(OR(O15="",P15=""),"",SQRT(0.5*(O15^2+P15^2)))</f>
@@ -14862,8 +13034,11 @@
       </c>
       <c r="T15" s="81" t="inlineStr">
         <is>
-          <t>Thicker wall works: fill +0.06, area +26%, sigma 16% better, for 1.50x the exposure.  peak 216.4, sat 0.0, fill 0.68, blend FAIL</t>
-        </is>
+          <t>cap 1, re-seat #2 (first: 1168us area730 fill0.66 sigma0.0243). Repeats to 5% area, 0.00 fill, 6% sigma.  flux 142</t>
+        </is>
+      </c>
+      <c r="U15" s="126" t="n">
+        <v>0.075</v>
       </c>
     </row>
     <row r="16">
@@ -14872,7 +13047,7 @@
           <t>drop</t>
         </is>
       </c>
-      <c r="B16" s="82" t="inlineStr">
+      <c r="B16" s="133" t="inlineStr">
         <is>
           <t>Kingbright</t>
         </is>
@@ -14913,7 +13088,7 @@
         <v>0.66</v>
       </c>
       <c r="N16" s="80">
-        <f>IF(OR(K16="",L16="",M16=""),"",IF(AND(K16=1,L16&gt;=0.9,L16&lt;=1.1,M16&gt;=0.85),"pass","FAIL"))</f>
+        <f>IF(OR(K16="",L16="",M16=""),"",IF(AND(K16=1,L16&gt;=0.9,L16&lt;=1.1,M16&gt;=0.70),"pass","FAIL"))</f>
         <v/>
       </c>
       <c r="O16" s="83" t="n">
@@ -14939,6 +13114,7 @@
           <t>DROPPED 2026-09-04. 0.5 mm measured worse than 0.4 mm at identical transmitted flux, i.e. cap variation not thickness. Ladder reduced to 0.2 / 0.4 mm with REPLICATE caps instead.</t>
         </is>
       </c>
+      <c r="U16" s="126" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="112" t="inlineStr">
@@ -14946,7 +13122,7 @@
           <t>done</t>
         </is>
       </c>
-      <c r="B17" s="82" t="inlineStr">
+      <c r="B17" s="133" t="inlineStr">
         <is>
           <t>Kingbright</t>
         </is>
@@ -14994,7 +13170,7 @@
         <v/>
       </c>
       <c r="N17" s="80">
-        <f>IF(OR(K17="",L17="",M17=""),"",IF(AND(K17=1,L17&gt;=0.9,L17&lt;=1.1,M17&gt;=0.85),"pass","FAIL"))</f>
+        <f>IF(OR(K17="",L17="",M17=""),"",IF(AND(K17=1,L17&gt;=0.9,L17&lt;=1.1,M17&gt;=0.70),"pass","FAIL"))</f>
         <v/>
       </c>
       <c r="O17" s="116">
@@ -15018,12 +13194,13 @@
         <v/>
       </c>
       <c r="T17" s="81" t="n"/>
+      <c r="U17" s="127" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="80" t="n">
         <v>1</v>
       </c>
-      <c r="B18" s="82" t="inlineStr">
+      <c r="B18" s="133" t="inlineStr">
         <is>
           <t>Kingbright</t>
         </is>
@@ -15043,35 +13220,35 @@
         <v/>
       </c>
       <c r="G18" s="74" t="n">
-        <v>736</v>
+        <v>1078</v>
       </c>
       <c r="H18" s="74" t="n">
-        <v>198.9</v>
+        <v>210.8</v>
       </c>
       <c r="I18" s="72" t="n">
         <v>0</v>
       </c>
       <c r="J18" s="74" t="n">
-        <v>615</v>
+        <v>697</v>
       </c>
       <c r="K18" s="74" t="n">
         <v>1</v>
       </c>
       <c r="L18" s="79" t="n">
-        <v>0.99</v>
+        <v>1.01</v>
       </c>
       <c r="M18" s="79" t="n">
         <v>0.67</v>
       </c>
       <c r="N18" s="80">
-        <f>IF(OR(K18="",L18="",M18=""),"",IF(AND(K18=1,L18&gt;=0.9,L18&lt;=1.1,M18&gt;=0.85),"pass","FAIL"))</f>
+        <f>IF(OR(K18="",L18="",M18=""),"",IF(AND(K18=1,L18&gt;=0.9,L18&lt;=1.1,M18&gt;=0.70),"pass","FAIL"))</f>
         <v/>
       </c>
       <c r="O18" s="83" t="n">
-        <v>0.0206</v>
+        <v>0.02</v>
       </c>
       <c r="P18" s="83" t="n">
-        <v>0.0232</v>
+        <v>0.0215</v>
       </c>
       <c r="Q18" s="84">
         <f>IF(OR(O18="",P18=""),"",SQRT(0.5*(O18^2+P18^2)))</f>
@@ -15087,8 +13264,11 @@
       </c>
       <c r="T18" s="81" t="inlineStr">
         <is>
-          <t>In-band re-run. First attempt at 647 us (peak 185) gave area 482 / fill 0.61 / sigma 0.0303 - SAME CAP. A 14% exposure change moved area 28%, so area and fill must be compared at matched peak, not just within 200-230.  peak 198.9, sat 0.0, fill 0.67, blend FAIL</t>
-        </is>
+          <t>cap 1, re-seat #2 (first: 1078us area694 fill0.67 sigma0.0286). Area and fill identical; sigma moved 28% - the widest of the four re-seats today (8/6/5/28%), so sigma repeatability is ~10-15%, not the 5% the tightest suggested.  flux 136</t>
+        </is>
+      </c>
+      <c r="U18" s="126" t="n">
+        <v>0.07199999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -15097,7 +13277,7 @@
           <t>drop</t>
         </is>
       </c>
-      <c r="B19" s="82" t="inlineStr">
+      <c r="B19" s="133" t="inlineStr">
         <is>
           <t>Kingbright</t>
         </is>
@@ -15124,7 +13304,7 @@
       <c r="L19" s="79" t="n"/>
       <c r="M19" s="79" t="n"/>
       <c r="N19" s="80">
-        <f>IF(OR(K19="",L19="",M19=""),"",IF(AND(K19=1,L19&gt;=0.9,L19&lt;=1.1,M19&gt;=0.85),"pass","FAIL"))</f>
+        <f>IF(OR(K19="",L19="",M19=""),"",IF(AND(K19=1,L19&gt;=0.9,L19&lt;=1.1,M19&gt;=0.70),"pass","FAIL"))</f>
         <v/>
       </c>
       <c r="O19" s="83" t="n"/>
@@ -15146,6 +13326,7 @@
           <t>DROPPED 2026-09-04. 0.5 mm measured worse than 0.4 mm at identical transmitted flux, i.e. cap variation not thickness. Ladder reduced to 0.2 / 0.4 mm with REPLICATE caps instead.</t>
         </is>
       </c>
+      <c r="U19" s="126" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="98" t="inlineStr">
@@ -15153,7 +13334,7 @@
           <t>done</t>
         </is>
       </c>
-      <c r="B20" s="99" t="inlineStr">
+      <c r="B20" s="128" t="inlineStr">
         <is>
           <t>Everlight</t>
         </is>
@@ -15201,7 +13382,7 @@
         <v/>
       </c>
       <c r="N20" s="105">
-        <f>IF(OR(K20="",L20="",M20=""),"",IF(AND(K20=1,L20&gt;=0.9,L20&lt;=1.1,M20&gt;=0.85),"pass","FAIL"))</f>
+        <f>IF(OR(K20="",L20="",M20=""),"",IF(AND(K20=1,L20&gt;=0.9,L20&lt;=1.1,M20&gt;=0.70),"pass","FAIL"))</f>
         <v/>
       </c>
       <c r="O20" s="106">
@@ -15225,12 +13406,13 @@
         <v/>
       </c>
       <c r="T20" s="110" t="n"/>
+      <c r="U20" s="125" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="80" t="n">
         <v>2</v>
       </c>
-      <c r="B21" s="82" t="inlineStr">
+      <c r="B21" s="133" t="inlineStr">
         <is>
           <t>Everlight</t>
         </is>
@@ -15249,19 +13431,37 @@
         <f>IF(OR(E21="",$B$4=""),"",E21/2-$B$4)</f>
         <v/>
       </c>
-      <c r="G21" s="74" t="n"/>
-      <c r="H21" s="74" t="n"/>
-      <c r="I21" s="72" t="n"/>
-      <c r="J21" s="74" t="n"/>
-      <c r="K21" s="74" t="n"/>
-      <c r="L21" s="79" t="n"/>
-      <c r="M21" s="79" t="n"/>
+      <c r="G21" s="74" t="n">
+        <v>3235</v>
+      </c>
+      <c r="H21" s="74" t="n">
+        <v>210.2</v>
+      </c>
+      <c r="I21" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="74" t="n">
+        <v>814</v>
+      </c>
+      <c r="K21" s="74" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" s="79" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="M21" s="79" t="n">
+        <v>0.8</v>
+      </c>
       <c r="N21" s="80">
-        <f>IF(OR(K21="",L21="",M21=""),"",IF(AND(K21=1,L21&gt;=0.9,L21&lt;=1.1,M21&gt;=0.85),"pass","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="O21" s="83" t="n"/>
-      <c r="P21" s="83" t="n"/>
+        <f>IF(OR(K21="",L21="",M21=""),"",IF(AND(K21=1,L21&gt;=0.9,L21&lt;=1.1,M21&gt;=0.70),"pass","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="O21" s="83" t="n">
+        <v>0.0163</v>
+      </c>
+      <c r="P21" s="83" t="n">
+        <v>0.0202</v>
+      </c>
       <c r="Q21" s="84">
         <f>IF(OR(O21="",P21=""),"",SQRT(0.5*(O21^2+P21^2)))</f>
         <v/>
@@ -15274,7 +13474,14 @@
         <f>IF(OR(M21="",$M$20=""),"",M21-$M$20)</f>
         <v/>
       </c>
-      <c r="T21" s="81" t="n"/>
+      <c r="T21" s="81" t="inlineStr">
+        <is>
+          <t>cap 1. Lowest sigma of the session (0.0184), though statistically tied with XL 25/0.2 (0.0187) given ~10-15% sigma repeatability. Thickness buys +0.03 fill for 1.42x exposure.  flux 53</t>
+        </is>
+      </c>
+      <c r="U21" s="126" t="n">
+        <v>0.062</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="80" t="inlineStr">
@@ -15282,7 +13489,7 @@
           <t>drop</t>
         </is>
       </c>
-      <c r="B22" s="82" t="inlineStr">
+      <c r="B22" s="133" t="inlineStr">
         <is>
           <t>Everlight</t>
         </is>
@@ -15309,7 +13516,7 @@
       <c r="L22" s="79" t="n"/>
       <c r="M22" s="79" t="n"/>
       <c r="N22" s="80">
-        <f>IF(OR(K22="",L22="",M22=""),"",IF(AND(K22=1,L22&gt;=0.9,L22&lt;=1.1,M22&gt;=0.85),"pass","FAIL"))</f>
+        <f>IF(OR(K22="",L22="",M22=""),"",IF(AND(K22=1,L22&gt;=0.9,L22&lt;=1.1,M22&gt;=0.70),"pass","FAIL"))</f>
         <v/>
       </c>
       <c r="O22" s="83" t="n"/>
@@ -15331,6 +13538,7 @@
           <t>DROPPED 2026-09-04. 0.5 mm measured worse than 0.4 mm at identical transmitted flux, i.e. cap variation not thickness. Ladder reduced to 0.2 / 0.4 mm with REPLICATE caps instead.</t>
         </is>
       </c>
+      <c r="U22" s="126" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="112" t="inlineStr">
@@ -15338,7 +13546,7 @@
           <t>done</t>
         </is>
       </c>
-      <c r="B23" s="82" t="inlineStr">
+      <c r="B23" s="133" t="inlineStr">
         <is>
           <t>Everlight</t>
         </is>
@@ -15386,7 +13594,7 @@
         <v/>
       </c>
       <c r="N23" s="80">
-        <f>IF(OR(K23="",L23="",M23=""),"",IF(AND(K23=1,L23&gt;=0.9,L23&lt;=1.1,M23&gt;=0.85),"pass","FAIL"))</f>
+        <f>IF(OR(K23="",L23="",M23=""),"",IF(AND(K23=1,L23&gt;=0.9,L23&lt;=1.1,M23&gt;=0.70),"pass","FAIL"))</f>
         <v/>
       </c>
       <c r="O23" s="116">
@@ -15410,12 +13618,13 @@
         <v/>
       </c>
       <c r="T23" s="81" t="n"/>
+      <c r="U23" s="127" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="80" t="n">
         <v>2</v>
       </c>
-      <c r="B24" s="82" t="inlineStr">
+      <c r="B24" s="133" t="inlineStr">
         <is>
           <t>Everlight</t>
         </is>
@@ -15434,19 +13643,37 @@
         <f>IF(OR(E24="",$B$4=""),"",E24/2-$B$4)</f>
         <v/>
       </c>
-      <c r="G24" s="74" t="n"/>
-      <c r="H24" s="74" t="n"/>
-      <c r="I24" s="72" t="n"/>
-      <c r="J24" s="74" t="n"/>
-      <c r="K24" s="74" t="n"/>
-      <c r="L24" s="79" t="n"/>
-      <c r="M24" s="79" t="n"/>
+      <c r="G24" s="74" t="n">
+        <v>3756</v>
+      </c>
+      <c r="H24" s="74" t="n">
+        <v>215.4</v>
+      </c>
+      <c r="I24" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="74" t="n">
+        <v>910</v>
+      </c>
+      <c r="K24" s="74" t="n">
+        <v>1</v>
+      </c>
+      <c r="L24" s="79" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="M24" s="79" t="n">
+        <v>0.9399999999999999</v>
+      </c>
       <c r="N24" s="80">
-        <f>IF(OR(K24="",L24="",M24=""),"",IF(AND(K24=1,L24&gt;=0.9,L24&lt;=1.1,M24&gt;=0.85),"pass","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="O24" s="83" t="n"/>
-      <c r="P24" s="83" t="n"/>
+        <f>IF(OR(K24="",L24="",M24=""),"",IF(AND(K24=1,L24&gt;=0.9,L24&lt;=1.1,M24&gt;=0.70),"pass","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="O24" s="83" t="n">
+        <v>0.0176</v>
+      </c>
+      <c r="P24" s="83" t="n">
+        <v>0.0288</v>
+      </c>
       <c r="Q24" s="84">
         <f>IF(OR(O24="",P24=""),"",SQRT(0.5*(O24^2+P24^2)))</f>
         <v/>
@@ -15459,7 +13686,14 @@
         <f>IF(OR(M24="",$M$23=""),"",M24-$M$23)</f>
         <v/>
       </c>
-      <c r="T24" s="81" t="n"/>
+      <c r="T24" s="81" t="inlineStr">
+        <is>
+          <t>cap 1. Thickness adds +0.02 fill for 1.08x exposure - marginal, same as the other LEDs at 25 mm. Confirms: go 25 mm, skip the thick wall.  flux 52</t>
+        </is>
+      </c>
+      <c r="U24" s="126" t="n">
+        <v>0.058</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="80" t="inlineStr">
@@ -15467,7 +13701,7 @@
           <t>drop</t>
         </is>
       </c>
-      <c r="B25" s="82" t="inlineStr">
+      <c r="B25" s="133" t="inlineStr">
         <is>
           <t>Everlight</t>
         </is>
@@ -15494,7 +13728,7 @@
       <c r="L25" s="79" t="n"/>
       <c r="M25" s="79" t="n"/>
       <c r="N25" s="80">
-        <f>IF(OR(K25="",L25="",M25=""),"",IF(AND(K25=1,L25&gt;=0.9,L25&lt;=1.1,M25&gt;=0.85),"pass","FAIL"))</f>
+        <f>IF(OR(K25="",L25="",M25=""),"",IF(AND(K25=1,L25&gt;=0.9,L25&lt;=1.1,M25&gt;=0.70),"pass","FAIL"))</f>
         <v/>
       </c>
       <c r="O25" s="83" t="n"/>
@@ -15516,6 +13750,7 @@
           <t>DROPPED 2026-09-04. 0.5 mm measured worse than 0.4 mm at identical transmitted flux, i.e. cap variation not thickness. Ladder reduced to 0.2 / 0.4 mm with REPLICATE caps instead.</t>
         </is>
       </c>
+      <c r="U25" s="126" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="98" t="inlineStr">
@@ -15523,7 +13758,7 @@
           <t>done</t>
         </is>
       </c>
-      <c r="B26" s="99" t="inlineStr">
+      <c r="B26" s="128" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -15571,7 +13806,7 @@
         <v/>
       </c>
       <c r="N26" s="105">
-        <f>IF(OR(K26="",L26="",M26=""),"",IF(AND(K26=1,L26&gt;=0.9,L26&lt;=1.1,M26&gt;=0.85),"pass","FAIL"))</f>
+        <f>IF(OR(K26="",L26="",M26=""),"",IF(AND(K26=1,L26&gt;=0.9,L26&lt;=1.1,M26&gt;=0.70),"pass","FAIL"))</f>
         <v/>
       </c>
       <c r="O26" s="106">
@@ -15595,12 +13830,13 @@
         <v/>
       </c>
       <c r="T26" s="110" t="n"/>
+      <c r="U26" s="125" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="80" t="n">
         <v>3</v>
       </c>
-      <c r="B27" s="82" t="inlineStr">
+      <c r="B27" s="133" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -15619,19 +13855,37 @@
         <f>IF(OR(E27="",$B$4=""),"",E27/2-$B$4)</f>
         <v/>
       </c>
-      <c r="G27" s="74" t="n"/>
-      <c r="H27" s="74" t="n"/>
-      <c r="I27" s="72" t="n"/>
-      <c r="J27" s="74" t="n"/>
-      <c r="K27" s="74" t="n"/>
-      <c r="L27" s="79" t="n"/>
-      <c r="M27" s="79" t="n"/>
+      <c r="G27" s="74" t="n">
+        <v>7351</v>
+      </c>
+      <c r="H27" s="74" t="n">
+        <v>203.8</v>
+      </c>
+      <c r="I27" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="74" t="n">
+        <v>846</v>
+      </c>
+      <c r="K27" s="74" t="n">
+        <v>1</v>
+      </c>
+      <c r="L27" s="79" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M27" s="79" t="n">
+        <v>0.85</v>
+      </c>
       <c r="N27" s="80">
-        <f>IF(OR(K27="",L27="",M27=""),"",IF(AND(K27=1,L27&gt;=0.9,L27&lt;=1.1,M27&gt;=0.85),"pass","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="O27" s="83" t="n"/>
-      <c r="P27" s="83" t="n"/>
+        <f>IF(OR(K27="",L27="",M27=""),"",IF(AND(K27=1,L27&gt;=0.9,L27&lt;=1.1,M27&gt;=0.70),"pass","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="O27" s="83" t="n">
+        <v>0.0185</v>
+      </c>
+      <c r="P27" s="83" t="n">
+        <v>0.0309</v>
+      </c>
       <c r="Q27" s="84">
         <f>IF(OR(O27="",P27=""),"",SQRT(0.5*(O27^2+P27^2)))</f>
         <v/>
@@ -15644,7 +13898,14 @@
         <f>IF(OR(M27="",$M$26=""),"",M27-$M$26)</f>
         <v/>
       </c>
-      <c r="T27" s="81" t="n"/>
+      <c r="T27" s="81" t="inlineStr">
+        <is>
+          <t>cap 1. FIRST BUILD TO PASS THE BLEND GATE: fill 0.85, lobe 0.059, blobs 1, w/h 1.01. Thickness cost only 1.23x here vs 2.10x for Kingbright on the SAME caps - a wide beam already takes a long oblique path through the shell, so extra wall adds proportionally less.  flux 23</t>
+        </is>
+      </c>
+      <c r="U27" s="126" t="n">
+        <v>0.059</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="80" t="inlineStr">
@@ -15652,7 +13913,7 @@
           <t>drop</t>
         </is>
       </c>
-      <c r="B28" s="82" t="inlineStr">
+      <c r="B28" s="133" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -15679,7 +13940,7 @@
       <c r="L28" s="79" t="n"/>
       <c r="M28" s="79" t="n"/>
       <c r="N28" s="80">
-        <f>IF(OR(K28="",L28="",M28=""),"",IF(AND(K28=1,L28&gt;=0.9,L28&lt;=1.1,M28&gt;=0.85),"pass","FAIL"))</f>
+        <f>IF(OR(K28="",L28="",M28=""),"",IF(AND(K28=1,L28&gt;=0.9,L28&lt;=1.1,M28&gt;=0.70),"pass","FAIL"))</f>
         <v/>
       </c>
       <c r="O28" s="83" t="n"/>
@@ -15701,6 +13962,7 @@
           <t>DROPPED 2026-09-04. 0.5 mm measured worse than 0.4 mm at identical transmitted flux, i.e. cap variation not thickness. Ladder reduced to 0.2 / 0.4 mm with REPLICATE caps instead.</t>
         </is>
       </c>
+      <c r="U28" s="126" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="112" t="inlineStr">
@@ -15708,7 +13970,7 @@
           <t>done</t>
         </is>
       </c>
-      <c r="B29" s="82" t="inlineStr">
+      <c r="B29" s="133" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -15756,7 +14018,7 @@
         <v/>
       </c>
       <c r="N29" s="80">
-        <f>IF(OR(K29="",L29="",M29=""),"",IF(AND(K29=1,L29&gt;=0.9,L29&lt;=1.1,M29&gt;=0.85),"pass","FAIL"))</f>
+        <f>IF(OR(K29="",L29="",M29=""),"",IF(AND(K29=1,L29&gt;=0.9,L29&lt;=1.1,M29&gt;=0.70),"pass","FAIL"))</f>
         <v/>
       </c>
       <c r="O29" s="116">
@@ -15780,12 +14042,13 @@
         <v/>
       </c>
       <c r="T29" s="81" t="n"/>
+      <c r="U29" s="127" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="80" t="n">
         <v>3</v>
       </c>
-      <c r="B30" s="82" t="inlineStr">
+      <c r="B30" s="133" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -15804,19 +14067,37 @@
         <f>IF(OR(E30="",$B$4=""),"",E30/2-$B$4)</f>
         <v/>
       </c>
-      <c r="G30" s="74" t="n"/>
-      <c r="H30" s="74" t="n"/>
-      <c r="I30" s="72" t="n"/>
-      <c r="J30" s="74" t="n"/>
-      <c r="K30" s="74" t="n"/>
-      <c r="L30" s="79" t="n"/>
-      <c r="M30" s="79" t="n"/>
+      <c r="G30" s="74" t="n">
+        <v>8628</v>
+      </c>
+      <c r="H30" s="74" t="n">
+        <v>213.7</v>
+      </c>
+      <c r="I30" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="74" t="n">
+        <v>967</v>
+      </c>
+      <c r="K30" s="74" t="n">
+        <v>1</v>
+      </c>
+      <c r="L30" s="79" t="n">
+        <v>1</v>
+      </c>
+      <c r="M30" s="79" t="n">
+        <v>1.03</v>
+      </c>
       <c r="N30" s="80">
-        <f>IF(OR(K30="",L30="",M30=""),"",IF(AND(K30=1,L30&gt;=0.9,L30&lt;=1.1,M30&gt;=0.85),"pass","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="O30" s="83" t="n"/>
-      <c r="P30" s="83" t="n"/>
+        <f>IF(OR(K30="",L30="",M30=""),"",IF(AND(K30=1,L30&gt;=0.9,L30&lt;=1.1,M30&gt;=0.70),"pass","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="O30" s="83" t="n">
+        <v>0.0206</v>
+      </c>
+      <c r="P30" s="83" t="n">
+        <v>0.0245</v>
+      </c>
       <c r="Q30" s="84">
         <f>IF(OR(O30="",P30=""),"",SQRT(0.5*(O30^2+P30^2)))</f>
         <v/>
@@ -15829,7 +14110,14 @@
         <f>IF(OR(M30="",$M$29=""),"",M30-$M$29)</f>
         <v/>
       </c>
-      <c r="T30" s="81" t="n"/>
+      <c r="T30" s="81" t="inlineStr">
+        <is>
+          <t>cap 1. First attempt gave sigma 0.1856 (sv/su 3.4) while area/fill/lobe were identical - a rig disturbance mid-run, rejected and re-measured. Thickness adds nothing at 25 mm: same fill, same lobe, 5% more exposure.  flux 24</t>
+        </is>
+      </c>
+      <c r="U30" s="126" t="n">
+        <v>0.062</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="80" t="inlineStr">
@@ -15837,7 +14125,7 @@
           <t>drop</t>
         </is>
       </c>
-      <c r="B31" s="82" t="inlineStr">
+      <c r="B31" s="133" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -15864,7 +14152,7 @@
       <c r="L31" s="79" t="n"/>
       <c r="M31" s="79" t="n"/>
       <c r="N31" s="80">
-        <f>IF(OR(K31="",L31="",M31=""),"",IF(AND(K31=1,L31&gt;=0.9,L31&lt;=1.1,M31&gt;=0.85),"pass","FAIL"))</f>
+        <f>IF(OR(K31="",L31="",M31=""),"",IF(AND(K31=1,L31&gt;=0.9,L31&lt;=1.1,M31&gt;=0.70),"pass","FAIL"))</f>
         <v/>
       </c>
       <c r="O31" s="83" t="n"/>
@@ -15886,6 +14174,7 @@
           <t>DROPPED 2026-09-04. 0.5 mm measured worse than 0.4 mm at identical transmitted flux, i.e. cap variation not thickness. Ladder reduced to 0.2 / 0.4 mm with REPLICATE caps instead.</t>
         </is>
       </c>
+      <c r="U31" s="126" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="76" t="inlineStr">

--- a/LED_characterisation.xlsx
+++ b/LED_characterisation.xlsx
@@ -289,7 +289,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="134">
+  <cellXfs count="140">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -596,6 +596,20 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="18" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7350,2429 +7364,2016 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O91"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <dimension ref="A1:R66"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="9" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="7" customWidth="1" min="10" max="10"/>
+    <col width="7" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="9" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="30" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>TEST C - Range (sample 1 of each type / build)</t>
+    <row r="1">
+      <c r="A1" s="65" t="inlineStr">
+        <is>
+          <t>TEST C - Range, at 0 deg and 90 deg</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
-        <is>
-          <t>Blue on yellow = fill in.  Black = calculated.  Each diffused marker holds FOUR LEDs in series off 9 V; 'bare (ref)' is a single LED, kept as a reference and never ranked.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A2" s="66" t="inlineStr">
+        <is>
+          <t>25 mm / 0.2 mm caps. Kingbright dropped - 19.7x anisotropy puts it out regardless of range. The 90 deg rows are the BINDING case: a marker detected at 90 deg is certainly detected at 0 deg, so the 90 deg far limit IS the operating range and it sets how many cameras the arena needs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="66" t="inlineStr">
+        <is>
+          <t>Arena ambient ceiling today: ~14.5 ms in frame, ~40 ms away from the right-hand windows (overcast 16:25).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="34" customHeight="1">
+      <c r="A6" s="77" t="inlineStr">
         <is>
           <t>LED Type</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="C3" s="8" t="inlineStr">
-        <is>
-          <t>Sample</t>
-        </is>
-      </c>
-      <c r="D3" s="8" t="inlineStr">
+      <c r="B6" s="77" t="inlineStr">
+        <is>
+          <t>Angle
+(deg)</t>
+        </is>
+      </c>
+      <c r="C6" s="77" t="inlineStr">
         <is>
           <t>Distance
 (m)</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="D6" s="77" t="inlineStr">
         <is>
           <t>Exposure
 (us)</t>
         </is>
       </c>
-      <c r="F3" s="8" t="inlineStr">
-        <is>
-          <t>Peak
-(0-255)</t>
-        </is>
-      </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="E6" s="77" t="inlineStr">
+        <is>
+          <t>Peak</t>
+        </is>
+      </c>
+      <c r="F6" s="77" t="inlineStr">
         <is>
           <t>Sat px</t>
         </is>
       </c>
-      <c r="H3" s="8" t="inlineStr">
+      <c r="G6" s="77" t="inlineStr">
         <is>
           <t>Sensor area
 (px)</t>
         </is>
       </c>
-      <c r="I3" s="8" t="inlineStr">
+      <c r="H6" s="77" t="inlineStr">
+        <is>
+          <t>npix</t>
+        </is>
+      </c>
+      <c r="I6" s="77" t="inlineStr">
         <is>
           <t>blobs</t>
         </is>
       </c>
-      <c r="J3" s="8" t="inlineStr">
+      <c r="J6" s="77" t="inlineStr">
+        <is>
+          <t>w/h</t>
+        </is>
+      </c>
+      <c r="K6" s="77" t="inlineStr">
+        <is>
+          <t>Fill</t>
+        </is>
+      </c>
+      <c r="L6" s="77" t="inlineStr">
+        <is>
+          <t>Lobe</t>
+        </is>
+      </c>
+      <c r="M6" s="77" t="inlineStr">
+        <is>
+          <t>sigma_u
+(px)</t>
+        </is>
+      </c>
+      <c r="N6" s="77" t="inlineStr">
+        <is>
+          <t>sigma_v
+(px)</t>
+        </is>
+      </c>
+      <c r="O6" s="77" t="inlineStr">
         <is>
           <t>sigma_RMS
 (px)</t>
         </is>
       </c>
-      <c r="K3" s="8" t="inlineStr">
+      <c r="P6" s="77" t="inlineStr">
         <is>
           <t>Detected?
 (Y/N)</t>
         </is>
       </c>
-      <c r="L3" s="8" t="inlineStr">
-        <is>
-          <t>Valid range
-(calc)</t>
-        </is>
-      </c>
-      <c r="M3" s="8" t="inlineStr">
+      <c r="Q6" s="77" t="inlineStr">
+        <is>
+          <t>area x d^2
+(const if resolved)</t>
+        </is>
+      </c>
+      <c r="R6" s="77" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="128" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="B7" s="100" t="n">
+        <v>90</v>
+      </c>
+      <c r="C7" s="136" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D7" s="129" t="n">
+        <v>1997</v>
+      </c>
+      <c r="E7" s="129" t="n">
+        <v>210.2</v>
+      </c>
+      <c r="F7" s="134" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="129" t="n">
+        <v>4999</v>
+      </c>
+      <c r="H7" s="129" t="n">
+        <v>6098</v>
+      </c>
+      <c r="I7" s="129" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" s="130" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="K7" s="130" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="L7" s="131" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="M7" s="132" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="N7" s="132" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="O7" s="107">
+        <f>IF(OR(M7="",N7=""),"",SQRT(0.5*(M7^2+N7^2)))</f>
+        <v/>
+      </c>
+      <c r="P7" s="135" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q7" s="100">
+        <f>IF(OR(C7="",G7=""),"",G7*C7^2)</f>
+        <v/>
+      </c>
+      <c r="R7" s="110" t="inlineStr">
+        <is>
+          <t>VGA 640x480 window (blob ~103 px). QVGA compresses at this blob size - black-level depression when the marker fills &gt;10% of frame.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="133" t="n"/>
+      <c r="B8" s="85" t="n"/>
+      <c r="C8" s="137" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D8" s="74" t="n">
+        <v>3187</v>
+      </c>
+      <c r="E8" s="74" t="n">
+        <v>205.2</v>
+      </c>
+      <c r="F8" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="74" t="n">
+        <v>1732</v>
+      </c>
+      <c r="H8" s="74" t="n">
+        <v>2188</v>
+      </c>
+      <c r="I8" s="74" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" s="79" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="K8" s="79" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="L8" s="126" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="M8" s="83" t="n">
+        <v>0.0108</v>
+      </c>
+      <c r="N8" s="83" t="n">
+        <v>0.0213</v>
+      </c>
+      <c r="O8" s="84">
+        <f>IF(OR(M8="",N8=""),"",SQRT(0.5*(M8^2+N8^2)))</f>
+        <v/>
+      </c>
+      <c r="P8" s="78" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q8" s="85">
+        <f>IF(OR(C8="",G8=""),"",G8*C8^2)</f>
+        <v/>
+      </c>
+      <c r="R8" s="81" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="133" t="n"/>
+      <c r="B9" s="85" t="n"/>
+      <c r="C9" s="137" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D9" s="74" t="n">
+        <v>9760</v>
+      </c>
+      <c r="E9" s="74" t="n">
+        <v>204.8</v>
+      </c>
+      <c r="F9" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="74" t="n">
+        <v>1267</v>
+      </c>
+      <c r="H9" s="74" t="n">
+        <v>1441</v>
+      </c>
+      <c r="I9" s="74" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" s="79" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="K9" s="79" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="L9" s="126" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="M9" s="83" t="n">
+        <v>0.0163</v>
+      </c>
+      <c r="N9" s="83" t="n">
+        <v>0.0219</v>
+      </c>
+      <c r="O9" s="84">
+        <f>IF(OR(M9="",N9=""),"",SQRT(0.5*(M9^2+N9^2)))</f>
+        <v/>
+      </c>
+      <c r="P9" s="78" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q9" s="85">
+        <f>IF(OR(C9="",G9=""),"",G9*C9^2)</f>
+        <v/>
+      </c>
+      <c r="R9" s="81" t="inlineStr">
+        <is>
+          <t>Exposure now scaling as d^2 (3.06x for 1.67x distance) - the marker has gone point-like between 1.5 and 2.5 m.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="133" t="n"/>
+      <c r="B10" s="85" t="n"/>
+      <c r="C10" s="137" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D10" s="74" t="n"/>
+      <c r="E10" s="74" t="n"/>
+      <c r="F10" s="72" t="n"/>
+      <c r="G10" s="74" t="n"/>
+      <c r="H10" s="74" t="n"/>
+      <c r="I10" s="74" t="n"/>
+      <c r="J10" s="79" t="n"/>
+      <c r="K10" s="79" t="n"/>
+      <c r="L10" s="126" t="n"/>
+      <c r="M10" s="83" t="n"/>
+      <c r="N10" s="83" t="n"/>
+      <c r="O10" s="84">
+        <f>IF(OR(M10="",N10=""),"",SQRT(0.5*(M10^2+N10^2)))</f>
+        <v/>
+      </c>
+      <c r="P10" s="78" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q10" s="85">
+        <f>IF(OR(C10="",G10=""),"",G10*C10^2)</f>
+        <v/>
+      </c>
+      <c r="R10" s="81" t="inlineStr">
+        <is>
+          <t>AMBIENT-LIMITED, not marker-limited. Targeting ran to 101702 us (7x the ~14.5 ms arena ceiling) and locked onto window light: blobs 3, w/h 1.59, lobe 0.787 - not a marker. XL at 90 deg is unusable beyond ~2.5-3 m under this afternoon's overcast. Re-measure at night.  NOT DETECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="133" t="n"/>
+      <c r="B11" s="85" t="n"/>
+      <c r="C11" s="137" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D11" s="74" t="n"/>
+      <c r="E11" s="74" t="n"/>
+      <c r="F11" s="72" t="n"/>
+      <c r="G11" s="74" t="n"/>
+      <c r="H11" s="74" t="n"/>
+      <c r="I11" s="74" t="n"/>
+      <c r="J11" s="79" t="n"/>
+      <c r="K11" s="79" t="n"/>
+      <c r="L11" s="126" t="n"/>
+      <c r="M11" s="83" t="n"/>
+      <c r="N11" s="83" t="n"/>
+      <c r="O11" s="84">
+        <f>IF(OR(M11="",N11=""),"",SQRT(0.5*(M11^2+N11^2)))</f>
+        <v/>
+      </c>
+      <c r="P11" s="78" t="n"/>
+      <c r="Q11" s="85">
+        <f>IF(OR(C11="",G11=""),"",G11*C11^2)</f>
+        <v/>
+      </c>
+      <c r="R11" s="81" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="133" t="n"/>
+      <c r="B12" s="85" t="n"/>
+      <c r="C12" s="137" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D12" s="74" t="n"/>
+      <c r="E12" s="74" t="n"/>
+      <c r="F12" s="72" t="n"/>
+      <c r="G12" s="74" t="n"/>
+      <c r="H12" s="74" t="n"/>
+      <c r="I12" s="74" t="n"/>
+      <c r="J12" s="79" t="n"/>
+      <c r="K12" s="79" t="n"/>
+      <c r="L12" s="126" t="n"/>
+      <c r="M12" s="83" t="n"/>
+      <c r="N12" s="83" t="n"/>
+      <c r="O12" s="84">
+        <f>IF(OR(M12="",N12=""),"",SQRT(0.5*(M12^2+N12^2)))</f>
+        <v/>
+      </c>
+      <c r="P12" s="78" t="n"/>
+      <c r="Q12" s="85">
+        <f>IF(OR(C12="",G12=""),"",G12*C12^2)</f>
+        <v/>
+      </c>
+      <c r="R12" s="81" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="133" t="n"/>
+      <c r="B13" s="85" t="n"/>
+      <c r="C13" s="137" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D13" s="74" t="n"/>
+      <c r="E13" s="74" t="n"/>
+      <c r="F13" s="72" t="n"/>
+      <c r="G13" s="74" t="n"/>
+      <c r="H13" s="74" t="n"/>
+      <c r="I13" s="74" t="n"/>
+      <c r="J13" s="79" t="n"/>
+      <c r="K13" s="79" t="n"/>
+      <c r="L13" s="126" t="n"/>
+      <c r="M13" s="83" t="n"/>
+      <c r="N13" s="83" t="n"/>
+      <c r="O13" s="84">
+        <f>IF(OR(M13="",N13=""),"",SQRT(0.5*(M13^2+N13^2)))</f>
+        <v/>
+      </c>
+      <c r="P13" s="78" t="n"/>
+      <c r="Q13" s="85">
+        <f>IF(OR(C13="",G13=""),"",G13*C13^2)</f>
+        <v/>
+      </c>
+      <c r="R13" s="81" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="133" t="n"/>
+      <c r="B14" s="85" t="n"/>
+      <c r="C14" s="137" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D14" s="74" t="n"/>
+      <c r="E14" s="74" t="n"/>
+      <c r="F14" s="72" t="n"/>
+      <c r="G14" s="74" t="n"/>
+      <c r="H14" s="74" t="n"/>
+      <c r="I14" s="74" t="n"/>
+      <c r="J14" s="79" t="n"/>
+      <c r="K14" s="79" t="n"/>
+      <c r="L14" s="126" t="n"/>
+      <c r="M14" s="83" t="n"/>
+      <c r="N14" s="83" t="n"/>
+      <c r="O14" s="84">
+        <f>IF(OR(M14="",N14=""),"",SQRT(0.5*(M14^2+N14^2)))</f>
+        <v/>
+      </c>
+      <c r="P14" s="78" t="n"/>
+      <c r="Q14" s="85">
+        <f>IF(OR(C14="",G14=""),"",G14*C14^2)</f>
+        <v/>
+      </c>
+      <c r="R14" s="81" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="133" t="n"/>
+      <c r="B15" s="85" t="n"/>
+      <c r="C15" s="137" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="D15" s="74" t="n"/>
+      <c r="E15" s="74" t="n"/>
+      <c r="F15" s="72" t="n"/>
+      <c r="G15" s="74" t="n"/>
+      <c r="H15" s="74" t="n"/>
+      <c r="I15" s="74" t="n"/>
+      <c r="J15" s="79" t="n"/>
+      <c r="K15" s="79" t="n"/>
+      <c r="L15" s="126" t="n"/>
+      <c r="M15" s="83" t="n"/>
+      <c r="N15" s="83" t="n"/>
+      <c r="O15" s="84">
+        <f>IF(OR(M15="",N15=""),"",SQRT(0.5*(M15^2+N15^2)))</f>
+        <v/>
+      </c>
+      <c r="P15" s="78" t="n"/>
+      <c r="Q15" s="85">
+        <f>IF(OR(C15="",G15=""),"",G15*C15^2)</f>
+        <v/>
+      </c>
+      <c r="R15" s="81" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="133" t="n"/>
+      <c r="B16" s="85" t="n"/>
+      <c r="C16" s="137" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="D16" s="74" t="n"/>
+      <c r="E16" s="74" t="n"/>
+      <c r="F16" s="72" t="n"/>
+      <c r="G16" s="74" t="n"/>
+      <c r="H16" s="74" t="n"/>
+      <c r="I16" s="74" t="n"/>
+      <c r="J16" s="79" t="n"/>
+      <c r="K16" s="79" t="n"/>
+      <c r="L16" s="126" t="n"/>
+      <c r="M16" s="83" t="n"/>
+      <c r="N16" s="83" t="n"/>
+      <c r="O16" s="84">
+        <f>IF(OR(M16="",N16=""),"",SQRT(0.5*(M16^2+N16^2)))</f>
+        <v/>
+      </c>
+      <c r="P16" s="78" t="n"/>
+      <c r="Q16" s="85">
+        <f>IF(OR(C16="",G16=""),"",G16*C16^2)</f>
+        <v/>
+      </c>
+      <c r="R16" s="81" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="133" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="B17" s="85" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="137" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D17" s="74" t="n"/>
+      <c r="E17" s="74" t="n"/>
+      <c r="F17" s="72" t="n"/>
+      <c r="G17" s="74" t="n"/>
+      <c r="H17" s="74" t="n"/>
+      <c r="I17" s="74" t="n"/>
+      <c r="J17" s="79" t="n"/>
+      <c r="K17" s="79" t="n"/>
+      <c r="L17" s="126" t="n"/>
+      <c r="M17" s="83" t="n"/>
+      <c r="N17" s="83" t="n"/>
+      <c r="O17" s="84">
+        <f>IF(OR(M17="",N17=""),"",SQRT(0.5*(M17^2+N17^2)))</f>
+        <v/>
+      </c>
+      <c r="P17" s="78" t="n"/>
+      <c r="Q17" s="85">
+        <f>IF(OR(C17="",G17=""),"",G17*C17^2)</f>
+        <v/>
+      </c>
+      <c r="R17" s="81" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="133" t="n"/>
+      <c r="B18" s="85" t="n"/>
+      <c r="C18" s="137" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D18" s="74" t="n"/>
+      <c r="E18" s="74" t="n"/>
+      <c r="F18" s="72" t="n"/>
+      <c r="G18" s="74" t="n"/>
+      <c r="H18" s="74" t="n"/>
+      <c r="I18" s="74" t="n"/>
+      <c r="J18" s="79" t="n"/>
+      <c r="K18" s="79" t="n"/>
+      <c r="L18" s="126" t="n"/>
+      <c r="M18" s="83" t="n"/>
+      <c r="N18" s="83" t="n"/>
+      <c r="O18" s="84">
+        <f>IF(OR(M18="",N18=""),"",SQRT(0.5*(M18^2+N18^2)))</f>
+        <v/>
+      </c>
+      <c r="P18" s="78" t="n"/>
+      <c r="Q18" s="85">
+        <f>IF(OR(C18="",G18=""),"",G18*C18^2)</f>
+        <v/>
+      </c>
+      <c r="R18" s="81" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="133" t="n"/>
+      <c r="B19" s="85" t="n"/>
+      <c r="C19" s="137" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D19" s="74" t="n"/>
+      <c r="E19" s="74" t="n"/>
+      <c r="F19" s="72" t="n"/>
+      <c r="G19" s="74" t="n"/>
+      <c r="H19" s="74" t="n"/>
+      <c r="I19" s="74" t="n"/>
+      <c r="J19" s="79" t="n"/>
+      <c r="K19" s="79" t="n"/>
+      <c r="L19" s="126" t="n"/>
+      <c r="M19" s="83" t="n"/>
+      <c r="N19" s="83" t="n"/>
+      <c r="O19" s="84">
+        <f>IF(OR(M19="",N19=""),"",SQRT(0.5*(M19^2+N19^2)))</f>
+        <v/>
+      </c>
+      <c r="P19" s="78" t="n"/>
+      <c r="Q19" s="85">
+        <f>IF(OR(C19="",G19=""),"",G19*C19^2)</f>
+        <v/>
+      </c>
+      <c r="R19" s="81" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="133" t="n"/>
+      <c r="B20" s="85" t="n"/>
+      <c r="C20" s="137" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D20" s="74" t="n"/>
+      <c r="E20" s="74" t="n"/>
+      <c r="F20" s="72" t="n"/>
+      <c r="G20" s="74" t="n"/>
+      <c r="H20" s="74" t="n"/>
+      <c r="I20" s="74" t="n"/>
+      <c r="J20" s="79" t="n"/>
+      <c r="K20" s="79" t="n"/>
+      <c r="L20" s="126" t="n"/>
+      <c r="M20" s="83" t="n"/>
+      <c r="N20" s="83" t="n"/>
+      <c r="O20" s="84">
+        <f>IF(OR(M20="",N20=""),"",SQRT(0.5*(M20^2+N20^2)))</f>
+        <v/>
+      </c>
+      <c r="P20" s="78" t="n"/>
+      <c r="Q20" s="85">
+        <f>IF(OR(C20="",G20=""),"",G20*C20^2)</f>
+        <v/>
+      </c>
+      <c r="R20" s="81" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="133" t="n"/>
+      <c r="B21" s="85" t="n"/>
+      <c r="C21" s="137" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D21" s="74" t="n"/>
+      <c r="E21" s="74" t="n"/>
+      <c r="F21" s="72" t="n"/>
+      <c r="G21" s="74" t="n"/>
+      <c r="H21" s="74" t="n"/>
+      <c r="I21" s="74" t="n"/>
+      <c r="J21" s="79" t="n"/>
+      <c r="K21" s="79" t="n"/>
+      <c r="L21" s="126" t="n"/>
+      <c r="M21" s="83" t="n"/>
+      <c r="N21" s="83" t="n"/>
+      <c r="O21" s="84">
+        <f>IF(OR(M21="",N21=""),"",SQRT(0.5*(M21^2+N21^2)))</f>
+        <v/>
+      </c>
+      <c r="P21" s="78" t="n"/>
+      <c r="Q21" s="85">
+        <f>IF(OR(C21="",G21=""),"",G21*C21^2)</f>
+        <v/>
+      </c>
+      <c r="R21" s="81" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="133" t="n"/>
+      <c r="B22" s="85" t="n"/>
+      <c r="C22" s="137" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D22" s="74" t="n"/>
+      <c r="E22" s="74" t="n"/>
+      <c r="F22" s="72" t="n"/>
+      <c r="G22" s="74" t="n"/>
+      <c r="H22" s="74" t="n"/>
+      <c r="I22" s="74" t="n"/>
+      <c r="J22" s="79" t="n"/>
+      <c r="K22" s="79" t="n"/>
+      <c r="L22" s="126" t="n"/>
+      <c r="M22" s="83" t="n"/>
+      <c r="N22" s="83" t="n"/>
+      <c r="O22" s="84">
+        <f>IF(OR(M22="",N22=""),"",SQRT(0.5*(M22^2+N22^2)))</f>
+        <v/>
+      </c>
+      <c r="P22" s="78" t="n"/>
+      <c r="Q22" s="85">
+        <f>IF(OR(C22="",G22=""),"",G22*C22^2)</f>
+        <v/>
+      </c>
+      <c r="R22" s="81" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="133" t="n"/>
+      <c r="B23" s="85" t="n"/>
+      <c r="C23" s="137" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D23" s="74" t="n"/>
+      <c r="E23" s="74" t="n"/>
+      <c r="F23" s="72" t="n"/>
+      <c r="G23" s="74" t="n"/>
+      <c r="H23" s="74" t="n"/>
+      <c r="I23" s="74" t="n"/>
+      <c r="J23" s="79" t="n"/>
+      <c r="K23" s="79" t="n"/>
+      <c r="L23" s="126" t="n"/>
+      <c r="M23" s="83" t="n"/>
+      <c r="N23" s="83" t="n"/>
+      <c r="O23" s="84">
+        <f>IF(OR(M23="",N23=""),"",SQRT(0.5*(M23^2+N23^2)))</f>
+        <v/>
+      </c>
+      <c r="P23" s="78" t="n"/>
+      <c r="Q23" s="85">
+        <f>IF(OR(C23="",G23=""),"",G23*C23^2)</f>
+        <v/>
+      </c>
+      <c r="R23" s="81" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="133" t="n"/>
+      <c r="B24" s="85" t="n"/>
+      <c r="C24" s="137" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D24" s="74" t="n"/>
+      <c r="E24" s="74" t="n"/>
+      <c r="F24" s="72" t="n"/>
+      <c r="G24" s="74" t="n"/>
+      <c r="H24" s="74" t="n"/>
+      <c r="I24" s="74" t="n"/>
+      <c r="J24" s="79" t="n"/>
+      <c r="K24" s="79" t="n"/>
+      <c r="L24" s="126" t="n"/>
+      <c r="M24" s="83" t="n"/>
+      <c r="N24" s="83" t="n"/>
+      <c r="O24" s="84">
+        <f>IF(OR(M24="",N24=""),"",SQRT(0.5*(M24^2+N24^2)))</f>
+        <v/>
+      </c>
+      <c r="P24" s="78" t="n"/>
+      <c r="Q24" s="85">
+        <f>IF(OR(C24="",G24=""),"",G24*C24^2)</f>
+        <v/>
+      </c>
+      <c r="R24" s="81" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="133" t="n"/>
+      <c r="B25" s="85" t="n"/>
+      <c r="C25" s="137" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="D25" s="74" t="n"/>
+      <c r="E25" s="74" t="n"/>
+      <c r="F25" s="72" t="n"/>
+      <c r="G25" s="74" t="n"/>
+      <c r="H25" s="74" t="n"/>
+      <c r="I25" s="74" t="n"/>
+      <c r="J25" s="79" t="n"/>
+      <c r="K25" s="79" t="n"/>
+      <c r="L25" s="126" t="n"/>
+      <c r="M25" s="83" t="n"/>
+      <c r="N25" s="83" t="n"/>
+      <c r="O25" s="84">
+        <f>IF(OR(M25="",N25=""),"",SQRT(0.5*(M25^2+N25^2)))</f>
+        <v/>
+      </c>
+      <c r="P25" s="78" t="n"/>
+      <c r="Q25" s="85">
+        <f>IF(OR(C25="",G25=""),"",G25*C25^2)</f>
+        <v/>
+      </c>
+      <c r="R25" s="81" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="133" t="n"/>
+      <c r="B26" s="85" t="n"/>
+      <c r="C26" s="137" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="D26" s="74" t="n"/>
+      <c r="E26" s="74" t="n"/>
+      <c r="F26" s="72" t="n"/>
+      <c r="G26" s="74" t="n"/>
+      <c r="H26" s="74" t="n"/>
+      <c r="I26" s="74" t="n"/>
+      <c r="J26" s="79" t="n"/>
+      <c r="K26" s="79" t="n"/>
+      <c r="L26" s="126" t="n"/>
+      <c r="M26" s="83" t="n"/>
+      <c r="N26" s="83" t="n"/>
+      <c r="O26" s="84">
+        <f>IF(OR(M26="",N26=""),"",SQRT(0.5*(M26^2+N26^2)))</f>
+        <v/>
+      </c>
+      <c r="P26" s="78" t="n"/>
+      <c r="Q26" s="85">
+        <f>IF(OR(C26="",G26=""),"",G26*C26^2)</f>
+        <v/>
+      </c>
+      <c r="R26" s="81" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="128" t="inlineStr">
+        <is>
+          <t>Everlight</t>
+        </is>
+      </c>
+      <c r="B27" s="100" t="n">
+        <v>90</v>
+      </c>
+      <c r="C27" s="136" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D27" s="129" t="n"/>
+      <c r="E27" s="129" t="n"/>
+      <c r="F27" s="134" t="n"/>
+      <c r="G27" s="129" t="n"/>
+      <c r="H27" s="129" t="n"/>
+      <c r="I27" s="129" t="n"/>
+      <c r="J27" s="130" t="n"/>
+      <c r="K27" s="130" t="n"/>
+      <c r="L27" s="131" t="n"/>
+      <c r="M27" s="132" t="n"/>
+      <c r="N27" s="132" t="n"/>
+      <c r="O27" s="107">
+        <f>IF(OR(M27="",N27=""),"",SQRT(0.5*(M27^2+N27^2)))</f>
+        <v/>
+      </c>
+      <c r="P27" s="135" t="n"/>
+      <c r="Q27" s="100">
+        <f>IF(OR(C27="",G27=""),"",G27*C27^2)</f>
+        <v/>
+      </c>
+      <c r="R27" s="110" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="133" t="n"/>
+      <c r="B28" s="85" t="n"/>
+      <c r="C28" s="137" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D28" s="74" t="n"/>
+      <c r="E28" s="74" t="n"/>
+      <c r="F28" s="72" t="n"/>
+      <c r="G28" s="74" t="n"/>
+      <c r="H28" s="74" t="n"/>
+      <c r="I28" s="74" t="n"/>
+      <c r="J28" s="79" t="n"/>
+      <c r="K28" s="79" t="n"/>
+      <c r="L28" s="126" t="n"/>
+      <c r="M28" s="83" t="n"/>
+      <c r="N28" s="83" t="n"/>
+      <c r="O28" s="84">
+        <f>IF(OR(M28="",N28=""),"",SQRT(0.5*(M28^2+N28^2)))</f>
+        <v/>
+      </c>
+      <c r="P28" s="78" t="n"/>
+      <c r="Q28" s="85">
+        <f>IF(OR(C28="",G28=""),"",G28*C28^2)</f>
+        <v/>
+      </c>
+      <c r="R28" s="81" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="133" t="n"/>
+      <c r="B29" s="85" t="n"/>
+      <c r="C29" s="137" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D29" s="74" t="n"/>
+      <c r="E29" s="74" t="n"/>
+      <c r="F29" s="72" t="n"/>
+      <c r="G29" s="74" t="n"/>
+      <c r="H29" s="74" t="n"/>
+      <c r="I29" s="74" t="n"/>
+      <c r="J29" s="79" t="n"/>
+      <c r="K29" s="79" t="n"/>
+      <c r="L29" s="126" t="n"/>
+      <c r="M29" s="83" t="n"/>
+      <c r="N29" s="83" t="n"/>
+      <c r="O29" s="84">
+        <f>IF(OR(M29="",N29=""),"",SQRT(0.5*(M29^2+N29^2)))</f>
+        <v/>
+      </c>
+      <c r="P29" s="78" t="n"/>
+      <c r="Q29" s="85">
+        <f>IF(OR(C29="",G29=""),"",G29*C29^2)</f>
+        <v/>
+      </c>
+      <c r="R29" s="81" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="133" t="n"/>
+      <c r="B30" s="85" t="n"/>
+      <c r="C30" s="137" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D30" s="74" t="n"/>
+      <c r="E30" s="74" t="n"/>
+      <c r="F30" s="72" t="n"/>
+      <c r="G30" s="74" t="n"/>
+      <c r="H30" s="74" t="n"/>
+      <c r="I30" s="74" t="n"/>
+      <c r="J30" s="79" t="n"/>
+      <c r="K30" s="79" t="n"/>
+      <c r="L30" s="126" t="n"/>
+      <c r="M30" s="83" t="n"/>
+      <c r="N30" s="83" t="n"/>
+      <c r="O30" s="84">
+        <f>IF(OR(M30="",N30=""),"",SQRT(0.5*(M30^2+N30^2)))</f>
+        <v/>
+      </c>
+      <c r="P30" s="78" t="n"/>
+      <c r="Q30" s="85">
+        <f>IF(OR(C30="",G30=""),"",G30*C30^2)</f>
+        <v/>
+      </c>
+      <c r="R30" s="81" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="133" t="n"/>
+      <c r="B31" s="85" t="n"/>
+      <c r="C31" s="137" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D31" s="74" t="n"/>
+      <c r="E31" s="74" t="n"/>
+      <c r="F31" s="72" t="n"/>
+      <c r="G31" s="74" t="n"/>
+      <c r="H31" s="74" t="n"/>
+      <c r="I31" s="74" t="n"/>
+      <c r="J31" s="79" t="n"/>
+      <c r="K31" s="79" t="n"/>
+      <c r="L31" s="126" t="n"/>
+      <c r="M31" s="83" t="n"/>
+      <c r="N31" s="83" t="n"/>
+      <c r="O31" s="84">
+        <f>IF(OR(M31="",N31=""),"",SQRT(0.5*(M31^2+N31^2)))</f>
+        <v/>
+      </c>
+      <c r="P31" s="78" t="n"/>
+      <c r="Q31" s="85">
+        <f>IF(OR(C31="",G31=""),"",G31*C31^2)</f>
+        <v/>
+      </c>
+      <c r="R31" s="81" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="133" t="n"/>
+      <c r="B32" s="85" t="n"/>
+      <c r="C32" s="137" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D32" s="74" t="n"/>
+      <c r="E32" s="74" t="n"/>
+      <c r="F32" s="72" t="n"/>
+      <c r="G32" s="74" t="n"/>
+      <c r="H32" s="74" t="n"/>
+      <c r="I32" s="74" t="n"/>
+      <c r="J32" s="79" t="n"/>
+      <c r="K32" s="79" t="n"/>
+      <c r="L32" s="126" t="n"/>
+      <c r="M32" s="83" t="n"/>
+      <c r="N32" s="83" t="n"/>
+      <c r="O32" s="84">
+        <f>IF(OR(M32="",N32=""),"",SQRT(0.5*(M32^2+N32^2)))</f>
+        <v/>
+      </c>
+      <c r="P32" s="78" t="n"/>
+      <c r="Q32" s="85">
+        <f>IF(OR(C32="",G32=""),"",G32*C32^2)</f>
+        <v/>
+      </c>
+      <c r="R32" s="81" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="133" t="n"/>
+      <c r="B33" s="85" t="n"/>
+      <c r="C33" s="137" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D33" s="74" t="n"/>
+      <c r="E33" s="74" t="n"/>
+      <c r="F33" s="72" t="n"/>
+      <c r="G33" s="74" t="n"/>
+      <c r="H33" s="74" t="n"/>
+      <c r="I33" s="74" t="n"/>
+      <c r="J33" s="79" t="n"/>
+      <c r="K33" s="79" t="n"/>
+      <c r="L33" s="126" t="n"/>
+      <c r="M33" s="83" t="n"/>
+      <c r="N33" s="83" t="n"/>
+      <c r="O33" s="84">
+        <f>IF(OR(M33="",N33=""),"",SQRT(0.5*(M33^2+N33^2)))</f>
+        <v/>
+      </c>
+      <c r="P33" s="78" t="n"/>
+      <c r="Q33" s="85">
+        <f>IF(OR(C33="",G33=""),"",G33*C33^2)</f>
+        <v/>
+      </c>
+      <c r="R33" s="81" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="133" t="n"/>
+      <c r="B34" s="85" t="n"/>
+      <c r="C34" s="137" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D34" s="74" t="n"/>
+      <c r="E34" s="74" t="n"/>
+      <c r="F34" s="72" t="n"/>
+      <c r="G34" s="74" t="n"/>
+      <c r="H34" s="74" t="n"/>
+      <c r="I34" s="74" t="n"/>
+      <c r="J34" s="79" t="n"/>
+      <c r="K34" s="79" t="n"/>
+      <c r="L34" s="126" t="n"/>
+      <c r="M34" s="83" t="n"/>
+      <c r="N34" s="83" t="n"/>
+      <c r="O34" s="84">
+        <f>IF(OR(M34="",N34=""),"",SQRT(0.5*(M34^2+N34^2)))</f>
+        <v/>
+      </c>
+      <c r="P34" s="78" t="n"/>
+      <c r="Q34" s="85">
+        <f>IF(OR(C34="",G34=""),"",G34*C34^2)</f>
+        <v/>
+      </c>
+      <c r="R34" s="81" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="133" t="n"/>
+      <c r="B35" s="85" t="n"/>
+      <c r="C35" s="137" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="D35" s="74" t="n"/>
+      <c r="E35" s="74" t="n"/>
+      <c r="F35" s="72" t="n"/>
+      <c r="G35" s="74" t="n"/>
+      <c r="H35" s="74" t="n"/>
+      <c r="I35" s="74" t="n"/>
+      <c r="J35" s="79" t="n"/>
+      <c r="K35" s="79" t="n"/>
+      <c r="L35" s="126" t="n"/>
+      <c r="M35" s="83" t="n"/>
+      <c r="N35" s="83" t="n"/>
+      <c r="O35" s="84">
+        <f>IF(OR(M35="",N35=""),"",SQRT(0.5*(M35^2+N35^2)))</f>
+        <v/>
+      </c>
+      <c r="P35" s="78" t="n"/>
+      <c r="Q35" s="85">
+        <f>IF(OR(C35="",G35=""),"",G35*C35^2)</f>
+        <v/>
+      </c>
+      <c r="R35" s="81" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="133" t="n"/>
+      <c r="B36" s="85" t="n"/>
+      <c r="C36" s="137" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="D36" s="74" t="n"/>
+      <c r="E36" s="74" t="n"/>
+      <c r="F36" s="72" t="n"/>
+      <c r="G36" s="74" t="n"/>
+      <c r="H36" s="74" t="n"/>
+      <c r="I36" s="74" t="n"/>
+      <c r="J36" s="79" t="n"/>
+      <c r="K36" s="79" t="n"/>
+      <c r="L36" s="126" t="n"/>
+      <c r="M36" s="83" t="n"/>
+      <c r="N36" s="83" t="n"/>
+      <c r="O36" s="84">
+        <f>IF(OR(M36="",N36=""),"",SQRT(0.5*(M36^2+N36^2)))</f>
+        <v/>
+      </c>
+      <c r="P36" s="78" t="n"/>
+      <c r="Q36" s="85">
+        <f>IF(OR(C36="",G36=""),"",G36*C36^2)</f>
+        <v/>
+      </c>
+      <c r="R36" s="81" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="133" t="inlineStr">
+        <is>
+          <t>Everlight</t>
+        </is>
+      </c>
+      <c r="B37" s="85" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="86" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D37" s="74" t="n"/>
+      <c r="E37" s="74" t="n"/>
+      <c r="F37" s="72" t="n"/>
+      <c r="G37" s="74" t="n"/>
+      <c r="H37" s="74" t="n"/>
+      <c r="I37" s="74" t="n"/>
+      <c r="J37" s="79" t="n"/>
+      <c r="K37" s="79" t="n"/>
+      <c r="L37" s="126" t="n"/>
+      <c r="M37" s="83" t="n"/>
+      <c r="N37" s="83" t="n"/>
+      <c r="O37" s="84">
+        <f>IF(OR(M37="",N37=""),"",SQRT(0.5*(M37^2+N37^2)))</f>
+        <v/>
+      </c>
+      <c r="P37" s="78" t="n"/>
+      <c r="Q37" s="85">
+        <f>IF(OR(C37="",G37=""),"",G37*C37^2)</f>
+        <v/>
+      </c>
+      <c r="R37" s="81" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="138" t="n"/>
+      <c r="B38" s="85" t="n"/>
+      <c r="C38" s="86" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D38" s="74" t="n"/>
+      <c r="E38" s="74" t="n"/>
+      <c r="F38" s="72" t="n"/>
+      <c r="G38" s="74" t="n"/>
+      <c r="H38" s="74" t="n"/>
+      <c r="I38" s="74" t="n"/>
+      <c r="J38" s="79" t="n"/>
+      <c r="K38" s="79" t="n"/>
+      <c r="L38" s="126" t="n"/>
+      <c r="M38" s="83" t="n"/>
+      <c r="N38" s="83" t="n"/>
+      <c r="O38" s="84">
+        <f>IF(OR(M38="",N38=""),"",SQRT(0.5*(M38^2+N38^2)))</f>
+        <v/>
+      </c>
+      <c r="P38" s="78" t="n"/>
+      <c r="Q38" s="85">
+        <f>IF(OR(C38="",G38=""),"",G38*C38^2)</f>
+        <v/>
+      </c>
+      <c r="R38" s="81" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="133" t="n"/>
+      <c r="B39" s="85" t="n"/>
+      <c r="C39" s="86" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D39" s="74" t="n"/>
+      <c r="E39" s="74" t="n"/>
+      <c r="F39" s="72" t="n"/>
+      <c r="G39" s="74" t="n"/>
+      <c r="H39" s="74" t="n"/>
+      <c r="I39" s="74" t="n"/>
+      <c r="J39" s="79" t="n"/>
+      <c r="K39" s="79" t="n"/>
+      <c r="L39" s="126" t="n"/>
+      <c r="M39" s="83" t="n"/>
+      <c r="N39" s="83" t="n"/>
+      <c r="O39" s="84">
+        <f>IF(OR(M39="",N39=""),"",SQRT(0.5*(M39^2+N39^2)))</f>
+        <v/>
+      </c>
+      <c r="P39" s="78" t="n"/>
+      <c r="Q39" s="85">
+        <f>IF(OR(C39="",G39=""),"",G39*C39^2)</f>
+        <v/>
+      </c>
+      <c r="R39" s="81" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="133" t="n"/>
+      <c r="B40" s="85" t="n"/>
+      <c r="C40" s="86" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D40" s="74" t="n"/>
+      <c r="E40" s="74" t="n"/>
+      <c r="F40" s="72" t="n"/>
+      <c r="G40" s="74" t="n"/>
+      <c r="H40" s="74" t="n"/>
+      <c r="I40" s="74" t="n"/>
+      <c r="J40" s="79" t="n"/>
+      <c r="K40" s="79" t="n"/>
+      <c r="L40" s="126" t="n"/>
+      <c r="M40" s="83" t="n"/>
+      <c r="N40" s="83" t="n"/>
+      <c r="O40" s="84">
+        <f>IF(OR(M40="",N40=""),"",SQRT(0.5*(M40^2+N40^2)))</f>
+        <v/>
+      </c>
+      <c r="P40" s="78" t="n"/>
+      <c r="Q40" s="85">
+        <f>IF(OR(C40="",G40=""),"",G40*C40^2)</f>
+        <v/>
+      </c>
+      <c r="R40" s="81" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="133" t="n"/>
+      <c r="B41" s="85" t="n"/>
+      <c r="C41" s="86" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D41" s="74" t="n"/>
+      <c r="E41" s="74" t="n"/>
+      <c r="F41" s="72" t="n"/>
+      <c r="G41" s="74" t="n"/>
+      <c r="H41" s="74" t="n"/>
+      <c r="I41" s="74" t="n"/>
+      <c r="J41" s="79" t="n"/>
+      <c r="K41" s="79" t="n"/>
+      <c r="L41" s="126" t="n"/>
+      <c r="M41" s="83" t="n"/>
+      <c r="N41" s="83" t="n"/>
+      <c r="O41" s="84">
+        <f>IF(OR(M41="",N41=""),"",SQRT(0.5*(M41^2+N41^2)))</f>
+        <v/>
+      </c>
+      <c r="P41" s="78" t="n"/>
+      <c r="Q41" s="85">
+        <f>IF(OR(C41="",G41=""),"",G41*C41^2)</f>
+        <v/>
+      </c>
+      <c r="R41" s="81" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="133" t="n"/>
+      <c r="B42" s="85" t="n"/>
+      <c r="C42" s="86" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D42" s="74" t="n"/>
+      <c r="E42" s="74" t="n"/>
+      <c r="F42" s="72" t="n"/>
+      <c r="G42" s="74" t="n"/>
+      <c r="H42" s="74" t="n"/>
+      <c r="I42" s="74" t="n"/>
+      <c r="J42" s="79" t="n"/>
+      <c r="K42" s="79" t="n"/>
+      <c r="L42" s="126" t="n"/>
+      <c r="M42" s="83" t="n"/>
+      <c r="N42" s="83" t="n"/>
+      <c r="O42" s="84">
+        <f>IF(OR(M42="",N42=""),"",SQRT(0.5*(M42^2+N42^2)))</f>
+        <v/>
+      </c>
+      <c r="P42" s="78" t="n"/>
+      <c r="Q42" s="85">
+        <f>IF(OR(C42="",G42=""),"",G42*C42^2)</f>
+        <v/>
+      </c>
+      <c r="R42" s="81" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="133" t="n"/>
+      <c r="B43" s="85" t="n"/>
+      <c r="C43" s="86" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D43" s="74" t="n"/>
+      <c r="E43" s="74" t="n"/>
+      <c r="F43" s="72" t="n"/>
+      <c r="G43" s="74" t="n"/>
+      <c r="H43" s="74" t="n"/>
+      <c r="I43" s="74" t="n"/>
+      <c r="J43" s="79" t="n"/>
+      <c r="K43" s="79" t="n"/>
+      <c r="L43" s="126" t="n"/>
+      <c r="M43" s="83" t="n"/>
+      <c r="N43" s="83" t="n"/>
+      <c r="O43" s="84">
+        <f>IF(OR(M43="",N43=""),"",SQRT(0.5*(M43^2+N43^2)))</f>
+        <v/>
+      </c>
+      <c r="P43" s="78" t="n"/>
+      <c r="Q43" s="85">
+        <f>IF(OR(C43="",G43=""),"",G43*C43^2)</f>
+        <v/>
+      </c>
+      <c r="R43" s="81" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="133" t="n"/>
+      <c r="B44" s="85" t="n"/>
+      <c r="C44" s="86" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D44" s="74" t="n"/>
+      <c r="E44" s="74" t="n"/>
+      <c r="F44" s="72" t="n"/>
+      <c r="G44" s="74" t="n"/>
+      <c r="H44" s="74" t="n"/>
+      <c r="I44" s="74" t="n"/>
+      <c r="J44" s="79" t="n"/>
+      <c r="K44" s="79" t="n"/>
+      <c r="L44" s="126" t="n"/>
+      <c r="M44" s="83" t="n"/>
+      <c r="N44" s="83" t="n"/>
+      <c r="O44" s="84">
+        <f>IF(OR(M44="",N44=""),"",SQRT(0.5*(M44^2+N44^2)))</f>
+        <v/>
+      </c>
+      <c r="P44" s="78" t="n"/>
+      <c r="Q44" s="85">
+        <f>IF(OR(C44="",G44=""),"",G44*C44^2)</f>
+        <v/>
+      </c>
+      <c r="R44" s="81" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="133" t="n"/>
+      <c r="B45" s="85" t="n"/>
+      <c r="C45" s="86" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="D45" s="74" t="n"/>
+      <c r="E45" s="74" t="n"/>
+      <c r="F45" s="72" t="n"/>
+      <c r="G45" s="74" t="n"/>
+      <c r="H45" s="74" t="n"/>
+      <c r="I45" s="74" t="n"/>
+      <c r="J45" s="79" t="n"/>
+      <c r="K45" s="79" t="n"/>
+      <c r="L45" s="126" t="n"/>
+      <c r="M45" s="83" t="n"/>
+      <c r="N45" s="83" t="n"/>
+      <c r="O45" s="84">
+        <f>IF(OR(M45="",N45=""),"",SQRT(0.5*(M45^2+N45^2)))</f>
+        <v/>
+      </c>
+      <c r="P45" s="78" t="n"/>
+      <c r="Q45" s="85">
+        <f>IF(OR(C45="",G45=""),"",G45*C45^2)</f>
+        <v/>
+      </c>
+      <c r="R45" s="81" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="133" t="n"/>
+      <c r="B46" s="85" t="n"/>
+      <c r="C46" s="86" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="D46" s="74" t="n"/>
+      <c r="E46" s="74" t="n"/>
+      <c r="F46" s="72" t="n"/>
+      <c r="G46" s="74" t="n"/>
+      <c r="H46" s="74" t="n"/>
+      <c r="I46" s="74" t="n"/>
+      <c r="J46" s="79" t="n"/>
+      <c r="K46" s="79" t="n"/>
+      <c r="L46" s="126" t="n"/>
+      <c r="M46" s="83" t="n"/>
+      <c r="N46" s="83" t="n"/>
+      <c r="O46" s="84">
+        <f>IF(OR(M46="",N46=""),"",SQRT(0.5*(M46^2+N46^2)))</f>
+        <v/>
+      </c>
+      <c r="P46" s="78" t="n"/>
+      <c r="Q46" s="85">
+        <f>IF(OR(C46="",G46=""),"",G46*C46^2)</f>
+        <v/>
+      </c>
+      <c r="R46" s="81" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="128" t="inlineStr">
         <is>
           <t>Vishay</t>
         </is>
       </c>
-      <c r="B4" s="16" t="inlineStr">
-        <is>
-          <t>bare (ref)</t>
-        </is>
-      </c>
-      <c r="C4" s="17" t="n">
+      <c r="B47" s="100" t="n">
+        <v>90</v>
+      </c>
+      <c r="C47" s="101" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D47" s="129" t="n"/>
+      <c r="E47" s="129" t="n"/>
+      <c r="F47" s="134" t="n"/>
+      <c r="G47" s="129" t="n"/>
+      <c r="H47" s="129" t="n"/>
+      <c r="I47" s="129" t="n"/>
+      <c r="J47" s="130" t="n"/>
+      <c r="K47" s="130" t="n"/>
+      <c r="L47" s="131" t="n"/>
+      <c r="M47" s="132" t="n"/>
+      <c r="N47" s="132" t="n"/>
+      <c r="O47" s="107">
+        <f>IF(OR(M47="",N47=""),"",SQRT(0.5*(M47^2+N47^2)))</f>
+        <v/>
+      </c>
+      <c r="P47" s="135" t="n"/>
+      <c r="Q47" s="100">
+        <f>IF(OR(C47="",G47=""),"",G47*C47^2)</f>
+        <v/>
+      </c>
+      <c r="R47" s="110" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="133" t="n"/>
+      <c r="B48" s="85" t="n"/>
+      <c r="C48" s="86" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D48" s="74" t="n"/>
+      <c r="E48" s="74" t="n"/>
+      <c r="F48" s="72" t="n"/>
+      <c r="G48" s="74" t="n"/>
+      <c r="H48" s="74" t="n"/>
+      <c r="I48" s="74" t="n"/>
+      <c r="J48" s="79" t="n"/>
+      <c r="K48" s="79" t="n"/>
+      <c r="L48" s="126" t="n"/>
+      <c r="M48" s="83" t="n"/>
+      <c r="N48" s="83" t="n"/>
+      <c r="O48" s="84">
+        <f>IF(OR(M48="",N48=""),"",SQRT(0.5*(M48^2+N48^2)))</f>
+        <v/>
+      </c>
+      <c r="P48" s="78" t="n"/>
+      <c r="Q48" s="85">
+        <f>IF(OR(C48="",G48=""),"",G48*C48^2)</f>
+        <v/>
+      </c>
+      <c r="R48" s="81" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="133" t="n"/>
+      <c r="B49" s="85" t="n"/>
+      <c r="C49" s="86" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D49" s="74" t="n"/>
+      <c r="E49" s="74" t="n"/>
+      <c r="F49" s="72" t="n"/>
+      <c r="G49" s="74" t="n"/>
+      <c r="H49" s="74" t="n"/>
+      <c r="I49" s="74" t="n"/>
+      <c r="J49" s="79" t="n"/>
+      <c r="K49" s="79" t="n"/>
+      <c r="L49" s="126" t="n"/>
+      <c r="M49" s="83" t="n"/>
+      <c r="N49" s="83" t="n"/>
+      <c r="O49" s="84">
+        <f>IF(OR(M49="",N49=""),"",SQRT(0.5*(M49^2+N49^2)))</f>
+        <v/>
+      </c>
+      <c r="P49" s="78" t="n"/>
+      <c r="Q49" s="85">
+        <f>IF(OR(C49="",G49=""),"",G49*C49^2)</f>
+        <v/>
+      </c>
+      <c r="R49" s="81" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="133" t="n"/>
+      <c r="B50" s="85" t="n"/>
+      <c r="C50" s="86" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D50" s="74" t="n"/>
+      <c r="E50" s="74" t="n"/>
+      <c r="F50" s="72" t="n"/>
+      <c r="G50" s="74" t="n"/>
+      <c r="H50" s="74" t="n"/>
+      <c r="I50" s="74" t="n"/>
+      <c r="J50" s="79" t="n"/>
+      <c r="K50" s="79" t="n"/>
+      <c r="L50" s="126" t="n"/>
+      <c r="M50" s="83" t="n"/>
+      <c r="N50" s="83" t="n"/>
+      <c r="O50" s="84">
+        <f>IF(OR(M50="",N50=""),"",SQRT(0.5*(M50^2+N50^2)))</f>
+        <v/>
+      </c>
+      <c r="P50" s="78" t="n"/>
+      <c r="Q50" s="85">
+        <f>IF(OR(C50="",G50=""),"",G50*C50^2)</f>
+        <v/>
+      </c>
+      <c r="R50" s="81" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="133" t="n"/>
+      <c r="B51" s="85" t="n"/>
+      <c r="C51" s="86" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D51" s="74" t="n"/>
+      <c r="E51" s="74" t="n"/>
+      <c r="F51" s="72" t="n"/>
+      <c r="G51" s="74" t="n"/>
+      <c r="H51" s="74" t="n"/>
+      <c r="I51" s="74" t="n"/>
+      <c r="J51" s="79" t="n"/>
+      <c r="K51" s="79" t="n"/>
+      <c r="L51" s="126" t="n"/>
+      <c r="M51" s="83" t="n"/>
+      <c r="N51" s="83" t="n"/>
+      <c r="O51" s="84">
+        <f>IF(OR(M51="",N51=""),"",SQRT(0.5*(M51^2+N51^2)))</f>
+        <v/>
+      </c>
+      <c r="P51" s="78" t="n"/>
+      <c r="Q51" s="85">
+        <f>IF(OR(C51="",G51=""),"",G51*C51^2)</f>
+        <v/>
+      </c>
+      <c r="R51" s="81" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="133" t="n"/>
+      <c r="B52" s="85" t="n"/>
+      <c r="C52" s="86" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D52" s="74" t="n"/>
+      <c r="E52" s="74" t="n"/>
+      <c r="F52" s="72" t="n"/>
+      <c r="G52" s="74" t="n"/>
+      <c r="H52" s="74" t="n"/>
+      <c r="I52" s="74" t="n"/>
+      <c r="J52" s="79" t="n"/>
+      <c r="K52" s="79" t="n"/>
+      <c r="L52" s="126" t="n"/>
+      <c r="M52" s="83" t="n"/>
+      <c r="N52" s="83" t="n"/>
+      <c r="O52" s="84">
+        <f>IF(OR(M52="",N52=""),"",SQRT(0.5*(M52^2+N52^2)))</f>
+        <v/>
+      </c>
+      <c r="P52" s="78" t="n"/>
+      <c r="Q52" s="85">
+        <f>IF(OR(C52="",G52=""),"",G52*C52^2)</f>
+        <v/>
+      </c>
+      <c r="R52" s="81" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="133" t="n"/>
+      <c r="B53" s="85" t="n"/>
+      <c r="C53" s="86" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D53" s="74" t="n"/>
+      <c r="E53" s="74" t="n"/>
+      <c r="F53" s="72" t="n"/>
+      <c r="G53" s="74" t="n"/>
+      <c r="H53" s="74" t="n"/>
+      <c r="I53" s="74" t="n"/>
+      <c r="J53" s="79" t="n"/>
+      <c r="K53" s="79" t="n"/>
+      <c r="L53" s="126" t="n"/>
+      <c r="M53" s="83" t="n"/>
+      <c r="N53" s="83" t="n"/>
+      <c r="O53" s="84">
+        <f>IF(OR(M53="",N53=""),"",SQRT(0.5*(M53^2+N53^2)))</f>
+        <v/>
+      </c>
+      <c r="P53" s="78" t="n"/>
+      <c r="Q53" s="85">
+        <f>IF(OR(C53="",G53=""),"",G53*C53^2)</f>
+        <v/>
+      </c>
+      <c r="R53" s="81" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="133" t="n"/>
+      <c r="B54" s="85" t="n"/>
+      <c r="C54" s="86" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D54" s="74" t="n"/>
+      <c r="E54" s="74" t="n"/>
+      <c r="F54" s="72" t="n"/>
+      <c r="G54" s="74" t="n"/>
+      <c r="H54" s="74" t="n"/>
+      <c r="I54" s="74" t="n"/>
+      <c r="J54" s="79" t="n"/>
+      <c r="K54" s="79" t="n"/>
+      <c r="L54" s="126" t="n"/>
+      <c r="M54" s="83" t="n"/>
+      <c r="N54" s="83" t="n"/>
+      <c r="O54" s="84">
+        <f>IF(OR(M54="",N54=""),"",SQRT(0.5*(M54^2+N54^2)))</f>
+        <v/>
+      </c>
+      <c r="P54" s="78" t="n"/>
+      <c r="Q54" s="85">
+        <f>IF(OR(C54="",G54=""),"",G54*C54^2)</f>
+        <v/>
+      </c>
+      <c r="R54" s="81" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="133" t="n"/>
+      <c r="B55" s="85" t="n"/>
+      <c r="C55" s="86" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="D55" s="74" t="n"/>
+      <c r="E55" s="74" t="n"/>
+      <c r="F55" s="72" t="n"/>
+      <c r="G55" s="74" t="n"/>
+      <c r="H55" s="74" t="n"/>
+      <c r="I55" s="74" t="n"/>
+      <c r="J55" s="79" t="n"/>
+      <c r="K55" s="79" t="n"/>
+      <c r="L55" s="126" t="n"/>
+      <c r="M55" s="83" t="n"/>
+      <c r="N55" s="83" t="n"/>
+      <c r="O55" s="84">
+        <f>IF(OR(M55="",N55=""),"",SQRT(0.5*(M55^2+N55^2)))</f>
+        <v/>
+      </c>
+      <c r="P55" s="78" t="n"/>
+      <c r="Q55" s="85">
+        <f>IF(OR(C55="",G55=""),"",G55*C55^2)</f>
+        <v/>
+      </c>
+      <c r="R55" s="81" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="133" t="n"/>
+      <c r="B56" s="85" t="n"/>
+      <c r="C56" s="86" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="D56" s="74" t="n"/>
+      <c r="E56" s="74" t="n"/>
+      <c r="F56" s="72" t="n"/>
+      <c r="G56" s="74" t="n"/>
+      <c r="H56" s="74" t="n"/>
+      <c r="I56" s="74" t="n"/>
+      <c r="J56" s="79" t="n"/>
+      <c r="K56" s="79" t="n"/>
+      <c r="L56" s="126" t="n"/>
+      <c r="M56" s="83" t="n"/>
+      <c r="N56" s="83" t="n"/>
+      <c r="O56" s="84">
+        <f>IF(OR(M56="",N56=""),"",SQRT(0.5*(M56^2+N56^2)))</f>
+        <v/>
+      </c>
+      <c r="P56" s="78" t="n"/>
+      <c r="Q56" s="85">
+        <f>IF(OR(C56="",G56=""),"",G56*C56^2)</f>
+        <v/>
+      </c>
+      <c r="R56" s="81" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="133" t="inlineStr">
+        <is>
+          <t>Vishay</t>
+        </is>
+      </c>
+      <c r="B57" s="85" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="86" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D57" s="74" t="n">
+        <v>21</v>
+      </c>
+      <c r="E57" s="74" t="n">
+        <v>145</v>
+      </c>
+      <c r="F57" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" s="74" t="n"/>
+      <c r="H57" s="74" t="n"/>
+      <c r="I57" s="74" t="n"/>
+      <c r="J57" s="79" t="n"/>
+      <c r="K57" s="79" t="n"/>
+      <c r="L57" s="126" t="n"/>
+      <c r="M57" s="83" t="n"/>
+      <c r="N57" s="83" t="n"/>
+      <c r="O57" s="84">
+        <f>IF(OR(M57="",N57=""),"",SQRT(0.5*(M57^2+N57^2)))</f>
+        <v/>
+      </c>
+      <c r="P57" s="78" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q57" s="85">
+        <f>IF(OR(C57="",G57=""),"",G57*C57^2)</f>
+        <v/>
+      </c>
+      <c r="R57" s="139" t="inlineStr">
+        <is>
+          <t>TOO BRIGHT - no in-band exposure at 0.7 m. 21 us gives peak 145 unsaturated; the next grid step (42 us) is fully clipped, 545 sat px. Detected but not characterisable here. Shape metrics withheld - the saturated attempt read 33 blobs / wh 23.2 / sigma 1.22, which is banding.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="133" t="n"/>
+      <c r="B58" s="85" t="n"/>
+      <c r="C58" s="86" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D58" s="74" t="n"/>
+      <c r="E58" s="74" t="n"/>
+      <c r="F58" s="72" t="n"/>
+      <c r="G58" s="74" t="n"/>
+      <c r="H58" s="74" t="n"/>
+      <c r="I58" s="74" t="n"/>
+      <c r="J58" s="79" t="n"/>
+      <c r="K58" s="79" t="n"/>
+      <c r="L58" s="126" t="n"/>
+      <c r="M58" s="83" t="n"/>
+      <c r="N58" s="83" t="n"/>
+      <c r="O58" s="84">
+        <f>IF(OR(M58="",N58=""),"",SQRT(0.5*(M58^2+N58^2)))</f>
+        <v/>
+      </c>
+      <c r="P58" s="78" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q58" s="85">
+        <f>IF(OR(C58="",G58=""),"",G58*C58^2)</f>
+        <v/>
+      </c>
+      <c r="R58" s="139" t="inlineStr">
+        <is>
+          <t>TOO BRIGHT - 17 us leaves the blob below THRESH_LO, 35 us is fully clipped (290 sat px). The grid straddles at the short end and the response is non-linear there. Detected, not characterisable. Vishay near limit is ~2 m at 0 deg.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="133" t="n"/>
+      <c r="B59" s="85" t="n"/>
+      <c r="C59" s="86" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D59" s="74" t="n">
+        <v>251</v>
+      </c>
+      <c r="E59" s="74" t="n">
+        <v>208.1</v>
+      </c>
+      <c r="F59" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" s="74" t="n">
+        <v>825</v>
+      </c>
+      <c r="H59" s="74" t="n">
+        <v>947</v>
+      </c>
+      <c r="I59" s="74" t="n">
         <v>1</v>
       </c>
-      <c r="D4" s="57" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" s="19" t="n"/>
-      <c r="F4" s="19" t="n"/>
-      <c r="G4" s="58" t="n"/>
-      <c r="H4" s="19" t="n"/>
-      <c r="I4" s="19" t="n"/>
-      <c r="J4" s="59" t="n"/>
-      <c r="K4" s="43" t="n"/>
-      <c r="L4" s="57">
-        <f>IF(UPPER(K4)="Y",D4,0)</f>
-        <v/>
-      </c>
-      <c r="M4" s="24" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="25" t="inlineStr">
-        <is>
-          <t>Vishay</t>
-        </is>
-      </c>
-      <c r="B5" s="26" t="inlineStr">
-        <is>
-          <t>bare (ref)</t>
-        </is>
-      </c>
-      <c r="C5" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" s="53" t="n">
-        <v>2</v>
-      </c>
-      <c r="E5" s="29" t="n"/>
-      <c r="F5" s="29" t="n"/>
-      <c r="G5" s="62" t="n"/>
-      <c r="H5" s="29" t="n"/>
-      <c r="I5" s="29" t="n"/>
-      <c r="J5" s="63" t="n"/>
-      <c r="K5" s="44" t="n"/>
-      <c r="L5" s="53">
-        <f>IF(UPPER(K5)="Y",D5,0)</f>
-        <v/>
-      </c>
-      <c r="M5" s="34" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="25" t="inlineStr">
-        <is>
-          <t>Vishay</t>
-        </is>
-      </c>
-      <c r="B6" s="26" t="inlineStr">
-        <is>
-          <t>bare (ref)</t>
-        </is>
-      </c>
-      <c r="C6" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" s="53" t="n">
-        <v>3</v>
-      </c>
-      <c r="E6" s="29" t="n"/>
-      <c r="F6" s="29" t="n"/>
-      <c r="G6" s="62" t="n"/>
-      <c r="H6" s="29" t="n"/>
-      <c r="I6" s="29" t="n"/>
-      <c r="J6" s="63" t="n"/>
-      <c r="K6" s="44" t="n"/>
-      <c r="L6" s="53">
-        <f>IF(UPPER(K6)="Y",D6,0)</f>
-        <v/>
-      </c>
-      <c r="M6" s="34" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="25" t="inlineStr">
-        <is>
-          <t>Vishay</t>
-        </is>
-      </c>
-      <c r="B7" s="26" t="inlineStr">
-        <is>
-          <t>bare (ref)</t>
-        </is>
-      </c>
-      <c r="C7" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" s="53" t="n">
-        <v>4</v>
-      </c>
-      <c r="E7" s="29" t="n"/>
-      <c r="F7" s="29" t="n"/>
-      <c r="G7" s="62" t="n"/>
-      <c r="H7" s="29" t="n"/>
-      <c r="I7" s="29" t="n"/>
-      <c r="J7" s="63" t="n"/>
-      <c r="K7" s="44" t="n"/>
-      <c r="L7" s="53">
-        <f>IF(UPPER(K7)="Y",D7,0)</f>
-        <v/>
-      </c>
-      <c r="M7" s="34" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="25" t="inlineStr">
-        <is>
-          <t>Vishay</t>
-        </is>
-      </c>
-      <c r="B8" s="26" t="inlineStr">
-        <is>
-          <t>bare (ref)</t>
-        </is>
-      </c>
-      <c r="C8" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" s="53" t="n">
-        <v>5</v>
-      </c>
-      <c r="E8" s="29" t="n"/>
-      <c r="F8" s="29" t="n"/>
-      <c r="G8" s="62" t="n"/>
-      <c r="H8" s="29" t="n"/>
-      <c r="I8" s="29" t="n"/>
-      <c r="J8" s="63" t="n"/>
-      <c r="K8" s="44" t="n"/>
-      <c r="L8" s="53">
-        <f>IF(UPPER(K8)="Y",D8,0)</f>
-        <v/>
-      </c>
-      <c r="M8" s="34" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="25" t="inlineStr">
-        <is>
-          <t>Everlight</t>
-        </is>
-      </c>
-      <c r="B9" s="26" t="inlineStr">
-        <is>
-          <t>bare (ref)</t>
-        </is>
-      </c>
-      <c r="C9" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" s="53" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" s="29" t="n"/>
-      <c r="F9" s="29" t="n"/>
-      <c r="G9" s="62" t="n"/>
-      <c r="H9" s="29" t="n"/>
-      <c r="I9" s="29" t="n"/>
-      <c r="J9" s="63" t="n"/>
-      <c r="K9" s="44" t="n"/>
-      <c r="L9" s="53">
-        <f>IF(UPPER(K9)="Y",D9,0)</f>
-        <v/>
-      </c>
-      <c r="M9" s="34" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="25" t="inlineStr">
-        <is>
-          <t>Everlight</t>
-        </is>
-      </c>
-      <c r="B10" s="26" t="inlineStr">
-        <is>
-          <t>bare (ref)</t>
-        </is>
-      </c>
-      <c r="C10" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" s="53" t="n">
-        <v>2</v>
-      </c>
-      <c r="E10" s="29" t="n"/>
-      <c r="F10" s="29" t="n"/>
-      <c r="G10" s="62" t="n"/>
-      <c r="H10" s="29" t="n"/>
-      <c r="I10" s="29" t="n"/>
-      <c r="J10" s="63" t="n"/>
-      <c r="K10" s="44" t="n"/>
-      <c r="L10" s="53">
-        <f>IF(UPPER(K10)="Y",D10,0)</f>
-        <v/>
-      </c>
-      <c r="M10" s="34" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="25" t="inlineStr">
-        <is>
-          <t>Everlight</t>
-        </is>
-      </c>
-      <c r="B11" s="26" t="inlineStr">
-        <is>
-          <t>bare (ref)</t>
-        </is>
-      </c>
-      <c r="C11" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" s="53" t="n">
-        <v>3</v>
-      </c>
-      <c r="E11" s="29" t="n"/>
-      <c r="F11" s="29" t="n"/>
-      <c r="G11" s="62" t="n"/>
-      <c r="H11" s="29" t="n"/>
-      <c r="I11" s="29" t="n"/>
-      <c r="J11" s="63" t="n"/>
-      <c r="K11" s="44" t="n"/>
-      <c r="L11" s="53">
-        <f>IF(UPPER(K11)="Y",D11,0)</f>
-        <v/>
-      </c>
-      <c r="M11" s="34" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="25" t="inlineStr">
-        <is>
-          <t>Everlight</t>
-        </is>
-      </c>
-      <c r="B12" s="26" t="inlineStr">
-        <is>
-          <t>bare (ref)</t>
-        </is>
-      </c>
-      <c r="C12" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" s="53" t="n">
-        <v>4</v>
-      </c>
-      <c r="E12" s="29" t="n"/>
-      <c r="F12" s="29" t="n"/>
-      <c r="G12" s="62" t="n"/>
-      <c r="H12" s="29" t="n"/>
-      <c r="I12" s="29" t="n"/>
-      <c r="J12" s="63" t="n"/>
-      <c r="K12" s="44" t="n"/>
-      <c r="L12" s="53">
-        <f>IF(UPPER(K12)="Y",D12,0)</f>
-        <v/>
-      </c>
-      <c r="M12" s="34" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="25" t="inlineStr">
-        <is>
-          <t>Everlight</t>
-        </is>
-      </c>
-      <c r="B13" s="26" t="inlineStr">
-        <is>
-          <t>bare (ref)</t>
-        </is>
-      </c>
-      <c r="C13" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" s="53" t="n">
-        <v>5</v>
-      </c>
-      <c r="E13" s="29" t="n"/>
-      <c r="F13" s="29" t="n"/>
-      <c r="G13" s="62" t="n"/>
-      <c r="H13" s="29" t="n"/>
-      <c r="I13" s="29" t="n"/>
-      <c r="J13" s="63" t="n"/>
-      <c r="K13" s="44" t="n"/>
-      <c r="L13" s="53">
-        <f>IF(UPPER(K13)="Y",D13,0)</f>
-        <v/>
-      </c>
-      <c r="M13" s="34" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="25" t="inlineStr">
-        <is>
-          <t>XL</t>
-        </is>
-      </c>
-      <c r="B14" s="26" t="inlineStr">
-        <is>
-          <t>bare (ref)</t>
-        </is>
-      </c>
-      <c r="C14" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" s="53" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" s="29" t="n"/>
-      <c r="F14" s="29" t="n"/>
-      <c r="G14" s="62" t="n"/>
-      <c r="H14" s="29" t="n"/>
-      <c r="I14" s="29" t="n"/>
-      <c r="J14" s="63" t="n"/>
-      <c r="K14" s="44" t="n"/>
-      <c r="L14" s="53">
-        <f>IF(UPPER(K14)="Y",D14,0)</f>
-        <v/>
-      </c>
-      <c r="M14" s="34" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="25" t="inlineStr">
-        <is>
-          <t>XL</t>
-        </is>
-      </c>
-      <c r="B15" s="26" t="inlineStr">
-        <is>
-          <t>bare (ref)</t>
-        </is>
-      </c>
-      <c r="C15" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" s="53" t="n">
-        <v>2</v>
-      </c>
-      <c r="E15" s="29" t="n"/>
-      <c r="F15" s="29" t="n"/>
-      <c r="G15" s="62" t="n"/>
-      <c r="H15" s="29" t="n"/>
-      <c r="I15" s="29" t="n"/>
-      <c r="J15" s="63" t="n"/>
-      <c r="K15" s="44" t="n"/>
-      <c r="L15" s="53">
-        <f>IF(UPPER(K15)="Y",D15,0)</f>
-        <v/>
-      </c>
-      <c r="M15" s="34" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="25" t="inlineStr">
-        <is>
-          <t>XL</t>
-        </is>
-      </c>
-      <c r="B16" s="26" t="inlineStr">
-        <is>
-          <t>bare (ref)</t>
-        </is>
-      </c>
-      <c r="C16" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" s="53" t="n">
-        <v>3</v>
-      </c>
-      <c r="E16" s="29" t="n"/>
-      <c r="F16" s="29" t="n"/>
-      <c r="G16" s="62" t="n"/>
-      <c r="H16" s="29" t="n"/>
-      <c r="I16" s="29" t="n"/>
-      <c r="J16" s="63" t="n"/>
-      <c r="K16" s="44" t="n"/>
-      <c r="L16" s="53">
-        <f>IF(UPPER(K16)="Y",D16,0)</f>
-        <v/>
-      </c>
-      <c r="M16" s="34" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="25" t="inlineStr">
-        <is>
-          <t>XL</t>
-        </is>
-      </c>
-      <c r="B17" s="26" t="inlineStr">
-        <is>
-          <t>bare (ref)</t>
-        </is>
-      </c>
-      <c r="C17" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" s="53" t="n">
-        <v>4</v>
-      </c>
-      <c r="E17" s="29" t="n"/>
-      <c r="F17" s="29" t="n"/>
-      <c r="G17" s="62" t="n"/>
-      <c r="H17" s="29" t="n"/>
-      <c r="I17" s="29" t="n"/>
-      <c r="J17" s="63" t="n"/>
-      <c r="K17" s="44" t="n"/>
-      <c r="L17" s="53">
-        <f>IF(UPPER(K17)="Y",D17,0)</f>
-        <v/>
-      </c>
-      <c r="M17" s="34" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="25" t="inlineStr">
-        <is>
-          <t>XL</t>
-        </is>
-      </c>
-      <c r="B18" s="26" t="inlineStr">
-        <is>
-          <t>bare (ref)</t>
-        </is>
-      </c>
-      <c r="C18" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" s="53" t="n">
-        <v>5</v>
-      </c>
-      <c r="E18" s="29" t="n"/>
-      <c r="F18" s="29" t="n"/>
-      <c r="G18" s="62" t="n"/>
-      <c r="H18" s="29" t="n"/>
-      <c r="I18" s="29" t="n"/>
-      <c r="J18" s="63" t="n"/>
-      <c r="K18" s="44" t="n"/>
-      <c r="L18" s="53">
-        <f>IF(UPPER(K18)="Y",D18,0)</f>
-        <v/>
-      </c>
-      <c r="M18" s="34" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="25" t="inlineStr">
-        <is>
-          <t>Kingbright</t>
-        </is>
-      </c>
-      <c r="B19" s="26" t="inlineStr">
-        <is>
-          <t>bare (ref)</t>
-        </is>
-      </c>
-      <c r="C19" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" s="53" t="n">
-        <v>1</v>
-      </c>
-      <c r="E19" s="29" t="n"/>
-      <c r="F19" s="29" t="n"/>
-      <c r="G19" s="62" t="n"/>
-      <c r="H19" s="29" t="n"/>
-      <c r="I19" s="29" t="n"/>
-      <c r="J19" s="63" t="n"/>
-      <c r="K19" s="44" t="n"/>
-      <c r="L19" s="53">
-        <f>IF(UPPER(K19)="Y",D19,0)</f>
-        <v/>
-      </c>
-      <c r="M19" s="34" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="25" t="inlineStr">
-        <is>
-          <t>Kingbright</t>
-        </is>
-      </c>
-      <c r="B20" s="26" t="inlineStr">
-        <is>
-          <t>bare (ref)</t>
-        </is>
-      </c>
-      <c r="C20" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" s="53" t="n">
-        <v>2</v>
-      </c>
-      <c r="E20" s="29" t="n"/>
-      <c r="F20" s="29" t="n"/>
-      <c r="G20" s="62" t="n"/>
-      <c r="H20" s="29" t="n"/>
-      <c r="I20" s="29" t="n"/>
-      <c r="J20" s="63" t="n"/>
-      <c r="K20" s="44" t="n"/>
-      <c r="L20" s="53">
-        <f>IF(UPPER(K20)="Y",D20,0)</f>
-        <v/>
-      </c>
-      <c r="M20" s="34" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="25" t="inlineStr">
-        <is>
-          <t>Kingbright</t>
-        </is>
-      </c>
-      <c r="B21" s="26" t="inlineStr">
-        <is>
-          <t>bare (ref)</t>
-        </is>
-      </c>
-      <c r="C21" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" s="53" t="n">
-        <v>3</v>
-      </c>
-      <c r="E21" s="29" t="n"/>
-      <c r="F21" s="29" t="n"/>
-      <c r="G21" s="62" t="n"/>
-      <c r="H21" s="29" t="n"/>
-      <c r="I21" s="29" t="n"/>
-      <c r="J21" s="63" t="n"/>
-      <c r="K21" s="44" t="n"/>
-      <c r="L21" s="53">
-        <f>IF(UPPER(K21)="Y",D21,0)</f>
-        <v/>
-      </c>
-      <c r="M21" s="34" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="25" t="inlineStr">
-        <is>
-          <t>Kingbright</t>
-        </is>
-      </c>
-      <c r="B22" s="26" t="inlineStr">
-        <is>
-          <t>bare (ref)</t>
-        </is>
-      </c>
-      <c r="C22" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D22" s="53" t="n">
-        <v>4</v>
-      </c>
-      <c r="E22" s="29" t="n"/>
-      <c r="F22" s="29" t="n"/>
-      <c r="G22" s="62" t="n"/>
-      <c r="H22" s="29" t="n"/>
-      <c r="I22" s="29" t="n"/>
-      <c r="J22" s="63" t="n"/>
-      <c r="K22" s="44" t="n"/>
-      <c r="L22" s="53">
-        <f>IF(UPPER(K22)="Y",D22,0)</f>
-        <v/>
-      </c>
-      <c r="M22" s="34" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="25" t="inlineStr">
-        <is>
-          <t>Kingbright</t>
-        </is>
-      </c>
-      <c r="B23" s="26" t="inlineStr">
-        <is>
-          <t>bare (ref)</t>
-        </is>
-      </c>
-      <c r="C23" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D23" s="53" t="n">
-        <v>5</v>
-      </c>
-      <c r="E23" s="29" t="n"/>
-      <c r="F23" s="29" t="n"/>
-      <c r="G23" s="62" t="n"/>
-      <c r="H23" s="29" t="n"/>
-      <c r="I23" s="29" t="n"/>
-      <c r="J23" s="63" t="n"/>
-      <c r="K23" s="44" t="n"/>
-      <c r="L23" s="53">
-        <f>IF(UPPER(K23)="Y",D23,0)</f>
-        <v/>
-      </c>
-      <c r="M23" s="34" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="15" t="inlineStr">
-        <is>
-          <t>Vishay</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
-        <is>
-          <t>20 mm</t>
-        </is>
-      </c>
-      <c r="C24" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="D24" s="57" t="n">
-        <v>1</v>
-      </c>
-      <c r="E24" s="19" t="n"/>
-      <c r="F24" s="19" t="n"/>
-      <c r="G24" s="58" t="n"/>
-      <c r="H24" s="19" t="n"/>
-      <c r="I24" s="19" t="n"/>
-      <c r="J24" s="59" t="n"/>
-      <c r="K24" s="43" t="n"/>
-      <c r="L24" s="57">
-        <f>IF(UPPER(K24)="Y",D24,0)</f>
-        <v/>
-      </c>
-      <c r="M24" s="24" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="25" t="inlineStr">
-        <is>
-          <t>Vishay</t>
-        </is>
-      </c>
-      <c r="B25" s="26" t="inlineStr">
-        <is>
-          <t>20 mm</t>
-        </is>
-      </c>
-      <c r="C25" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D25" s="53" t="n">
-        <v>2</v>
-      </c>
-      <c r="E25" s="29" t="n"/>
-      <c r="F25" s="29" t="n"/>
-      <c r="G25" s="62" t="n"/>
-      <c r="H25" s="29" t="n"/>
-      <c r="I25" s="29" t="n"/>
-      <c r="J25" s="63" t="n"/>
-      <c r="K25" s="44" t="n"/>
-      <c r="L25" s="53">
-        <f>IF(UPPER(K25)="Y",D25,0)</f>
-        <v/>
-      </c>
-      <c r="M25" s="34" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="25" t="inlineStr">
-        <is>
-          <t>Vishay</t>
-        </is>
-      </c>
-      <c r="B26" s="26" t="inlineStr">
-        <is>
-          <t>20 mm</t>
-        </is>
-      </c>
-      <c r="C26" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" s="53" t="n">
-        <v>3</v>
-      </c>
-      <c r="E26" s="29" t="n"/>
-      <c r="F26" s="29" t="n"/>
-      <c r="G26" s="62" t="n"/>
-      <c r="H26" s="29" t="n"/>
-      <c r="I26" s="29" t="n"/>
-      <c r="J26" s="63" t="n"/>
-      <c r="K26" s="44" t="n"/>
-      <c r="L26" s="53">
-        <f>IF(UPPER(K26)="Y",D26,0)</f>
-        <v/>
-      </c>
-      <c r="M26" s="34" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="25" t="inlineStr">
-        <is>
-          <t>Vishay</t>
-        </is>
-      </c>
-      <c r="B27" s="26" t="inlineStr">
-        <is>
-          <t>20 mm</t>
-        </is>
-      </c>
-      <c r="C27" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D27" s="53" t="n">
-        <v>4</v>
-      </c>
-      <c r="E27" s="29" t="n"/>
-      <c r="F27" s="29" t="n"/>
-      <c r="G27" s="62" t="n"/>
-      <c r="H27" s="29" t="n"/>
-      <c r="I27" s="29" t="n"/>
-      <c r="J27" s="63" t="n"/>
-      <c r="K27" s="44" t="n"/>
-      <c r="L27" s="53">
-        <f>IF(UPPER(K27)="Y",D27,0)</f>
-        <v/>
-      </c>
-      <c r="M27" s="34" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="25" t="inlineStr">
-        <is>
-          <t>Vishay</t>
-        </is>
-      </c>
-      <c r="B28" s="26" t="inlineStr">
-        <is>
-          <t>20 mm</t>
-        </is>
-      </c>
-      <c r="C28" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D28" s="53" t="n">
-        <v>5</v>
-      </c>
-      <c r="E28" s="29" t="n"/>
-      <c r="F28" s="29" t="n"/>
-      <c r="G28" s="62" t="n"/>
-      <c r="H28" s="29" t="n"/>
-      <c r="I28" s="29" t="n"/>
-      <c r="J28" s="63" t="n"/>
-      <c r="K28" s="44" t="n"/>
-      <c r="L28" s="53">
-        <f>IF(UPPER(K28)="Y",D28,0)</f>
-        <v/>
-      </c>
-      <c r="M28" s="34" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="25" t="inlineStr">
-        <is>
-          <t>Everlight</t>
-        </is>
-      </c>
-      <c r="B29" s="26" t="inlineStr">
-        <is>
-          <t>20 mm</t>
-        </is>
-      </c>
-      <c r="C29" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D29" s="53" t="n">
-        <v>1</v>
-      </c>
-      <c r="E29" s="29" t="n"/>
-      <c r="F29" s="29" t="n"/>
-      <c r="G29" s="62" t="n"/>
-      <c r="H29" s="29" t="n"/>
-      <c r="I29" s="29" t="n"/>
-      <c r="J29" s="63" t="n"/>
-      <c r="K29" s="44" t="n"/>
-      <c r="L29" s="53">
-        <f>IF(UPPER(K29)="Y",D29,0)</f>
-        <v/>
-      </c>
-      <c r="M29" s="34" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="25" t="inlineStr">
-        <is>
-          <t>Everlight</t>
-        </is>
-      </c>
-      <c r="B30" s="26" t="inlineStr">
-        <is>
-          <t>20 mm</t>
-        </is>
-      </c>
-      <c r="C30" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D30" s="53" t="n">
-        <v>2</v>
-      </c>
-      <c r="E30" s="29" t="n"/>
-      <c r="F30" s="29" t="n"/>
-      <c r="G30" s="62" t="n"/>
-      <c r="H30" s="29" t="n"/>
-      <c r="I30" s="29" t="n"/>
-      <c r="J30" s="63" t="n"/>
-      <c r="K30" s="44" t="n"/>
-      <c r="L30" s="53">
-        <f>IF(UPPER(K30)="Y",D30,0)</f>
-        <v/>
-      </c>
-      <c r="M30" s="34" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="25" t="inlineStr">
-        <is>
-          <t>Everlight</t>
-        </is>
-      </c>
-      <c r="B31" s="26" t="inlineStr">
-        <is>
-          <t>20 mm</t>
-        </is>
-      </c>
-      <c r="C31" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D31" s="53" t="n">
-        <v>3</v>
-      </c>
-      <c r="E31" s="29" t="n"/>
-      <c r="F31" s="29" t="n"/>
-      <c r="G31" s="62" t="n"/>
-      <c r="H31" s="29" t="n"/>
-      <c r="I31" s="29" t="n"/>
-      <c r="J31" s="63" t="n"/>
-      <c r="K31" s="44" t="n"/>
-      <c r="L31" s="53">
-        <f>IF(UPPER(K31)="Y",D31,0)</f>
-        <v/>
-      </c>
-      <c r="M31" s="34" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="25" t="inlineStr">
-        <is>
-          <t>Everlight</t>
-        </is>
-      </c>
-      <c r="B32" s="26" t="inlineStr">
-        <is>
-          <t>20 mm</t>
-        </is>
-      </c>
-      <c r="C32" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D32" s="53" t="n">
-        <v>4</v>
-      </c>
-      <c r="E32" s="29" t="n"/>
-      <c r="F32" s="29" t="n"/>
-      <c r="G32" s="62" t="n"/>
-      <c r="H32" s="29" t="n"/>
-      <c r="I32" s="29" t="n"/>
-      <c r="J32" s="63" t="n"/>
-      <c r="K32" s="44" t="n"/>
-      <c r="L32" s="53">
-        <f>IF(UPPER(K32)="Y",D32,0)</f>
-        <v/>
-      </c>
-      <c r="M32" s="34" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="25" t="inlineStr">
-        <is>
-          <t>Everlight</t>
-        </is>
-      </c>
-      <c r="B33" s="26" t="inlineStr">
-        <is>
-          <t>20 mm</t>
-        </is>
-      </c>
-      <c r="C33" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D33" s="53" t="n">
-        <v>5</v>
-      </c>
-      <c r="E33" s="29" t="n"/>
-      <c r="F33" s="29" t="n"/>
-      <c r="G33" s="62" t="n"/>
-      <c r="H33" s="29" t="n"/>
-      <c r="I33" s="29" t="n"/>
-      <c r="J33" s="63" t="n"/>
-      <c r="K33" s="44" t="n"/>
-      <c r="L33" s="53">
-        <f>IF(UPPER(K33)="Y",D33,0)</f>
-        <v/>
-      </c>
-      <c r="M33" s="34" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="25" t="inlineStr">
-        <is>
-          <t>XL</t>
-        </is>
-      </c>
-      <c r="B34" s="26" t="inlineStr">
-        <is>
-          <t>20 mm</t>
-        </is>
-      </c>
-      <c r="C34" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D34" s="53" t="n">
-        <v>1</v>
-      </c>
-      <c r="E34" s="29" t="n"/>
-      <c r="F34" s="29" t="n"/>
-      <c r="G34" s="62" t="n"/>
-      <c r="H34" s="29" t="n"/>
-      <c r="I34" s="29" t="n"/>
-      <c r="J34" s="63" t="n"/>
-      <c r="K34" s="44" t="n"/>
-      <c r="L34" s="53">
-        <f>IF(UPPER(K34)="Y",D34,0)</f>
-        <v/>
-      </c>
-      <c r="M34" s="34" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="25" t="inlineStr">
-        <is>
-          <t>XL</t>
-        </is>
-      </c>
-      <c r="B35" s="26" t="inlineStr">
-        <is>
-          <t>20 mm</t>
-        </is>
-      </c>
-      <c r="C35" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D35" s="53" t="n">
-        <v>2</v>
-      </c>
-      <c r="E35" s="29" t="n"/>
-      <c r="F35" s="29" t="n"/>
-      <c r="G35" s="62" t="n"/>
-      <c r="H35" s="29" t="n"/>
-      <c r="I35" s="29" t="n"/>
-      <c r="J35" s="63" t="n"/>
-      <c r="K35" s="44" t="n"/>
-      <c r="L35" s="53">
-        <f>IF(UPPER(K35)="Y",D35,0)</f>
-        <v/>
-      </c>
-      <c r="M35" s="34" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="25" t="inlineStr">
-        <is>
-          <t>XL</t>
-        </is>
-      </c>
-      <c r="B36" s="26" t="inlineStr">
-        <is>
-          <t>20 mm</t>
-        </is>
-      </c>
-      <c r="C36" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D36" s="53" t="n">
-        <v>3</v>
-      </c>
-      <c r="E36" s="29" t="n"/>
-      <c r="F36" s="29" t="n"/>
-      <c r="G36" s="62" t="n"/>
-      <c r="H36" s="29" t="n"/>
-      <c r="I36" s="29" t="n"/>
-      <c r="J36" s="63" t="n"/>
-      <c r="K36" s="44" t="n"/>
-      <c r="L36" s="53">
-        <f>IF(UPPER(K36)="Y",D36,0)</f>
-        <v/>
-      </c>
-      <c r="M36" s="34" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="25" t="inlineStr">
-        <is>
-          <t>XL</t>
-        </is>
-      </c>
-      <c r="B37" s="26" t="inlineStr">
-        <is>
-          <t>20 mm</t>
-        </is>
-      </c>
-      <c r="C37" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D37" s="53" t="n">
-        <v>4</v>
-      </c>
-      <c r="E37" s="29" t="n"/>
-      <c r="F37" s="29" t="n"/>
-      <c r="G37" s="62" t="n"/>
-      <c r="H37" s="29" t="n"/>
-      <c r="I37" s="29" t="n"/>
-      <c r="J37" s="63" t="n"/>
-      <c r="K37" s="44" t="n"/>
-      <c r="L37" s="53">
-        <f>IF(UPPER(K37)="Y",D37,0)</f>
-        <v/>
-      </c>
-      <c r="M37" s="34" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="25" t="inlineStr">
-        <is>
-          <t>XL</t>
-        </is>
-      </c>
-      <c r="B38" s="26" t="inlineStr">
-        <is>
-          <t>20 mm</t>
-        </is>
-      </c>
-      <c r="C38" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D38" s="53" t="n">
-        <v>5</v>
-      </c>
-      <c r="E38" s="29" t="n"/>
-      <c r="F38" s="29" t="n"/>
-      <c r="G38" s="62" t="n"/>
-      <c r="H38" s="29" t="n"/>
-      <c r="I38" s="29" t="n"/>
-      <c r="J38" s="63" t="n"/>
-      <c r="K38" s="44" t="n"/>
-      <c r="L38" s="53">
-        <f>IF(UPPER(K38)="Y",D38,0)</f>
-        <v/>
-      </c>
-      <c r="M38" s="34" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="25" t="inlineStr">
-        <is>
-          <t>Kingbright</t>
-        </is>
-      </c>
-      <c r="B39" s="26" t="inlineStr">
-        <is>
-          <t>20 mm</t>
-        </is>
-      </c>
-      <c r="C39" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D39" s="53" t="n">
-        <v>1</v>
-      </c>
-      <c r="E39" s="29" t="n"/>
-      <c r="F39" s="29" t="n"/>
-      <c r="G39" s="62" t="n"/>
-      <c r="H39" s="29" t="n"/>
-      <c r="I39" s="29" t="n"/>
-      <c r="J39" s="63" t="n"/>
-      <c r="K39" s="44" t="n"/>
-      <c r="L39" s="53">
-        <f>IF(UPPER(K39)="Y",D39,0)</f>
-        <v/>
-      </c>
-      <c r="M39" s="34" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="25" t="inlineStr">
-        <is>
-          <t>Kingbright</t>
-        </is>
-      </c>
-      <c r="B40" s="26" t="inlineStr">
-        <is>
-          <t>20 mm</t>
-        </is>
-      </c>
-      <c r="C40" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D40" s="53" t="n">
-        <v>2</v>
-      </c>
-      <c r="E40" s="29" t="n"/>
-      <c r="F40" s="29" t="n"/>
-      <c r="G40" s="62" t="n"/>
-      <c r="H40" s="29" t="n"/>
-      <c r="I40" s="29" t="n"/>
-      <c r="J40" s="63" t="n"/>
-      <c r="K40" s="44" t="n"/>
-      <c r="L40" s="53">
-        <f>IF(UPPER(K40)="Y",D40,0)</f>
-        <v/>
-      </c>
-      <c r="M40" s="34" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="25" t="inlineStr">
-        <is>
-          <t>Kingbright</t>
-        </is>
-      </c>
-      <c r="B41" s="26" t="inlineStr">
-        <is>
-          <t>20 mm</t>
-        </is>
-      </c>
-      <c r="C41" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D41" s="53" t="n">
-        <v>3</v>
-      </c>
-      <c r="E41" s="29" t="n"/>
-      <c r="F41" s="29" t="n"/>
-      <c r="G41" s="62" t="n"/>
-      <c r="H41" s="29" t="n"/>
-      <c r="I41" s="29" t="n"/>
-      <c r="J41" s="63" t="n"/>
-      <c r="K41" s="44" t="n"/>
-      <c r="L41" s="53">
-        <f>IF(UPPER(K41)="Y",D41,0)</f>
-        <v/>
-      </c>
-      <c r="M41" s="34" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="25" t="inlineStr">
-        <is>
-          <t>Kingbright</t>
-        </is>
-      </c>
-      <c r="B42" s="26" t="inlineStr">
-        <is>
-          <t>20 mm</t>
-        </is>
-      </c>
-      <c r="C42" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D42" s="53" t="n">
-        <v>4</v>
-      </c>
-      <c r="E42" s="29" t="n"/>
-      <c r="F42" s="29" t="n"/>
-      <c r="G42" s="62" t="n"/>
-      <c r="H42" s="29" t="n"/>
-      <c r="I42" s="29" t="n"/>
-      <c r="J42" s="63" t="n"/>
-      <c r="K42" s="44" t="n"/>
-      <c r="L42" s="53">
-        <f>IF(UPPER(K42)="Y",D42,0)</f>
-        <v/>
-      </c>
-      <c r="M42" s="34" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="25" t="inlineStr">
-        <is>
-          <t>Kingbright</t>
-        </is>
-      </c>
-      <c r="B43" s="26" t="inlineStr">
-        <is>
-          <t>20 mm</t>
-        </is>
-      </c>
-      <c r="C43" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D43" s="53" t="n">
-        <v>5</v>
-      </c>
-      <c r="E43" s="29" t="n"/>
-      <c r="F43" s="29" t="n"/>
-      <c r="G43" s="62" t="n"/>
-      <c r="H43" s="29" t="n"/>
-      <c r="I43" s="29" t="n"/>
-      <c r="J43" s="63" t="n"/>
-      <c r="K43" s="44" t="n"/>
-      <c r="L43" s="53">
-        <f>IF(UPPER(K43)="Y",D43,0)</f>
-        <v/>
-      </c>
-      <c r="M43" s="34" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="15" t="inlineStr">
-        <is>
-          <t>Vishay</t>
-        </is>
-      </c>
-      <c r="B44" s="16" t="inlineStr">
-        <is>
-          <t>25 mm</t>
-        </is>
-      </c>
-      <c r="C44" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="D44" s="57" t="n">
-        <v>1</v>
-      </c>
-      <c r="E44" s="19" t="n"/>
-      <c r="F44" s="19" t="n"/>
-      <c r="G44" s="58" t="n"/>
-      <c r="H44" s="19" t="n"/>
-      <c r="I44" s="19" t="n"/>
-      <c r="J44" s="59" t="n"/>
-      <c r="K44" s="43" t="n"/>
-      <c r="L44" s="57">
-        <f>IF(UPPER(K44)="Y",D44,0)</f>
-        <v/>
-      </c>
-      <c r="M44" s="24" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="25" t="inlineStr">
-        <is>
-          <t>Vishay</t>
-        </is>
-      </c>
-      <c r="B45" s="26" t="inlineStr">
-        <is>
-          <t>25 mm</t>
-        </is>
-      </c>
-      <c r="C45" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D45" s="53" t="n">
-        <v>2</v>
-      </c>
-      <c r="E45" s="29" t="n"/>
-      <c r="F45" s="29" t="n"/>
-      <c r="G45" s="62" t="n"/>
-      <c r="H45" s="29" t="n"/>
-      <c r="I45" s="29" t="n"/>
-      <c r="J45" s="63" t="n"/>
-      <c r="K45" s="44" t="n"/>
-      <c r="L45" s="53">
-        <f>IF(UPPER(K45)="Y",D45,0)</f>
-        <v/>
-      </c>
-      <c r="M45" s="34" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="25" t="inlineStr">
-        <is>
-          <t>Vishay</t>
-        </is>
-      </c>
-      <c r="B46" s="26" t="inlineStr">
-        <is>
-          <t>25 mm</t>
-        </is>
-      </c>
-      <c r="C46" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D46" s="53" t="n">
-        <v>3</v>
-      </c>
-      <c r="E46" s="29" t="n"/>
-      <c r="F46" s="29" t="n"/>
-      <c r="G46" s="62" t="n"/>
-      <c r="H46" s="29" t="n"/>
-      <c r="I46" s="29" t="n"/>
-      <c r="J46" s="63" t="n"/>
-      <c r="K46" s="44" t="n"/>
-      <c r="L46" s="53">
-        <f>IF(UPPER(K46)="Y",D46,0)</f>
-        <v/>
-      </c>
-      <c r="M46" s="34" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="25" t="inlineStr">
-        <is>
-          <t>Vishay</t>
-        </is>
-      </c>
-      <c r="B47" s="26" t="inlineStr">
-        <is>
-          <t>25 mm</t>
-        </is>
-      </c>
-      <c r="C47" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D47" s="53" t="n">
-        <v>4</v>
-      </c>
-      <c r="E47" s="29" t="n"/>
-      <c r="F47" s="29" t="n"/>
-      <c r="G47" s="62" t="n"/>
-      <c r="H47" s="29" t="n"/>
-      <c r="I47" s="29" t="n"/>
-      <c r="J47" s="63" t="n"/>
-      <c r="K47" s="44" t="n"/>
-      <c r="L47" s="53">
-        <f>IF(UPPER(K47)="Y",D47,0)</f>
-        <v/>
-      </c>
-      <c r="M47" s="34" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="25" t="inlineStr">
-        <is>
-          <t>Vishay</t>
-        </is>
-      </c>
-      <c r="B48" s="26" t="inlineStr">
-        <is>
-          <t>25 mm</t>
-        </is>
-      </c>
-      <c r="C48" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D48" s="53" t="n">
-        <v>5</v>
-      </c>
-      <c r="E48" s="29" t="n"/>
-      <c r="F48" s="29" t="n"/>
-      <c r="G48" s="62" t="n"/>
-      <c r="H48" s="29" t="n"/>
-      <c r="I48" s="29" t="n"/>
-      <c r="J48" s="63" t="n"/>
-      <c r="K48" s="44" t="n"/>
-      <c r="L48" s="53">
-        <f>IF(UPPER(K48)="Y",D48,0)</f>
-        <v/>
-      </c>
-      <c r="M48" s="34" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="25" t="inlineStr">
-        <is>
-          <t>Everlight</t>
-        </is>
-      </c>
-      <c r="B49" s="26" t="inlineStr">
-        <is>
-          <t>25 mm</t>
-        </is>
-      </c>
-      <c r="C49" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D49" s="53" t="n">
-        <v>1</v>
-      </c>
-      <c r="E49" s="29" t="n"/>
-      <c r="F49" s="29" t="n"/>
-      <c r="G49" s="62" t="n"/>
-      <c r="H49" s="29" t="n"/>
-      <c r="I49" s="29" t="n"/>
-      <c r="J49" s="63" t="n"/>
-      <c r="K49" s="44" t="n"/>
-      <c r="L49" s="53">
-        <f>IF(UPPER(K49)="Y",D49,0)</f>
-        <v/>
-      </c>
-      <c r="M49" s="34" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="25" t="inlineStr">
-        <is>
-          <t>Everlight</t>
-        </is>
-      </c>
-      <c r="B50" s="26" t="inlineStr">
-        <is>
-          <t>25 mm</t>
-        </is>
-      </c>
-      <c r="C50" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D50" s="53" t="n">
-        <v>2</v>
-      </c>
-      <c r="E50" s="29" t="n"/>
-      <c r="F50" s="29" t="n"/>
-      <c r="G50" s="62" t="n"/>
-      <c r="H50" s="29" t="n"/>
-      <c r="I50" s="29" t="n"/>
-      <c r="J50" s="63" t="n"/>
-      <c r="K50" s="44" t="n"/>
-      <c r="L50" s="53">
-        <f>IF(UPPER(K50)="Y",D50,0)</f>
-        <v/>
-      </c>
-      <c r="M50" s="34" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="25" t="inlineStr">
-        <is>
-          <t>Everlight</t>
-        </is>
-      </c>
-      <c r="B51" s="26" t="inlineStr">
-        <is>
-          <t>25 mm</t>
-        </is>
-      </c>
-      <c r="C51" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D51" s="53" t="n">
-        <v>3</v>
-      </c>
-      <c r="E51" s="29" t="n"/>
-      <c r="F51" s="29" t="n"/>
-      <c r="G51" s="62" t="n"/>
-      <c r="H51" s="29" t="n"/>
-      <c r="I51" s="29" t="n"/>
-      <c r="J51" s="63" t="n"/>
-      <c r="K51" s="44" t="n"/>
-      <c r="L51" s="53">
-        <f>IF(UPPER(K51)="Y",D51,0)</f>
-        <v/>
-      </c>
-      <c r="M51" s="34" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="25" t="inlineStr">
-        <is>
-          <t>Everlight</t>
-        </is>
-      </c>
-      <c r="B52" s="26" t="inlineStr">
-        <is>
-          <t>25 mm</t>
-        </is>
-      </c>
-      <c r="C52" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D52" s="53" t="n">
-        <v>4</v>
-      </c>
-      <c r="E52" s="29" t="n"/>
-      <c r="F52" s="29" t="n"/>
-      <c r="G52" s="62" t="n"/>
-      <c r="H52" s="29" t="n"/>
-      <c r="I52" s="29" t="n"/>
-      <c r="J52" s="63" t="n"/>
-      <c r="K52" s="44" t="n"/>
-      <c r="L52" s="53">
-        <f>IF(UPPER(K52)="Y",D52,0)</f>
-        <v/>
-      </c>
-      <c r="M52" s="34" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="25" t="inlineStr">
-        <is>
-          <t>Everlight</t>
-        </is>
-      </c>
-      <c r="B53" s="26" t="inlineStr">
-        <is>
-          <t>25 mm</t>
-        </is>
-      </c>
-      <c r="C53" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D53" s="53" t="n">
-        <v>5</v>
-      </c>
-      <c r="E53" s="29" t="n"/>
-      <c r="F53" s="29" t="n"/>
-      <c r="G53" s="62" t="n"/>
-      <c r="H53" s="29" t="n"/>
-      <c r="I53" s="29" t="n"/>
-      <c r="J53" s="63" t="n"/>
-      <c r="K53" s="44" t="n"/>
-      <c r="L53" s="53">
-        <f>IF(UPPER(K53)="Y",D53,0)</f>
-        <v/>
-      </c>
-      <c r="M53" s="34" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="25" t="inlineStr">
-        <is>
-          <t>XL</t>
-        </is>
-      </c>
-      <c r="B54" s="26" t="inlineStr">
-        <is>
-          <t>25 mm</t>
-        </is>
-      </c>
-      <c r="C54" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D54" s="53" t="n">
-        <v>1</v>
-      </c>
-      <c r="E54" s="29" t="n"/>
-      <c r="F54" s="29" t="n"/>
-      <c r="G54" s="62" t="n"/>
-      <c r="H54" s="29" t="n"/>
-      <c r="I54" s="29" t="n"/>
-      <c r="J54" s="63" t="n"/>
-      <c r="K54" s="44" t="n"/>
-      <c r="L54" s="53">
-        <f>IF(UPPER(K54)="Y",D54,0)</f>
-        <v/>
-      </c>
-      <c r="M54" s="34" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="25" t="inlineStr">
-        <is>
-          <t>XL</t>
-        </is>
-      </c>
-      <c r="B55" s="26" t="inlineStr">
-        <is>
-          <t>25 mm</t>
-        </is>
-      </c>
-      <c r="C55" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D55" s="53" t="n">
-        <v>2</v>
-      </c>
-      <c r="E55" s="29" t="n"/>
-      <c r="F55" s="29" t="n"/>
-      <c r="G55" s="62" t="n"/>
-      <c r="H55" s="29" t="n"/>
-      <c r="I55" s="29" t="n"/>
-      <c r="J55" s="63" t="n"/>
-      <c r="K55" s="44" t="n"/>
-      <c r="L55" s="53">
-        <f>IF(UPPER(K55)="Y",D55,0)</f>
-        <v/>
-      </c>
-      <c r="M55" s="34" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="25" t="inlineStr">
-        <is>
-          <t>XL</t>
-        </is>
-      </c>
-      <c r="B56" s="26" t="inlineStr">
-        <is>
-          <t>25 mm</t>
-        </is>
-      </c>
-      <c r="C56" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D56" s="53" t="n">
-        <v>3</v>
-      </c>
-      <c r="E56" s="29" t="n"/>
-      <c r="F56" s="29" t="n"/>
-      <c r="G56" s="62" t="n"/>
-      <c r="H56" s="29" t="n"/>
-      <c r="I56" s="29" t="n"/>
-      <c r="J56" s="63" t="n"/>
-      <c r="K56" s="44" t="n"/>
-      <c r="L56" s="53">
-        <f>IF(UPPER(K56)="Y",D56,0)</f>
-        <v/>
-      </c>
-      <c r="M56" s="34" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="25" t="inlineStr">
-        <is>
-          <t>XL</t>
-        </is>
-      </c>
-      <c r="B57" s="26" t="inlineStr">
-        <is>
-          <t>25 mm</t>
-        </is>
-      </c>
-      <c r="C57" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D57" s="53" t="n">
-        <v>4</v>
-      </c>
-      <c r="E57" s="29" t="n"/>
-      <c r="F57" s="29" t="n"/>
-      <c r="G57" s="62" t="n"/>
-      <c r="H57" s="29" t="n"/>
-      <c r="I57" s="29" t="n"/>
-      <c r="J57" s="63" t="n"/>
-      <c r="K57" s="44" t="n"/>
-      <c r="L57" s="53">
-        <f>IF(UPPER(K57)="Y",D57,0)</f>
-        <v/>
-      </c>
-      <c r="M57" s="34" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="25" t="inlineStr">
-        <is>
-          <t>XL</t>
-        </is>
-      </c>
-      <c r="B58" s="26" t="inlineStr">
-        <is>
-          <t>25 mm</t>
-        </is>
-      </c>
-      <c r="C58" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D58" s="53" t="n">
-        <v>5</v>
-      </c>
-      <c r="E58" s="29" t="n"/>
-      <c r="F58" s="29" t="n"/>
-      <c r="G58" s="62" t="n"/>
-      <c r="H58" s="29" t="n"/>
-      <c r="I58" s="29" t="n"/>
-      <c r="J58" s="63" t="n"/>
-      <c r="K58" s="44" t="n"/>
-      <c r="L58" s="53">
-        <f>IF(UPPER(K58)="Y",D58,0)</f>
-        <v/>
-      </c>
-      <c r="M58" s="34" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="25" t="inlineStr">
-        <is>
-          <t>Kingbright</t>
-        </is>
-      </c>
-      <c r="B59" s="26" t="inlineStr">
-        <is>
-          <t>25 mm</t>
-        </is>
-      </c>
-      <c r="C59" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D59" s="53" t="n">
-        <v>1</v>
-      </c>
-      <c r="E59" s="29" t="n"/>
-      <c r="F59" s="29" t="n"/>
-      <c r="G59" s="62" t="n"/>
-      <c r="H59" s="29" t="n"/>
-      <c r="I59" s="29" t="n"/>
-      <c r="J59" s="63" t="n"/>
-      <c r="K59" s="44" t="n"/>
-      <c r="L59" s="53">
-        <f>IF(UPPER(K59)="Y",D59,0)</f>
-        <v/>
-      </c>
-      <c r="M59" s="34" t="n"/>
+      <c r="J59" s="79" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="K59" s="79" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="L59" s="126" t="n">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="M59" s="83" t="n">
+        <v>0.0487</v>
+      </c>
+      <c r="N59" s="83" t="n">
+        <v>0.08210000000000001</v>
+      </c>
+      <c r="O59" s="84">
+        <f>IF(OR(M59="",N59=""),"",SQRT(0.5*(M59^2+N59^2)))</f>
+        <v/>
+      </c>
+      <c r="P59" s="78" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q59" s="85">
+        <f>IF(OR(C59="",G59=""),"",G59*C59^2)</f>
+        <v/>
+      </c>
+      <c r="R59" s="139" t="inlineStr">
+        <is>
+          <t>VOID - BATTERY DYING. sigma 0.2018 then 0.0675 (3x this marker at 4 m) and a transient blob split. The battery failed completely at the next distance. With only ~2.6 V of headroom above 4x Vf, current is hypersensitive to supply sag, so a fading battery fluctuates the brightness and wanders the centroid. RE-MEASURE with a fresh cell.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
-      <c r="A60" s="25" t="inlineStr">
-        <is>
-          <t>Kingbright</t>
-        </is>
-      </c>
-      <c r="B60" s="26" t="inlineStr">
-        <is>
-          <t>25 mm</t>
-        </is>
-      </c>
-      <c r="C60" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D60" s="53" t="n">
-        <v>2</v>
-      </c>
-      <c r="E60" s="29" t="n"/>
-      <c r="F60" s="29" t="n"/>
-      <c r="G60" s="62" t="n"/>
-      <c r="H60" s="29" t="n"/>
-      <c r="I60" s="29" t="n"/>
-      <c r="J60" s="63" t="n"/>
-      <c r="K60" s="44" t="n"/>
-      <c r="L60" s="53">
-        <f>IF(UPPER(K60)="Y",D60,0)</f>
-        <v/>
-      </c>
-      <c r="M60" s="34" t="n"/>
+      <c r="A60" s="133" t="n"/>
+      <c r="B60" s="85" t="n"/>
+      <c r="C60" s="86" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D60" s="74" t="n"/>
+      <c r="E60" s="74" t="n"/>
+      <c r="F60" s="72" t="n"/>
+      <c r="G60" s="74" t="n"/>
+      <c r="H60" s="74" t="n"/>
+      <c r="I60" s="74" t="n"/>
+      <c r="J60" s="79" t="n"/>
+      <c r="K60" s="79" t="n"/>
+      <c r="L60" s="126" t="n"/>
+      <c r="M60" s="83" t="n"/>
+      <c r="N60" s="83" t="n"/>
+      <c r="O60" s="84">
+        <f>IF(OR(M60="",N60=""),"",SQRT(0.5*(M60^2+N60^2)))</f>
+        <v/>
+      </c>
+      <c r="P60" s="78" t="inlineStr"/>
+      <c r="Q60" s="85">
+        <f>IF(OR(C60="",G60=""),"",G60*C60^2)</f>
+        <v/>
+      </c>
+      <c r="R60" s="139" t="inlineStr">
+        <is>
+          <t>Battery flat - no marker in frame at any exposure to 30 ms. Not a range limit.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
-      <c r="A61" s="25" t="inlineStr">
-        <is>
-          <t>Kingbright</t>
-        </is>
-      </c>
-      <c r="B61" s="26" t="inlineStr">
-        <is>
-          <t>25 mm</t>
-        </is>
-      </c>
-      <c r="C61" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D61" s="53" t="n">
-        <v>3</v>
-      </c>
-      <c r="E61" s="29" t="n"/>
-      <c r="F61" s="29" t="n"/>
-      <c r="G61" s="62" t="n"/>
-      <c r="H61" s="29" t="n"/>
-      <c r="I61" s="29" t="n"/>
-      <c r="J61" s="63" t="n"/>
-      <c r="K61" s="44" t="n"/>
-      <c r="L61" s="53">
-        <f>IF(UPPER(K61)="Y",D61,0)</f>
-        <v/>
-      </c>
-      <c r="M61" s="34" t="n"/>
+      <c r="A61" s="133" t="n"/>
+      <c r="B61" s="85" t="n"/>
+      <c r="C61" s="86" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D61" s="74" t="n"/>
+      <c r="E61" s="74" t="n"/>
+      <c r="F61" s="72" t="n"/>
+      <c r="G61" s="74" t="n"/>
+      <c r="H61" s="74" t="n"/>
+      <c r="I61" s="74" t="n"/>
+      <c r="J61" s="79" t="n"/>
+      <c r="K61" s="79" t="n"/>
+      <c r="L61" s="126" t="n"/>
+      <c r="M61" s="83" t="n"/>
+      <c r="N61" s="83" t="n"/>
+      <c r="O61" s="84">
+        <f>IF(OR(M61="",N61=""),"",SQRT(0.5*(M61^2+N61^2)))</f>
+        <v/>
+      </c>
+      <c r="P61" s="78" t="n"/>
+      <c r="Q61" s="85">
+        <f>IF(OR(C61="",G61=""),"",G61*C61^2)</f>
+        <v/>
+      </c>
+      <c r="R61" s="81" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="25" t="inlineStr">
-        <is>
-          <t>Kingbright</t>
-        </is>
-      </c>
-      <c r="B62" s="26" t="inlineStr">
-        <is>
-          <t>25 mm</t>
-        </is>
-      </c>
-      <c r="C62" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D62" s="53" t="n">
-        <v>4</v>
-      </c>
-      <c r="E62" s="29" t="n"/>
-      <c r="F62" s="29" t="n"/>
-      <c r="G62" s="62" t="n"/>
-      <c r="H62" s="29" t="n"/>
-      <c r="I62" s="29" t="n"/>
-      <c r="J62" s="63" t="n"/>
-      <c r="K62" s="44" t="n"/>
-      <c r="L62" s="53">
-        <f>IF(UPPER(K62)="Y",D62,0)</f>
-        <v/>
-      </c>
-      <c r="M62" s="34" t="n"/>
+      <c r="A62" s="133" t="n"/>
+      <c r="B62" s="85" t="n"/>
+      <c r="C62" s="86" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D62" s="74" t="n"/>
+      <c r="E62" s="74" t="n"/>
+      <c r="F62" s="72" t="n"/>
+      <c r="G62" s="74" t="n"/>
+      <c r="H62" s="74" t="n"/>
+      <c r="I62" s="74" t="n"/>
+      <c r="J62" s="79" t="n"/>
+      <c r="K62" s="79" t="n"/>
+      <c r="L62" s="126" t="n"/>
+      <c r="M62" s="83" t="n"/>
+      <c r="N62" s="83" t="n"/>
+      <c r="O62" s="84">
+        <f>IF(OR(M62="",N62=""),"",SQRT(0.5*(M62^2+N62^2)))</f>
+        <v/>
+      </c>
+      <c r="P62" s="78" t="n"/>
+      <c r="Q62" s="85">
+        <f>IF(OR(C62="",G62=""),"",G62*C62^2)</f>
+        <v/>
+      </c>
+      <c r="R62" s="81" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="25" t="inlineStr">
-        <is>
-          <t>Kingbright</t>
-        </is>
-      </c>
-      <c r="B63" s="26" t="inlineStr">
-        <is>
-          <t>25 mm</t>
-        </is>
-      </c>
-      <c r="C63" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D63" s="53" t="n">
-        <v>5</v>
-      </c>
-      <c r="E63" s="29" t="n"/>
-      <c r="F63" s="29" t="n"/>
-      <c r="G63" s="62" t="n"/>
-      <c r="H63" s="29" t="n"/>
-      <c r="I63" s="29" t="n"/>
-      <c r="J63" s="63" t="n"/>
-      <c r="K63" s="44" t="n"/>
-      <c r="L63" s="53">
-        <f>IF(UPPER(K63)="Y",D63,0)</f>
-        <v/>
-      </c>
-      <c r="M63" s="34" t="n"/>
+      <c r="A63" s="133" t="n"/>
+      <c r="B63" s="85" t="n"/>
+      <c r="C63" s="86" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D63" s="74" t="n"/>
+      <c r="E63" s="74" t="n"/>
+      <c r="F63" s="72" t="n"/>
+      <c r="G63" s="74" t="n"/>
+      <c r="H63" s="74" t="n"/>
+      <c r="I63" s="74" t="n"/>
+      <c r="J63" s="79" t="n"/>
+      <c r="K63" s="79" t="n"/>
+      <c r="L63" s="126" t="n"/>
+      <c r="M63" s="83" t="n"/>
+      <c r="N63" s="83" t="n"/>
+      <c r="O63" s="84">
+        <f>IF(OR(M63="",N63=""),"",SQRT(0.5*(M63^2+N63^2)))</f>
+        <v/>
+      </c>
+      <c r="P63" s="78" t="n"/>
+      <c r="Q63" s="85">
+        <f>IF(OR(C63="",G63=""),"",G63*C63^2)</f>
+        <v/>
+      </c>
+      <c r="R63" s="81" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="133" t="n"/>
+      <c r="B64" s="85" t="n"/>
+      <c r="C64" s="86" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D64" s="74" t="n"/>
+      <c r="E64" s="74" t="n"/>
+      <c r="F64" s="72" t="n"/>
+      <c r="G64" s="74" t="n"/>
+      <c r="H64" s="74" t="n"/>
+      <c r="I64" s="74" t="n"/>
+      <c r="J64" s="79" t="n"/>
+      <c r="K64" s="79" t="n"/>
+      <c r="L64" s="126" t="n"/>
+      <c r="M64" s="83" t="n"/>
+      <c r="N64" s="83" t="n"/>
+      <c r="O64" s="84">
+        <f>IF(OR(M64="",N64=""),"",SQRT(0.5*(M64^2+N64^2)))</f>
+        <v/>
+      </c>
+      <c r="P64" s="78" t="n"/>
+      <c r="Q64" s="85">
+        <f>IF(OR(C64="",G64=""),"",G64*C64^2)</f>
+        <v/>
+      </c>
+      <c r="R64" s="81" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="76" t="inlineStr">
-        <is>
-          <t>C2 - THRESH_LO SWEEP AT MAXIMUM RANGE</t>
-        </is>
-      </c>
+      <c r="A65" s="133" t="n"/>
+      <c r="B65" s="85" t="n"/>
+      <c r="C65" s="86" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="D65" s="74" t="n"/>
+      <c r="E65" s="74" t="n"/>
+      <c r="F65" s="72" t="n"/>
+      <c r="G65" s="74" t="n"/>
+      <c r="H65" s="74" t="n"/>
+      <c r="I65" s="74" t="n"/>
+      <c r="J65" s="79" t="n"/>
+      <c r="K65" s="79" t="n"/>
+      <c r="L65" s="126" t="n"/>
+      <c r="M65" s="83" t="n"/>
+      <c r="N65" s="83" t="n"/>
+      <c r="O65" s="84">
+        <f>IF(OR(M65="",N65=""),"",SQRT(0.5*(M65^2+N65^2)))</f>
+        <v/>
+      </c>
+      <c r="P65" s="78" t="n"/>
+      <c r="Q65" s="85">
+        <f>IF(OR(C65="",G65=""),"",G65*C65^2)</f>
+        <v/>
+      </c>
+      <c r="R65" s="81" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="66" t="inlineStr">
-        <is>
-          <t>THRESH_LO has sat at 80 since run 1, but the background measured max 4 counts (2026-09-03, flat across 300x of exposure). 80 is therefore ~20x above anything the sensor floor produces, and it is throwing away the blob's dim skirt - which is exactly the signal that matters at maximum range, where the marker is smallest. Run this at the FAR limit with the winning build, and again at the NEAR limit to check nothing false appears.</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="32" customHeight="1">
-      <c r="A67" s="77" t="inlineStr">
-        <is>
-          <t>Distance
-(m)</t>
-        </is>
-      </c>
-      <c r="B67" s="77" t="inlineStr">
-        <is>
-          <t>THRESH_LO</t>
-        </is>
-      </c>
-      <c r="C67" s="77" t="inlineStr">
-        <is>
-          <t>Background
-max</t>
-        </is>
-      </c>
-      <c r="D67" s="77" t="inlineStr">
-        <is>
-          <t>Detected?
-(Y/N)</t>
-        </is>
-      </c>
-      <c r="E67" s="77" t="inlineStr">
-        <is>
-          <t>blobs
-(marker)</t>
-        </is>
-      </c>
-      <c r="F67" s="77" t="inlineStr">
-        <is>
-          <t>False blobs
-(frame)</t>
-        </is>
-      </c>
-      <c r="G67" s="77" t="inlineStr">
-        <is>
-          <t>Sensor area
-(px)</t>
-        </is>
-      </c>
-      <c r="H67" s="77" t="inlineStr">
-        <is>
-          <t>npix
-(refined)</t>
-        </is>
-      </c>
-      <c r="I67" s="77" t="inlineStr">
-        <is>
-          <t>Fill</t>
-        </is>
-      </c>
-      <c r="J67" s="77" t="inlineStr">
-        <is>
-          <t>sigma_u
-(px)</t>
-        </is>
-      </c>
-      <c r="K67" s="77" t="inlineStr">
-        <is>
-          <t>sigma_v
-(px)</t>
-        </is>
-      </c>
-      <c r="L67" s="77" t="inlineStr">
-        <is>
-          <t>sigma_RMS
-(px)</t>
-        </is>
-      </c>
-      <c r="M67" s="77" t="inlineStr">
-        <is>
-          <t>Area vs 80</t>
-        </is>
-      </c>
-      <c r="N67" s="77" t="inlineStr">
-        <is>
-          <t>sigma vs 80</t>
-        </is>
-      </c>
-      <c r="O67" s="77" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="72" t="n"/>
-      <c r="B68" s="85" t="n">
-        <v>80</v>
-      </c>
-      <c r="C68" s="74" t="n"/>
-      <c r="D68" s="74" t="n"/>
-      <c r="E68" s="74" t="n"/>
-      <c r="F68" s="74" t="n"/>
-      <c r="G68" s="74" t="n"/>
-      <c r="H68" s="74" t="n"/>
-      <c r="I68" s="79" t="n"/>
-      <c r="J68" s="83" t="n"/>
-      <c r="K68" s="83" t="n"/>
-      <c r="L68" s="84">
-        <f>IF(OR(J68="",K68=""),"",SQRT(0.5*(J68^2+K68^2)))</f>
-        <v/>
-      </c>
-      <c r="M68" s="75">
-        <f>IF(OR(G68="",$G$68="",$G$68=0),"",G68/$G$68)</f>
-        <v/>
-      </c>
-      <c r="N68" s="75">
-        <f>IF(OR(L68="",$L$68="",$L$68=0),"",L68/$L$68)</f>
-        <v/>
-      </c>
-      <c r="O68" s="81" t="inlineStr">
-        <is>
-          <t>far limit - the row that matters</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="72" t="n"/>
-      <c r="B69" s="85" t="n">
-        <v>60</v>
-      </c>
-      <c r="C69" s="74" t="n"/>
-      <c r="D69" s="74" t="n"/>
-      <c r="E69" s="74" t="n"/>
-      <c r="F69" s="74" t="n"/>
-      <c r="G69" s="74" t="n"/>
-      <c r="H69" s="74" t="n"/>
-      <c r="I69" s="79" t="n"/>
-      <c r="J69" s="83" t="n"/>
-      <c r="K69" s="83" t="n"/>
-      <c r="L69" s="84">
-        <f>IF(OR(J69="",K69=""),"",SQRT(0.5*(J69^2+K69^2)))</f>
-        <v/>
-      </c>
-      <c r="M69" s="75">
-        <f>IF(OR(G69="",$G$68="",$G$68=0),"",G69/$G$68)</f>
-        <v/>
-      </c>
-      <c r="N69" s="75">
-        <f>IF(OR(L69="",$L$68="",$L$68=0),"",L69/$L$68)</f>
-        <v/>
-      </c>
-      <c r="O69" s="81" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="72" t="n"/>
-      <c r="B70" s="85" t="n">
-        <v>50</v>
-      </c>
-      <c r="C70" s="74" t="n"/>
-      <c r="D70" s="74" t="n"/>
-      <c r="E70" s="74" t="n"/>
-      <c r="F70" s="74" t="n"/>
-      <c r="G70" s="74" t="n"/>
-      <c r="H70" s="74" t="n"/>
-      <c r="I70" s="79" t="n"/>
-      <c r="J70" s="83" t="n"/>
-      <c r="K70" s="83" t="n"/>
-      <c r="L70" s="84">
-        <f>IF(OR(J70="",K70=""),"",SQRT(0.5*(J70^2+K70^2)))</f>
-        <v/>
-      </c>
-      <c r="M70" s="75">
-        <f>IF(OR(G70="",$G$68="",$G$68=0),"",G70/$G$68)</f>
-        <v/>
-      </c>
-      <c r="N70" s="75">
-        <f>IF(OR(L70="",$L$68="",$L$68=0),"",L70/$L$68)</f>
-        <v/>
-      </c>
-      <c r="O70" s="81" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="72" t="n"/>
-      <c r="B71" s="85" t="n">
-        <v>40</v>
-      </c>
-      <c r="C71" s="74" t="n"/>
-      <c r="D71" s="74" t="n"/>
-      <c r="E71" s="74" t="n"/>
-      <c r="F71" s="74" t="n"/>
-      <c r="G71" s="74" t="n"/>
-      <c r="H71" s="74" t="n"/>
-      <c r="I71" s="79" t="n"/>
-      <c r="J71" s="83" t="n"/>
-      <c r="K71" s="83" t="n"/>
-      <c r="L71" s="84">
-        <f>IF(OR(J71="",K71=""),"",SQRT(0.5*(J71^2+K71^2)))</f>
-        <v/>
-      </c>
-      <c r="M71" s="75">
-        <f>IF(OR(G71="",$G$68="",$G$68=0),"",G71/$G$68)</f>
-        <v/>
-      </c>
-      <c r="N71" s="75">
-        <f>IF(OR(L71="",$L$68="",$L$68=0),"",L71/$L$68)</f>
-        <v/>
-      </c>
-      <c r="O71" s="81" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="72" t="n"/>
-      <c r="B72" s="85" t="n">
-        <v>30</v>
-      </c>
-      <c r="C72" s="74" t="n"/>
-      <c r="D72" s="74" t="n"/>
-      <c r="E72" s="74" t="n"/>
-      <c r="F72" s="74" t="n"/>
-      <c r="G72" s="74" t="n"/>
-      <c r="H72" s="74" t="n"/>
-      <c r="I72" s="79" t="n"/>
-      <c r="J72" s="83" t="n"/>
-      <c r="K72" s="83" t="n"/>
-      <c r="L72" s="84">
-        <f>IF(OR(J72="",K72=""),"",SQRT(0.5*(J72^2+K72^2)))</f>
-        <v/>
-      </c>
-      <c r="M72" s="75">
-        <f>IF(OR(G72="",$G$68="",$G$68=0),"",G72/$G$68)</f>
-        <v/>
-      </c>
-      <c r="N72" s="75">
-        <f>IF(OR(L72="",$L$68="",$L$68=0),"",L72/$L$68)</f>
-        <v/>
-      </c>
-      <c r="O72" s="81" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="72" t="n"/>
-      <c r="B73" s="85" t="n">
-        <v>20</v>
-      </c>
-      <c r="C73" s="74" t="n"/>
-      <c r="D73" s="74" t="n"/>
-      <c r="E73" s="74" t="n"/>
-      <c r="F73" s="74" t="n"/>
-      <c r="G73" s="74" t="n"/>
-      <c r="H73" s="74" t="n"/>
-      <c r="I73" s="79" t="n"/>
-      <c r="J73" s="83" t="n"/>
-      <c r="K73" s="83" t="n"/>
-      <c r="L73" s="84">
-        <f>IF(OR(J73="",K73=""),"",SQRT(0.5*(J73^2+K73^2)))</f>
-        <v/>
-      </c>
-      <c r="M73" s="75">
-        <f>IF(OR(G73="",$G$68="",$G$68=0),"",G73/$G$68)</f>
-        <v/>
-      </c>
-      <c r="N73" s="75">
-        <f>IF(OR(L73="",$L$68="",$L$68=0),"",L73/$L$68)</f>
-        <v/>
-      </c>
-      <c r="O73" s="81" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="72" t="n"/>
-      <c r="B75" s="85" t="n">
-        <v>80</v>
-      </c>
-      <c r="C75" s="74" t="n"/>
-      <c r="D75" s="74" t="n"/>
-      <c r="E75" s="74" t="n"/>
-      <c r="F75" s="74" t="n"/>
-      <c r="G75" s="74" t="n"/>
-      <c r="H75" s="74" t="n"/>
-      <c r="I75" s="79" t="n"/>
-      <c r="J75" s="83" t="n"/>
-      <c r="K75" s="83" t="n"/>
-      <c r="L75" s="84">
-        <f>IF(OR(J75="",K75=""),"",SQRT(0.5*(J75^2+K75^2)))</f>
-        <v/>
-      </c>
-      <c r="M75" s="75">
-        <f>IF(OR(G75="",$G$75="",$G$75=0),"",G75/$G$75)</f>
-        <v/>
-      </c>
-      <c r="N75" s="75">
-        <f>IF(OR(L75="",$L$75="",$L$75=0),"",L75/$L$75)</f>
-        <v/>
-      </c>
-      <c r="O75" s="81" t="inlineStr">
-        <is>
-          <t>near limit - watch False blobs</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="72" t="n"/>
-      <c r="B76" s="85" t="n">
-        <v>60</v>
-      </c>
-      <c r="C76" s="74" t="n"/>
-      <c r="D76" s="74" t="n"/>
-      <c r="E76" s="74" t="n"/>
-      <c r="F76" s="74" t="n"/>
-      <c r="G76" s="74" t="n"/>
-      <c r="H76" s="74" t="n"/>
-      <c r="I76" s="79" t="n"/>
-      <c r="J76" s="83" t="n"/>
-      <c r="K76" s="83" t="n"/>
-      <c r="L76" s="84">
-        <f>IF(OR(J76="",K76=""),"",SQRT(0.5*(J76^2+K76^2)))</f>
-        <v/>
-      </c>
-      <c r="M76" s="75">
-        <f>IF(OR(G76="",$G$75="",$G$75=0),"",G76/$G$75)</f>
-        <v/>
-      </c>
-      <c r="N76" s="75">
-        <f>IF(OR(L76="",$L$75="",$L$75=0),"",L76/$L$75)</f>
-        <v/>
-      </c>
-      <c r="O76" s="81" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="72" t="n"/>
-      <c r="B77" s="85" t="n">
-        <v>50</v>
-      </c>
-      <c r="C77" s="74" t="n"/>
-      <c r="D77" s="74" t="n"/>
-      <c r="E77" s="74" t="n"/>
-      <c r="F77" s="74" t="n"/>
-      <c r="G77" s="74" t="n"/>
-      <c r="H77" s="74" t="n"/>
-      <c r="I77" s="79" t="n"/>
-      <c r="J77" s="83" t="n"/>
-      <c r="K77" s="83" t="n"/>
-      <c r="L77" s="84">
-        <f>IF(OR(J77="",K77=""),"",SQRT(0.5*(J77^2+K77^2)))</f>
-        <v/>
-      </c>
-      <c r="M77" s="75">
-        <f>IF(OR(G77="",$G$75="",$G$75=0),"",G77/$G$75)</f>
-        <v/>
-      </c>
-      <c r="N77" s="75">
-        <f>IF(OR(L77="",$L$75="",$L$75=0),"",L77/$L$75)</f>
-        <v/>
-      </c>
-      <c r="O77" s="81" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="72" t="n"/>
-      <c r="B78" s="85" t="n">
-        <v>40</v>
-      </c>
-      <c r="C78" s="74" t="n"/>
-      <c r="D78" s="74" t="n"/>
-      <c r="E78" s="74" t="n"/>
-      <c r="F78" s="74" t="n"/>
-      <c r="G78" s="74" t="n"/>
-      <c r="H78" s="74" t="n"/>
-      <c r="I78" s="79" t="n"/>
-      <c r="J78" s="83" t="n"/>
-      <c r="K78" s="83" t="n"/>
-      <c r="L78" s="84">
-        <f>IF(OR(J78="",K78=""),"",SQRT(0.5*(J78^2+K78^2)))</f>
-        <v/>
-      </c>
-      <c r="M78" s="75">
-        <f>IF(OR(G78="",$G$75="",$G$75=0),"",G78/$G$75)</f>
-        <v/>
-      </c>
-      <c r="N78" s="75">
-        <f>IF(OR(L78="",$L$75="",$L$75=0),"",L78/$L$75)</f>
-        <v/>
-      </c>
-      <c r="O78" s="81" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="72" t="n"/>
-      <c r="B79" s="85" t="n">
-        <v>30</v>
-      </c>
-      <c r="C79" s="74" t="n"/>
-      <c r="D79" s="74" t="n"/>
-      <c r="E79" s="74" t="n"/>
-      <c r="F79" s="74" t="n"/>
-      <c r="G79" s="74" t="n"/>
-      <c r="H79" s="74" t="n"/>
-      <c r="I79" s="79" t="n"/>
-      <c r="J79" s="83" t="n"/>
-      <c r="K79" s="83" t="n"/>
-      <c r="L79" s="84">
-        <f>IF(OR(J79="",K79=""),"",SQRT(0.5*(J79^2+K79^2)))</f>
-        <v/>
-      </c>
-      <c r="M79" s="75">
-        <f>IF(OR(G79="",$G$75="",$G$75=0),"",G79/$G$75)</f>
-        <v/>
-      </c>
-      <c r="N79" s="75">
-        <f>IF(OR(L79="",$L$75="",$L$75=0),"",L79/$L$75)</f>
-        <v/>
-      </c>
-      <c r="O79" s="81" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="72" t="n"/>
-      <c r="B80" s="85" t="n">
-        <v>20</v>
-      </c>
-      <c r="C80" s="74" t="n"/>
-      <c r="D80" s="74" t="n"/>
-      <c r="E80" s="74" t="n"/>
-      <c r="F80" s="74" t="n"/>
-      <c r="G80" s="74" t="n"/>
-      <c r="H80" s="74" t="n"/>
-      <c r="I80" s="79" t="n"/>
-      <c r="J80" s="83" t="n"/>
-      <c r="K80" s="83" t="n"/>
-      <c r="L80" s="84">
-        <f>IF(OR(J80="",K80=""),"",SQRT(0.5*(J80^2+K80^2)))</f>
-        <v/>
-      </c>
-      <c r="M80" s="75">
-        <f>IF(OR(G80="",$G$75="",$G$75=0),"",G80/$G$75)</f>
-        <v/>
-      </c>
-      <c r="N80" s="75">
-        <f>IF(OR(L80="",$L$75="",$L$75=0),"",L80/$L$75)</f>
-        <v/>
-      </c>
-      <c r="O80" s="81" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="120" t="inlineStr">
-        <is>
-          <t>Chosen THRESH_LO</t>
-        </is>
-      </c>
-      <c r="B82" s="74" t="n"/>
-      <c r="C82" s="121" t="inlineStr">
-        <is>
-          <t>CHANGING THIS INVALIDATES every area figure taken at 80 - re-measure Test A if you adopt a new value</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="120" t="inlineStr">
-        <is>
-          <t>New AREA_MIN_SENSOR</t>
-        </is>
-      </c>
-      <c r="B83" s="74" t="n"/>
-      <c r="C83" s="121" t="inlineStr">
-        <is>
-          <t>~0.7x the area seen at max range AT THE CHOSEN THRESHOLD</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="76" t="inlineStr">
-        <is>
-          <t>HOW TO READ THIS</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="91" t="inlineStr">
-        <is>
-          <t>Lowering THRESH_LO admits more of the blob's dim skirt. Area should GROW and sigma should IMPROVE, because the weighted centroid gets more pixels to interpolate across - and at maximum range that is the whole game.</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="91" t="inlineStr">
-        <is>
-          <t>The limit is NOT the sensor floor. Background max is 4, so even a threshold of 20 sits 5x above it. The limit is FALSE BLOBS from reflections, stray IR and marker glare off nearby surfaces - which is why the False blobs column counts what appears in the whole frame, not just at the marker.</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="91" t="inlineStr">
-        <is>
-          <t>Run the near limit too. A threshold that is ideal at 5 m may pick up reflections at 1 m, where the marker is brightest and glare off the rig is worst. The chosen value has to survive BOTH ends.</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="91" t="inlineStr">
-        <is>
-          <t>AREA_MIN_SENSOR is defined in pixels above THRESH_LO, so it MUST be recomputed if the threshold changes: set it to ~0.7x the area seen at maximum range at the new threshold. It is still carrying its 'STILL NEED to calibrate' comment in kalmanFilter.py at 120.</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="91" t="inlineStr">
-        <is>
-          <t>REFINE_FLOOR is a separate knob and does not have to follow. It sits at 50 against a background of 4, so it has enormous margin - but it is what mode_floor optimised sigma against, so re-sweep it after any THRESH_LO change rather than assuming 50 still wins.</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="91" t="inlineStr">
-        <is>
-          <t>If you adopt a new THRESH_LO, every Sensor area figure measured at 80 becomes incomparable and Test A has to be repeated. Decide this BEFORE the final Test A run, not after.</t>
-        </is>
-      </c>
+      <c r="A66" s="133" t="n"/>
+      <c r="B66" s="85" t="n"/>
+      <c r="C66" s="86" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="D66" s="74" t="n"/>
+      <c r="E66" s="74" t="n"/>
+      <c r="F66" s="72" t="n"/>
+      <c r="G66" s="74" t="n"/>
+      <c r="H66" s="74" t="n"/>
+      <c r="I66" s="74" t="n"/>
+      <c r="J66" s="79" t="n"/>
+      <c r="K66" s="79" t="n"/>
+      <c r="L66" s="126" t="n"/>
+      <c r="M66" s="83" t="n"/>
+      <c r="N66" s="83" t="n"/>
+      <c r="O66" s="84">
+        <f>IF(OR(M66="",N66=""),"",SQRT(0.5*(M66^2+N66^2)))</f>
+        <v/>
+      </c>
+      <c r="P66" s="78" t="n"/>
+      <c r="Q66" s="85">
+        <f>IF(OR(C66="",G66=""),"",G66*C66^2)</f>
+        <v/>
+      </c>
+      <c r="R66" s="81" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10714,7 +10315,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M72"/>
+  <dimension ref="A1:M88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -12247,6 +11848,386 @@
       <c r="A72" s="91" t="inlineStr">
         <is>
           <t>This settles the filter question. Blackout or an 850 nm bandpass is a system requirement for daytime operation, not an optimisation. Mesh shades are not a substitute.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="76" t="inlineStr">
+        <is>
+          <t>F1d - TESTING ARENA, camera in range-test position, 2026-09-09 16:25, OVERCAST, windows on the right</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="30" customHeight="1">
+      <c r="A75" s="77" t="inlineStr">
+        <is>
+          <t>Condition</t>
+        </is>
+      </c>
+      <c r="B75" s="77" t="inlineStr">
+        <is>
+          <t>Exposure req (us)</t>
+        </is>
+      </c>
+      <c r="C75" s="77" t="inlineStr">
+        <is>
+          <t>Exposure act (us)</t>
+        </is>
+      </c>
+      <c r="D75" s="77" t="inlineStr">
+        <is>
+          <t>bg mean</t>
+        </is>
+      </c>
+      <c r="E75" s="77" t="inlineStr">
+        <is>
+          <t>bg SD</t>
+        </is>
+      </c>
+      <c r="F75" s="77" t="inlineStr">
+        <is>
+          <t>bg max</t>
+        </is>
+      </c>
+      <c r="G75" s="77" t="inlineStr">
+        <is>
+          <t>Uniformity (max-min)</t>
+        </is>
+      </c>
+      <c r="H75" s="77" t="inlineStr">
+        <is>
+          <t>Headroom (255-max)</t>
+        </is>
+      </c>
+      <c r="I75" s="77" t="inlineStr">
+        <is>
+          <t>REFINE_FLOOR needed</t>
+        </is>
+      </c>
+      <c r="J75" s="77" t="inlineStr">
+        <is>
+          <t>Usable?</t>
+        </is>
+      </c>
+      <c r="K75" s="77" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="80" t="inlineStr">
+        <is>
+          <t>arena overcast</t>
+        </is>
+      </c>
+      <c r="B76" s="80" t="n">
+        <v>100</v>
+      </c>
+      <c r="C76" s="80" t="n">
+        <v>85</v>
+      </c>
+      <c r="D76" s="80" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E76" s="80" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F76" s="80" t="n">
+        <v>4</v>
+      </c>
+      <c r="G76" s="80" t="n">
+        <v>2</v>
+      </c>
+      <c r="H76" s="80" t="n">
+        <v>251</v>
+      </c>
+      <c r="I76" s="80" t="n">
+        <v>5</v>
+      </c>
+      <c r="J76" s="80" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="80" t="inlineStr">
+        <is>
+          <t>arena overcast</t>
+        </is>
+      </c>
+      <c r="B77" s="80" t="n">
+        <v>500</v>
+      </c>
+      <c r="C77" s="80" t="n">
+        <v>493</v>
+      </c>
+      <c r="D77" s="80" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E77" s="80" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F77" s="80" t="n">
+        <v>4</v>
+      </c>
+      <c r="G77" s="80" t="n">
+        <v>1</v>
+      </c>
+      <c r="H77" s="80" t="n">
+        <v>251</v>
+      </c>
+      <c r="I77" s="80" t="n">
+        <v>5</v>
+      </c>
+      <c r="J77" s="80" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="80" t="inlineStr">
+        <is>
+          <t>arena overcast</t>
+        </is>
+      </c>
+      <c r="B78" s="80" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C78" s="80" t="n">
+        <v>986</v>
+      </c>
+      <c r="D78" s="80" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E78" s="80" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F78" s="80" t="n">
+        <v>5</v>
+      </c>
+      <c r="G78" s="80" t="n">
+        <v>3</v>
+      </c>
+      <c r="H78" s="80" t="n">
+        <v>250</v>
+      </c>
+      <c r="I78" s="80" t="n">
+        <v>5</v>
+      </c>
+      <c r="J78" s="80" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="80" t="inlineStr">
+        <is>
+          <t>arena overcast</t>
+        </is>
+      </c>
+      <c r="B79" s="80" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C79" s="80" t="n">
+        <v>1994</v>
+      </c>
+      <c r="D79" s="80" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E79" s="80" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F79" s="80" t="n">
+        <v>10</v>
+      </c>
+      <c r="G79" s="80" t="n">
+        <v>8</v>
+      </c>
+      <c r="H79" s="80" t="n">
+        <v>245</v>
+      </c>
+      <c r="I79" s="80" t="n">
+        <v>5</v>
+      </c>
+      <c r="J79" s="80" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="80" t="inlineStr">
+        <is>
+          <t>arena overcast</t>
+        </is>
+      </c>
+      <c r="B80" s="80" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C80" s="80" t="n">
+        <v>4997</v>
+      </c>
+      <c r="D80" s="80" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E80" s="80" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F80" s="80" t="n">
+        <v>26</v>
+      </c>
+      <c r="G80" s="80" t="n">
+        <v>24</v>
+      </c>
+      <c r="H80" s="80" t="n">
+        <v>229</v>
+      </c>
+      <c r="I80" s="80" t="n">
+        <v>8</v>
+      </c>
+      <c r="J80" s="80" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="80" t="inlineStr">
+        <is>
+          <t>arena overcast</t>
+        </is>
+      </c>
+      <c r="B81" s="80" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C81" s="80" t="n">
+        <v>9995</v>
+      </c>
+      <c r="D81" s="80" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="E81" s="80" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="F81" s="80" t="n">
+        <v>51</v>
+      </c>
+      <c r="G81" s="80" t="n">
+        <v>49</v>
+      </c>
+      <c r="H81" s="80" t="n">
+        <v>204</v>
+      </c>
+      <c r="I81" s="80" t="n">
+        <v>16</v>
+      </c>
+      <c r="J81" s="80" t="inlineStr">
+        <is>
+          <t>marginal</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="80" t="inlineStr">
+        <is>
+          <t>arena overcast</t>
+        </is>
+      </c>
+      <c r="B82" s="80" t="n">
+        <v>20000</v>
+      </c>
+      <c r="C82" s="80" t="n">
+        <v>19991</v>
+      </c>
+      <c r="D82" s="80" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="E82" s="80" t="n">
+        <v>8</v>
+      </c>
+      <c r="F82" s="80" t="n">
+        <v>98</v>
+      </c>
+      <c r="G82" s="80" t="n">
+        <v>96</v>
+      </c>
+      <c r="H82" s="80" t="n">
+        <v>157</v>
+      </c>
+      <c r="I82" s="80" t="n">
+        <v>31</v>
+      </c>
+      <c r="J82" s="80" t="inlineStr">
+        <is>
+          <t>FLOODED</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="80" t="inlineStr">
+        <is>
+          <t>arena overcast</t>
+        </is>
+      </c>
+      <c r="B83" s="80" t="n">
+        <v>30000</v>
+      </c>
+      <c r="C83" s="80" t="n">
+        <v>29987</v>
+      </c>
+      <c r="D83" s="80" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="E83" s="80" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="F83" s="80" t="n">
+        <v>133</v>
+      </c>
+      <c r="G83" s="80" t="n">
+        <v>131</v>
+      </c>
+      <c r="H83" s="80" t="n">
+        <v>122</v>
+      </c>
+      <c r="I83" s="80" t="n">
+        <v>46</v>
+      </c>
+      <c r="J83" s="80" t="inlineStr">
+        <is>
+          <t>FLOODED</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="122" t="inlineStr">
+        <is>
+          <t>ARENA IS ESSENTIALLY DARK. 44 of 48 cells in an 8x6 map sit at the sensor pedestal (4 counts) at 2 ms. A small cluster right-of-centre reaches 11 - that is the WINDOWS on the right-hand side. Frame mean moves only 3.4 -&gt; 9.8 across a 350x exposure range while the max goes 4 -&gt; 133, so the light is entirely localised.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="91" t="inlineStr">
+        <is>
+          <t>Usable ceiling TODAY: ~14.5 ms anywhere in frame; ~40 ms if the marker avoids the right-hand window cells. That covers every exposure in the study - the longest were XL at 90 deg (16 ms) and Kingbright at 90 deg (18.8 ms), both borderline; everything else has large headroom. NO BLACKOUT NEEDED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="122" t="inlineStr">
+        <is>
+          <t>CONDITIONS: 16:25, OVERCAST, windows right. This is a MILD case, not the worst. Direct sun through those windows will be far brighter - at the desk the night-to-sun difference was 14x at short exposure and total flooding at long. Re-run this ladder before any session in different weather or at a different time of day.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="91" t="inlineStr">
+        <is>
+          <t>Camera was already in its range-test position, so these numbers apply to Test C as measured. They do NOT transfer if the camera is re-aimed.</t>
         </is>
       </c>
     </row>

--- a/LED_characterisation.xlsx
+++ b/LED_characterisation.xlsx
@@ -12,10 +12,11 @@
     <sheet name="A_Bench_run2" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="B_Angle" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="C_Range" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="E_Strobe" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="F_Ambient" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="G_Diffuser" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Summary" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="C_Range_run1" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="E_Strobe" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="F_Ambient" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="G_Diffuser" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Summary" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -289,7 +290,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="140">
+  <cellXfs count="141">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -610,6 +611,7 @@
     </xf>
     <xf numFmtId="0" fontId="21" fillId="2" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -976,7 +978,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M97"/>
+  <dimension ref="A1:M116"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1855,12 +1857,2095 @@
         </is>
       </c>
     </row>
+    <row r="99">
+      <c r="A99" s="6" t="inlineStr">
+        <is>
+          <t>LENS FOCUS - PREREQUISITE FOR INTRINSICS AND EXTRINSICS (added 2026-09-09)</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Each camera's lens focus must be SET, VERIFIED and LOCKED before intrinsics are captured, and re-verified before extrinsics.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>This belongs in the GUI as a formal calibration step, not something done by memory.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102"/>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Why:</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>1. Focus silently corrupts the range test. A near-focused lens makes the blob hollow out and grow with distance, mimicking and partly cancelling 1/d^2. The exposure-vs-distance curve flattens and the apparent detection range is wrong. Not detectable from the data alone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2. Focus corrupts intrinsics. Defocus degrades corner/blob localisation, so distortion coefficients absorb focus error. Changing focus AFTER intrinsics shifts the effective focal length and silently invalidates them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>3. Focus must not move between intrinsics and extrinsics. If the ring is not mechanically locked it will drift when the camera is handled.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>4. All cameras must be focused at the same working distance, or per-camera centroid precision differs and triangulation is weighted wrongly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108"/>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Procedure:</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>a. Place a marker at mid-flight-space distance (~4-5 m for a 9x7x4 m volume).</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>b. Run the focus readout at fixed exposure. BEST FOCUS = MAX peak, MIN area. fill must be &gt; 1 (peaked); fill &lt; 1 means hollow, i.e. defocused.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>c. Lock the ring mechanically (grub screw / paint / tape). Record the locked position.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>d. Capture intrinsics. Do not touch the ring again.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>e. Before extrinsics, re-run (b) VERIFY-ONLY and confirm peak/area match the recorded values. If not, the ring moved - recapture intrinsics.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115"/>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Tooling gotcha: exposure MUST be re-applied AFTER IOCTL_SET_READOUT_WINDOW. Programming the readout window resets it (25000 us came back as 10880 us), which at range drops the marker below THRESH_LO and finds no blob at all.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="FF1F3864"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:U39"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="11" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="11" customWidth="1" min="18" max="18"/>
+    <col width="11" customWidth="1" min="19" max="19"/>
+    <col width="34" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="65" t="inlineStr">
+        <is>
+          <t>TEST G - Diffuser geometry: diameter x wall thickness</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="66" t="inlineStr">
+        <is>
+          <t>Blue on yellow = fill in.  Grey = pulled live from A_Bench (the 0.2 mm rows - do NOT re-measure them here). At these wall thicknesses the cavity barely changes, so wall thickness and LED standoff are effectively decoupled: this is a clean scattering experiment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="66" t="inlineStr">
+        <is>
+          <t>Diffusers are WHITE (pigmented) resin - scattering is volumetric, so wall thickness sets optical depth. Caps are reused across all four LEDs, so LED-to-LED rows share the same physical cap; only the WALL ladder compares different objects. Every take re-seats the cap, which costs ~16% on sigma (measured). Reprint plan: 20 and 25 mm at 0.2 and 0.4 mm ONLY, 4.5 s cure (was 3.5), post-cured together, 2-3 replicate caps per condition - record the cap ID in Notes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="96" t="inlineStr">
+        <is>
+          <t>LED ring radius (mm)</t>
+        </is>
+      </c>
+      <c r="B4" s="72" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C4" s="97" t="inlineStr">
+        <is>
+          <t>centre of the board to each LED. Measured 2026-09-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="96" t="inlineStr">
+        <is>
+          <t>Wall grows</t>
+        </is>
+      </c>
+      <c r="B5" s="78" t="inlineStr">
+        <is>
+          <t>inward</t>
+        </is>
+      </c>
+      <c r="C5" s="97" t="inlineStr">
+        <is>
+          <t>'inward' = outer diameter fixed, cavity shrinks.  'outward' = cavity fixed, marker grows</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="34" customHeight="1">
+      <c r="A7" s="77" t="inlineStr">
+        <is>
+          <t>Pri</t>
+        </is>
+      </c>
+      <c r="B7" s="77" t="inlineStr">
+        <is>
+          <t>LED Type</t>
+        </is>
+      </c>
+      <c r="C7" s="77" t="inlineStr">
+        <is>
+          <t>Diameter
+(mm)</t>
+        </is>
+      </c>
+      <c r="D7" s="77" t="inlineStr">
+        <is>
+          <t>Wall
+(mm)</t>
+        </is>
+      </c>
+      <c r="E7" s="77" t="inlineStr">
+        <is>
+          <t>Cavity
+(mm)</t>
+        </is>
+      </c>
+      <c r="F7" s="77" t="inlineStr">
+        <is>
+          <t>Standoff
+(mm)</t>
+        </is>
+      </c>
+      <c r="G7" s="77" t="inlineStr">
+        <is>
+          <t>Exposure
+(us)</t>
+        </is>
+      </c>
+      <c r="H7" s="77" t="inlineStr">
+        <is>
+          <t>Peak</t>
+        </is>
+      </c>
+      <c r="I7" s="77" t="inlineStr">
+        <is>
+          <t>Sat px</t>
+        </is>
+      </c>
+      <c r="J7" s="77" t="inlineStr">
+        <is>
+          <t>Sensor area
+(px)</t>
+        </is>
+      </c>
+      <c r="K7" s="77" t="inlineStr">
+        <is>
+          <t>blobs</t>
+        </is>
+      </c>
+      <c r="L7" s="77" t="inlineStr">
+        <is>
+          <t>w/h</t>
+        </is>
+      </c>
+      <c r="M7" s="77" t="inlineStr">
+        <is>
+          <t>Fill
+(centre/rim)</t>
+        </is>
+      </c>
+      <c r="N7" s="77" t="inlineStr">
+        <is>
+          <t>Blend
+gate</t>
+        </is>
+      </c>
+      <c r="O7" s="77" t="inlineStr">
+        <is>
+          <t>sigma_u
+(px)</t>
+        </is>
+      </c>
+      <c r="P7" s="77" t="inlineStr">
+        <is>
+          <t>sigma_v
+(px)</t>
+        </is>
+      </c>
+      <c r="Q7" s="77" t="inlineStr">
+        <is>
+          <t>sigma_RMS
+(px)</t>
+        </is>
+      </c>
+      <c r="R7" s="77" t="inlineStr">
+        <is>
+          <t>Exposure
+vs 2 mm</t>
+        </is>
+      </c>
+      <c r="S7" s="77" t="inlineStr">
+        <is>
+          <t>Fill
+vs 2 mm</t>
+        </is>
+      </c>
+      <c r="T7" s="77" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="U7" s="77" t="inlineStr">
+        <is>
+          <t>Lobe
+(0=circular)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="98" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="B8" s="128" t="inlineStr">
+        <is>
+          <t>Vishay</t>
+        </is>
+      </c>
+      <c r="C8" s="100" t="n">
+        <v>20</v>
+      </c>
+      <c r="D8" s="101" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E8" s="101">
+        <f>IF($B$5="inward",C8-2*D8,C8)</f>
+        <v/>
+      </c>
+      <c r="F8" s="101">
+        <f>IF(OR(E8="",$B$4=""),"",E8/2-$B$4)</f>
+        <v/>
+      </c>
+      <c r="G8" s="102">
+        <f>IFERROR(A_Bench!F9,"")</f>
+        <v/>
+      </c>
+      <c r="H8" s="102">
+        <f>IFERROR(A_Bench!G9,"")</f>
+        <v/>
+      </c>
+      <c r="I8" s="103">
+        <f>IFERROR(A_Bench!H9,"")</f>
+        <v/>
+      </c>
+      <c r="J8" s="102">
+        <f>IFERROR(A_Bench!K9,"")</f>
+        <v/>
+      </c>
+      <c r="K8" s="102">
+        <f>IFERROR(A_Bench!M9,"")</f>
+        <v/>
+      </c>
+      <c r="L8" s="104">
+        <f>IFERROR(A_Bench!N9,"")</f>
+        <v/>
+      </c>
+      <c r="M8" s="104">
+        <f>IFERROR(A_Bench!U9,"")</f>
+        <v/>
+      </c>
+      <c r="N8" s="105">
+        <f>IF(OR(K8="",L8="",M8=""),"",IF(AND(K8=1,L8&gt;=0.9,L8&lt;=1.1,M8&gt;=0.70),"pass","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="O8" s="106">
+        <f>IFERROR(A_Bench!P9,"")</f>
+        <v/>
+      </c>
+      <c r="P8" s="106">
+        <f>IFERROR(A_Bench!Q9,"")</f>
+        <v/>
+      </c>
+      <c r="Q8" s="107">
+        <f>IF(OR(O8="",P8=""),"",SQRT(0.5*(O8^2+P8^2)))</f>
+        <v/>
+      </c>
+      <c r="R8" s="108">
+        <f>IF(OR(G8="",$G$8="",$G$8=0),"",G8/$G$8)</f>
+        <v/>
+      </c>
+      <c r="S8" s="109">
+        <f>IF(OR(M8="",$M$8=""),"",M8-$M$8)</f>
+        <v/>
+      </c>
+      <c r="T8" s="110" t="n"/>
+      <c r="U8" s="125" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="80" t="n">
+        <v>1</v>
+      </c>
+      <c r="B9" s="133" t="inlineStr">
+        <is>
+          <t>Vishay</t>
+        </is>
+      </c>
+      <c r="C9" s="85" t="n">
+        <v>20</v>
+      </c>
+      <c r="D9" s="86" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E9" s="86">
+        <f>IF($B$5="inward",C9-2*D9,C9)</f>
+        <v/>
+      </c>
+      <c r="F9" s="86">
+        <f>IF(OR(E9="",$B$4=""),"",E9/2-$B$4)</f>
+        <v/>
+      </c>
+      <c r="G9" s="74" t="n">
+        <v>413</v>
+      </c>
+      <c r="H9" s="74" t="n">
+        <v>212.3</v>
+      </c>
+      <c r="I9" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="74" t="n">
+        <v>606</v>
+      </c>
+      <c r="K9" s="74" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" s="79" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="M9" s="79" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="N9" s="80">
+        <f>IF(OR(K9="",L9="",M9=""),"",IF(AND(K9=1,L9&gt;=0.9,L9&lt;=1.1,M9&gt;=0.70),"pass","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="O9" s="83" t="n">
+        <v>0.0283</v>
+      </c>
+      <c r="P9" s="83" t="n">
+        <v>0.0357</v>
+      </c>
+      <c r="Q9" s="84">
+        <f>IF(OR(O9="",P9=""),"",SQRT(0.5*(O9^2+P9^2)))</f>
+        <v/>
+      </c>
+      <c r="R9" s="75">
+        <f>IF(OR(G9="",$G$8="",$G$8=0),"",G9/$G$8)</f>
+        <v/>
+      </c>
+      <c r="S9" s="111">
+        <f>IF(OR(M9="",$M$8=""),"",M9-$M$8)</f>
+        <v/>
+      </c>
+      <c r="T9" s="81" t="inlineStr">
+        <is>
+          <t>cap 1. BIGGEST thickness gain of any LED: fill +0.10 (0.53-&gt;0.63) and lobe 0.120-&gt;0.076, so the extra wall largely merged the four lobes. Thickness helps in inverse proportion to beam angle: Vishay +0.10, Kingbright +0.06, Everlight +0.03, XL +0.03.  flux 312</t>
+        </is>
+      </c>
+      <c r="U9" s="126" t="n">
+        <v>0.076</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="80" t="inlineStr">
+        <is>
+          <t>drop</t>
+        </is>
+      </c>
+      <c r="B10" s="133" t="inlineStr">
+        <is>
+          <t>Vishay</t>
+        </is>
+      </c>
+      <c r="C10" s="85" t="n">
+        <v>20</v>
+      </c>
+      <c r="D10" s="86" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E10" s="86">
+        <f>IF($B$5="inward",C10-2*D10,C10)</f>
+        <v/>
+      </c>
+      <c r="F10" s="86">
+        <f>IF(OR(E10="",$B$4=""),"",E10/2-$B$4)</f>
+        <v/>
+      </c>
+      <c r="G10" s="74" t="n"/>
+      <c r="H10" s="74" t="n"/>
+      <c r="I10" s="72" t="n"/>
+      <c r="J10" s="74" t="n"/>
+      <c r="K10" s="74" t="n"/>
+      <c r="L10" s="79" t="n"/>
+      <c r="M10" s="79" t="n"/>
+      <c r="N10" s="80">
+        <f>IF(OR(K10="",L10="",M10=""),"",IF(AND(K10=1,L10&gt;=0.9,L10&lt;=1.1,M10&gt;=0.70),"pass","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="O10" s="83" t="n"/>
+      <c r="P10" s="83" t="n"/>
+      <c r="Q10" s="84">
+        <f>IF(OR(O10="",P10=""),"",SQRT(0.5*(O10^2+P10^2)))</f>
+        <v/>
+      </c>
+      <c r="R10" s="75">
+        <f>IF(OR(G10="",$G$8="",$G$8=0),"",G10/$G$8)</f>
+        <v/>
+      </c>
+      <c r="S10" s="111">
+        <f>IF(OR(M10="",$M$8=""),"",M10-$M$8)</f>
+        <v/>
+      </c>
+      <c r="T10" s="123" t="inlineStr">
+        <is>
+          <t>DROPPED 2026-09-04. 0.5 mm measured worse than 0.4 mm at identical transmitted flux, i.e. cap variation not thickness. Ladder reduced to 0.2 / 0.4 mm with REPLICATE caps instead.</t>
+        </is>
+      </c>
+      <c r="U10" s="126" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="112" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="B11" s="133" t="inlineStr">
+        <is>
+          <t>Vishay</t>
+        </is>
+      </c>
+      <c r="C11" s="85" t="n">
+        <v>25</v>
+      </c>
+      <c r="D11" s="86" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E11" s="86">
+        <f>IF($B$5="inward",C11-2*D11,C11)</f>
+        <v/>
+      </c>
+      <c r="F11" s="86">
+        <f>IF(OR(E11="",$B$4=""),"",E11/2-$B$4)</f>
+        <v/>
+      </c>
+      <c r="G11" s="113">
+        <f>IFERROR(A_Bench!F13,"")</f>
+        <v/>
+      </c>
+      <c r="H11" s="113">
+        <f>IFERROR(A_Bench!G13,"")</f>
+        <v/>
+      </c>
+      <c r="I11" s="114">
+        <f>IFERROR(A_Bench!H13,"")</f>
+        <v/>
+      </c>
+      <c r="J11" s="113">
+        <f>IFERROR(A_Bench!K13,"")</f>
+        <v/>
+      </c>
+      <c r="K11" s="113">
+        <f>IFERROR(A_Bench!M13,"")</f>
+        <v/>
+      </c>
+      <c r="L11" s="115">
+        <f>IFERROR(A_Bench!N13,"")</f>
+        <v/>
+      </c>
+      <c r="M11" s="115">
+        <f>IFERROR(A_Bench!U13,"")</f>
+        <v/>
+      </c>
+      <c r="N11" s="80">
+        <f>IF(OR(K11="",L11="",M11=""),"",IF(AND(K11=1,L11&gt;=0.9,L11&lt;=1.1,M11&gt;=0.70),"pass","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="O11" s="116">
+        <f>IFERROR(A_Bench!P13,"")</f>
+        <v/>
+      </c>
+      <c r="P11" s="116">
+        <f>IFERROR(A_Bench!Q13,"")</f>
+        <v/>
+      </c>
+      <c r="Q11" s="84">
+        <f>IF(OR(O11="",P11=""),"",SQRT(0.5*(O11^2+P11^2)))</f>
+        <v/>
+      </c>
+      <c r="R11" s="75">
+        <f>IF(OR(G11="",$G$11="",$G$11=0),"",G11/$G$11)</f>
+        <v/>
+      </c>
+      <c r="S11" s="111">
+        <f>IF(OR(M11="",$M$11=""),"",M11-$M$11)</f>
+        <v/>
+      </c>
+      <c r="T11" s="81" t="n"/>
+      <c r="U11" s="127" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="80" t="n">
+        <v>1</v>
+      </c>
+      <c r="B12" s="133" t="inlineStr">
+        <is>
+          <t>Vishay</t>
+        </is>
+      </c>
+      <c r="C12" s="85" t="n">
+        <v>25</v>
+      </c>
+      <c r="D12" s="86" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E12" s="86">
+        <f>IF($B$5="inward",C12-2*D12,C12)</f>
+        <v/>
+      </c>
+      <c r="F12" s="86">
+        <f>IF(OR(E12="",$B$4=""),"",E12/2-$B$4)</f>
+        <v/>
+      </c>
+      <c r="G12" s="74" t="n">
+        <v>602</v>
+      </c>
+      <c r="H12" s="74" t="n">
+        <v>209.9</v>
+      </c>
+      <c r="I12" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="74" t="n">
+        <v>751</v>
+      </c>
+      <c r="K12" s="74" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" s="79" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="M12" s="79" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="N12" s="80">
+        <f>IF(OR(K12="",L12="",M12=""),"",IF(AND(K12=1,L12&gt;=0.9,L12&lt;=1.1,M12&gt;=0.70),"pass","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="O12" s="83" t="n">
+        <v>0.0198</v>
+      </c>
+      <c r="P12" s="83" t="n">
+        <v>0.0273</v>
+      </c>
+      <c r="Q12" s="84">
+        <f>IF(OR(O12="",P12=""),"",SQRT(0.5*(O12^2+P12^2)))</f>
+        <v/>
+      </c>
+      <c r="R12" s="75">
+        <f>IF(OR(G12="",$G$11="",$G$11=0),"",G12/$G$11)</f>
+        <v/>
+      </c>
+      <c r="S12" s="111">
+        <f>IF(OR(M12="",$M$11=""),"",M12-$M$11)</f>
+        <v/>
+      </c>
+      <c r="T12" s="81" t="inlineStr">
+        <is>
+          <t>MEAN OF 4 REPLICATE CAPS (575/485/575/772 us). Cap-to-cap: exposure CV 20%, area 2.7%, fill 2.5%, lobe 4%, sigma 11%. So fill = 0.74 +/- 0.02 and sigma = 0.0240 +/- 0.0027; fill differences under ~0.05 and sigma differences under ~25% are not significant.  flux 262</t>
+        </is>
+      </c>
+      <c r="U12" s="126" t="n">
+        <v>0.062</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="80" t="inlineStr">
+        <is>
+          <t>drop</t>
+        </is>
+      </c>
+      <c r="B13" s="133" t="inlineStr">
+        <is>
+          <t>Vishay</t>
+        </is>
+      </c>
+      <c r="C13" s="85" t="n">
+        <v>25</v>
+      </c>
+      <c r="D13" s="86" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E13" s="86">
+        <f>IF($B$5="inward",C13-2*D13,C13)</f>
+        <v/>
+      </c>
+      <c r="F13" s="86">
+        <f>IF(OR(E13="",$B$4=""),"",E13/2-$B$4)</f>
+        <v/>
+      </c>
+      <c r="G13" s="74" t="n"/>
+      <c r="H13" s="74" t="n"/>
+      <c r="I13" s="72" t="n"/>
+      <c r="J13" s="74" t="n"/>
+      <c r="K13" s="74" t="n"/>
+      <c r="L13" s="79" t="n"/>
+      <c r="M13" s="79" t="n"/>
+      <c r="N13" s="80">
+        <f>IF(OR(K13="",L13="",M13=""),"",IF(AND(K13=1,L13&gt;=0.9,L13&lt;=1.1,M13&gt;=0.70),"pass","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="O13" s="83" t="n"/>
+      <c r="P13" s="83" t="n"/>
+      <c r="Q13" s="84">
+        <f>IF(OR(O13="",P13=""),"",SQRT(0.5*(O13^2+P13^2)))</f>
+        <v/>
+      </c>
+      <c r="R13" s="75">
+        <f>IF(OR(G13="",$G$11="",$G$11=0),"",G13/$G$11)</f>
+        <v/>
+      </c>
+      <c r="S13" s="111">
+        <f>IF(OR(M13="",$M$11=""),"",M13-$M$11)</f>
+        <v/>
+      </c>
+      <c r="T13" s="123" t="inlineStr">
+        <is>
+          <t>DROPPED 2026-09-04. 0.5 mm measured worse than 0.4 mm at identical transmitted flux, i.e. cap variation not thickness. Ladder reduced to 0.2 / 0.4 mm with REPLICATE caps instead.</t>
+        </is>
+      </c>
+      <c r="U13" s="126" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="98" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="B14" s="128" t="inlineStr">
+        <is>
+          <t>Kingbright</t>
+        </is>
+      </c>
+      <c r="C14" s="100" t="n">
+        <v>20</v>
+      </c>
+      <c r="D14" s="101" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E14" s="101">
+        <f>IF($B$5="inward",C14-2*D14,C14)</f>
+        <v/>
+      </c>
+      <c r="F14" s="101">
+        <f>IF(OR(E14="",$B$4=""),"",E14/2-$B$4)</f>
+        <v/>
+      </c>
+      <c r="G14" s="102">
+        <f>IFERROR(A_Bench!F12,"")</f>
+        <v/>
+      </c>
+      <c r="H14" s="102">
+        <f>IFERROR(A_Bench!G12,"")</f>
+        <v/>
+      </c>
+      <c r="I14" s="103">
+        <f>IFERROR(A_Bench!H12,"")</f>
+        <v/>
+      </c>
+      <c r="J14" s="102">
+        <f>IFERROR(A_Bench!K12,"")</f>
+        <v/>
+      </c>
+      <c r="K14" s="102">
+        <f>IFERROR(A_Bench!M12,"")</f>
+        <v/>
+      </c>
+      <c r="L14" s="104">
+        <f>IFERROR(A_Bench!N12,"")</f>
+        <v/>
+      </c>
+      <c r="M14" s="104">
+        <f>IFERROR(A_Bench!U12,"")</f>
+        <v/>
+      </c>
+      <c r="N14" s="105">
+        <f>IF(OR(K14="",L14="",M14=""),"",IF(AND(K14=1,L14&gt;=0.9,L14&lt;=1.1,M14&gt;=0.70),"pass","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="O14" s="106">
+        <f>IFERROR(A_Bench!P12,"")</f>
+        <v/>
+      </c>
+      <c r="P14" s="106">
+        <f>IFERROR(A_Bench!Q12,"")</f>
+        <v/>
+      </c>
+      <c r="Q14" s="107">
+        <f>IF(OR(O14="",P14=""),"",SQRT(0.5*(O14^2+P14^2)))</f>
+        <v/>
+      </c>
+      <c r="R14" s="108">
+        <f>IF(OR(G14="",$G$14="",$G$14=0),"",G14/$G$14)</f>
+        <v/>
+      </c>
+      <c r="S14" s="109">
+        <f>IF(OR(M14="",$M$14=""),"",M14-$M$14)</f>
+        <v/>
+      </c>
+      <c r="T14" s="110" t="n"/>
+      <c r="U14" s="125" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="80" t="n">
+        <v>1</v>
+      </c>
+      <c r="B15" s="133" t="inlineStr">
+        <is>
+          <t>Kingbright</t>
+        </is>
+      </c>
+      <c r="C15" s="85" t="n">
+        <v>20</v>
+      </c>
+      <c r="D15" s="86" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E15" s="86">
+        <f>IF($B$5="inward",C15-2*D15,C15)</f>
+        <v/>
+      </c>
+      <c r="F15" s="86">
+        <f>IF(OR(E15="",$B$4=""),"",E15/2-$B$4)</f>
+        <v/>
+      </c>
+      <c r="G15" s="74" t="n">
+        <v>1060</v>
+      </c>
+      <c r="H15" s="74" t="n">
+        <v>216.6</v>
+      </c>
+      <c r="I15" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="74" t="n">
+        <v>694</v>
+      </c>
+      <c r="K15" s="74" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" s="79" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="M15" s="79" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="N15" s="80">
+        <f>IF(OR(K15="",L15="",M15=""),"",IF(AND(K15=1,L15&gt;=0.9,L15&lt;=1.1,M15&gt;=0.70),"pass","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="O15" s="83" t="n">
+        <v>0.0243</v>
+      </c>
+      <c r="P15" s="83" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="Q15" s="84">
+        <f>IF(OR(O15="",P15=""),"",SQRT(0.5*(O15^2+P15^2)))</f>
+        <v/>
+      </c>
+      <c r="R15" s="75">
+        <f>IF(OR(G15="",$G$14="",$G$14=0),"",G15/$G$14)</f>
+        <v/>
+      </c>
+      <c r="S15" s="111">
+        <f>IF(OR(M15="",$M$14=""),"",M15-$M$14)</f>
+        <v/>
+      </c>
+      <c r="T15" s="81" t="inlineStr">
+        <is>
+          <t>cap 1, re-seat #2 (first: 1168us area730 fill0.66 sigma0.0243). Repeats to 5% area, 0.00 fill, 6% sigma.  flux 142</t>
+        </is>
+      </c>
+      <c r="U15" s="126" t="n">
+        <v>0.075</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="80" t="inlineStr">
+        <is>
+          <t>drop</t>
+        </is>
+      </c>
+      <c r="B16" s="133" t="inlineStr">
+        <is>
+          <t>Kingbright</t>
+        </is>
+      </c>
+      <c r="C16" s="85" t="n">
+        <v>20</v>
+      </c>
+      <c r="D16" s="86" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E16" s="86">
+        <f>IF($B$5="inward",C16-2*D16,C16)</f>
+        <v/>
+      </c>
+      <c r="F16" s="86">
+        <f>IF(OR(E16="",$B$4=""),"",E16/2-$B$4)</f>
+        <v/>
+      </c>
+      <c r="G16" s="74" t="n">
+        <v>1042</v>
+      </c>
+      <c r="H16" s="74" t="n">
+        <v>201.8</v>
+      </c>
+      <c r="I16" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="74" t="n">
+        <v>608</v>
+      </c>
+      <c r="K16" s="74" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" s="79" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="M16" s="79" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="N16" s="80">
+        <f>IF(OR(K16="",L16="",M16=""),"",IF(AND(K16=1,L16&gt;=0.9,L16&lt;=1.1,M16&gt;=0.70),"pass","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="O16" s="83" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="P16" s="83" t="n">
+        <v>0.0334</v>
+      </c>
+      <c r="Q16" s="84">
+        <f>IF(OR(O16="",P16=""),"",SQRT(0.5*(O16^2+P16^2)))</f>
+        <v/>
+      </c>
+      <c r="R16" s="75">
+        <f>IF(OR(G16="",$G$14="",$G$14=0),"",G16/$G$14)</f>
+        <v/>
+      </c>
+      <c r="S16" s="111">
+        <f>IF(OR(M16="",$M$14=""),"",M16-$M$14)</f>
+        <v/>
+      </c>
+      <c r="T16" s="123" t="inlineStr">
+        <is>
+          <t>DROPPED 2026-09-04. 0.5 mm measured worse than 0.4 mm at identical transmitted flux, i.e. cap variation not thickness. Ladder reduced to 0.2 / 0.4 mm with REPLICATE caps instead.</t>
+        </is>
+      </c>
+      <c r="U16" s="126" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="112" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="B17" s="133" t="inlineStr">
+        <is>
+          <t>Kingbright</t>
+        </is>
+      </c>
+      <c r="C17" s="85" t="n">
+        <v>25</v>
+      </c>
+      <c r="D17" s="86" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E17" s="86">
+        <f>IF($B$5="inward",C17-2*D17,C17)</f>
+        <v/>
+      </c>
+      <c r="F17" s="86">
+        <f>IF(OR(E17="",$B$4=""),"",E17/2-$B$4)</f>
+        <v/>
+      </c>
+      <c r="G17" s="113">
+        <f>IFERROR(A_Bench!F16,"")</f>
+        <v/>
+      </c>
+      <c r="H17" s="113">
+        <f>IFERROR(A_Bench!G16,"")</f>
+        <v/>
+      </c>
+      <c r="I17" s="114">
+        <f>IFERROR(A_Bench!H16,"")</f>
+        <v/>
+      </c>
+      <c r="J17" s="113">
+        <f>IFERROR(A_Bench!K16,"")</f>
+        <v/>
+      </c>
+      <c r="K17" s="113">
+        <f>IFERROR(A_Bench!M16,"")</f>
+        <v/>
+      </c>
+      <c r="L17" s="115">
+        <f>IFERROR(A_Bench!N16,"")</f>
+        <v/>
+      </c>
+      <c r="M17" s="115">
+        <f>IFERROR(A_Bench!U16,"")</f>
+        <v/>
+      </c>
+      <c r="N17" s="80">
+        <f>IF(OR(K17="",L17="",M17=""),"",IF(AND(K17=1,L17&gt;=0.9,L17&lt;=1.1,M17&gt;=0.70),"pass","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="O17" s="116">
+        <f>IFERROR(A_Bench!P16,"")</f>
+        <v/>
+      </c>
+      <c r="P17" s="116">
+        <f>IFERROR(A_Bench!Q16,"")</f>
+        <v/>
+      </c>
+      <c r="Q17" s="84">
+        <f>IF(OR(O17="",P17=""),"",SQRT(0.5*(O17^2+P17^2)))</f>
+        <v/>
+      </c>
+      <c r="R17" s="75">
+        <f>IF(OR(G17="",$G$17="",$G$17=0),"",G17/$G$17)</f>
+        <v/>
+      </c>
+      <c r="S17" s="111">
+        <f>IF(OR(M17="",$M$17=""),"",M17-$M$17)</f>
+        <v/>
+      </c>
+      <c r="T17" s="81" t="n"/>
+      <c r="U17" s="127" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="80" t="n">
+        <v>1</v>
+      </c>
+      <c r="B18" s="133" t="inlineStr">
+        <is>
+          <t>Kingbright</t>
+        </is>
+      </c>
+      <c r="C18" s="85" t="n">
+        <v>25</v>
+      </c>
+      <c r="D18" s="86" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E18" s="86">
+        <f>IF($B$5="inward",C18-2*D18,C18)</f>
+        <v/>
+      </c>
+      <c r="F18" s="86">
+        <f>IF(OR(E18="",$B$4=""),"",E18/2-$B$4)</f>
+        <v/>
+      </c>
+      <c r="G18" s="74" t="n">
+        <v>1078</v>
+      </c>
+      <c r="H18" s="74" t="n">
+        <v>210.8</v>
+      </c>
+      <c r="I18" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="74" t="n">
+        <v>697</v>
+      </c>
+      <c r="K18" s="74" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" s="79" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M18" s="79" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="N18" s="80">
+        <f>IF(OR(K18="",L18="",M18=""),"",IF(AND(K18=1,L18&gt;=0.9,L18&lt;=1.1,M18&gt;=0.70),"pass","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="O18" s="83" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="P18" s="83" t="n">
+        <v>0.0215</v>
+      </c>
+      <c r="Q18" s="84">
+        <f>IF(OR(O18="",P18=""),"",SQRT(0.5*(O18^2+P18^2)))</f>
+        <v/>
+      </c>
+      <c r="R18" s="75">
+        <f>IF(OR(G18="",$G$17="",$G$17=0),"",G18/$G$17)</f>
+        <v/>
+      </c>
+      <c r="S18" s="111">
+        <f>IF(OR(M18="",$M$17=""),"",M18-$M$17)</f>
+        <v/>
+      </c>
+      <c r="T18" s="81" t="inlineStr">
+        <is>
+          <t>cap 1, re-seat #2 (first: 1078us area694 fill0.67 sigma0.0286). Area and fill identical; sigma moved 28% - the widest of the four re-seats today (8/6/5/28%), so sigma repeatability is ~10-15%, not the 5% the tightest suggested.  flux 136</t>
+        </is>
+      </c>
+      <c r="U18" s="126" t="n">
+        <v>0.07199999999999999</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="80" t="inlineStr">
+        <is>
+          <t>drop</t>
+        </is>
+      </c>
+      <c r="B19" s="133" t="inlineStr">
+        <is>
+          <t>Kingbright</t>
+        </is>
+      </c>
+      <c r="C19" s="85" t="n">
+        <v>25</v>
+      </c>
+      <c r="D19" s="86" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E19" s="86">
+        <f>IF($B$5="inward",C19-2*D19,C19)</f>
+        <v/>
+      </c>
+      <c r="F19" s="86">
+        <f>IF(OR(E19="",$B$4=""),"",E19/2-$B$4)</f>
+        <v/>
+      </c>
+      <c r="G19" s="74" t="n"/>
+      <c r="H19" s="74" t="n"/>
+      <c r="I19" s="72" t="n"/>
+      <c r="J19" s="74" t="n"/>
+      <c r="K19" s="74" t="n"/>
+      <c r="L19" s="79" t="n"/>
+      <c r="M19" s="79" t="n"/>
+      <c r="N19" s="80">
+        <f>IF(OR(K19="",L19="",M19=""),"",IF(AND(K19=1,L19&gt;=0.9,L19&lt;=1.1,M19&gt;=0.70),"pass","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="O19" s="83" t="n"/>
+      <c r="P19" s="83" t="n"/>
+      <c r="Q19" s="84">
+        <f>IF(OR(O19="",P19=""),"",SQRT(0.5*(O19^2+P19^2)))</f>
+        <v/>
+      </c>
+      <c r="R19" s="75">
+        <f>IF(OR(G19="",$G$17="",$G$17=0),"",G19/$G$17)</f>
+        <v/>
+      </c>
+      <c r="S19" s="111">
+        <f>IF(OR(M19="",$M$17=""),"",M19-$M$17)</f>
+        <v/>
+      </c>
+      <c r="T19" s="123" t="inlineStr">
+        <is>
+          <t>DROPPED 2026-09-04. 0.5 mm measured worse than 0.4 mm at identical transmitted flux, i.e. cap variation not thickness. Ladder reduced to 0.2 / 0.4 mm with REPLICATE caps instead.</t>
+        </is>
+      </c>
+      <c r="U19" s="126" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="98" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="B20" s="128" t="inlineStr">
+        <is>
+          <t>Everlight</t>
+        </is>
+      </c>
+      <c r="C20" s="100" t="n">
+        <v>20</v>
+      </c>
+      <c r="D20" s="101" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E20" s="101">
+        <f>IF($B$5="inward",C20-2*D20,C20)</f>
+        <v/>
+      </c>
+      <c r="F20" s="101">
+        <f>IF(OR(E20="",$B$4=""),"",E20/2-$B$4)</f>
+        <v/>
+      </c>
+      <c r="G20" s="102">
+        <f>IFERROR(A_Bench!F10,"")</f>
+        <v/>
+      </c>
+      <c r="H20" s="102">
+        <f>IFERROR(A_Bench!G10,"")</f>
+        <v/>
+      </c>
+      <c r="I20" s="103">
+        <f>IFERROR(A_Bench!H10,"")</f>
+        <v/>
+      </c>
+      <c r="J20" s="102">
+        <f>IFERROR(A_Bench!K10,"")</f>
+        <v/>
+      </c>
+      <c r="K20" s="102">
+        <f>IFERROR(A_Bench!M10,"")</f>
+        <v/>
+      </c>
+      <c r="L20" s="104">
+        <f>IFERROR(A_Bench!N10,"")</f>
+        <v/>
+      </c>
+      <c r="M20" s="104">
+        <f>IFERROR(A_Bench!U10,"")</f>
+        <v/>
+      </c>
+      <c r="N20" s="105">
+        <f>IF(OR(K20="",L20="",M20=""),"",IF(AND(K20=1,L20&gt;=0.9,L20&lt;=1.1,M20&gt;=0.70),"pass","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="O20" s="106">
+        <f>IFERROR(A_Bench!P10,"")</f>
+        <v/>
+      </c>
+      <c r="P20" s="106">
+        <f>IFERROR(A_Bench!Q10,"")</f>
+        <v/>
+      </c>
+      <c r="Q20" s="107">
+        <f>IF(OR(O20="",P20=""),"",SQRT(0.5*(O20^2+P20^2)))</f>
+        <v/>
+      </c>
+      <c r="R20" s="108">
+        <f>IF(OR(G20="",$G$20="",$G$20=0),"",G20/$G$20)</f>
+        <v/>
+      </c>
+      <c r="S20" s="109">
+        <f>IF(OR(M20="",$M$20=""),"",M20-$M$20)</f>
+        <v/>
+      </c>
+      <c r="T20" s="110" t="n"/>
+      <c r="U20" s="125" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="80" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="133" t="inlineStr">
+        <is>
+          <t>Everlight</t>
+        </is>
+      </c>
+      <c r="C21" s="85" t="n">
+        <v>20</v>
+      </c>
+      <c r="D21" s="86" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E21" s="86">
+        <f>IF($B$5="inward",C21-2*D21,C21)</f>
+        <v/>
+      </c>
+      <c r="F21" s="86">
+        <f>IF(OR(E21="",$B$4=""),"",E21/2-$B$4)</f>
+        <v/>
+      </c>
+      <c r="G21" s="74" t="n">
+        <v>3235</v>
+      </c>
+      <c r="H21" s="74" t="n">
+        <v>210.2</v>
+      </c>
+      <c r="I21" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="74" t="n">
+        <v>814</v>
+      </c>
+      <c r="K21" s="74" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" s="79" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="M21" s="79" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N21" s="80">
+        <f>IF(OR(K21="",L21="",M21=""),"",IF(AND(K21=1,L21&gt;=0.9,L21&lt;=1.1,M21&gt;=0.70),"pass","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="O21" s="83" t="n">
+        <v>0.0163</v>
+      </c>
+      <c r="P21" s="83" t="n">
+        <v>0.0202</v>
+      </c>
+      <c r="Q21" s="84">
+        <f>IF(OR(O21="",P21=""),"",SQRT(0.5*(O21^2+P21^2)))</f>
+        <v/>
+      </c>
+      <c r="R21" s="75">
+        <f>IF(OR(G21="",$G$20="",$G$20=0),"",G21/$G$20)</f>
+        <v/>
+      </c>
+      <c r="S21" s="111">
+        <f>IF(OR(M21="",$M$20=""),"",M21-$M$20)</f>
+        <v/>
+      </c>
+      <c r="T21" s="81" t="inlineStr">
+        <is>
+          <t>cap 1. Lowest sigma of the session (0.0184), though statistically tied with XL 25/0.2 (0.0187) given ~10-15% sigma repeatability. Thickness buys +0.03 fill for 1.42x exposure.  flux 53</t>
+        </is>
+      </c>
+      <c r="U21" s="126" t="n">
+        <v>0.062</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="80" t="inlineStr">
+        <is>
+          <t>drop</t>
+        </is>
+      </c>
+      <c r="B22" s="133" t="inlineStr">
+        <is>
+          <t>Everlight</t>
+        </is>
+      </c>
+      <c r="C22" s="85" t="n">
+        <v>20</v>
+      </c>
+      <c r="D22" s="86" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E22" s="86">
+        <f>IF($B$5="inward",C22-2*D22,C22)</f>
+        <v/>
+      </c>
+      <c r="F22" s="86">
+        <f>IF(OR(E22="",$B$4=""),"",E22/2-$B$4)</f>
+        <v/>
+      </c>
+      <c r="G22" s="74" t="n"/>
+      <c r="H22" s="74" t="n"/>
+      <c r="I22" s="72" t="n"/>
+      <c r="J22" s="74" t="n"/>
+      <c r="K22" s="74" t="n"/>
+      <c r="L22" s="79" t="n"/>
+      <c r="M22" s="79" t="n"/>
+      <c r="N22" s="80">
+        <f>IF(OR(K22="",L22="",M22=""),"",IF(AND(K22=1,L22&gt;=0.9,L22&lt;=1.1,M22&gt;=0.70),"pass","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="O22" s="83" t="n"/>
+      <c r="P22" s="83" t="n"/>
+      <c r="Q22" s="84">
+        <f>IF(OR(O22="",P22=""),"",SQRT(0.5*(O22^2+P22^2)))</f>
+        <v/>
+      </c>
+      <c r="R22" s="75">
+        <f>IF(OR(G22="",$G$20="",$G$20=0),"",G22/$G$20)</f>
+        <v/>
+      </c>
+      <c r="S22" s="111">
+        <f>IF(OR(M22="",$M$20=""),"",M22-$M$20)</f>
+        <v/>
+      </c>
+      <c r="T22" s="123" t="inlineStr">
+        <is>
+          <t>DROPPED 2026-09-04. 0.5 mm measured worse than 0.4 mm at identical transmitted flux, i.e. cap variation not thickness. Ladder reduced to 0.2 / 0.4 mm with REPLICATE caps instead.</t>
+        </is>
+      </c>
+      <c r="U22" s="126" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="112" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="B23" s="133" t="inlineStr">
+        <is>
+          <t>Everlight</t>
+        </is>
+      </c>
+      <c r="C23" s="85" t="n">
+        <v>25</v>
+      </c>
+      <c r="D23" s="86" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E23" s="86">
+        <f>IF($B$5="inward",C23-2*D23,C23)</f>
+        <v/>
+      </c>
+      <c r="F23" s="86">
+        <f>IF(OR(E23="",$B$4=""),"",E23/2-$B$4)</f>
+        <v/>
+      </c>
+      <c r="G23" s="113">
+        <f>IFERROR(A_Bench!F14,"")</f>
+        <v/>
+      </c>
+      <c r="H23" s="113">
+        <f>IFERROR(A_Bench!G14,"")</f>
+        <v/>
+      </c>
+      <c r="I23" s="114">
+        <f>IFERROR(A_Bench!H14,"")</f>
+        <v/>
+      </c>
+      <c r="J23" s="113">
+        <f>IFERROR(A_Bench!K14,"")</f>
+        <v/>
+      </c>
+      <c r="K23" s="113">
+        <f>IFERROR(A_Bench!M14,"")</f>
+        <v/>
+      </c>
+      <c r="L23" s="115">
+        <f>IFERROR(A_Bench!N14,"")</f>
+        <v/>
+      </c>
+      <c r="M23" s="115">
+        <f>IFERROR(A_Bench!U14,"")</f>
+        <v/>
+      </c>
+      <c r="N23" s="80">
+        <f>IF(OR(K23="",L23="",M23=""),"",IF(AND(K23=1,L23&gt;=0.9,L23&lt;=1.1,M23&gt;=0.70),"pass","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="O23" s="116">
+        <f>IFERROR(A_Bench!P14,"")</f>
+        <v/>
+      </c>
+      <c r="P23" s="116">
+        <f>IFERROR(A_Bench!Q14,"")</f>
+        <v/>
+      </c>
+      <c r="Q23" s="84">
+        <f>IF(OR(O23="",P23=""),"",SQRT(0.5*(O23^2+P23^2)))</f>
+        <v/>
+      </c>
+      <c r="R23" s="75">
+        <f>IF(OR(G23="",$G$23="",$G$23=0),"",G23/$G$23)</f>
+        <v/>
+      </c>
+      <c r="S23" s="111">
+        <f>IF(OR(M23="",$M$23=""),"",M23-$M$23)</f>
+        <v/>
+      </c>
+      <c r="T23" s="81" t="n"/>
+      <c r="U23" s="127" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="80" t="n">
+        <v>2</v>
+      </c>
+      <c r="B24" s="133" t="inlineStr">
+        <is>
+          <t>Everlight</t>
+        </is>
+      </c>
+      <c r="C24" s="85" t="n">
+        <v>25</v>
+      </c>
+      <c r="D24" s="86" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E24" s="86">
+        <f>IF($B$5="inward",C24-2*D24,C24)</f>
+        <v/>
+      </c>
+      <c r="F24" s="86">
+        <f>IF(OR(E24="",$B$4=""),"",E24/2-$B$4)</f>
+        <v/>
+      </c>
+      <c r="G24" s="74" t="n">
+        <v>3756</v>
+      </c>
+      <c r="H24" s="74" t="n">
+        <v>215.4</v>
+      </c>
+      <c r="I24" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="74" t="n">
+        <v>910</v>
+      </c>
+      <c r="K24" s="74" t="n">
+        <v>1</v>
+      </c>
+      <c r="L24" s="79" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="M24" s="79" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="N24" s="80">
+        <f>IF(OR(K24="",L24="",M24=""),"",IF(AND(K24=1,L24&gt;=0.9,L24&lt;=1.1,M24&gt;=0.70),"pass","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="O24" s="83" t="n">
+        <v>0.0176</v>
+      </c>
+      <c r="P24" s="83" t="n">
+        <v>0.0288</v>
+      </c>
+      <c r="Q24" s="84">
+        <f>IF(OR(O24="",P24=""),"",SQRT(0.5*(O24^2+P24^2)))</f>
+        <v/>
+      </c>
+      <c r="R24" s="75">
+        <f>IF(OR(G24="",$G$23="",$G$23=0),"",G24/$G$23)</f>
+        <v/>
+      </c>
+      <c r="S24" s="111">
+        <f>IF(OR(M24="",$M$23=""),"",M24-$M$23)</f>
+        <v/>
+      </c>
+      <c r="T24" s="81" t="inlineStr">
+        <is>
+          <t>cap 1. Thickness adds +0.02 fill for 1.08x exposure - marginal, same as the other LEDs at 25 mm. Confirms: go 25 mm, skip the thick wall.  flux 52</t>
+        </is>
+      </c>
+      <c r="U24" s="126" t="n">
+        <v>0.058</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="80" t="inlineStr">
+        <is>
+          <t>drop</t>
+        </is>
+      </c>
+      <c r="B25" s="133" t="inlineStr">
+        <is>
+          <t>Everlight</t>
+        </is>
+      </c>
+      <c r="C25" s="85" t="n">
+        <v>25</v>
+      </c>
+      <c r="D25" s="86" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E25" s="86">
+        <f>IF($B$5="inward",C25-2*D25,C25)</f>
+        <v/>
+      </c>
+      <c r="F25" s="86">
+        <f>IF(OR(E25="",$B$4=""),"",E25/2-$B$4)</f>
+        <v/>
+      </c>
+      <c r="G25" s="74" t="n"/>
+      <c r="H25" s="74" t="n"/>
+      <c r="I25" s="72" t="n"/>
+      <c r="J25" s="74" t="n"/>
+      <c r="K25" s="74" t="n"/>
+      <c r="L25" s="79" t="n"/>
+      <c r="M25" s="79" t="n"/>
+      <c r="N25" s="80">
+        <f>IF(OR(K25="",L25="",M25=""),"",IF(AND(K25=1,L25&gt;=0.9,L25&lt;=1.1,M25&gt;=0.70),"pass","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="O25" s="83" t="n"/>
+      <c r="P25" s="83" t="n"/>
+      <c r="Q25" s="84">
+        <f>IF(OR(O25="",P25=""),"",SQRT(0.5*(O25^2+P25^2)))</f>
+        <v/>
+      </c>
+      <c r="R25" s="75">
+        <f>IF(OR(G25="",$G$23="",$G$23=0),"",G25/$G$23)</f>
+        <v/>
+      </c>
+      <c r="S25" s="111">
+        <f>IF(OR(M25="",$M$23=""),"",M25-$M$23)</f>
+        <v/>
+      </c>
+      <c r="T25" s="123" t="inlineStr">
+        <is>
+          <t>DROPPED 2026-09-04. 0.5 mm measured worse than 0.4 mm at identical transmitted flux, i.e. cap variation not thickness. Ladder reduced to 0.2 / 0.4 mm with REPLICATE caps instead.</t>
+        </is>
+      </c>
+      <c r="U25" s="126" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="98" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="B26" s="128" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="C26" s="100" t="n">
+        <v>20</v>
+      </c>
+      <c r="D26" s="101" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E26" s="101">
+        <f>IF($B$5="inward",C26-2*D26,C26)</f>
+        <v/>
+      </c>
+      <c r="F26" s="101">
+        <f>IF(OR(E26="",$B$4=""),"",E26/2-$B$4)</f>
+        <v/>
+      </c>
+      <c r="G26" s="102">
+        <f>IFERROR(A_Bench!F11,"")</f>
+        <v/>
+      </c>
+      <c r="H26" s="102">
+        <f>IFERROR(A_Bench!G11,"")</f>
+        <v/>
+      </c>
+      <c r="I26" s="103">
+        <f>IFERROR(A_Bench!H11,"")</f>
+        <v/>
+      </c>
+      <c r="J26" s="102">
+        <f>IFERROR(A_Bench!K11,"")</f>
+        <v/>
+      </c>
+      <c r="K26" s="102">
+        <f>IFERROR(A_Bench!M11,"")</f>
+        <v/>
+      </c>
+      <c r="L26" s="104">
+        <f>IFERROR(A_Bench!N11,"")</f>
+        <v/>
+      </c>
+      <c r="M26" s="104">
+        <f>IFERROR(A_Bench!U11,"")</f>
+        <v/>
+      </c>
+      <c r="N26" s="105">
+        <f>IF(OR(K26="",L26="",M26=""),"",IF(AND(K26=1,L26&gt;=0.9,L26&lt;=1.1,M26&gt;=0.70),"pass","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="O26" s="106">
+        <f>IFERROR(A_Bench!P11,"")</f>
+        <v/>
+      </c>
+      <c r="P26" s="106">
+        <f>IFERROR(A_Bench!Q11,"")</f>
+        <v/>
+      </c>
+      <c r="Q26" s="107">
+        <f>IF(OR(O26="",P26=""),"",SQRT(0.5*(O26^2+P26^2)))</f>
+        <v/>
+      </c>
+      <c r="R26" s="108">
+        <f>IF(OR(G26="",$G$26="",$G$26=0),"",G26/$G$26)</f>
+        <v/>
+      </c>
+      <c r="S26" s="109">
+        <f>IF(OR(M26="",$M$26=""),"",M26-$M$26)</f>
+        <v/>
+      </c>
+      <c r="T26" s="110" t="n"/>
+      <c r="U26" s="125" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="80" t="n">
+        <v>3</v>
+      </c>
+      <c r="B27" s="133" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="C27" s="85" t="n">
+        <v>20</v>
+      </c>
+      <c r="D27" s="86" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E27" s="86">
+        <f>IF($B$5="inward",C27-2*D27,C27)</f>
+        <v/>
+      </c>
+      <c r="F27" s="86">
+        <f>IF(OR(E27="",$B$4=""),"",E27/2-$B$4)</f>
+        <v/>
+      </c>
+      <c r="G27" s="74" t="n">
+        <v>7351</v>
+      </c>
+      <c r="H27" s="74" t="n">
+        <v>203.8</v>
+      </c>
+      <c r="I27" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="74" t="n">
+        <v>846</v>
+      </c>
+      <c r="K27" s="74" t="n">
+        <v>1</v>
+      </c>
+      <c r="L27" s="79" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M27" s="79" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="N27" s="80">
+        <f>IF(OR(K27="",L27="",M27=""),"",IF(AND(K27=1,L27&gt;=0.9,L27&lt;=1.1,M27&gt;=0.70),"pass","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="O27" s="83" t="n">
+        <v>0.0185</v>
+      </c>
+      <c r="P27" s="83" t="n">
+        <v>0.0309</v>
+      </c>
+      <c r="Q27" s="84">
+        <f>IF(OR(O27="",P27=""),"",SQRT(0.5*(O27^2+P27^2)))</f>
+        <v/>
+      </c>
+      <c r="R27" s="75">
+        <f>IF(OR(G27="",$G$26="",$G$26=0),"",G27/$G$26)</f>
+        <v/>
+      </c>
+      <c r="S27" s="111">
+        <f>IF(OR(M27="",$M$26=""),"",M27-$M$26)</f>
+        <v/>
+      </c>
+      <c r="T27" s="81" t="inlineStr">
+        <is>
+          <t>cap 1. FIRST BUILD TO PASS THE BLEND GATE: fill 0.85, lobe 0.059, blobs 1, w/h 1.01. Thickness cost only 1.23x here vs 2.10x for Kingbright on the SAME caps - a wide beam already takes a long oblique path through the shell, so extra wall adds proportionally less.  flux 23</t>
+        </is>
+      </c>
+      <c r="U27" s="126" t="n">
+        <v>0.059</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="80" t="inlineStr">
+        <is>
+          <t>drop</t>
+        </is>
+      </c>
+      <c r="B28" s="133" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="C28" s="85" t="n">
+        <v>20</v>
+      </c>
+      <c r="D28" s="86" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E28" s="86">
+        <f>IF($B$5="inward",C28-2*D28,C28)</f>
+        <v/>
+      </c>
+      <c r="F28" s="86">
+        <f>IF(OR(E28="",$B$4=""),"",E28/2-$B$4)</f>
+        <v/>
+      </c>
+      <c r="G28" s="74" t="n"/>
+      <c r="H28" s="74" t="n"/>
+      <c r="I28" s="72" t="n"/>
+      <c r="J28" s="74" t="n"/>
+      <c r="K28" s="74" t="n"/>
+      <c r="L28" s="79" t="n"/>
+      <c r="M28" s="79" t="n"/>
+      <c r="N28" s="80">
+        <f>IF(OR(K28="",L28="",M28=""),"",IF(AND(K28=1,L28&gt;=0.9,L28&lt;=1.1,M28&gt;=0.70),"pass","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="O28" s="83" t="n"/>
+      <c r="P28" s="83" t="n"/>
+      <c r="Q28" s="84">
+        <f>IF(OR(O28="",P28=""),"",SQRT(0.5*(O28^2+P28^2)))</f>
+        <v/>
+      </c>
+      <c r="R28" s="75">
+        <f>IF(OR(G28="",$G$26="",$G$26=0),"",G28/$G$26)</f>
+        <v/>
+      </c>
+      <c r="S28" s="111">
+        <f>IF(OR(M28="",$M$26=""),"",M28-$M$26)</f>
+        <v/>
+      </c>
+      <c r="T28" s="123" t="inlineStr">
+        <is>
+          <t>DROPPED 2026-09-04. 0.5 mm measured worse than 0.4 mm at identical transmitted flux, i.e. cap variation not thickness. Ladder reduced to 0.2 / 0.4 mm with REPLICATE caps instead.</t>
+        </is>
+      </c>
+      <c r="U28" s="126" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="112" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="B29" s="133" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="C29" s="85" t="n">
+        <v>25</v>
+      </c>
+      <c r="D29" s="86" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E29" s="86">
+        <f>IF($B$5="inward",C29-2*D29,C29)</f>
+        <v/>
+      </c>
+      <c r="F29" s="86">
+        <f>IF(OR(E29="",$B$4=""),"",E29/2-$B$4)</f>
+        <v/>
+      </c>
+      <c r="G29" s="113">
+        <f>IFERROR(A_Bench!F15,"")</f>
+        <v/>
+      </c>
+      <c r="H29" s="113">
+        <f>IFERROR(A_Bench!G15,"")</f>
+        <v/>
+      </c>
+      <c r="I29" s="114">
+        <f>IFERROR(A_Bench!H15,"")</f>
+        <v/>
+      </c>
+      <c r="J29" s="113">
+        <f>IFERROR(A_Bench!K15,"")</f>
+        <v/>
+      </c>
+      <c r="K29" s="113">
+        <f>IFERROR(A_Bench!M15,"")</f>
+        <v/>
+      </c>
+      <c r="L29" s="115">
+        <f>IFERROR(A_Bench!N15,"")</f>
+        <v/>
+      </c>
+      <c r="M29" s="115">
+        <f>IFERROR(A_Bench!U15,"")</f>
+        <v/>
+      </c>
+      <c r="N29" s="80">
+        <f>IF(OR(K29="",L29="",M29=""),"",IF(AND(K29=1,L29&gt;=0.9,L29&lt;=1.1,M29&gt;=0.70),"pass","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="O29" s="116">
+        <f>IFERROR(A_Bench!P15,"")</f>
+        <v/>
+      </c>
+      <c r="P29" s="116">
+        <f>IFERROR(A_Bench!Q15,"")</f>
+        <v/>
+      </c>
+      <c r="Q29" s="84">
+        <f>IF(OR(O29="",P29=""),"",SQRT(0.5*(O29^2+P29^2)))</f>
+        <v/>
+      </c>
+      <c r="R29" s="75">
+        <f>IF(OR(G29="",$G$29="",$G$29=0),"",G29/$G$29)</f>
+        <v/>
+      </c>
+      <c r="S29" s="111">
+        <f>IF(OR(M29="",$M$29=""),"",M29-$M$29)</f>
+        <v/>
+      </c>
+      <c r="T29" s="81" t="n"/>
+      <c r="U29" s="127" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="80" t="n">
+        <v>3</v>
+      </c>
+      <c r="B30" s="133" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="C30" s="85" t="n">
+        <v>25</v>
+      </c>
+      <c r="D30" s="86" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E30" s="86">
+        <f>IF($B$5="inward",C30-2*D30,C30)</f>
+        <v/>
+      </c>
+      <c r="F30" s="86">
+        <f>IF(OR(E30="",$B$4=""),"",E30/2-$B$4)</f>
+        <v/>
+      </c>
+      <c r="G30" s="74" t="n">
+        <v>8628</v>
+      </c>
+      <c r="H30" s="74" t="n">
+        <v>213.7</v>
+      </c>
+      <c r="I30" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="74" t="n">
+        <v>967</v>
+      </c>
+      <c r="K30" s="74" t="n">
+        <v>1</v>
+      </c>
+      <c r="L30" s="79" t="n">
+        <v>1</v>
+      </c>
+      <c r="M30" s="79" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N30" s="80">
+        <f>IF(OR(K30="",L30="",M30=""),"",IF(AND(K30=1,L30&gt;=0.9,L30&lt;=1.1,M30&gt;=0.70),"pass","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="O30" s="83" t="n">
+        <v>0.0206</v>
+      </c>
+      <c r="P30" s="83" t="n">
+        <v>0.0245</v>
+      </c>
+      <c r="Q30" s="84">
+        <f>IF(OR(O30="",P30=""),"",SQRT(0.5*(O30^2+P30^2)))</f>
+        <v/>
+      </c>
+      <c r="R30" s="75">
+        <f>IF(OR(G30="",$G$29="",$G$29=0),"",G30/$G$29)</f>
+        <v/>
+      </c>
+      <c r="S30" s="111">
+        <f>IF(OR(M30="",$M$29=""),"",M30-$M$29)</f>
+        <v/>
+      </c>
+      <c r="T30" s="81" t="inlineStr">
+        <is>
+          <t>cap 1. First attempt gave sigma 0.1856 (sv/su 3.4) while area/fill/lobe were identical - a rig disturbance mid-run, rejected and re-measured. Thickness adds nothing at 25 mm: same fill, same lobe, 5% more exposure.  flux 24</t>
+        </is>
+      </c>
+      <c r="U30" s="126" t="n">
+        <v>0.062</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="80" t="inlineStr">
+        <is>
+          <t>drop</t>
+        </is>
+      </c>
+      <c r="B31" s="133" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="C31" s="85" t="n">
+        <v>25</v>
+      </c>
+      <c r="D31" s="86" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E31" s="86">
+        <f>IF($B$5="inward",C31-2*D31,C31)</f>
+        <v/>
+      </c>
+      <c r="F31" s="86">
+        <f>IF(OR(E31="",$B$4=""),"",E31/2-$B$4)</f>
+        <v/>
+      </c>
+      <c r="G31" s="74" t="n"/>
+      <c r="H31" s="74" t="n"/>
+      <c r="I31" s="72" t="n"/>
+      <c r="J31" s="74" t="n"/>
+      <c r="K31" s="74" t="n"/>
+      <c r="L31" s="79" t="n"/>
+      <c r="M31" s="79" t="n"/>
+      <c r="N31" s="80">
+        <f>IF(OR(K31="",L31="",M31=""),"",IF(AND(K31=1,L31&gt;=0.9,L31&lt;=1.1,M31&gt;=0.70),"pass","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="O31" s="83" t="n"/>
+      <c r="P31" s="83" t="n"/>
+      <c r="Q31" s="84">
+        <f>IF(OR(O31="",P31=""),"",SQRT(0.5*(O31^2+P31^2)))</f>
+        <v/>
+      </c>
+      <c r="R31" s="75">
+        <f>IF(OR(G31="",$G$29="",$G$29=0),"",G31/$G$29)</f>
+        <v/>
+      </c>
+      <c r="S31" s="111">
+        <f>IF(OR(M31="",$M$29=""),"",M31-$M$29)</f>
+        <v/>
+      </c>
+      <c r="T31" s="123" t="inlineStr">
+        <is>
+          <t>DROPPED 2026-09-04. 0.5 mm measured worse than 0.4 mm at identical transmitted flux, i.e. cap variation not thickness. Ladder reduced to 0.2 / 0.4 mm with REPLICATE caps instead.</t>
+        </is>
+      </c>
+      <c r="U31" s="126" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="76" t="inlineStr">
+        <is>
+          <t>HOW TO READ THIS</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="91" t="inlineStr">
+        <is>
+          <t>Priority 1 is Kingbright and Vishay. They are the parts that RING (fill 0.77-0.82 and 0.67-0.69 at 0.2 mm) and the only ones with the light budget to pay for a thicker wall - 251-1186 us against XL's 6057. Kingbright first: it needs the smallest lift (0.82 -&gt; 0.85) and already has the study's best sigma.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="91" t="inlineStr">
+        <is>
+          <t>Priority 3 is XL, and only as a control. It already reads fill 0.99-1.08, so a thicker wall can only cost it light, and it has the least to spare. Its value is that it is already uniform, so its exposure-vs-wall curve is the cleanest measurement of the MATERIAL's attenuation per mm - which then predicts the cost for the others.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="91" t="inlineStr">
+        <is>
+          <t>Standoff is NOT a confound at these thicknesses. Going 0.2 -&gt; 0.5 mm on a 20 mm shell moves the wall 0.3 mm closer to the LEDs - against a cavity radius of ~10 mm, that is negligible. This is a clean test of scattering versus transmission: a thicker wall scatters more (better fill) and transmits less (more exposure). Exposure vs 0.2 mm is the price, Fill vs 0.2 mm is what you bought.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="91" t="inlineStr">
+        <is>
+          <t>Diameter and thickness interact differently per part. On the 2 mm caps, diameter helped Kingbright (fill 0.77 -&gt; 0.82, sigma 0.0230 -&gt; 0.0162), barely moved Vishay (0.67 -&gt; 0.69) and was irrelevant to XL (already ~1.0). Expect wall thickness to follow the same ordering: most useful where the beam is narrowest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="91" t="inlineStr">
+        <is>
+          <t>Exposure vs 2 mm is the price. Fill vs 2 mm is what you bought. A row is only interesting if it buys enough fill to pass the gate without pricing itself out on smear - at ~1300 px/s per m/s, every 1000 us of exposure is 1.3 px of smear at 1 m/s.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="91" t="inlineStr">
+        <is>
+          <t>Do NOT re-measure the 0.2 mm rows here - they are pulled live from A_Bench and shown in grey. They will be blank until Test A run 3 is done, since the rig was torn down after run 2.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF1F3864"/>
@@ -7364,6 +9449,2239 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:S66"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="7" customWidth="1" min="10" max="10"/>
+    <col width="7" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="9" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="30" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="19" max="19"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="65" t="inlineStr">
+        <is>
+          <t>TEST C - Range, at 0 deg and 90 deg</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="66" t="inlineStr">
+        <is>
+          <t>25 mm / 0.2 mm caps. Kingbright dropped - 19.7x anisotropy puts it out regardless of range. The 90 deg rows are the BINDING case: a marker detected at 90 deg is certainly detected at 0 deg, so the 90 deg far limit IS the operating range and it sets how many cameras the arena needs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="66" t="inlineStr">
+        <is>
+          <t>RUN 2 - night session, 9 Sep. Arena ambient is FLAT from 85 us to 100 ms (3.3-3.5 counts = sensor pedestal, not light); first real signal above 100 ms, still only 10 counts at 200 ms vs THRESH_LO 80. No ambient ceiling below ~200 ms. CAVEAT: run on a lab 9V battery of unknown charge - the marker measured 2.4x dimmer than run 1 at matched geometry (same cap: fill/lobe/w-h reproduce to 3%, so all four LEDs are lit and it is drive current, not optics). ABSOLUTE exposures therefore carry an unknown scale factor; column S normalises it away. A DETECTION is a valid lower bound; a NON-detection is provisional and flagged battery-limited until re-checked on a known 9.0 V pack.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>INSTRUMENT: all run-2 rows use a FORCED VGA 640x480 ratio-1 readout window. The old auto-size rule (QVGA below a 60 px blob) introduced a step in sigma at the switch point - QVGA measured 35% higher sigma than VGA on an identical blob. Placement repeatability at 90 deg is 3.2% (1 sigma, n=3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="34" customHeight="1">
+      <c r="A6" s="77" t="inlineStr">
+        <is>
+          <t>ROWS 7-11 VOID: measured 2026-09-09 before the lens focus problem was found. The lens was focused near, so the blob hollows out and grows with distance, flattening the exposure curve and faking the range limit. Focus was corrected at the end of that session (at 5 m, same exposure: fill 0.73-&gt;1.46, area 571-&gt;316, diameter 27.0-&gt;20.0 px). Re-sweep from 1 m with focus locked. See PROTOCOL.md section 1.</t>
+        </is>
+      </c>
+      <c r="B6" s="77" t="inlineStr">
+        <is>
+          <t>Angle
+(deg)</t>
+        </is>
+      </c>
+      <c r="C6" s="77" t="inlineStr">
+        <is>
+          <t>Distance
+(m)</t>
+        </is>
+      </c>
+      <c r="D6" s="77" t="inlineStr">
+        <is>
+          <t>Exposure
+(us)</t>
+        </is>
+      </c>
+      <c r="E6" s="77" t="inlineStr">
+        <is>
+          <t>Peak</t>
+        </is>
+      </c>
+      <c r="F6" s="77" t="inlineStr">
+        <is>
+          <t>Sat px</t>
+        </is>
+      </c>
+      <c r="G6" s="77" t="inlineStr">
+        <is>
+          <t>Sensor area
+(px)</t>
+        </is>
+      </c>
+      <c r="H6" s="77" t="inlineStr">
+        <is>
+          <t>npix</t>
+        </is>
+      </c>
+      <c r="I6" s="77" t="inlineStr">
+        <is>
+          <t>blobs</t>
+        </is>
+      </c>
+      <c r="J6" s="77" t="inlineStr">
+        <is>
+          <t>w/h</t>
+        </is>
+      </c>
+      <c r="K6" s="77" t="inlineStr">
+        <is>
+          <t>Fill</t>
+        </is>
+      </c>
+      <c r="L6" s="77" t="inlineStr">
+        <is>
+          <t>Lobe</t>
+        </is>
+      </c>
+      <c r="M6" s="77" t="inlineStr">
+        <is>
+          <t>sigma_u
+(px)</t>
+        </is>
+      </c>
+      <c r="N6" s="77" t="inlineStr">
+        <is>
+          <t>sigma_v
+(px)</t>
+        </is>
+      </c>
+      <c r="O6" s="77" t="inlineStr">
+        <is>
+          <t>sigma_RMS
+(px)</t>
+        </is>
+      </c>
+      <c r="P6" s="77" t="inlineStr">
+        <is>
+          <t>Detected?
+(Y/N)</t>
+        </is>
+      </c>
+      <c r="Q6" s="77" t="inlineStr">
+        <is>
+          <t>area x d^2
+(const if resolved)</t>
+        </is>
+      </c>
+      <c r="R6" s="77" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="S6" s="77" t="inlineStr">
+        <is>
+          <t>Exp / exp(1 m)
+(battery-independent)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="128" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="B7" s="100" t="n">
+        <v>90</v>
+      </c>
+      <c r="C7" s="136" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="129" t="n">
+        <v>6035</v>
+      </c>
+      <c r="E7" s="129" t="n">
+        <v>208.7</v>
+      </c>
+      <c r="F7" s="134" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="129" t="n">
+        <v>2458</v>
+      </c>
+      <c r="H7" s="129" t="n">
+        <v>3065</v>
+      </c>
+      <c r="I7" s="129" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" s="130" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="K7" s="130" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="L7" s="131" t="n">
+        <v>0.121</v>
+      </c>
+      <c r="M7" s="132" t="n">
+        <v>0.0108</v>
+      </c>
+      <c r="N7" s="132" t="n">
+        <v>0.0137</v>
+      </c>
+      <c r="O7" s="107">
+        <f>IF(OR(M7="",N7=""),"",SQRT(0.5*(M7^2+N7^2)))</f>
+        <v/>
+      </c>
+      <c r="P7" s="135" t="n"/>
+      <c r="Q7" s="100">
+        <f>IF(OR(C7="",G7=""),"",G7*C7^2)</f>
+        <v/>
+      </c>
+      <c r="R7" s="110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VOID - OLD (NEAR) LENS FOCUS. </t>
+        </is>
+      </c>
+      <c r="S7" s="140">
+        <f>IF(OR(D7="",D7=""),"",D7/D7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="133" t="n"/>
+      <c r="B8" s="85" t="n"/>
+      <c r="C8" s="137" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" s="74" t="n">
+        <v>20617</v>
+      </c>
+      <c r="E8" s="74" t="n">
+        <v>212.6</v>
+      </c>
+      <c r="F8" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="74" t="n">
+        <v>1546</v>
+      </c>
+      <c r="H8" s="74" t="n">
+        <v>1793</v>
+      </c>
+      <c r="I8" s="74" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" s="79" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="K8" s="79" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L8" s="126" t="n">
+        <v>0.081</v>
+      </c>
+      <c r="M8" s="83" t="n">
+        <v>0.0129</v>
+      </c>
+      <c r="N8" s="83" t="n">
+        <v>0.0269</v>
+      </c>
+      <c r="O8" s="84">
+        <f>IF(OR(M8="",N8=""),"",SQRT(0.5*(M8^2+N8^2)))</f>
+        <v/>
+      </c>
+      <c r="P8" s="78" t="n"/>
+      <c r="Q8" s="85">
+        <f>IF(OR(C8="",G8=""),"",G8*C8^2)</f>
+        <v/>
+      </c>
+      <c r="R8" s="81" t="inlineStr">
+        <is>
+          <t>VOID - OLD (NEAR) LENS FOCUS. QVGA 320x240 (blob ~55 px) - REDO IN VGA. sigma here is inflated ~35% by the window mode (see row 9), so it is not comparable with the VGA rows. Exposure 3.42x for 2x distance.</t>
+        </is>
+      </c>
+      <c r="S8" s="140">
+        <f>IF(OR(D8="",D7=""),"",D8/D7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="133" t="n"/>
+      <c r="B9" s="85" t="n"/>
+      <c r="C9" s="137" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" s="74" t="n">
+        <v>32215</v>
+      </c>
+      <c r="E9" s="74" t="n">
+        <v>207.3</v>
+      </c>
+      <c r="F9" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="74" t="n">
+        <v>1186</v>
+      </c>
+      <c r="H9" s="74" t="n">
+        <v>1350</v>
+      </c>
+      <c r="I9" s="74" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" s="79" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" s="79" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="L9" s="126" t="n">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="M9" s="83" t="n">
+        <v>0.0113</v>
+      </c>
+      <c r="N9" s="83" t="n">
+        <v>0.0183</v>
+      </c>
+      <c r="O9" s="84">
+        <f>IF(OR(M9="",N9=""),"",SQRT(0.5*(M9^2+N9^2)))</f>
+        <v/>
+      </c>
+      <c r="P9" s="78" t="n"/>
+      <c r="Q9" s="85">
+        <f>IF(OR(C9="",G9=""),"",G9*C9^2)</f>
+        <v/>
+      </c>
+      <c r="R9" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VOID - OLD (NEAR) LENS FOCUS. </t>
+        </is>
+      </c>
+      <c r="S9" s="140">
+        <f>IF(OR(D9="",D7=""),"",D9/D7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="133" t="n"/>
+      <c r="B10" s="85" t="n"/>
+      <c r="C10" s="137" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" s="74" t="n">
+        <v>50320</v>
+      </c>
+      <c r="E10" s="74" t="n">
+        <v>213.5</v>
+      </c>
+      <c r="F10" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="74" t="n">
+        <v>1008</v>
+      </c>
+      <c r="H10" s="74" t="n">
+        <v>1124</v>
+      </c>
+      <c r="I10" s="74" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="79" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K10" s="79" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="L10" s="126" t="n">
+        <v>0.064</v>
+      </c>
+      <c r="M10" s="83" t="n">
+        <v>0.0117</v>
+      </c>
+      <c r="N10" s="83" t="n">
+        <v>0.0224</v>
+      </c>
+      <c r="O10" s="84">
+        <f>IF(OR(M10="",N10=""),"",SQRT(0.5*(M10^2+N10^2)))</f>
+        <v/>
+      </c>
+      <c r="P10" s="78" t="n"/>
+      <c r="Q10" s="85">
+        <f>IF(OR(C10="",G10=""),"",G10*C10^2)</f>
+        <v/>
+      </c>
+      <c r="R10" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VOID - OLD (NEAR) LENS FOCUS. </t>
+        </is>
+      </c>
+      <c r="S10" s="140">
+        <f>IF(OR(D10="",D7=""),"",D10/D7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="133" t="n"/>
+      <c r="B11" s="85" t="n"/>
+      <c r="C11" s="137" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" s="74" t="n">
+        <v>63558</v>
+      </c>
+      <c r="E11" s="74" t="n">
+        <v>212.2</v>
+      </c>
+      <c r="F11" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="74" t="n">
+        <v>894</v>
+      </c>
+      <c r="H11" s="74" t="n">
+        <v>991</v>
+      </c>
+      <c r="I11" s="74" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" s="79" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="K11" s="79" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="L11" s="126" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="M11" s="83" t="n">
+        <v>0.0145</v>
+      </c>
+      <c r="N11" s="83" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="O11" s="84">
+        <f>IF(OR(M11="",N11=""),"",SQRT(0.5*(M11^2+N11^2)))</f>
+        <v/>
+      </c>
+      <c r="P11" s="78" t="n"/>
+      <c r="Q11" s="85">
+        <f>IF(OR(C11="",G11=""),"",G11*C11^2)</f>
+        <v/>
+      </c>
+      <c r="R11" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VOID - OLD (NEAR) LENS FOCUS. </t>
+        </is>
+      </c>
+      <c r="S11" s="140">
+        <f>IF(OR(D11="",D7=""),"",D11/D7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="133" t="n"/>
+      <c r="B12" s="85" t="n"/>
+      <c r="C12" s="137" t="n">
+        <v>6</v>
+      </c>
+      <c r="D12" s="74" t="n"/>
+      <c r="E12" s="74" t="n"/>
+      <c r="F12" s="72" t="n"/>
+      <c r="G12" s="74" t="n"/>
+      <c r="H12" s="74" t="n"/>
+      <c r="I12" s="74" t="n"/>
+      <c r="J12" s="79" t="n"/>
+      <c r="K12" s="79" t="n"/>
+      <c r="L12" s="126" t="n"/>
+      <c r="M12" s="83" t="n"/>
+      <c r="N12" s="83" t="n"/>
+      <c r="O12" s="84">
+        <f>IF(OR(M12="",N12=""),"",SQRT(0.5*(M12^2+N12^2)))</f>
+        <v/>
+      </c>
+      <c r="P12" s="78" t="n"/>
+      <c r="Q12" s="85">
+        <f>IF(OR(C12="",G12=""),"",G12*C12^2)</f>
+        <v/>
+      </c>
+      <c r="R12" s="81" t="n"/>
+      <c r="S12" s="140">
+        <f>IF(OR(D12="",D7=""),"",D12/D7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="133" t="n"/>
+      <c r="B13" s="85" t="n"/>
+      <c r="C13" s="137" t="n">
+        <v>7</v>
+      </c>
+      <c r="D13" s="74" t="n"/>
+      <c r="E13" s="74" t="n"/>
+      <c r="F13" s="72" t="n"/>
+      <c r="G13" s="74" t="n"/>
+      <c r="H13" s="74" t="n"/>
+      <c r="I13" s="74" t="n"/>
+      <c r="J13" s="79" t="n"/>
+      <c r="K13" s="79" t="n"/>
+      <c r="L13" s="126" t="n"/>
+      <c r="M13" s="83" t="n"/>
+      <c r="N13" s="83" t="n"/>
+      <c r="O13" s="84">
+        <f>IF(OR(M13="",N13=""),"",SQRT(0.5*(M13^2+N13^2)))</f>
+        <v/>
+      </c>
+      <c r="P13" s="78" t="n"/>
+      <c r="Q13" s="85">
+        <f>IF(OR(C13="",G13=""),"",G13*C13^2)</f>
+        <v/>
+      </c>
+      <c r="R13" s="81" t="n"/>
+      <c r="S13" s="140">
+        <f>IF(OR(D13="",D7=""),"",D13/D7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="133" t="n"/>
+      <c r="B14" s="85" t="n"/>
+      <c r="C14" s="137" t="n">
+        <v>8</v>
+      </c>
+      <c r="D14" s="74" t="n"/>
+      <c r="E14" s="74" t="n"/>
+      <c r="F14" s="72" t="n"/>
+      <c r="G14" s="74" t="n"/>
+      <c r="H14" s="74" t="n"/>
+      <c r="I14" s="74" t="n"/>
+      <c r="J14" s="79" t="n"/>
+      <c r="K14" s="79" t="n"/>
+      <c r="L14" s="126" t="n"/>
+      <c r="M14" s="83" t="n"/>
+      <c r="N14" s="83" t="n"/>
+      <c r="O14" s="84">
+        <f>IF(OR(M14="",N14=""),"",SQRT(0.5*(M14^2+N14^2)))</f>
+        <v/>
+      </c>
+      <c r="P14" s="78" t="n"/>
+      <c r="Q14" s="85">
+        <f>IF(OR(C14="",G14=""),"",G14*C14^2)</f>
+        <v/>
+      </c>
+      <c r="R14" s="81" t="n"/>
+      <c r="S14" s="140">
+        <f>IF(OR(D14="",D7=""),"",D14/D7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="133" t="n"/>
+      <c r="B15" s="85" t="n"/>
+      <c r="C15" s="137" t="n"/>
+      <c r="D15" s="74" t="n"/>
+      <c r="E15" s="74" t="n"/>
+      <c r="F15" s="72" t="n"/>
+      <c r="G15" s="74" t="n"/>
+      <c r="H15" s="74" t="n"/>
+      <c r="I15" s="74" t="n"/>
+      <c r="J15" s="79" t="n"/>
+      <c r="K15" s="79" t="n"/>
+      <c r="L15" s="126" t="n"/>
+      <c r="M15" s="83" t="n"/>
+      <c r="N15" s="83" t="n"/>
+      <c r="O15" s="84">
+        <f>IF(OR(M15="",N15=""),"",SQRT(0.5*(M15^2+N15^2)))</f>
+        <v/>
+      </c>
+      <c r="P15" s="78" t="n"/>
+      <c r="Q15" s="85">
+        <f>IF(OR(C15="",G15=""),"",G15*C15^2)</f>
+        <v/>
+      </c>
+      <c r="R15" s="81" t="inlineStr">
+        <is>
+          <t>unused - grid is 1-8 m</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="133" t="n"/>
+      <c r="B16" s="85" t="n"/>
+      <c r="C16" s="137" t="n"/>
+      <c r="D16" s="74" t="n"/>
+      <c r="E16" s="74" t="n"/>
+      <c r="F16" s="72" t="n"/>
+      <c r="G16" s="74" t="n"/>
+      <c r="H16" s="74" t="n"/>
+      <c r="I16" s="74" t="n"/>
+      <c r="J16" s="79" t="n"/>
+      <c r="K16" s="79" t="n"/>
+      <c r="L16" s="126" t="n"/>
+      <c r="M16" s="83" t="n"/>
+      <c r="N16" s="83" t="n"/>
+      <c r="O16" s="84">
+        <f>IF(OR(M16="",N16=""),"",SQRT(0.5*(M16^2+N16^2)))</f>
+        <v/>
+      </c>
+      <c r="P16" s="78" t="n"/>
+      <c r="Q16" s="85">
+        <f>IF(OR(C16="",G16=""),"",G16*C16^2)</f>
+        <v/>
+      </c>
+      <c r="R16" s="81" t="inlineStr">
+        <is>
+          <t>unused - grid is 1-8 m</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="133" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="B17" s="85" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="137" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="74" t="n"/>
+      <c r="E17" s="74" t="n"/>
+      <c r="F17" s="72" t="n"/>
+      <c r="G17" s="74" t="n"/>
+      <c r="H17" s="74" t="n"/>
+      <c r="I17" s="74" t="n"/>
+      <c r="J17" s="79" t="n"/>
+      <c r="K17" s="79" t="n"/>
+      <c r="L17" s="126" t="n"/>
+      <c r="M17" s="83" t="n"/>
+      <c r="N17" s="83" t="n"/>
+      <c r="O17" s="84">
+        <f>IF(OR(M17="",N17=""),"",SQRT(0.5*(M17^2+N17^2)))</f>
+        <v/>
+      </c>
+      <c r="P17" s="78" t="n"/>
+      <c r="Q17" s="85">
+        <f>IF(OR(C17="",G17=""),"",G17*C17^2)</f>
+        <v/>
+      </c>
+      <c r="R17" s="81" t="n"/>
+      <c r="S17" s="140">
+        <f>IF(OR(D17="",D17=""),"",D17/D17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="133" t="n"/>
+      <c r="B18" s="85" t="n"/>
+      <c r="C18" s="137" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" s="74" t="n"/>
+      <c r="E18" s="74" t="n"/>
+      <c r="F18" s="72" t="n"/>
+      <c r="G18" s="74" t="n"/>
+      <c r="H18" s="74" t="n"/>
+      <c r="I18" s="74" t="n"/>
+      <c r="J18" s="79" t="n"/>
+      <c r="K18" s="79" t="n"/>
+      <c r="L18" s="126" t="n"/>
+      <c r="M18" s="83" t="n"/>
+      <c r="N18" s="83" t="n"/>
+      <c r="O18" s="84">
+        <f>IF(OR(M18="",N18=""),"",SQRT(0.5*(M18^2+N18^2)))</f>
+        <v/>
+      </c>
+      <c r="P18" s="78" t="n"/>
+      <c r="Q18" s="85">
+        <f>IF(OR(C18="",G18=""),"",G18*C18^2)</f>
+        <v/>
+      </c>
+      <c r="R18" s="81" t="n"/>
+      <c r="S18" s="140">
+        <f>IF(OR(D18="",D17=""),"",D18/D17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="133" t="n"/>
+      <c r="B19" s="85" t="n"/>
+      <c r="C19" s="137" t="n">
+        <v>3</v>
+      </c>
+      <c r="D19" s="74" t="n"/>
+      <c r="E19" s="74" t="n"/>
+      <c r="F19" s="72" t="n"/>
+      <c r="G19" s="74" t="n"/>
+      <c r="H19" s="74" t="n"/>
+      <c r="I19" s="74" t="n"/>
+      <c r="J19" s="79" t="n"/>
+      <c r="K19" s="79" t="n"/>
+      <c r="L19" s="126" t="n"/>
+      <c r="M19" s="83" t="n"/>
+      <c r="N19" s="83" t="n"/>
+      <c r="O19" s="84">
+        <f>IF(OR(M19="",N19=""),"",SQRT(0.5*(M19^2+N19^2)))</f>
+        <v/>
+      </c>
+      <c r="P19" s="78" t="n"/>
+      <c r="Q19" s="85">
+        <f>IF(OR(C19="",G19=""),"",G19*C19^2)</f>
+        <v/>
+      </c>
+      <c r="R19" s="81" t="n"/>
+      <c r="S19" s="140">
+        <f>IF(OR(D19="",D17=""),"",D19/D17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="133" t="n"/>
+      <c r="B20" s="85" t="n"/>
+      <c r="C20" s="137" t="n">
+        <v>4</v>
+      </c>
+      <c r="D20" s="74" t="n"/>
+      <c r="E20" s="74" t="n"/>
+      <c r="F20" s="72" t="n"/>
+      <c r="G20" s="74" t="n"/>
+      <c r="H20" s="74" t="n"/>
+      <c r="I20" s="74" t="n"/>
+      <c r="J20" s="79" t="n"/>
+      <c r="K20" s="79" t="n"/>
+      <c r="L20" s="126" t="n"/>
+      <c r="M20" s="83" t="n"/>
+      <c r="N20" s="83" t="n"/>
+      <c r="O20" s="84">
+        <f>IF(OR(M20="",N20=""),"",SQRT(0.5*(M20^2+N20^2)))</f>
+        <v/>
+      </c>
+      <c r="P20" s="78" t="n"/>
+      <c r="Q20" s="85">
+        <f>IF(OR(C20="",G20=""),"",G20*C20^2)</f>
+        <v/>
+      </c>
+      <c r="R20" s="81" t="n"/>
+      <c r="S20" s="140">
+        <f>IF(OR(D20="",D17=""),"",D20/D17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="133" t="n"/>
+      <c r="B21" s="85" t="n"/>
+      <c r="C21" s="137" t="n">
+        <v>5</v>
+      </c>
+      <c r="D21" s="74" t="n"/>
+      <c r="E21" s="74" t="n"/>
+      <c r="F21" s="72" t="n"/>
+      <c r="G21" s="74" t="n"/>
+      <c r="H21" s="74" t="n"/>
+      <c r="I21" s="74" t="n"/>
+      <c r="J21" s="79" t="n"/>
+      <c r="K21" s="79" t="n"/>
+      <c r="L21" s="126" t="n"/>
+      <c r="M21" s="83" t="n"/>
+      <c r="N21" s="83" t="n"/>
+      <c r="O21" s="84">
+        <f>IF(OR(M21="",N21=""),"",SQRT(0.5*(M21^2+N21^2)))</f>
+        <v/>
+      </c>
+      <c r="P21" s="78" t="n"/>
+      <c r="Q21" s="85">
+        <f>IF(OR(C21="",G21=""),"",G21*C21^2)</f>
+        <v/>
+      </c>
+      <c r="R21" s="81" t="n"/>
+      <c r="S21" s="140">
+        <f>IF(OR(D21="",D17=""),"",D21/D17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="133" t="n"/>
+      <c r="B22" s="85" t="n"/>
+      <c r="C22" s="137" t="n">
+        <v>6</v>
+      </c>
+      <c r="D22" s="74" t="n"/>
+      <c r="E22" s="74" t="n"/>
+      <c r="F22" s="72" t="n"/>
+      <c r="G22" s="74" t="n"/>
+      <c r="H22" s="74" t="n"/>
+      <c r="I22" s="74" t="n"/>
+      <c r="J22" s="79" t="n"/>
+      <c r="K22" s="79" t="n"/>
+      <c r="L22" s="126" t="n"/>
+      <c r="M22" s="83" t="n"/>
+      <c r="N22" s="83" t="n"/>
+      <c r="O22" s="84">
+        <f>IF(OR(M22="",N22=""),"",SQRT(0.5*(M22^2+N22^2)))</f>
+        <v/>
+      </c>
+      <c r="P22" s="78" t="n"/>
+      <c r="Q22" s="85">
+        <f>IF(OR(C22="",G22=""),"",G22*C22^2)</f>
+        <v/>
+      </c>
+      <c r="R22" s="81" t="n"/>
+      <c r="S22" s="140">
+        <f>IF(OR(D22="",D17=""),"",D22/D17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="133" t="n"/>
+      <c r="B23" s="85" t="n"/>
+      <c r="C23" s="137" t="n">
+        <v>7</v>
+      </c>
+      <c r="D23" s="74" t="n"/>
+      <c r="E23" s="74" t="n"/>
+      <c r="F23" s="72" t="n"/>
+      <c r="G23" s="74" t="n"/>
+      <c r="H23" s="74" t="n"/>
+      <c r="I23" s="74" t="n"/>
+      <c r="J23" s="79" t="n"/>
+      <c r="K23" s="79" t="n"/>
+      <c r="L23" s="126" t="n"/>
+      <c r="M23" s="83" t="n"/>
+      <c r="N23" s="83" t="n"/>
+      <c r="O23" s="84">
+        <f>IF(OR(M23="",N23=""),"",SQRT(0.5*(M23^2+N23^2)))</f>
+        <v/>
+      </c>
+      <c r="P23" s="78" t="n"/>
+      <c r="Q23" s="85">
+        <f>IF(OR(C23="",G23=""),"",G23*C23^2)</f>
+        <v/>
+      </c>
+      <c r="R23" s="81" t="n"/>
+      <c r="S23" s="140">
+        <f>IF(OR(D23="",D17=""),"",D23/D17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="133" t="n"/>
+      <c r="B24" s="85" t="n"/>
+      <c r="C24" s="137" t="n">
+        <v>8</v>
+      </c>
+      <c r="D24" s="74" t="n"/>
+      <c r="E24" s="74" t="n"/>
+      <c r="F24" s="72" t="n"/>
+      <c r="G24" s="74" t="n"/>
+      <c r="H24" s="74" t="n"/>
+      <c r="I24" s="74" t="n"/>
+      <c r="J24" s="79" t="n"/>
+      <c r="K24" s="79" t="n"/>
+      <c r="L24" s="126" t="n"/>
+      <c r="M24" s="83" t="n"/>
+      <c r="N24" s="83" t="n"/>
+      <c r="O24" s="84">
+        <f>IF(OR(M24="",N24=""),"",SQRT(0.5*(M24^2+N24^2)))</f>
+        <v/>
+      </c>
+      <c r="P24" s="78" t="n"/>
+      <c r="Q24" s="85">
+        <f>IF(OR(C24="",G24=""),"",G24*C24^2)</f>
+        <v/>
+      </c>
+      <c r="R24" s="81" t="n"/>
+      <c r="S24" s="140">
+        <f>IF(OR(D24="",D17=""),"",D24/D17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="133" t="n"/>
+      <c r="B25" s="85" t="n"/>
+      <c r="C25" s="137" t="n"/>
+      <c r="D25" s="74" t="n"/>
+      <c r="E25" s="74" t="n"/>
+      <c r="F25" s="72" t="n"/>
+      <c r="G25" s="74" t="n"/>
+      <c r="H25" s="74" t="n"/>
+      <c r="I25" s="74" t="n"/>
+      <c r="J25" s="79" t="n"/>
+      <c r="K25" s="79" t="n"/>
+      <c r="L25" s="126" t="n"/>
+      <c r="M25" s="83" t="n"/>
+      <c r="N25" s="83" t="n"/>
+      <c r="O25" s="84">
+        <f>IF(OR(M25="",N25=""),"",SQRT(0.5*(M25^2+N25^2)))</f>
+        <v/>
+      </c>
+      <c r="P25" s="78" t="n"/>
+      <c r="Q25" s="85">
+        <f>IF(OR(C25="",G25=""),"",G25*C25^2)</f>
+        <v/>
+      </c>
+      <c r="R25" s="81" t="inlineStr">
+        <is>
+          <t>unused - grid is 1-8 m</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="133" t="n"/>
+      <c r="B26" s="85" t="n"/>
+      <c r="C26" s="137" t="n"/>
+      <c r="D26" s="74" t="n"/>
+      <c r="E26" s="74" t="n"/>
+      <c r="F26" s="72" t="n"/>
+      <c r="G26" s="74" t="n"/>
+      <c r="H26" s="74" t="n"/>
+      <c r="I26" s="74" t="n"/>
+      <c r="J26" s="79" t="n"/>
+      <c r="K26" s="79" t="n"/>
+      <c r="L26" s="126" t="n"/>
+      <c r="M26" s="83" t="n"/>
+      <c r="N26" s="83" t="n"/>
+      <c r="O26" s="84">
+        <f>IF(OR(M26="",N26=""),"",SQRT(0.5*(M26^2+N26^2)))</f>
+        <v/>
+      </c>
+      <c r="P26" s="78" t="n"/>
+      <c r="Q26" s="85">
+        <f>IF(OR(C26="",G26=""),"",G26*C26^2)</f>
+        <v/>
+      </c>
+      <c r="R26" s="81" t="inlineStr">
+        <is>
+          <t>unused - grid is 1-8 m</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="128" t="inlineStr">
+        <is>
+          <t>Everlight</t>
+        </is>
+      </c>
+      <c r="B27" s="100" t="n">
+        <v>90</v>
+      </c>
+      <c r="C27" s="136" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" s="129" t="n"/>
+      <c r="E27" s="129" t="n"/>
+      <c r="F27" s="134" t="n"/>
+      <c r="G27" s="129" t="n"/>
+      <c r="H27" s="129" t="n"/>
+      <c r="I27" s="129" t="n"/>
+      <c r="J27" s="130" t="n"/>
+      <c r="K27" s="130" t="n"/>
+      <c r="L27" s="131" t="n"/>
+      <c r="M27" s="132" t="n"/>
+      <c r="N27" s="132" t="n"/>
+      <c r="O27" s="107">
+        <f>IF(OR(M27="",N27=""),"",SQRT(0.5*(M27^2+N27^2)))</f>
+        <v/>
+      </c>
+      <c r="P27" s="135" t="n"/>
+      <c r="Q27" s="100">
+        <f>IF(OR(C27="",G27=""),"",G27*C27^2)</f>
+        <v/>
+      </c>
+      <c r="R27" s="110" t="n"/>
+      <c r="S27" s="140">
+        <f>IF(OR(D27="",D27=""),"",D27/D27)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="133" t="n"/>
+      <c r="B28" s="85" t="n"/>
+      <c r="C28" s="137" t="n">
+        <v>2</v>
+      </c>
+      <c r="D28" s="74" t="n"/>
+      <c r="E28" s="74" t="n"/>
+      <c r="F28" s="72" t="n"/>
+      <c r="G28" s="74" t="n"/>
+      <c r="H28" s="74" t="n"/>
+      <c r="I28" s="74" t="n"/>
+      <c r="J28" s="79" t="n"/>
+      <c r="K28" s="79" t="n"/>
+      <c r="L28" s="126" t="n"/>
+      <c r="M28" s="83" t="n"/>
+      <c r="N28" s="83" t="n"/>
+      <c r="O28" s="84">
+        <f>IF(OR(M28="",N28=""),"",SQRT(0.5*(M28^2+N28^2)))</f>
+        <v/>
+      </c>
+      <c r="P28" s="78" t="n"/>
+      <c r="Q28" s="85">
+        <f>IF(OR(C28="",G28=""),"",G28*C28^2)</f>
+        <v/>
+      </c>
+      <c r="R28" s="81" t="n"/>
+      <c r="S28" s="140">
+        <f>IF(OR(D28="",D27=""),"",D28/D27)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="133" t="n"/>
+      <c r="B29" s="85" t="n"/>
+      <c r="C29" s="137" t="n">
+        <v>3</v>
+      </c>
+      <c r="D29" s="74" t="n"/>
+      <c r="E29" s="74" t="n"/>
+      <c r="F29" s="72" t="n"/>
+      <c r="G29" s="74" t="n"/>
+      <c r="H29" s="74" t="n"/>
+      <c r="I29" s="74" t="n"/>
+      <c r="J29" s="79" t="n"/>
+      <c r="K29" s="79" t="n"/>
+      <c r="L29" s="126" t="n"/>
+      <c r="M29" s="83" t="n"/>
+      <c r="N29" s="83" t="n"/>
+      <c r="O29" s="84">
+        <f>IF(OR(M29="",N29=""),"",SQRT(0.5*(M29^2+N29^2)))</f>
+        <v/>
+      </c>
+      <c r="P29" s="78" t="n"/>
+      <c r="Q29" s="85">
+        <f>IF(OR(C29="",G29=""),"",G29*C29^2)</f>
+        <v/>
+      </c>
+      <c r="R29" s="81" t="n"/>
+      <c r="S29" s="140">
+        <f>IF(OR(D29="",D27=""),"",D29/D27)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="133" t="n"/>
+      <c r="B30" s="85" t="n"/>
+      <c r="C30" s="137" t="n">
+        <v>4</v>
+      </c>
+      <c r="D30" s="74" t="n"/>
+      <c r="E30" s="74" t="n"/>
+      <c r="F30" s="72" t="n"/>
+      <c r="G30" s="74" t="n"/>
+      <c r="H30" s="74" t="n"/>
+      <c r="I30" s="74" t="n"/>
+      <c r="J30" s="79" t="n"/>
+      <c r="K30" s="79" t="n"/>
+      <c r="L30" s="126" t="n"/>
+      <c r="M30" s="83" t="n"/>
+      <c r="N30" s="83" t="n"/>
+      <c r="O30" s="84">
+        <f>IF(OR(M30="",N30=""),"",SQRT(0.5*(M30^2+N30^2)))</f>
+        <v/>
+      </c>
+      <c r="P30" s="78" t="n"/>
+      <c r="Q30" s="85">
+        <f>IF(OR(C30="",G30=""),"",G30*C30^2)</f>
+        <v/>
+      </c>
+      <c r="R30" s="81" t="n"/>
+      <c r="S30" s="140">
+        <f>IF(OR(D30="",D27=""),"",D30/D27)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="133" t="n"/>
+      <c r="B31" s="85" t="n"/>
+      <c r="C31" s="137" t="n">
+        <v>5</v>
+      </c>
+      <c r="D31" s="74" t="n"/>
+      <c r="E31" s="74" t="n"/>
+      <c r="F31" s="72" t="n"/>
+      <c r="G31" s="74" t="n"/>
+      <c r="H31" s="74" t="n"/>
+      <c r="I31" s="74" t="n"/>
+      <c r="J31" s="79" t="n"/>
+      <c r="K31" s="79" t="n"/>
+      <c r="L31" s="126" t="n"/>
+      <c r="M31" s="83" t="n"/>
+      <c r="N31" s="83" t="n"/>
+      <c r="O31" s="84">
+        <f>IF(OR(M31="",N31=""),"",SQRT(0.5*(M31^2+N31^2)))</f>
+        <v/>
+      </c>
+      <c r="P31" s="78" t="n"/>
+      <c r="Q31" s="85">
+        <f>IF(OR(C31="",G31=""),"",G31*C31^2)</f>
+        <v/>
+      </c>
+      <c r="R31" s="81" t="n"/>
+      <c r="S31" s="140">
+        <f>IF(OR(D31="",D27=""),"",D31/D27)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="133" t="n"/>
+      <c r="B32" s="85" t="n"/>
+      <c r="C32" s="137" t="n">
+        <v>6</v>
+      </c>
+      <c r="D32" s="74" t="n"/>
+      <c r="E32" s="74" t="n"/>
+      <c r="F32" s="72" t="n"/>
+      <c r="G32" s="74" t="n"/>
+      <c r="H32" s="74" t="n"/>
+      <c r="I32" s="74" t="n"/>
+      <c r="J32" s="79" t="n"/>
+      <c r="K32" s="79" t="n"/>
+      <c r="L32" s="126" t="n"/>
+      <c r="M32" s="83" t="n"/>
+      <c r="N32" s="83" t="n"/>
+      <c r="O32" s="84">
+        <f>IF(OR(M32="",N32=""),"",SQRT(0.5*(M32^2+N32^2)))</f>
+        <v/>
+      </c>
+      <c r="P32" s="78" t="n"/>
+      <c r="Q32" s="85">
+        <f>IF(OR(C32="",G32=""),"",G32*C32^2)</f>
+        <v/>
+      </c>
+      <c r="R32" s="81" t="n"/>
+      <c r="S32" s="140">
+        <f>IF(OR(D32="",D27=""),"",D32/D27)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="133" t="n"/>
+      <c r="B33" s="85" t="n"/>
+      <c r="C33" s="137" t="n">
+        <v>7</v>
+      </c>
+      <c r="D33" s="74" t="n"/>
+      <c r="E33" s="74" t="n"/>
+      <c r="F33" s="72" t="n"/>
+      <c r="G33" s="74" t="n"/>
+      <c r="H33" s="74" t="n"/>
+      <c r="I33" s="74" t="n"/>
+      <c r="J33" s="79" t="n"/>
+      <c r="K33" s="79" t="n"/>
+      <c r="L33" s="126" t="n"/>
+      <c r="M33" s="83" t="n"/>
+      <c r="N33" s="83" t="n"/>
+      <c r="O33" s="84">
+        <f>IF(OR(M33="",N33=""),"",SQRT(0.5*(M33^2+N33^2)))</f>
+        <v/>
+      </c>
+      <c r="P33" s="78" t="n"/>
+      <c r="Q33" s="85">
+        <f>IF(OR(C33="",G33=""),"",G33*C33^2)</f>
+        <v/>
+      </c>
+      <c r="R33" s="81" t="n"/>
+      <c r="S33" s="140">
+        <f>IF(OR(D33="",D27=""),"",D33/D27)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="133" t="n"/>
+      <c r="B34" s="85" t="n"/>
+      <c r="C34" s="137" t="n">
+        <v>8</v>
+      </c>
+      <c r="D34" s="74" t="n"/>
+      <c r="E34" s="74" t="n"/>
+      <c r="F34" s="72" t="n"/>
+      <c r="G34" s="74" t="n"/>
+      <c r="H34" s="74" t="n"/>
+      <c r="I34" s="74" t="n"/>
+      <c r="J34" s="79" t="n"/>
+      <c r="K34" s="79" t="n"/>
+      <c r="L34" s="126" t="n"/>
+      <c r="M34" s="83" t="n"/>
+      <c r="N34" s="83" t="n"/>
+      <c r="O34" s="84">
+        <f>IF(OR(M34="",N34=""),"",SQRT(0.5*(M34^2+N34^2)))</f>
+        <v/>
+      </c>
+      <c r="P34" s="78" t="n"/>
+      <c r="Q34" s="85">
+        <f>IF(OR(C34="",G34=""),"",G34*C34^2)</f>
+        <v/>
+      </c>
+      <c r="R34" s="81" t="n"/>
+      <c r="S34" s="140">
+        <f>IF(OR(D34="",D27=""),"",D34/D27)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="133" t="n"/>
+      <c r="B35" s="85" t="n"/>
+      <c r="C35" s="137" t="n"/>
+      <c r="D35" s="74" t="n"/>
+      <c r="E35" s="74" t="n"/>
+      <c r="F35" s="72" t="n"/>
+      <c r="G35" s="74" t="n"/>
+      <c r="H35" s="74" t="n"/>
+      <c r="I35" s="74" t="n"/>
+      <c r="J35" s="79" t="n"/>
+      <c r="K35" s="79" t="n"/>
+      <c r="L35" s="126" t="n"/>
+      <c r="M35" s="83" t="n"/>
+      <c r="N35" s="83" t="n"/>
+      <c r="O35" s="84">
+        <f>IF(OR(M35="",N35=""),"",SQRT(0.5*(M35^2+N35^2)))</f>
+        <v/>
+      </c>
+      <c r="P35" s="78" t="n"/>
+      <c r="Q35" s="85">
+        <f>IF(OR(C35="",G35=""),"",G35*C35^2)</f>
+        <v/>
+      </c>
+      <c r="R35" s="81" t="inlineStr">
+        <is>
+          <t>unused - grid is 1-8 m</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="133" t="n"/>
+      <c r="B36" s="85" t="n"/>
+      <c r="C36" s="137" t="n"/>
+      <c r="D36" s="74" t="n"/>
+      <c r="E36" s="74" t="n"/>
+      <c r="F36" s="72" t="n"/>
+      <c r="G36" s="74" t="n"/>
+      <c r="H36" s="74" t="n"/>
+      <c r="I36" s="74" t="n"/>
+      <c r="J36" s="79" t="n"/>
+      <c r="K36" s="79" t="n"/>
+      <c r="L36" s="126" t="n"/>
+      <c r="M36" s="83" t="n"/>
+      <c r="N36" s="83" t="n"/>
+      <c r="O36" s="84">
+        <f>IF(OR(M36="",N36=""),"",SQRT(0.5*(M36^2+N36^2)))</f>
+        <v/>
+      </c>
+      <c r="P36" s="78" t="n"/>
+      <c r="Q36" s="85">
+        <f>IF(OR(C36="",G36=""),"",G36*C36^2)</f>
+        <v/>
+      </c>
+      <c r="R36" s="81" t="inlineStr">
+        <is>
+          <t>unused - grid is 1-8 m</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="133" t="inlineStr">
+        <is>
+          <t>Everlight</t>
+        </is>
+      </c>
+      <c r="B37" s="85" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="86" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" s="74" t="n"/>
+      <c r="E37" s="74" t="n"/>
+      <c r="F37" s="72" t="n"/>
+      <c r="G37" s="74" t="n"/>
+      <c r="H37" s="74" t="n"/>
+      <c r="I37" s="74" t="n"/>
+      <c r="J37" s="79" t="n"/>
+      <c r="K37" s="79" t="n"/>
+      <c r="L37" s="126" t="n"/>
+      <c r="M37" s="83" t="n"/>
+      <c r="N37" s="83" t="n"/>
+      <c r="O37" s="84">
+        <f>IF(OR(M37="",N37=""),"",SQRT(0.5*(M37^2+N37^2)))</f>
+        <v/>
+      </c>
+      <c r="P37" s="78" t="n"/>
+      <c r="Q37" s="85">
+        <f>IF(OR(C37="",G37=""),"",G37*C37^2)</f>
+        <v/>
+      </c>
+      <c r="R37" s="81" t="n"/>
+      <c r="S37" s="140">
+        <f>IF(OR(D37="",D37=""),"",D37/D37)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="138" t="n"/>
+      <c r="B38" s="85" t="n"/>
+      <c r="C38" s="86" t="n">
+        <v>2</v>
+      </c>
+      <c r="D38" s="74" t="n"/>
+      <c r="E38" s="74" t="n"/>
+      <c r="F38" s="72" t="n"/>
+      <c r="G38" s="74" t="n"/>
+      <c r="H38" s="74" t="n"/>
+      <c r="I38" s="74" t="n"/>
+      <c r="J38" s="79" t="n"/>
+      <c r="K38" s="79" t="n"/>
+      <c r="L38" s="126" t="n"/>
+      <c r="M38" s="83" t="n"/>
+      <c r="N38" s="83" t="n"/>
+      <c r="O38" s="84">
+        <f>IF(OR(M38="",N38=""),"",SQRT(0.5*(M38^2+N38^2)))</f>
+        <v/>
+      </c>
+      <c r="P38" s="78" t="n"/>
+      <c r="Q38" s="85">
+        <f>IF(OR(C38="",G38=""),"",G38*C38^2)</f>
+        <v/>
+      </c>
+      <c r="R38" s="81" t="n"/>
+      <c r="S38" s="140">
+        <f>IF(OR(D38="",D37=""),"",D38/D37)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="133" t="n"/>
+      <c r="B39" s="85" t="n"/>
+      <c r="C39" s="86" t="n">
+        <v>3</v>
+      </c>
+      <c r="D39" s="74" t="n"/>
+      <c r="E39" s="74" t="n"/>
+      <c r="F39" s="72" t="n"/>
+      <c r="G39" s="74" t="n"/>
+      <c r="H39" s="74" t="n"/>
+      <c r="I39" s="74" t="n"/>
+      <c r="J39" s="79" t="n"/>
+      <c r="K39" s="79" t="n"/>
+      <c r="L39" s="126" t="n"/>
+      <c r="M39" s="83" t="n"/>
+      <c r="N39" s="83" t="n"/>
+      <c r="O39" s="84">
+        <f>IF(OR(M39="",N39=""),"",SQRT(0.5*(M39^2+N39^2)))</f>
+        <v/>
+      </c>
+      <c r="P39" s="78" t="n"/>
+      <c r="Q39" s="85">
+        <f>IF(OR(C39="",G39=""),"",G39*C39^2)</f>
+        <v/>
+      </c>
+      <c r="R39" s="81" t="n"/>
+      <c r="S39" s="140">
+        <f>IF(OR(D39="",D37=""),"",D39/D37)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="133" t="n"/>
+      <c r="B40" s="85" t="n"/>
+      <c r="C40" s="86" t="n">
+        <v>4</v>
+      </c>
+      <c r="D40" s="74" t="n"/>
+      <c r="E40" s="74" t="n"/>
+      <c r="F40" s="72" t="n"/>
+      <c r="G40" s="74" t="n"/>
+      <c r="H40" s="74" t="n"/>
+      <c r="I40" s="74" t="n"/>
+      <c r="J40" s="79" t="n"/>
+      <c r="K40" s="79" t="n"/>
+      <c r="L40" s="126" t="n"/>
+      <c r="M40" s="83" t="n"/>
+      <c r="N40" s="83" t="n"/>
+      <c r="O40" s="84">
+        <f>IF(OR(M40="",N40=""),"",SQRT(0.5*(M40^2+N40^2)))</f>
+        <v/>
+      </c>
+      <c r="P40" s="78" t="n"/>
+      <c r="Q40" s="85">
+        <f>IF(OR(C40="",G40=""),"",G40*C40^2)</f>
+        <v/>
+      </c>
+      <c r="R40" s="81" t="n"/>
+      <c r="S40" s="140">
+        <f>IF(OR(D40="",D37=""),"",D40/D37)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="133" t="n"/>
+      <c r="B41" s="85" t="n"/>
+      <c r="C41" s="86" t="n">
+        <v>5</v>
+      </c>
+      <c r="D41" s="74" t="n"/>
+      <c r="E41" s="74" t="n"/>
+      <c r="F41" s="72" t="n"/>
+      <c r="G41" s="74" t="n"/>
+      <c r="H41" s="74" t="n"/>
+      <c r="I41" s="74" t="n"/>
+      <c r="J41" s="79" t="n"/>
+      <c r="K41" s="79" t="n"/>
+      <c r="L41" s="126" t="n"/>
+      <c r="M41" s="83" t="n"/>
+      <c r="N41" s="83" t="n"/>
+      <c r="O41" s="84">
+        <f>IF(OR(M41="",N41=""),"",SQRT(0.5*(M41^2+N41^2)))</f>
+        <v/>
+      </c>
+      <c r="P41" s="78" t="n"/>
+      <c r="Q41" s="85">
+        <f>IF(OR(C41="",G41=""),"",G41*C41^2)</f>
+        <v/>
+      </c>
+      <c r="R41" s="81" t="n"/>
+      <c r="S41" s="140">
+        <f>IF(OR(D41="",D37=""),"",D41/D37)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="133" t="n"/>
+      <c r="B42" s="85" t="n"/>
+      <c r="C42" s="86" t="n">
+        <v>6</v>
+      </c>
+      <c r="D42" s="74" t="n"/>
+      <c r="E42" s="74" t="n"/>
+      <c r="F42" s="72" t="n"/>
+      <c r="G42" s="74" t="n"/>
+      <c r="H42" s="74" t="n"/>
+      <c r="I42" s="74" t="n"/>
+      <c r="J42" s="79" t="n"/>
+      <c r="K42" s="79" t="n"/>
+      <c r="L42" s="126" t="n"/>
+      <c r="M42" s="83" t="n"/>
+      <c r="N42" s="83" t="n"/>
+      <c r="O42" s="84">
+        <f>IF(OR(M42="",N42=""),"",SQRT(0.5*(M42^2+N42^2)))</f>
+        <v/>
+      </c>
+      <c r="P42" s="78" t="n"/>
+      <c r="Q42" s="85">
+        <f>IF(OR(C42="",G42=""),"",G42*C42^2)</f>
+        <v/>
+      </c>
+      <c r="R42" s="81" t="n"/>
+      <c r="S42" s="140">
+        <f>IF(OR(D42="",D37=""),"",D42/D37)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="133" t="n"/>
+      <c r="B43" s="85" t="n"/>
+      <c r="C43" s="86" t="n">
+        <v>7</v>
+      </c>
+      <c r="D43" s="74" t="n"/>
+      <c r="E43" s="74" t="n"/>
+      <c r="F43" s="72" t="n"/>
+      <c r="G43" s="74" t="n"/>
+      <c r="H43" s="74" t="n"/>
+      <c r="I43" s="74" t="n"/>
+      <c r="J43" s="79" t="n"/>
+      <c r="K43" s="79" t="n"/>
+      <c r="L43" s="126" t="n"/>
+      <c r="M43" s="83" t="n"/>
+      <c r="N43" s="83" t="n"/>
+      <c r="O43" s="84">
+        <f>IF(OR(M43="",N43=""),"",SQRT(0.5*(M43^2+N43^2)))</f>
+        <v/>
+      </c>
+      <c r="P43" s="78" t="n"/>
+      <c r="Q43" s="85">
+        <f>IF(OR(C43="",G43=""),"",G43*C43^2)</f>
+        <v/>
+      </c>
+      <c r="R43" s="81" t="n"/>
+      <c r="S43" s="140">
+        <f>IF(OR(D43="",D37=""),"",D43/D37)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="133" t="n"/>
+      <c r="B44" s="85" t="n"/>
+      <c r="C44" s="86" t="n">
+        <v>8</v>
+      </c>
+      <c r="D44" s="74" t="n"/>
+      <c r="E44" s="74" t="n"/>
+      <c r="F44" s="72" t="n"/>
+      <c r="G44" s="74" t="n"/>
+      <c r="H44" s="74" t="n"/>
+      <c r="I44" s="74" t="n"/>
+      <c r="J44" s="79" t="n"/>
+      <c r="K44" s="79" t="n"/>
+      <c r="L44" s="126" t="n"/>
+      <c r="M44" s="83" t="n"/>
+      <c r="N44" s="83" t="n"/>
+      <c r="O44" s="84">
+        <f>IF(OR(M44="",N44=""),"",SQRT(0.5*(M44^2+N44^2)))</f>
+        <v/>
+      </c>
+      <c r="P44" s="78" t="n"/>
+      <c r="Q44" s="85">
+        <f>IF(OR(C44="",G44=""),"",G44*C44^2)</f>
+        <v/>
+      </c>
+      <c r="R44" s="81" t="n"/>
+      <c r="S44" s="140">
+        <f>IF(OR(D44="",D37=""),"",D44/D37)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="133" t="n"/>
+      <c r="B45" s="85" t="n"/>
+      <c r="C45" s="86" t="n"/>
+      <c r="D45" s="74" t="n"/>
+      <c r="E45" s="74" t="n"/>
+      <c r="F45" s="72" t="n"/>
+      <c r="G45" s="74" t="n"/>
+      <c r="H45" s="74" t="n"/>
+      <c r="I45" s="74" t="n"/>
+      <c r="J45" s="79" t="n"/>
+      <c r="K45" s="79" t="n"/>
+      <c r="L45" s="126" t="n"/>
+      <c r="M45" s="83" t="n"/>
+      <c r="N45" s="83" t="n"/>
+      <c r="O45" s="84">
+        <f>IF(OR(M45="",N45=""),"",SQRT(0.5*(M45^2+N45^2)))</f>
+        <v/>
+      </c>
+      <c r="P45" s="78" t="n"/>
+      <c r="Q45" s="85">
+        <f>IF(OR(C45="",G45=""),"",G45*C45^2)</f>
+        <v/>
+      </c>
+      <c r="R45" s="81" t="inlineStr">
+        <is>
+          <t>unused - grid is 1-8 m</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="133" t="n"/>
+      <c r="B46" s="85" t="n"/>
+      <c r="C46" s="86" t="n"/>
+      <c r="D46" s="74" t="n"/>
+      <c r="E46" s="74" t="n"/>
+      <c r="F46" s="72" t="n"/>
+      <c r="G46" s="74" t="n"/>
+      <c r="H46" s="74" t="n"/>
+      <c r="I46" s="74" t="n"/>
+      <c r="J46" s="79" t="n"/>
+      <c r="K46" s="79" t="n"/>
+      <c r="L46" s="126" t="n"/>
+      <c r="M46" s="83" t="n"/>
+      <c r="N46" s="83" t="n"/>
+      <c r="O46" s="84">
+        <f>IF(OR(M46="",N46=""),"",SQRT(0.5*(M46^2+N46^2)))</f>
+        <v/>
+      </c>
+      <c r="P46" s="78" t="n"/>
+      <c r="Q46" s="85">
+        <f>IF(OR(C46="",G46=""),"",G46*C46^2)</f>
+        <v/>
+      </c>
+      <c r="R46" s="81" t="inlineStr">
+        <is>
+          <t>unused - grid is 1-8 m</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="128" t="inlineStr">
+        <is>
+          <t>Vishay</t>
+        </is>
+      </c>
+      <c r="B47" s="100" t="n">
+        <v>90</v>
+      </c>
+      <c r="C47" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" s="129" t="n"/>
+      <c r="E47" s="129" t="n"/>
+      <c r="F47" s="134" t="n"/>
+      <c r="G47" s="129" t="n"/>
+      <c r="H47" s="129" t="n"/>
+      <c r="I47" s="129" t="n"/>
+      <c r="J47" s="130" t="n"/>
+      <c r="K47" s="130" t="n"/>
+      <c r="L47" s="131" t="n"/>
+      <c r="M47" s="132" t="n"/>
+      <c r="N47" s="132" t="n"/>
+      <c r="O47" s="107">
+        <f>IF(OR(M47="",N47=""),"",SQRT(0.5*(M47^2+N47^2)))</f>
+        <v/>
+      </c>
+      <c r="P47" s="135" t="n"/>
+      <c r="Q47" s="100">
+        <f>IF(OR(C47="",G47=""),"",G47*C47^2)</f>
+        <v/>
+      </c>
+      <c r="R47" s="110" t="n"/>
+      <c r="S47" s="140">
+        <f>IF(OR(D47="",D47=""),"",D47/D47)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="133" t="n"/>
+      <c r="B48" s="85" t="n"/>
+      <c r="C48" s="86" t="n">
+        <v>2</v>
+      </c>
+      <c r="D48" s="74" t="n"/>
+      <c r="E48" s="74" t="n"/>
+      <c r="F48" s="72" t="n"/>
+      <c r="G48" s="74" t="n"/>
+      <c r="H48" s="74" t="n"/>
+      <c r="I48" s="74" t="n"/>
+      <c r="J48" s="79" t="n"/>
+      <c r="K48" s="79" t="n"/>
+      <c r="L48" s="126" t="n"/>
+      <c r="M48" s="83" t="n"/>
+      <c r="N48" s="83" t="n"/>
+      <c r="O48" s="84">
+        <f>IF(OR(M48="",N48=""),"",SQRT(0.5*(M48^2+N48^2)))</f>
+        <v/>
+      </c>
+      <c r="P48" s="78" t="n"/>
+      <c r="Q48" s="85">
+        <f>IF(OR(C48="",G48=""),"",G48*C48^2)</f>
+        <v/>
+      </c>
+      <c r="R48" s="81" t="n"/>
+      <c r="S48" s="140">
+        <f>IF(OR(D48="",D47=""),"",D48/D47)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="133" t="n"/>
+      <c r="B49" s="85" t="n"/>
+      <c r="C49" s="86" t="n">
+        <v>3</v>
+      </c>
+      <c r="D49" s="74" t="n"/>
+      <c r="E49" s="74" t="n"/>
+      <c r="F49" s="72" t="n"/>
+      <c r="G49" s="74" t="n"/>
+      <c r="H49" s="74" t="n"/>
+      <c r="I49" s="74" t="n"/>
+      <c r="J49" s="79" t="n"/>
+      <c r="K49" s="79" t="n"/>
+      <c r="L49" s="126" t="n"/>
+      <c r="M49" s="83" t="n"/>
+      <c r="N49" s="83" t="n"/>
+      <c r="O49" s="84">
+        <f>IF(OR(M49="",N49=""),"",SQRT(0.5*(M49^2+N49^2)))</f>
+        <v/>
+      </c>
+      <c r="P49" s="78" t="n"/>
+      <c r="Q49" s="85">
+        <f>IF(OR(C49="",G49=""),"",G49*C49^2)</f>
+        <v/>
+      </c>
+      <c r="R49" s="81" t="n"/>
+      <c r="S49" s="140">
+        <f>IF(OR(D49="",D47=""),"",D49/D47)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="133" t="n"/>
+      <c r="B50" s="85" t="n"/>
+      <c r="C50" s="86" t="n">
+        <v>4</v>
+      </c>
+      <c r="D50" s="74" t="n"/>
+      <c r="E50" s="74" t="n"/>
+      <c r="F50" s="72" t="n"/>
+      <c r="G50" s="74" t="n"/>
+      <c r="H50" s="74" t="n"/>
+      <c r="I50" s="74" t="n"/>
+      <c r="J50" s="79" t="n"/>
+      <c r="K50" s="79" t="n"/>
+      <c r="L50" s="126" t="n"/>
+      <c r="M50" s="83" t="n"/>
+      <c r="N50" s="83" t="n"/>
+      <c r="O50" s="84">
+        <f>IF(OR(M50="",N50=""),"",SQRT(0.5*(M50^2+N50^2)))</f>
+        <v/>
+      </c>
+      <c r="P50" s="78" t="n"/>
+      <c r="Q50" s="85">
+        <f>IF(OR(C50="",G50=""),"",G50*C50^2)</f>
+        <v/>
+      </c>
+      <c r="R50" s="81" t="n"/>
+      <c r="S50" s="140">
+        <f>IF(OR(D50="",D47=""),"",D50/D47)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="133" t="n"/>
+      <c r="B51" s="85" t="n"/>
+      <c r="C51" s="86" t="n">
+        <v>5</v>
+      </c>
+      <c r="D51" s="74" t="n"/>
+      <c r="E51" s="74" t="n"/>
+      <c r="F51" s="72" t="n"/>
+      <c r="G51" s="74" t="n"/>
+      <c r="H51" s="74" t="n"/>
+      <c r="I51" s="74" t="n"/>
+      <c r="J51" s="79" t="n"/>
+      <c r="K51" s="79" t="n"/>
+      <c r="L51" s="126" t="n"/>
+      <c r="M51" s="83" t="n"/>
+      <c r="N51" s="83" t="n"/>
+      <c r="O51" s="84">
+        <f>IF(OR(M51="",N51=""),"",SQRT(0.5*(M51^2+N51^2)))</f>
+        <v/>
+      </c>
+      <c r="P51" s="78" t="n"/>
+      <c r="Q51" s="85">
+        <f>IF(OR(C51="",G51=""),"",G51*C51^2)</f>
+        <v/>
+      </c>
+      <c r="R51" s="81" t="n"/>
+      <c r="S51" s="140">
+        <f>IF(OR(D51="",D47=""),"",D51/D47)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="133" t="n"/>
+      <c r="B52" s="85" t="n"/>
+      <c r="C52" s="86" t="n">
+        <v>6</v>
+      </c>
+      <c r="D52" s="74" t="n"/>
+      <c r="E52" s="74" t="n"/>
+      <c r="F52" s="72" t="n"/>
+      <c r="G52" s="74" t="n"/>
+      <c r="H52" s="74" t="n"/>
+      <c r="I52" s="74" t="n"/>
+      <c r="J52" s="79" t="n"/>
+      <c r="K52" s="79" t="n"/>
+      <c r="L52" s="126" t="n"/>
+      <c r="M52" s="83" t="n"/>
+      <c r="N52" s="83" t="n"/>
+      <c r="O52" s="84">
+        <f>IF(OR(M52="",N52=""),"",SQRT(0.5*(M52^2+N52^2)))</f>
+        <v/>
+      </c>
+      <c r="P52" s="78" t="n"/>
+      <c r="Q52" s="85">
+        <f>IF(OR(C52="",G52=""),"",G52*C52^2)</f>
+        <v/>
+      </c>
+      <c r="R52" s="81" t="n"/>
+      <c r="S52" s="140">
+        <f>IF(OR(D52="",D47=""),"",D52/D47)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="133" t="n"/>
+      <c r="B53" s="85" t="n"/>
+      <c r="C53" s="86" t="n">
+        <v>7</v>
+      </c>
+      <c r="D53" s="74" t="n"/>
+      <c r="E53" s="74" t="n"/>
+      <c r="F53" s="72" t="n"/>
+      <c r="G53" s="74" t="n"/>
+      <c r="H53" s="74" t="n"/>
+      <c r="I53" s="74" t="n"/>
+      <c r="J53" s="79" t="n"/>
+      <c r="K53" s="79" t="n"/>
+      <c r="L53" s="126" t="n"/>
+      <c r="M53" s="83" t="n"/>
+      <c r="N53" s="83" t="n"/>
+      <c r="O53" s="84">
+        <f>IF(OR(M53="",N53=""),"",SQRT(0.5*(M53^2+N53^2)))</f>
+        <v/>
+      </c>
+      <c r="P53" s="78" t="n"/>
+      <c r="Q53" s="85">
+        <f>IF(OR(C53="",G53=""),"",G53*C53^2)</f>
+        <v/>
+      </c>
+      <c r="R53" s="81" t="n"/>
+      <c r="S53" s="140">
+        <f>IF(OR(D53="",D47=""),"",D53/D47)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="133" t="n"/>
+      <c r="B54" s="85" t="n"/>
+      <c r="C54" s="86" t="n">
+        <v>8</v>
+      </c>
+      <c r="D54" s="74" t="n"/>
+      <c r="E54" s="74" t="n"/>
+      <c r="F54" s="72" t="n"/>
+      <c r="G54" s="74" t="n"/>
+      <c r="H54" s="74" t="n"/>
+      <c r="I54" s="74" t="n"/>
+      <c r="J54" s="79" t="n"/>
+      <c r="K54" s="79" t="n"/>
+      <c r="L54" s="126" t="n"/>
+      <c r="M54" s="83" t="n"/>
+      <c r="N54" s="83" t="n"/>
+      <c r="O54" s="84">
+        <f>IF(OR(M54="",N54=""),"",SQRT(0.5*(M54^2+N54^2)))</f>
+        <v/>
+      </c>
+      <c r="P54" s="78" t="n"/>
+      <c r="Q54" s="85">
+        <f>IF(OR(C54="",G54=""),"",G54*C54^2)</f>
+        <v/>
+      </c>
+      <c r="R54" s="81" t="n"/>
+      <c r="S54" s="140">
+        <f>IF(OR(D54="",D47=""),"",D54/D47)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="133" t="n"/>
+      <c r="B55" s="85" t="n"/>
+      <c r="C55" s="86" t="n"/>
+      <c r="D55" s="74" t="n"/>
+      <c r="E55" s="74" t="n"/>
+      <c r="F55" s="72" t="n"/>
+      <c r="G55" s="74" t="n"/>
+      <c r="H55" s="74" t="n"/>
+      <c r="I55" s="74" t="n"/>
+      <c r="J55" s="79" t="n"/>
+      <c r="K55" s="79" t="n"/>
+      <c r="L55" s="126" t="n"/>
+      <c r="M55" s="83" t="n"/>
+      <c r="N55" s="83" t="n"/>
+      <c r="O55" s="84">
+        <f>IF(OR(M55="",N55=""),"",SQRT(0.5*(M55^2+N55^2)))</f>
+        <v/>
+      </c>
+      <c r="P55" s="78" t="n"/>
+      <c r="Q55" s="85">
+        <f>IF(OR(C55="",G55=""),"",G55*C55^2)</f>
+        <v/>
+      </c>
+      <c r="R55" s="81" t="inlineStr">
+        <is>
+          <t>unused - grid is 1-8 m</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="133" t="n"/>
+      <c r="B56" s="85" t="n"/>
+      <c r="C56" s="86" t="n"/>
+      <c r="D56" s="74" t="n"/>
+      <c r="E56" s="74" t="n"/>
+      <c r="F56" s="72" t="n"/>
+      <c r="G56" s="74" t="n"/>
+      <c r="H56" s="74" t="n"/>
+      <c r="I56" s="74" t="n"/>
+      <c r="J56" s="79" t="n"/>
+      <c r="K56" s="79" t="n"/>
+      <c r="L56" s="126" t="n"/>
+      <c r="M56" s="83" t="n"/>
+      <c r="N56" s="83" t="n"/>
+      <c r="O56" s="84">
+        <f>IF(OR(M56="",N56=""),"",SQRT(0.5*(M56^2+N56^2)))</f>
+        <v/>
+      </c>
+      <c r="P56" s="78" t="n"/>
+      <c r="Q56" s="85">
+        <f>IF(OR(C56="",G56=""),"",G56*C56^2)</f>
+        <v/>
+      </c>
+      <c r="R56" s="81" t="inlineStr">
+        <is>
+          <t>unused - grid is 1-8 m</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="133" t="inlineStr">
+        <is>
+          <t>Vishay</t>
+        </is>
+      </c>
+      <c r="B57" s="85" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="86" t="n">
+        <v>1</v>
+      </c>
+      <c r="D57" s="74" t="n"/>
+      <c r="E57" s="74" t="n"/>
+      <c r="F57" s="72" t="n"/>
+      <c r="G57" s="74" t="n"/>
+      <c r="H57" s="74" t="n"/>
+      <c r="I57" s="74" t="n"/>
+      <c r="J57" s="79" t="n"/>
+      <c r="K57" s="79" t="n"/>
+      <c r="L57" s="126" t="n"/>
+      <c r="M57" s="83" t="n"/>
+      <c r="N57" s="83" t="n"/>
+      <c r="O57" s="84">
+        <f>IF(OR(M57="",N57=""),"",SQRT(0.5*(M57^2+N57^2)))</f>
+        <v/>
+      </c>
+      <c r="P57" s="78" t="n"/>
+      <c r="Q57" s="85">
+        <f>IF(OR(C57="",G57=""),"",G57*C57^2)</f>
+        <v/>
+      </c>
+      <c r="R57" s="139" t="n"/>
+      <c r="S57" s="140">
+        <f>IF(OR(D57="",D57=""),"",D57/D57)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="133" t="n"/>
+      <c r="B58" s="85" t="n"/>
+      <c r="C58" s="86" t="n">
+        <v>2</v>
+      </c>
+      <c r="D58" s="74" t="n"/>
+      <c r="E58" s="74" t="n"/>
+      <c r="F58" s="72" t="n"/>
+      <c r="G58" s="74" t="n"/>
+      <c r="H58" s="74" t="n"/>
+      <c r="I58" s="74" t="n"/>
+      <c r="J58" s="79" t="n"/>
+      <c r="K58" s="79" t="n"/>
+      <c r="L58" s="126" t="n"/>
+      <c r="M58" s="83" t="n"/>
+      <c r="N58" s="83" t="n"/>
+      <c r="O58" s="84">
+        <f>IF(OR(M58="",N58=""),"",SQRT(0.5*(M58^2+N58^2)))</f>
+        <v/>
+      </c>
+      <c r="P58" s="78" t="n"/>
+      <c r="Q58" s="85">
+        <f>IF(OR(C58="",G58=""),"",G58*C58^2)</f>
+        <v/>
+      </c>
+      <c r="R58" s="139" t="n"/>
+      <c r="S58" s="140">
+        <f>IF(OR(D58="",D57=""),"",D58/D57)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="133" t="n"/>
+      <c r="B59" s="85" t="n"/>
+      <c r="C59" s="86" t="n">
+        <v>3</v>
+      </c>
+      <c r="D59" s="74" t="n"/>
+      <c r="E59" s="74" t="n"/>
+      <c r="F59" s="72" t="n"/>
+      <c r="G59" s="74" t="n"/>
+      <c r="H59" s="74" t="n"/>
+      <c r="I59" s="74" t="n"/>
+      <c r="J59" s="79" t="n"/>
+      <c r="K59" s="79" t="n"/>
+      <c r="L59" s="126" t="n"/>
+      <c r="M59" s="83" t="n"/>
+      <c r="N59" s="83" t="n"/>
+      <c r="O59" s="84">
+        <f>IF(OR(M59="",N59=""),"",SQRT(0.5*(M59^2+N59^2)))</f>
+        <v/>
+      </c>
+      <c r="P59" s="78" t="n"/>
+      <c r="Q59" s="85">
+        <f>IF(OR(C59="",G59=""),"",G59*C59^2)</f>
+        <v/>
+      </c>
+      <c r="R59" s="139" t="n"/>
+      <c r="S59" s="140">
+        <f>IF(OR(D59="",D57=""),"",D59/D57)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="133" t="n"/>
+      <c r="B60" s="85" t="n"/>
+      <c r="C60" s="86" t="n">
+        <v>4</v>
+      </c>
+      <c r="D60" s="74" t="n"/>
+      <c r="E60" s="74" t="n"/>
+      <c r="F60" s="72" t="n"/>
+      <c r="G60" s="74" t="n"/>
+      <c r="H60" s="74" t="n"/>
+      <c r="I60" s="74" t="n"/>
+      <c r="J60" s="79" t="n"/>
+      <c r="K60" s="79" t="n"/>
+      <c r="L60" s="126" t="n"/>
+      <c r="M60" s="83" t="n"/>
+      <c r="N60" s="83" t="n"/>
+      <c r="O60" s="84">
+        <f>IF(OR(M60="",N60=""),"",SQRT(0.5*(M60^2+N60^2)))</f>
+        <v/>
+      </c>
+      <c r="P60" s="78" t="n"/>
+      <c r="Q60" s="85">
+        <f>IF(OR(C60="",G60=""),"",G60*C60^2)</f>
+        <v/>
+      </c>
+      <c r="R60" s="139" t="n"/>
+      <c r="S60" s="140">
+        <f>IF(OR(D60="",D57=""),"",D60/D57)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="133" t="n"/>
+      <c r="B61" s="85" t="n"/>
+      <c r="C61" s="86" t="n">
+        <v>5</v>
+      </c>
+      <c r="D61" s="74" t="n"/>
+      <c r="E61" s="74" t="n"/>
+      <c r="F61" s="72" t="n"/>
+      <c r="G61" s="74" t="n"/>
+      <c r="H61" s="74" t="n"/>
+      <c r="I61" s="74" t="n"/>
+      <c r="J61" s="79" t="n"/>
+      <c r="K61" s="79" t="n"/>
+      <c r="L61" s="126" t="n"/>
+      <c r="M61" s="83" t="n"/>
+      <c r="N61" s="83" t="n"/>
+      <c r="O61" s="84">
+        <f>IF(OR(M61="",N61=""),"",SQRT(0.5*(M61^2+N61^2)))</f>
+        <v/>
+      </c>
+      <c r="P61" s="78" t="n"/>
+      <c r="Q61" s="85">
+        <f>IF(OR(C61="",G61=""),"",G61*C61^2)</f>
+        <v/>
+      </c>
+      <c r="R61" s="81" t="n"/>
+      <c r="S61" s="140">
+        <f>IF(OR(D61="",D57=""),"",D61/D57)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="133" t="n"/>
+      <c r="B62" s="85" t="n"/>
+      <c r="C62" s="86" t="n">
+        <v>6</v>
+      </c>
+      <c r="D62" s="74" t="n"/>
+      <c r="E62" s="74" t="n"/>
+      <c r="F62" s="72" t="n"/>
+      <c r="G62" s="74" t="n"/>
+      <c r="H62" s="74" t="n"/>
+      <c r="I62" s="74" t="n"/>
+      <c r="J62" s="79" t="n"/>
+      <c r="K62" s="79" t="n"/>
+      <c r="L62" s="126" t="n"/>
+      <c r="M62" s="83" t="n"/>
+      <c r="N62" s="83" t="n"/>
+      <c r="O62" s="84">
+        <f>IF(OR(M62="",N62=""),"",SQRT(0.5*(M62^2+N62^2)))</f>
+        <v/>
+      </c>
+      <c r="P62" s="78" t="n"/>
+      <c r="Q62" s="85">
+        <f>IF(OR(C62="",G62=""),"",G62*C62^2)</f>
+        <v/>
+      </c>
+      <c r="R62" s="81" t="n"/>
+      <c r="S62" s="140">
+        <f>IF(OR(D62="",D57=""),"",D62/D57)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="133" t="n"/>
+      <c r="B63" s="85" t="n"/>
+      <c r="C63" s="86" t="n">
+        <v>7</v>
+      </c>
+      <c r="D63" s="74" t="n"/>
+      <c r="E63" s="74" t="n"/>
+      <c r="F63" s="72" t="n"/>
+      <c r="G63" s="74" t="n"/>
+      <c r="H63" s="74" t="n"/>
+      <c r="I63" s="74" t="n"/>
+      <c r="J63" s="79" t="n"/>
+      <c r="K63" s="79" t="n"/>
+      <c r="L63" s="126" t="n"/>
+      <c r="M63" s="83" t="n"/>
+      <c r="N63" s="83" t="n"/>
+      <c r="O63" s="84">
+        <f>IF(OR(M63="",N63=""),"",SQRT(0.5*(M63^2+N63^2)))</f>
+        <v/>
+      </c>
+      <c r="P63" s="78" t="n"/>
+      <c r="Q63" s="85">
+        <f>IF(OR(C63="",G63=""),"",G63*C63^2)</f>
+        <v/>
+      </c>
+      <c r="R63" s="81" t="n"/>
+      <c r="S63" s="140">
+        <f>IF(OR(D63="",D57=""),"",D63/D57)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="133" t="n"/>
+      <c r="B64" s="85" t="n"/>
+      <c r="C64" s="86" t="n">
+        <v>8</v>
+      </c>
+      <c r="D64" s="74" t="n"/>
+      <c r="E64" s="74" t="n"/>
+      <c r="F64" s="72" t="n"/>
+      <c r="G64" s="74" t="n"/>
+      <c r="H64" s="74" t="n"/>
+      <c r="I64" s="74" t="n"/>
+      <c r="J64" s="79" t="n"/>
+      <c r="K64" s="79" t="n"/>
+      <c r="L64" s="126" t="n"/>
+      <c r="M64" s="83" t="n"/>
+      <c r="N64" s="83" t="n"/>
+      <c r="O64" s="84">
+        <f>IF(OR(M64="",N64=""),"",SQRT(0.5*(M64^2+N64^2)))</f>
+        <v/>
+      </c>
+      <c r="P64" s="78" t="n"/>
+      <c r="Q64" s="85">
+        <f>IF(OR(C64="",G64=""),"",G64*C64^2)</f>
+        <v/>
+      </c>
+      <c r="R64" s="81" t="n"/>
+      <c r="S64" s="140">
+        <f>IF(OR(D64="",D57=""),"",D64/D57)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="133" t="n"/>
+      <c r="B65" s="85" t="n"/>
+      <c r="C65" s="86" t="n"/>
+      <c r="D65" s="74" t="n"/>
+      <c r="E65" s="74" t="n"/>
+      <c r="F65" s="72" t="n"/>
+      <c r="G65" s="74" t="n"/>
+      <c r="H65" s="74" t="n"/>
+      <c r="I65" s="74" t="n"/>
+      <c r="J65" s="79" t="n"/>
+      <c r="K65" s="79" t="n"/>
+      <c r="L65" s="126" t="n"/>
+      <c r="M65" s="83" t="n"/>
+      <c r="N65" s="83" t="n"/>
+      <c r="O65" s="84">
+        <f>IF(OR(M65="",N65=""),"",SQRT(0.5*(M65^2+N65^2)))</f>
+        <v/>
+      </c>
+      <c r="P65" s="78" t="n"/>
+      <c r="Q65" s="85">
+        <f>IF(OR(C65="",G65=""),"",G65*C65^2)</f>
+        <v/>
+      </c>
+      <c r="R65" s="81" t="inlineStr">
+        <is>
+          <t>unused - grid is 1-8 m</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="133" t="n"/>
+      <c r="B66" s="85" t="n"/>
+      <c r="C66" s="86" t="n"/>
+      <c r="D66" s="74" t="n"/>
+      <c r="E66" s="74" t="n"/>
+      <c r="F66" s="72" t="n"/>
+      <c r="G66" s="74" t="n"/>
+      <c r="H66" s="74" t="n"/>
+      <c r="I66" s="74" t="n"/>
+      <c r="J66" s="79" t="n"/>
+      <c r="K66" s="79" t="n"/>
+      <c r="L66" s="126" t="n"/>
+      <c r="M66" s="83" t="n"/>
+      <c r="N66" s="83" t="n"/>
+      <c r="O66" s="84">
+        <f>IF(OR(M66="",N66=""),"",SQRT(0.5*(M66^2+N66^2)))</f>
+        <v/>
+      </c>
+      <c r="P66" s="78" t="n"/>
+      <c r="Q66" s="85">
+        <f>IF(OR(C66="",G66=""),"",G66*C66^2)</f>
+        <v/>
+      </c>
+      <c r="R66" s="81" t="inlineStr">
+        <is>
+          <t>unused - grid is 1-8 m</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="FF1F3864"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:R66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -7397,7 +11715,7 @@
     <row r="2">
       <c r="A2" s="66" t="inlineStr">
         <is>
-          <t>25 mm / 0.2 mm caps. Kingbright dropped - 19.7x anisotropy puts it out regardless of range. The 90 deg rows are the BINDING case: a marker detected at 90 deg is certainly detected at 0 deg, so the 90 deg far limit IS the operating range and it sets how many cameras the arena needs.</t>
+          <t>FROZEN - run 1, 20 Feb daylight session. Superseded: taken on a different (later failing) battery, so the ABSOLUTE exposures are not comparable with run 2. Shape metrics (fill/lobe/w-h) and sigma ARE comparable, being measured at matched peak. Distance grid was 0.7/1.5/2.5...9.5 m.</t>
         </is>
       </c>
     </row>
@@ -9380,7 +13698,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF1F3864"/>
@@ -10308,7 +14626,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF1F3864"/>
@@ -12234,1979 +16552,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="FF1F3864"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:U39"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="8" customWidth="1" min="11" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="8" customWidth="1" min="14" max="14"/>
-    <col width="11" customWidth="1" min="15" max="15"/>
-    <col width="11" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="11" customWidth="1" min="18" max="18"/>
-    <col width="11" customWidth="1" min="19" max="19"/>
-    <col width="34" customWidth="1" min="20" max="20"/>
-    <col width="12" customWidth="1" min="21" max="21"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="65" t="inlineStr">
-        <is>
-          <t>TEST G - Diffuser geometry: diameter x wall thickness</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="66" t="inlineStr">
-        <is>
-          <t>Blue on yellow = fill in.  Grey = pulled live from A_Bench (the 0.2 mm rows - do NOT re-measure them here). At these wall thicknesses the cavity barely changes, so wall thickness and LED standoff are effectively decoupled: this is a clean scattering experiment.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="66" t="inlineStr">
-        <is>
-          <t>Diffusers are WHITE (pigmented) resin - scattering is volumetric, so wall thickness sets optical depth. Caps are reused across all four LEDs, so LED-to-LED rows share the same physical cap; only the WALL ladder compares different objects. Every take re-seats the cap, which costs ~16% on sigma (measured). Reprint plan: 20 and 25 mm at 0.2 and 0.4 mm ONLY, 4.5 s cure (was 3.5), post-cured together, 2-3 replicate caps per condition - record the cap ID in Notes.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="96" t="inlineStr">
-        <is>
-          <t>LED ring radius (mm)</t>
-        </is>
-      </c>
-      <c r="B4" s="72" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="C4" s="97" t="inlineStr">
-        <is>
-          <t>centre of the board to each LED. Measured 2026-09-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="96" t="inlineStr">
-        <is>
-          <t>Wall grows</t>
-        </is>
-      </c>
-      <c r="B5" s="78" t="inlineStr">
-        <is>
-          <t>inward</t>
-        </is>
-      </c>
-      <c r="C5" s="97" t="inlineStr">
-        <is>
-          <t>'inward' = outer diameter fixed, cavity shrinks.  'outward' = cavity fixed, marker grows</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="34" customHeight="1">
-      <c r="A7" s="77" t="inlineStr">
-        <is>
-          <t>Pri</t>
-        </is>
-      </c>
-      <c r="B7" s="77" t="inlineStr">
-        <is>
-          <t>LED Type</t>
-        </is>
-      </c>
-      <c r="C7" s="77" t="inlineStr">
-        <is>
-          <t>Diameter
-(mm)</t>
-        </is>
-      </c>
-      <c r="D7" s="77" t="inlineStr">
-        <is>
-          <t>Wall
-(mm)</t>
-        </is>
-      </c>
-      <c r="E7" s="77" t="inlineStr">
-        <is>
-          <t>Cavity
-(mm)</t>
-        </is>
-      </c>
-      <c r="F7" s="77" t="inlineStr">
-        <is>
-          <t>Standoff
-(mm)</t>
-        </is>
-      </c>
-      <c r="G7" s="77" t="inlineStr">
-        <is>
-          <t>Exposure
-(us)</t>
-        </is>
-      </c>
-      <c r="H7" s="77" t="inlineStr">
-        <is>
-          <t>Peak</t>
-        </is>
-      </c>
-      <c r="I7" s="77" t="inlineStr">
-        <is>
-          <t>Sat px</t>
-        </is>
-      </c>
-      <c r="J7" s="77" t="inlineStr">
-        <is>
-          <t>Sensor area
-(px)</t>
-        </is>
-      </c>
-      <c r="K7" s="77" t="inlineStr">
-        <is>
-          <t>blobs</t>
-        </is>
-      </c>
-      <c r="L7" s="77" t="inlineStr">
-        <is>
-          <t>w/h</t>
-        </is>
-      </c>
-      <c r="M7" s="77" t="inlineStr">
-        <is>
-          <t>Fill
-(centre/rim)</t>
-        </is>
-      </c>
-      <c r="N7" s="77" t="inlineStr">
-        <is>
-          <t>Blend
-gate</t>
-        </is>
-      </c>
-      <c r="O7" s="77" t="inlineStr">
-        <is>
-          <t>sigma_u
-(px)</t>
-        </is>
-      </c>
-      <c r="P7" s="77" t="inlineStr">
-        <is>
-          <t>sigma_v
-(px)</t>
-        </is>
-      </c>
-      <c r="Q7" s="77" t="inlineStr">
-        <is>
-          <t>sigma_RMS
-(px)</t>
-        </is>
-      </c>
-      <c r="R7" s="77" t="inlineStr">
-        <is>
-          <t>Exposure
-vs 2 mm</t>
-        </is>
-      </c>
-      <c r="S7" s="77" t="inlineStr">
-        <is>
-          <t>Fill
-vs 2 mm</t>
-        </is>
-      </c>
-      <c r="T7" s="77" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="U7" s="77" t="inlineStr">
-        <is>
-          <t>Lobe
-(0=circular)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="98" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="B8" s="128" t="inlineStr">
-        <is>
-          <t>Vishay</t>
-        </is>
-      </c>
-      <c r="C8" s="100" t="n">
-        <v>20</v>
-      </c>
-      <c r="D8" s="101" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E8" s="101">
-        <f>IF($B$5="inward",C8-2*D8,C8)</f>
-        <v/>
-      </c>
-      <c r="F8" s="101">
-        <f>IF(OR(E8="",$B$4=""),"",E8/2-$B$4)</f>
-        <v/>
-      </c>
-      <c r="G8" s="102">
-        <f>IFERROR(A_Bench!F9,"")</f>
-        <v/>
-      </c>
-      <c r="H8" s="102">
-        <f>IFERROR(A_Bench!G9,"")</f>
-        <v/>
-      </c>
-      <c r="I8" s="103">
-        <f>IFERROR(A_Bench!H9,"")</f>
-        <v/>
-      </c>
-      <c r="J8" s="102">
-        <f>IFERROR(A_Bench!K9,"")</f>
-        <v/>
-      </c>
-      <c r="K8" s="102">
-        <f>IFERROR(A_Bench!M9,"")</f>
-        <v/>
-      </c>
-      <c r="L8" s="104">
-        <f>IFERROR(A_Bench!N9,"")</f>
-        <v/>
-      </c>
-      <c r="M8" s="104">
-        <f>IFERROR(A_Bench!U9,"")</f>
-        <v/>
-      </c>
-      <c r="N8" s="105">
-        <f>IF(OR(K8="",L8="",M8=""),"",IF(AND(K8=1,L8&gt;=0.9,L8&lt;=1.1,M8&gt;=0.70),"pass","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="O8" s="106">
-        <f>IFERROR(A_Bench!P9,"")</f>
-        <v/>
-      </c>
-      <c r="P8" s="106">
-        <f>IFERROR(A_Bench!Q9,"")</f>
-        <v/>
-      </c>
-      <c r="Q8" s="107">
-        <f>IF(OR(O8="",P8=""),"",SQRT(0.5*(O8^2+P8^2)))</f>
-        <v/>
-      </c>
-      <c r="R8" s="108">
-        <f>IF(OR(G8="",$G$8="",$G$8=0),"",G8/$G$8)</f>
-        <v/>
-      </c>
-      <c r="S8" s="109">
-        <f>IF(OR(M8="",$M$8=""),"",M8-$M$8)</f>
-        <v/>
-      </c>
-      <c r="T8" s="110" t="n"/>
-      <c r="U8" s="125" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="80" t="n">
-        <v>1</v>
-      </c>
-      <c r="B9" s="133" t="inlineStr">
-        <is>
-          <t>Vishay</t>
-        </is>
-      </c>
-      <c r="C9" s="85" t="n">
-        <v>20</v>
-      </c>
-      <c r="D9" s="86" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E9" s="86">
-        <f>IF($B$5="inward",C9-2*D9,C9)</f>
-        <v/>
-      </c>
-      <c r="F9" s="86">
-        <f>IF(OR(E9="",$B$4=""),"",E9/2-$B$4)</f>
-        <v/>
-      </c>
-      <c r="G9" s="74" t="n">
-        <v>413</v>
-      </c>
-      <c r="H9" s="74" t="n">
-        <v>212.3</v>
-      </c>
-      <c r="I9" s="72" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="74" t="n">
-        <v>606</v>
-      </c>
-      <c r="K9" s="74" t="n">
-        <v>1</v>
-      </c>
-      <c r="L9" s="79" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="M9" s="79" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="N9" s="80">
-        <f>IF(OR(K9="",L9="",M9=""),"",IF(AND(K9=1,L9&gt;=0.9,L9&lt;=1.1,M9&gt;=0.70),"pass","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="O9" s="83" t="n">
-        <v>0.0283</v>
-      </c>
-      <c r="P9" s="83" t="n">
-        <v>0.0357</v>
-      </c>
-      <c r="Q9" s="84">
-        <f>IF(OR(O9="",P9=""),"",SQRT(0.5*(O9^2+P9^2)))</f>
-        <v/>
-      </c>
-      <c r="R9" s="75">
-        <f>IF(OR(G9="",$G$8="",$G$8=0),"",G9/$G$8)</f>
-        <v/>
-      </c>
-      <c r="S9" s="111">
-        <f>IF(OR(M9="",$M$8=""),"",M9-$M$8)</f>
-        <v/>
-      </c>
-      <c r="T9" s="81" t="inlineStr">
-        <is>
-          <t>cap 1. BIGGEST thickness gain of any LED: fill +0.10 (0.53-&gt;0.63) and lobe 0.120-&gt;0.076, so the extra wall largely merged the four lobes. Thickness helps in inverse proportion to beam angle: Vishay +0.10, Kingbright +0.06, Everlight +0.03, XL +0.03.  flux 312</t>
-        </is>
-      </c>
-      <c r="U9" s="126" t="n">
-        <v>0.076</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="80" t="inlineStr">
-        <is>
-          <t>drop</t>
-        </is>
-      </c>
-      <c r="B10" s="133" t="inlineStr">
-        <is>
-          <t>Vishay</t>
-        </is>
-      </c>
-      <c r="C10" s="85" t="n">
-        <v>20</v>
-      </c>
-      <c r="D10" s="86" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E10" s="86">
-        <f>IF($B$5="inward",C10-2*D10,C10)</f>
-        <v/>
-      </c>
-      <c r="F10" s="86">
-        <f>IF(OR(E10="",$B$4=""),"",E10/2-$B$4)</f>
-        <v/>
-      </c>
-      <c r="G10" s="74" t="n"/>
-      <c r="H10" s="74" t="n"/>
-      <c r="I10" s="72" t="n"/>
-      <c r="J10" s="74" t="n"/>
-      <c r="K10" s="74" t="n"/>
-      <c r="L10" s="79" t="n"/>
-      <c r="M10" s="79" t="n"/>
-      <c r="N10" s="80">
-        <f>IF(OR(K10="",L10="",M10=""),"",IF(AND(K10=1,L10&gt;=0.9,L10&lt;=1.1,M10&gt;=0.70),"pass","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="O10" s="83" t="n"/>
-      <c r="P10" s="83" t="n"/>
-      <c r="Q10" s="84">
-        <f>IF(OR(O10="",P10=""),"",SQRT(0.5*(O10^2+P10^2)))</f>
-        <v/>
-      </c>
-      <c r="R10" s="75">
-        <f>IF(OR(G10="",$G$8="",$G$8=0),"",G10/$G$8)</f>
-        <v/>
-      </c>
-      <c r="S10" s="111">
-        <f>IF(OR(M10="",$M$8=""),"",M10-$M$8)</f>
-        <v/>
-      </c>
-      <c r="T10" s="123" t="inlineStr">
-        <is>
-          <t>DROPPED 2026-09-04. 0.5 mm measured worse than 0.4 mm at identical transmitted flux, i.e. cap variation not thickness. Ladder reduced to 0.2 / 0.4 mm with REPLICATE caps instead.</t>
-        </is>
-      </c>
-      <c r="U10" s="126" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="112" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="B11" s="133" t="inlineStr">
-        <is>
-          <t>Vishay</t>
-        </is>
-      </c>
-      <c r="C11" s="85" t="n">
-        <v>25</v>
-      </c>
-      <c r="D11" s="86" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E11" s="86">
-        <f>IF($B$5="inward",C11-2*D11,C11)</f>
-        <v/>
-      </c>
-      <c r="F11" s="86">
-        <f>IF(OR(E11="",$B$4=""),"",E11/2-$B$4)</f>
-        <v/>
-      </c>
-      <c r="G11" s="113">
-        <f>IFERROR(A_Bench!F13,"")</f>
-        <v/>
-      </c>
-      <c r="H11" s="113">
-        <f>IFERROR(A_Bench!G13,"")</f>
-        <v/>
-      </c>
-      <c r="I11" s="114">
-        <f>IFERROR(A_Bench!H13,"")</f>
-        <v/>
-      </c>
-      <c r="J11" s="113">
-        <f>IFERROR(A_Bench!K13,"")</f>
-        <v/>
-      </c>
-      <c r="K11" s="113">
-        <f>IFERROR(A_Bench!M13,"")</f>
-        <v/>
-      </c>
-      <c r="L11" s="115">
-        <f>IFERROR(A_Bench!N13,"")</f>
-        <v/>
-      </c>
-      <c r="M11" s="115">
-        <f>IFERROR(A_Bench!U13,"")</f>
-        <v/>
-      </c>
-      <c r="N11" s="80">
-        <f>IF(OR(K11="",L11="",M11=""),"",IF(AND(K11=1,L11&gt;=0.9,L11&lt;=1.1,M11&gt;=0.70),"pass","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="O11" s="116">
-        <f>IFERROR(A_Bench!P13,"")</f>
-        <v/>
-      </c>
-      <c r="P11" s="116">
-        <f>IFERROR(A_Bench!Q13,"")</f>
-        <v/>
-      </c>
-      <c r="Q11" s="84">
-        <f>IF(OR(O11="",P11=""),"",SQRT(0.5*(O11^2+P11^2)))</f>
-        <v/>
-      </c>
-      <c r="R11" s="75">
-        <f>IF(OR(G11="",$G$11="",$G$11=0),"",G11/$G$11)</f>
-        <v/>
-      </c>
-      <c r="S11" s="111">
-        <f>IF(OR(M11="",$M$11=""),"",M11-$M$11)</f>
-        <v/>
-      </c>
-      <c r="T11" s="81" t="n"/>
-      <c r="U11" s="127" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="80" t="n">
-        <v>1</v>
-      </c>
-      <c r="B12" s="133" t="inlineStr">
-        <is>
-          <t>Vishay</t>
-        </is>
-      </c>
-      <c r="C12" s="85" t="n">
-        <v>25</v>
-      </c>
-      <c r="D12" s="86" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E12" s="86">
-        <f>IF($B$5="inward",C12-2*D12,C12)</f>
-        <v/>
-      </c>
-      <c r="F12" s="86">
-        <f>IF(OR(E12="",$B$4=""),"",E12/2-$B$4)</f>
-        <v/>
-      </c>
-      <c r="G12" s="74" t="n">
-        <v>602</v>
-      </c>
-      <c r="H12" s="74" t="n">
-        <v>209.9</v>
-      </c>
-      <c r="I12" s="72" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="74" t="n">
-        <v>751</v>
-      </c>
-      <c r="K12" s="74" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" s="79" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="M12" s="79" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="N12" s="80">
-        <f>IF(OR(K12="",L12="",M12=""),"",IF(AND(K12=1,L12&gt;=0.9,L12&lt;=1.1,M12&gt;=0.70),"pass","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="O12" s="83" t="n">
-        <v>0.0198</v>
-      </c>
-      <c r="P12" s="83" t="n">
-        <v>0.0273</v>
-      </c>
-      <c r="Q12" s="84">
-        <f>IF(OR(O12="",P12=""),"",SQRT(0.5*(O12^2+P12^2)))</f>
-        <v/>
-      </c>
-      <c r="R12" s="75">
-        <f>IF(OR(G12="",$G$11="",$G$11=0),"",G12/$G$11)</f>
-        <v/>
-      </c>
-      <c r="S12" s="111">
-        <f>IF(OR(M12="",$M$11=""),"",M12-$M$11)</f>
-        <v/>
-      </c>
-      <c r="T12" s="81" t="inlineStr">
-        <is>
-          <t>MEAN OF 4 REPLICATE CAPS (575/485/575/772 us). Cap-to-cap: exposure CV 20%, area 2.7%, fill 2.5%, lobe 4%, sigma 11%. So fill = 0.74 +/- 0.02 and sigma = 0.0240 +/- 0.0027; fill differences under ~0.05 and sigma differences under ~25% are not significant.  flux 262</t>
-        </is>
-      </c>
-      <c r="U12" s="126" t="n">
-        <v>0.062</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="80" t="inlineStr">
-        <is>
-          <t>drop</t>
-        </is>
-      </c>
-      <c r="B13" s="133" t="inlineStr">
-        <is>
-          <t>Vishay</t>
-        </is>
-      </c>
-      <c r="C13" s="85" t="n">
-        <v>25</v>
-      </c>
-      <c r="D13" s="86" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E13" s="86">
-        <f>IF($B$5="inward",C13-2*D13,C13)</f>
-        <v/>
-      </c>
-      <c r="F13" s="86">
-        <f>IF(OR(E13="",$B$4=""),"",E13/2-$B$4)</f>
-        <v/>
-      </c>
-      <c r="G13" s="74" t="n"/>
-      <c r="H13" s="74" t="n"/>
-      <c r="I13" s="72" t="n"/>
-      <c r="J13" s="74" t="n"/>
-      <c r="K13" s="74" t="n"/>
-      <c r="L13" s="79" t="n"/>
-      <c r="M13" s="79" t="n"/>
-      <c r="N13" s="80">
-        <f>IF(OR(K13="",L13="",M13=""),"",IF(AND(K13=1,L13&gt;=0.9,L13&lt;=1.1,M13&gt;=0.70),"pass","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="O13" s="83" t="n"/>
-      <c r="P13" s="83" t="n"/>
-      <c r="Q13" s="84">
-        <f>IF(OR(O13="",P13=""),"",SQRT(0.5*(O13^2+P13^2)))</f>
-        <v/>
-      </c>
-      <c r="R13" s="75">
-        <f>IF(OR(G13="",$G$11="",$G$11=0),"",G13/$G$11)</f>
-        <v/>
-      </c>
-      <c r="S13" s="111">
-        <f>IF(OR(M13="",$M$11=""),"",M13-$M$11)</f>
-        <v/>
-      </c>
-      <c r="T13" s="123" t="inlineStr">
-        <is>
-          <t>DROPPED 2026-09-04. 0.5 mm measured worse than 0.4 mm at identical transmitted flux, i.e. cap variation not thickness. Ladder reduced to 0.2 / 0.4 mm with REPLICATE caps instead.</t>
-        </is>
-      </c>
-      <c r="U13" s="126" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="98" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="B14" s="128" t="inlineStr">
-        <is>
-          <t>Kingbright</t>
-        </is>
-      </c>
-      <c r="C14" s="100" t="n">
-        <v>20</v>
-      </c>
-      <c r="D14" s="101" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E14" s="101">
-        <f>IF($B$5="inward",C14-2*D14,C14)</f>
-        <v/>
-      </c>
-      <c r="F14" s="101">
-        <f>IF(OR(E14="",$B$4=""),"",E14/2-$B$4)</f>
-        <v/>
-      </c>
-      <c r="G14" s="102">
-        <f>IFERROR(A_Bench!F12,"")</f>
-        <v/>
-      </c>
-      <c r="H14" s="102">
-        <f>IFERROR(A_Bench!G12,"")</f>
-        <v/>
-      </c>
-      <c r="I14" s="103">
-        <f>IFERROR(A_Bench!H12,"")</f>
-        <v/>
-      </c>
-      <c r="J14" s="102">
-        <f>IFERROR(A_Bench!K12,"")</f>
-        <v/>
-      </c>
-      <c r="K14" s="102">
-        <f>IFERROR(A_Bench!M12,"")</f>
-        <v/>
-      </c>
-      <c r="L14" s="104">
-        <f>IFERROR(A_Bench!N12,"")</f>
-        <v/>
-      </c>
-      <c r="M14" s="104">
-        <f>IFERROR(A_Bench!U12,"")</f>
-        <v/>
-      </c>
-      <c r="N14" s="105">
-        <f>IF(OR(K14="",L14="",M14=""),"",IF(AND(K14=1,L14&gt;=0.9,L14&lt;=1.1,M14&gt;=0.70),"pass","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="O14" s="106">
-        <f>IFERROR(A_Bench!P12,"")</f>
-        <v/>
-      </c>
-      <c r="P14" s="106">
-        <f>IFERROR(A_Bench!Q12,"")</f>
-        <v/>
-      </c>
-      <c r="Q14" s="107">
-        <f>IF(OR(O14="",P14=""),"",SQRT(0.5*(O14^2+P14^2)))</f>
-        <v/>
-      </c>
-      <c r="R14" s="108">
-        <f>IF(OR(G14="",$G$14="",$G$14=0),"",G14/$G$14)</f>
-        <v/>
-      </c>
-      <c r="S14" s="109">
-        <f>IF(OR(M14="",$M$14=""),"",M14-$M$14)</f>
-        <v/>
-      </c>
-      <c r="T14" s="110" t="n"/>
-      <c r="U14" s="125" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="80" t="n">
-        <v>1</v>
-      </c>
-      <c r="B15" s="133" t="inlineStr">
-        <is>
-          <t>Kingbright</t>
-        </is>
-      </c>
-      <c r="C15" s="85" t="n">
-        <v>20</v>
-      </c>
-      <c r="D15" s="86" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E15" s="86">
-        <f>IF($B$5="inward",C15-2*D15,C15)</f>
-        <v/>
-      </c>
-      <c r="F15" s="86">
-        <f>IF(OR(E15="",$B$4=""),"",E15/2-$B$4)</f>
-        <v/>
-      </c>
-      <c r="G15" s="74" t="n">
-        <v>1060</v>
-      </c>
-      <c r="H15" s="74" t="n">
-        <v>216.6</v>
-      </c>
-      <c r="I15" s="72" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="74" t="n">
-        <v>694</v>
-      </c>
-      <c r="K15" s="74" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" s="79" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="M15" s="79" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="N15" s="80">
-        <f>IF(OR(K15="",L15="",M15=""),"",IF(AND(K15=1,L15&gt;=0.9,L15&lt;=1.1,M15&gt;=0.70),"pass","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="O15" s="83" t="n">
-        <v>0.0243</v>
-      </c>
-      <c r="P15" s="83" t="n">
-        <v>0.027</v>
-      </c>
-      <c r="Q15" s="84">
-        <f>IF(OR(O15="",P15=""),"",SQRT(0.5*(O15^2+P15^2)))</f>
-        <v/>
-      </c>
-      <c r="R15" s="75">
-        <f>IF(OR(G15="",$G$14="",$G$14=0),"",G15/$G$14)</f>
-        <v/>
-      </c>
-      <c r="S15" s="111">
-        <f>IF(OR(M15="",$M$14=""),"",M15-$M$14)</f>
-        <v/>
-      </c>
-      <c r="T15" s="81" t="inlineStr">
-        <is>
-          <t>cap 1, re-seat #2 (first: 1168us area730 fill0.66 sigma0.0243). Repeats to 5% area, 0.00 fill, 6% sigma.  flux 142</t>
-        </is>
-      </c>
-      <c r="U15" s="126" t="n">
-        <v>0.075</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="80" t="inlineStr">
-        <is>
-          <t>drop</t>
-        </is>
-      </c>
-      <c r="B16" s="133" t="inlineStr">
-        <is>
-          <t>Kingbright</t>
-        </is>
-      </c>
-      <c r="C16" s="85" t="n">
-        <v>20</v>
-      </c>
-      <c r="D16" s="86" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E16" s="86">
-        <f>IF($B$5="inward",C16-2*D16,C16)</f>
-        <v/>
-      </c>
-      <c r="F16" s="86">
-        <f>IF(OR(E16="",$B$4=""),"",E16/2-$B$4)</f>
-        <v/>
-      </c>
-      <c r="G16" s="74" t="n">
-        <v>1042</v>
-      </c>
-      <c r="H16" s="74" t="n">
-        <v>201.8</v>
-      </c>
-      <c r="I16" s="72" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="74" t="n">
-        <v>608</v>
-      </c>
-      <c r="K16" s="74" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" s="79" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="M16" s="79" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="N16" s="80">
-        <f>IF(OR(K16="",L16="",M16=""),"",IF(AND(K16=1,L16&gt;=0.9,L16&lt;=1.1,M16&gt;=0.70),"pass","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="O16" s="83" t="n">
-        <v>0.026</v>
-      </c>
-      <c r="P16" s="83" t="n">
-        <v>0.0334</v>
-      </c>
-      <c r="Q16" s="84">
-        <f>IF(OR(O16="",P16=""),"",SQRT(0.5*(O16^2+P16^2)))</f>
-        <v/>
-      </c>
-      <c r="R16" s="75">
-        <f>IF(OR(G16="",$G$14="",$G$14=0),"",G16/$G$14)</f>
-        <v/>
-      </c>
-      <c r="S16" s="111">
-        <f>IF(OR(M16="",$M$14=""),"",M16-$M$14)</f>
-        <v/>
-      </c>
-      <c r="T16" s="123" t="inlineStr">
-        <is>
-          <t>DROPPED 2026-09-04. 0.5 mm measured worse than 0.4 mm at identical transmitted flux, i.e. cap variation not thickness. Ladder reduced to 0.2 / 0.4 mm with REPLICATE caps instead.</t>
-        </is>
-      </c>
-      <c r="U16" s="126" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="112" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="B17" s="133" t="inlineStr">
-        <is>
-          <t>Kingbright</t>
-        </is>
-      </c>
-      <c r="C17" s="85" t="n">
-        <v>25</v>
-      </c>
-      <c r="D17" s="86" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E17" s="86">
-        <f>IF($B$5="inward",C17-2*D17,C17)</f>
-        <v/>
-      </c>
-      <c r="F17" s="86">
-        <f>IF(OR(E17="",$B$4=""),"",E17/2-$B$4)</f>
-        <v/>
-      </c>
-      <c r="G17" s="113">
-        <f>IFERROR(A_Bench!F16,"")</f>
-        <v/>
-      </c>
-      <c r="H17" s="113">
-        <f>IFERROR(A_Bench!G16,"")</f>
-        <v/>
-      </c>
-      <c r="I17" s="114">
-        <f>IFERROR(A_Bench!H16,"")</f>
-        <v/>
-      </c>
-      <c r="J17" s="113">
-        <f>IFERROR(A_Bench!K16,"")</f>
-        <v/>
-      </c>
-      <c r="K17" s="113">
-        <f>IFERROR(A_Bench!M16,"")</f>
-        <v/>
-      </c>
-      <c r="L17" s="115">
-        <f>IFERROR(A_Bench!N16,"")</f>
-        <v/>
-      </c>
-      <c r="M17" s="115">
-        <f>IFERROR(A_Bench!U16,"")</f>
-        <v/>
-      </c>
-      <c r="N17" s="80">
-        <f>IF(OR(K17="",L17="",M17=""),"",IF(AND(K17=1,L17&gt;=0.9,L17&lt;=1.1,M17&gt;=0.70),"pass","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="O17" s="116">
-        <f>IFERROR(A_Bench!P16,"")</f>
-        <v/>
-      </c>
-      <c r="P17" s="116">
-        <f>IFERROR(A_Bench!Q16,"")</f>
-        <v/>
-      </c>
-      <c r="Q17" s="84">
-        <f>IF(OR(O17="",P17=""),"",SQRT(0.5*(O17^2+P17^2)))</f>
-        <v/>
-      </c>
-      <c r="R17" s="75">
-        <f>IF(OR(G17="",$G$17="",$G$17=0),"",G17/$G$17)</f>
-        <v/>
-      </c>
-      <c r="S17" s="111">
-        <f>IF(OR(M17="",$M$17=""),"",M17-$M$17)</f>
-        <v/>
-      </c>
-      <c r="T17" s="81" t="n"/>
-      <c r="U17" s="127" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="80" t="n">
-        <v>1</v>
-      </c>
-      <c r="B18" s="133" t="inlineStr">
-        <is>
-          <t>Kingbright</t>
-        </is>
-      </c>
-      <c r="C18" s="85" t="n">
-        <v>25</v>
-      </c>
-      <c r="D18" s="86" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E18" s="86">
-        <f>IF($B$5="inward",C18-2*D18,C18)</f>
-        <v/>
-      </c>
-      <c r="F18" s="86">
-        <f>IF(OR(E18="",$B$4=""),"",E18/2-$B$4)</f>
-        <v/>
-      </c>
-      <c r="G18" s="74" t="n">
-        <v>1078</v>
-      </c>
-      <c r="H18" s="74" t="n">
-        <v>210.8</v>
-      </c>
-      <c r="I18" s="72" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="74" t="n">
-        <v>697</v>
-      </c>
-      <c r="K18" s="74" t="n">
-        <v>1</v>
-      </c>
-      <c r="L18" s="79" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M18" s="79" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="N18" s="80">
-        <f>IF(OR(K18="",L18="",M18=""),"",IF(AND(K18=1,L18&gt;=0.9,L18&lt;=1.1,M18&gt;=0.70),"pass","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="O18" s="83" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="P18" s="83" t="n">
-        <v>0.0215</v>
-      </c>
-      <c r="Q18" s="84">
-        <f>IF(OR(O18="",P18=""),"",SQRT(0.5*(O18^2+P18^2)))</f>
-        <v/>
-      </c>
-      <c r="R18" s="75">
-        <f>IF(OR(G18="",$G$17="",$G$17=0),"",G18/$G$17)</f>
-        <v/>
-      </c>
-      <c r="S18" s="111">
-        <f>IF(OR(M18="",$M$17=""),"",M18-$M$17)</f>
-        <v/>
-      </c>
-      <c r="T18" s="81" t="inlineStr">
-        <is>
-          <t>cap 1, re-seat #2 (first: 1078us area694 fill0.67 sigma0.0286). Area and fill identical; sigma moved 28% - the widest of the four re-seats today (8/6/5/28%), so sigma repeatability is ~10-15%, not the 5% the tightest suggested.  flux 136</t>
-        </is>
-      </c>
-      <c r="U18" s="126" t="n">
-        <v>0.07199999999999999</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="80" t="inlineStr">
-        <is>
-          <t>drop</t>
-        </is>
-      </c>
-      <c r="B19" s="133" t="inlineStr">
-        <is>
-          <t>Kingbright</t>
-        </is>
-      </c>
-      <c r="C19" s="85" t="n">
-        <v>25</v>
-      </c>
-      <c r="D19" s="86" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E19" s="86">
-        <f>IF($B$5="inward",C19-2*D19,C19)</f>
-        <v/>
-      </c>
-      <c r="F19" s="86">
-        <f>IF(OR(E19="",$B$4=""),"",E19/2-$B$4)</f>
-        <v/>
-      </c>
-      <c r="G19" s="74" t="n"/>
-      <c r="H19" s="74" t="n"/>
-      <c r="I19" s="72" t="n"/>
-      <c r="J19" s="74" t="n"/>
-      <c r="K19" s="74" t="n"/>
-      <c r="L19" s="79" t="n"/>
-      <c r="M19" s="79" t="n"/>
-      <c r="N19" s="80">
-        <f>IF(OR(K19="",L19="",M19=""),"",IF(AND(K19=1,L19&gt;=0.9,L19&lt;=1.1,M19&gt;=0.70),"pass","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="O19" s="83" t="n"/>
-      <c r="P19" s="83" t="n"/>
-      <c r="Q19" s="84">
-        <f>IF(OR(O19="",P19=""),"",SQRT(0.5*(O19^2+P19^2)))</f>
-        <v/>
-      </c>
-      <c r="R19" s="75">
-        <f>IF(OR(G19="",$G$17="",$G$17=0),"",G19/$G$17)</f>
-        <v/>
-      </c>
-      <c r="S19" s="111">
-        <f>IF(OR(M19="",$M$17=""),"",M19-$M$17)</f>
-        <v/>
-      </c>
-      <c r="T19" s="123" t="inlineStr">
-        <is>
-          <t>DROPPED 2026-09-04. 0.5 mm measured worse than 0.4 mm at identical transmitted flux, i.e. cap variation not thickness. Ladder reduced to 0.2 / 0.4 mm with REPLICATE caps instead.</t>
-        </is>
-      </c>
-      <c r="U19" s="126" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="98" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="B20" s="128" t="inlineStr">
-        <is>
-          <t>Everlight</t>
-        </is>
-      </c>
-      <c r="C20" s="100" t="n">
-        <v>20</v>
-      </c>
-      <c r="D20" s="101" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E20" s="101">
-        <f>IF($B$5="inward",C20-2*D20,C20)</f>
-        <v/>
-      </c>
-      <c r="F20" s="101">
-        <f>IF(OR(E20="",$B$4=""),"",E20/2-$B$4)</f>
-        <v/>
-      </c>
-      <c r="G20" s="102">
-        <f>IFERROR(A_Bench!F10,"")</f>
-        <v/>
-      </c>
-      <c r="H20" s="102">
-        <f>IFERROR(A_Bench!G10,"")</f>
-        <v/>
-      </c>
-      <c r="I20" s="103">
-        <f>IFERROR(A_Bench!H10,"")</f>
-        <v/>
-      </c>
-      <c r="J20" s="102">
-        <f>IFERROR(A_Bench!K10,"")</f>
-        <v/>
-      </c>
-      <c r="K20" s="102">
-        <f>IFERROR(A_Bench!M10,"")</f>
-        <v/>
-      </c>
-      <c r="L20" s="104">
-        <f>IFERROR(A_Bench!N10,"")</f>
-        <v/>
-      </c>
-      <c r="M20" s="104">
-        <f>IFERROR(A_Bench!U10,"")</f>
-        <v/>
-      </c>
-      <c r="N20" s="105">
-        <f>IF(OR(K20="",L20="",M20=""),"",IF(AND(K20=1,L20&gt;=0.9,L20&lt;=1.1,M20&gt;=0.70),"pass","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="O20" s="106">
-        <f>IFERROR(A_Bench!P10,"")</f>
-        <v/>
-      </c>
-      <c r="P20" s="106">
-        <f>IFERROR(A_Bench!Q10,"")</f>
-        <v/>
-      </c>
-      <c r="Q20" s="107">
-        <f>IF(OR(O20="",P20=""),"",SQRT(0.5*(O20^2+P20^2)))</f>
-        <v/>
-      </c>
-      <c r="R20" s="108">
-        <f>IF(OR(G20="",$G$20="",$G$20=0),"",G20/$G$20)</f>
-        <v/>
-      </c>
-      <c r="S20" s="109">
-        <f>IF(OR(M20="",$M$20=""),"",M20-$M$20)</f>
-        <v/>
-      </c>
-      <c r="T20" s="110" t="n"/>
-      <c r="U20" s="125" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="80" t="n">
-        <v>2</v>
-      </c>
-      <c r="B21" s="133" t="inlineStr">
-        <is>
-          <t>Everlight</t>
-        </is>
-      </c>
-      <c r="C21" s="85" t="n">
-        <v>20</v>
-      </c>
-      <c r="D21" s="86" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E21" s="86">
-        <f>IF($B$5="inward",C21-2*D21,C21)</f>
-        <v/>
-      </c>
-      <c r="F21" s="86">
-        <f>IF(OR(E21="",$B$4=""),"",E21/2-$B$4)</f>
-        <v/>
-      </c>
-      <c r="G21" s="74" t="n">
-        <v>3235</v>
-      </c>
-      <c r="H21" s="74" t="n">
-        <v>210.2</v>
-      </c>
-      <c r="I21" s="72" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="74" t="n">
-        <v>814</v>
-      </c>
-      <c r="K21" s="74" t="n">
-        <v>1</v>
-      </c>
-      <c r="L21" s="79" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="M21" s="79" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="N21" s="80">
-        <f>IF(OR(K21="",L21="",M21=""),"",IF(AND(K21=1,L21&gt;=0.9,L21&lt;=1.1,M21&gt;=0.70),"pass","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="O21" s="83" t="n">
-        <v>0.0163</v>
-      </c>
-      <c r="P21" s="83" t="n">
-        <v>0.0202</v>
-      </c>
-      <c r="Q21" s="84">
-        <f>IF(OR(O21="",P21=""),"",SQRT(0.5*(O21^2+P21^2)))</f>
-        <v/>
-      </c>
-      <c r="R21" s="75">
-        <f>IF(OR(G21="",$G$20="",$G$20=0),"",G21/$G$20)</f>
-        <v/>
-      </c>
-      <c r="S21" s="111">
-        <f>IF(OR(M21="",$M$20=""),"",M21-$M$20)</f>
-        <v/>
-      </c>
-      <c r="T21" s="81" t="inlineStr">
-        <is>
-          <t>cap 1. Lowest sigma of the session (0.0184), though statistically tied with XL 25/0.2 (0.0187) given ~10-15% sigma repeatability. Thickness buys +0.03 fill for 1.42x exposure.  flux 53</t>
-        </is>
-      </c>
-      <c r="U21" s="126" t="n">
-        <v>0.062</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="80" t="inlineStr">
-        <is>
-          <t>drop</t>
-        </is>
-      </c>
-      <c r="B22" s="133" t="inlineStr">
-        <is>
-          <t>Everlight</t>
-        </is>
-      </c>
-      <c r="C22" s="85" t="n">
-        <v>20</v>
-      </c>
-      <c r="D22" s="86" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E22" s="86">
-        <f>IF($B$5="inward",C22-2*D22,C22)</f>
-        <v/>
-      </c>
-      <c r="F22" s="86">
-        <f>IF(OR(E22="",$B$4=""),"",E22/2-$B$4)</f>
-        <v/>
-      </c>
-      <c r="G22" s="74" t="n"/>
-      <c r="H22" s="74" t="n"/>
-      <c r="I22" s="72" t="n"/>
-      <c r="J22" s="74" t="n"/>
-      <c r="K22" s="74" t="n"/>
-      <c r="L22" s="79" t="n"/>
-      <c r="M22" s="79" t="n"/>
-      <c r="N22" s="80">
-        <f>IF(OR(K22="",L22="",M22=""),"",IF(AND(K22=1,L22&gt;=0.9,L22&lt;=1.1,M22&gt;=0.70),"pass","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="O22" s="83" t="n"/>
-      <c r="P22" s="83" t="n"/>
-      <c r="Q22" s="84">
-        <f>IF(OR(O22="",P22=""),"",SQRT(0.5*(O22^2+P22^2)))</f>
-        <v/>
-      </c>
-      <c r="R22" s="75">
-        <f>IF(OR(G22="",$G$20="",$G$20=0),"",G22/$G$20)</f>
-        <v/>
-      </c>
-      <c r="S22" s="111">
-        <f>IF(OR(M22="",$M$20=""),"",M22-$M$20)</f>
-        <v/>
-      </c>
-      <c r="T22" s="123" t="inlineStr">
-        <is>
-          <t>DROPPED 2026-09-04. 0.5 mm measured worse than 0.4 mm at identical transmitted flux, i.e. cap variation not thickness. Ladder reduced to 0.2 / 0.4 mm with REPLICATE caps instead.</t>
-        </is>
-      </c>
-      <c r="U22" s="126" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="112" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="B23" s="133" t="inlineStr">
-        <is>
-          <t>Everlight</t>
-        </is>
-      </c>
-      <c r="C23" s="85" t="n">
-        <v>25</v>
-      </c>
-      <c r="D23" s="86" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E23" s="86">
-        <f>IF($B$5="inward",C23-2*D23,C23)</f>
-        <v/>
-      </c>
-      <c r="F23" s="86">
-        <f>IF(OR(E23="",$B$4=""),"",E23/2-$B$4)</f>
-        <v/>
-      </c>
-      <c r="G23" s="113">
-        <f>IFERROR(A_Bench!F14,"")</f>
-        <v/>
-      </c>
-      <c r="H23" s="113">
-        <f>IFERROR(A_Bench!G14,"")</f>
-        <v/>
-      </c>
-      <c r="I23" s="114">
-        <f>IFERROR(A_Bench!H14,"")</f>
-        <v/>
-      </c>
-      <c r="J23" s="113">
-        <f>IFERROR(A_Bench!K14,"")</f>
-        <v/>
-      </c>
-      <c r="K23" s="113">
-        <f>IFERROR(A_Bench!M14,"")</f>
-        <v/>
-      </c>
-      <c r="L23" s="115">
-        <f>IFERROR(A_Bench!N14,"")</f>
-        <v/>
-      </c>
-      <c r="M23" s="115">
-        <f>IFERROR(A_Bench!U14,"")</f>
-        <v/>
-      </c>
-      <c r="N23" s="80">
-        <f>IF(OR(K23="",L23="",M23=""),"",IF(AND(K23=1,L23&gt;=0.9,L23&lt;=1.1,M23&gt;=0.70),"pass","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="O23" s="116">
-        <f>IFERROR(A_Bench!P14,"")</f>
-        <v/>
-      </c>
-      <c r="P23" s="116">
-        <f>IFERROR(A_Bench!Q14,"")</f>
-        <v/>
-      </c>
-      <c r="Q23" s="84">
-        <f>IF(OR(O23="",P23=""),"",SQRT(0.5*(O23^2+P23^2)))</f>
-        <v/>
-      </c>
-      <c r="R23" s="75">
-        <f>IF(OR(G23="",$G$23="",$G$23=0),"",G23/$G$23)</f>
-        <v/>
-      </c>
-      <c r="S23" s="111">
-        <f>IF(OR(M23="",$M$23=""),"",M23-$M$23)</f>
-        <v/>
-      </c>
-      <c r="T23" s="81" t="n"/>
-      <c r="U23" s="127" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="80" t="n">
-        <v>2</v>
-      </c>
-      <c r="B24" s="133" t="inlineStr">
-        <is>
-          <t>Everlight</t>
-        </is>
-      </c>
-      <c r="C24" s="85" t="n">
-        <v>25</v>
-      </c>
-      <c r="D24" s="86" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E24" s="86">
-        <f>IF($B$5="inward",C24-2*D24,C24)</f>
-        <v/>
-      </c>
-      <c r="F24" s="86">
-        <f>IF(OR(E24="",$B$4=""),"",E24/2-$B$4)</f>
-        <v/>
-      </c>
-      <c r="G24" s="74" t="n">
-        <v>3756</v>
-      </c>
-      <c r="H24" s="74" t="n">
-        <v>215.4</v>
-      </c>
-      <c r="I24" s="72" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="74" t="n">
-        <v>910</v>
-      </c>
-      <c r="K24" s="74" t="n">
-        <v>1</v>
-      </c>
-      <c r="L24" s="79" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="M24" s="79" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="N24" s="80">
-        <f>IF(OR(K24="",L24="",M24=""),"",IF(AND(K24=1,L24&gt;=0.9,L24&lt;=1.1,M24&gt;=0.70),"pass","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="O24" s="83" t="n">
-        <v>0.0176</v>
-      </c>
-      <c r="P24" s="83" t="n">
-        <v>0.0288</v>
-      </c>
-      <c r="Q24" s="84">
-        <f>IF(OR(O24="",P24=""),"",SQRT(0.5*(O24^2+P24^2)))</f>
-        <v/>
-      </c>
-      <c r="R24" s="75">
-        <f>IF(OR(G24="",$G$23="",$G$23=0),"",G24/$G$23)</f>
-        <v/>
-      </c>
-      <c r="S24" s="111">
-        <f>IF(OR(M24="",$M$23=""),"",M24-$M$23)</f>
-        <v/>
-      </c>
-      <c r="T24" s="81" t="inlineStr">
-        <is>
-          <t>cap 1. Thickness adds +0.02 fill for 1.08x exposure - marginal, same as the other LEDs at 25 mm. Confirms: go 25 mm, skip the thick wall.  flux 52</t>
-        </is>
-      </c>
-      <c r="U24" s="126" t="n">
-        <v>0.058</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="80" t="inlineStr">
-        <is>
-          <t>drop</t>
-        </is>
-      </c>
-      <c r="B25" s="133" t="inlineStr">
-        <is>
-          <t>Everlight</t>
-        </is>
-      </c>
-      <c r="C25" s="85" t="n">
-        <v>25</v>
-      </c>
-      <c r="D25" s="86" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E25" s="86">
-        <f>IF($B$5="inward",C25-2*D25,C25)</f>
-        <v/>
-      </c>
-      <c r="F25" s="86">
-        <f>IF(OR(E25="",$B$4=""),"",E25/2-$B$4)</f>
-        <v/>
-      </c>
-      <c r="G25" s="74" t="n"/>
-      <c r="H25" s="74" t="n"/>
-      <c r="I25" s="72" t="n"/>
-      <c r="J25" s="74" t="n"/>
-      <c r="K25" s="74" t="n"/>
-      <c r="L25" s="79" t="n"/>
-      <c r="M25" s="79" t="n"/>
-      <c r="N25" s="80">
-        <f>IF(OR(K25="",L25="",M25=""),"",IF(AND(K25=1,L25&gt;=0.9,L25&lt;=1.1,M25&gt;=0.70),"pass","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="O25" s="83" t="n"/>
-      <c r="P25" s="83" t="n"/>
-      <c r="Q25" s="84">
-        <f>IF(OR(O25="",P25=""),"",SQRT(0.5*(O25^2+P25^2)))</f>
-        <v/>
-      </c>
-      <c r="R25" s="75">
-        <f>IF(OR(G25="",$G$23="",$G$23=0),"",G25/$G$23)</f>
-        <v/>
-      </c>
-      <c r="S25" s="111">
-        <f>IF(OR(M25="",$M$23=""),"",M25-$M$23)</f>
-        <v/>
-      </c>
-      <c r="T25" s="123" t="inlineStr">
-        <is>
-          <t>DROPPED 2026-09-04. 0.5 mm measured worse than 0.4 mm at identical transmitted flux, i.e. cap variation not thickness. Ladder reduced to 0.2 / 0.4 mm with REPLICATE caps instead.</t>
-        </is>
-      </c>
-      <c r="U25" s="126" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="98" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="B26" s="128" t="inlineStr">
-        <is>
-          <t>XL</t>
-        </is>
-      </c>
-      <c r="C26" s="100" t="n">
-        <v>20</v>
-      </c>
-      <c r="D26" s="101" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E26" s="101">
-        <f>IF($B$5="inward",C26-2*D26,C26)</f>
-        <v/>
-      </c>
-      <c r="F26" s="101">
-        <f>IF(OR(E26="",$B$4=""),"",E26/2-$B$4)</f>
-        <v/>
-      </c>
-      <c r="G26" s="102">
-        <f>IFERROR(A_Bench!F11,"")</f>
-        <v/>
-      </c>
-      <c r="H26" s="102">
-        <f>IFERROR(A_Bench!G11,"")</f>
-        <v/>
-      </c>
-      <c r="I26" s="103">
-        <f>IFERROR(A_Bench!H11,"")</f>
-        <v/>
-      </c>
-      <c r="J26" s="102">
-        <f>IFERROR(A_Bench!K11,"")</f>
-        <v/>
-      </c>
-      <c r="K26" s="102">
-        <f>IFERROR(A_Bench!M11,"")</f>
-        <v/>
-      </c>
-      <c r="L26" s="104">
-        <f>IFERROR(A_Bench!N11,"")</f>
-        <v/>
-      </c>
-      <c r="M26" s="104">
-        <f>IFERROR(A_Bench!U11,"")</f>
-        <v/>
-      </c>
-      <c r="N26" s="105">
-        <f>IF(OR(K26="",L26="",M26=""),"",IF(AND(K26=1,L26&gt;=0.9,L26&lt;=1.1,M26&gt;=0.70),"pass","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="O26" s="106">
-        <f>IFERROR(A_Bench!P11,"")</f>
-        <v/>
-      </c>
-      <c r="P26" s="106">
-        <f>IFERROR(A_Bench!Q11,"")</f>
-        <v/>
-      </c>
-      <c r="Q26" s="107">
-        <f>IF(OR(O26="",P26=""),"",SQRT(0.5*(O26^2+P26^2)))</f>
-        <v/>
-      </c>
-      <c r="R26" s="108">
-        <f>IF(OR(G26="",$G$26="",$G$26=0),"",G26/$G$26)</f>
-        <v/>
-      </c>
-      <c r="S26" s="109">
-        <f>IF(OR(M26="",$M$26=""),"",M26-$M$26)</f>
-        <v/>
-      </c>
-      <c r="T26" s="110" t="n"/>
-      <c r="U26" s="125" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="80" t="n">
-        <v>3</v>
-      </c>
-      <c r="B27" s="133" t="inlineStr">
-        <is>
-          <t>XL</t>
-        </is>
-      </c>
-      <c r="C27" s="85" t="n">
-        <v>20</v>
-      </c>
-      <c r="D27" s="86" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E27" s="86">
-        <f>IF($B$5="inward",C27-2*D27,C27)</f>
-        <v/>
-      </c>
-      <c r="F27" s="86">
-        <f>IF(OR(E27="",$B$4=""),"",E27/2-$B$4)</f>
-        <v/>
-      </c>
-      <c r="G27" s="74" t="n">
-        <v>7351</v>
-      </c>
-      <c r="H27" s="74" t="n">
-        <v>203.8</v>
-      </c>
-      <c r="I27" s="72" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" s="74" t="n">
-        <v>846</v>
-      </c>
-      <c r="K27" s="74" t="n">
-        <v>1</v>
-      </c>
-      <c r="L27" s="79" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M27" s="79" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="N27" s="80">
-        <f>IF(OR(K27="",L27="",M27=""),"",IF(AND(K27=1,L27&gt;=0.9,L27&lt;=1.1,M27&gt;=0.70),"pass","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="O27" s="83" t="n">
-        <v>0.0185</v>
-      </c>
-      <c r="P27" s="83" t="n">
-        <v>0.0309</v>
-      </c>
-      <c r="Q27" s="84">
-        <f>IF(OR(O27="",P27=""),"",SQRT(0.5*(O27^2+P27^2)))</f>
-        <v/>
-      </c>
-      <c r="R27" s="75">
-        <f>IF(OR(G27="",$G$26="",$G$26=0),"",G27/$G$26)</f>
-        <v/>
-      </c>
-      <c r="S27" s="111">
-        <f>IF(OR(M27="",$M$26=""),"",M27-$M$26)</f>
-        <v/>
-      </c>
-      <c r="T27" s="81" t="inlineStr">
-        <is>
-          <t>cap 1. FIRST BUILD TO PASS THE BLEND GATE: fill 0.85, lobe 0.059, blobs 1, w/h 1.01. Thickness cost only 1.23x here vs 2.10x for Kingbright on the SAME caps - a wide beam already takes a long oblique path through the shell, so extra wall adds proportionally less.  flux 23</t>
-        </is>
-      </c>
-      <c r="U27" s="126" t="n">
-        <v>0.059</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="80" t="inlineStr">
-        <is>
-          <t>drop</t>
-        </is>
-      </c>
-      <c r="B28" s="133" t="inlineStr">
-        <is>
-          <t>XL</t>
-        </is>
-      </c>
-      <c r="C28" s="85" t="n">
-        <v>20</v>
-      </c>
-      <c r="D28" s="86" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E28" s="86">
-        <f>IF($B$5="inward",C28-2*D28,C28)</f>
-        <v/>
-      </c>
-      <c r="F28" s="86">
-        <f>IF(OR(E28="",$B$4=""),"",E28/2-$B$4)</f>
-        <v/>
-      </c>
-      <c r="G28" s="74" t="n"/>
-      <c r="H28" s="74" t="n"/>
-      <c r="I28" s="72" t="n"/>
-      <c r="J28" s="74" t="n"/>
-      <c r="K28" s="74" t="n"/>
-      <c r="L28" s="79" t="n"/>
-      <c r="M28" s="79" t="n"/>
-      <c r="N28" s="80">
-        <f>IF(OR(K28="",L28="",M28=""),"",IF(AND(K28=1,L28&gt;=0.9,L28&lt;=1.1,M28&gt;=0.70),"pass","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="O28" s="83" t="n"/>
-      <c r="P28" s="83" t="n"/>
-      <c r="Q28" s="84">
-        <f>IF(OR(O28="",P28=""),"",SQRT(0.5*(O28^2+P28^2)))</f>
-        <v/>
-      </c>
-      <c r="R28" s="75">
-        <f>IF(OR(G28="",$G$26="",$G$26=0),"",G28/$G$26)</f>
-        <v/>
-      </c>
-      <c r="S28" s="111">
-        <f>IF(OR(M28="",$M$26=""),"",M28-$M$26)</f>
-        <v/>
-      </c>
-      <c r="T28" s="123" t="inlineStr">
-        <is>
-          <t>DROPPED 2026-09-04. 0.5 mm measured worse than 0.4 mm at identical transmitted flux, i.e. cap variation not thickness. Ladder reduced to 0.2 / 0.4 mm with REPLICATE caps instead.</t>
-        </is>
-      </c>
-      <c r="U28" s="126" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="112" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="B29" s="133" t="inlineStr">
-        <is>
-          <t>XL</t>
-        </is>
-      </c>
-      <c r="C29" s="85" t="n">
-        <v>25</v>
-      </c>
-      <c r="D29" s="86" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E29" s="86">
-        <f>IF($B$5="inward",C29-2*D29,C29)</f>
-        <v/>
-      </c>
-      <c r="F29" s="86">
-        <f>IF(OR(E29="",$B$4=""),"",E29/2-$B$4)</f>
-        <v/>
-      </c>
-      <c r="G29" s="113">
-        <f>IFERROR(A_Bench!F15,"")</f>
-        <v/>
-      </c>
-      <c r="H29" s="113">
-        <f>IFERROR(A_Bench!G15,"")</f>
-        <v/>
-      </c>
-      <c r="I29" s="114">
-        <f>IFERROR(A_Bench!H15,"")</f>
-        <v/>
-      </c>
-      <c r="J29" s="113">
-        <f>IFERROR(A_Bench!K15,"")</f>
-        <v/>
-      </c>
-      <c r="K29" s="113">
-        <f>IFERROR(A_Bench!M15,"")</f>
-        <v/>
-      </c>
-      <c r="L29" s="115">
-        <f>IFERROR(A_Bench!N15,"")</f>
-        <v/>
-      </c>
-      <c r="M29" s="115">
-        <f>IFERROR(A_Bench!U15,"")</f>
-        <v/>
-      </c>
-      <c r="N29" s="80">
-        <f>IF(OR(K29="",L29="",M29=""),"",IF(AND(K29=1,L29&gt;=0.9,L29&lt;=1.1,M29&gt;=0.70),"pass","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="O29" s="116">
-        <f>IFERROR(A_Bench!P15,"")</f>
-        <v/>
-      </c>
-      <c r="P29" s="116">
-        <f>IFERROR(A_Bench!Q15,"")</f>
-        <v/>
-      </c>
-      <c r="Q29" s="84">
-        <f>IF(OR(O29="",P29=""),"",SQRT(0.5*(O29^2+P29^2)))</f>
-        <v/>
-      </c>
-      <c r="R29" s="75">
-        <f>IF(OR(G29="",$G$29="",$G$29=0),"",G29/$G$29)</f>
-        <v/>
-      </c>
-      <c r="S29" s="111">
-        <f>IF(OR(M29="",$M$29=""),"",M29-$M$29)</f>
-        <v/>
-      </c>
-      <c r="T29" s="81" t="n"/>
-      <c r="U29" s="127" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="80" t="n">
-        <v>3</v>
-      </c>
-      <c r="B30" s="133" t="inlineStr">
-        <is>
-          <t>XL</t>
-        </is>
-      </c>
-      <c r="C30" s="85" t="n">
-        <v>25</v>
-      </c>
-      <c r="D30" s="86" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E30" s="86">
-        <f>IF($B$5="inward",C30-2*D30,C30)</f>
-        <v/>
-      </c>
-      <c r="F30" s="86">
-        <f>IF(OR(E30="",$B$4=""),"",E30/2-$B$4)</f>
-        <v/>
-      </c>
-      <c r="G30" s="74" t="n">
-        <v>8628</v>
-      </c>
-      <c r="H30" s="74" t="n">
-        <v>213.7</v>
-      </c>
-      <c r="I30" s="72" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="74" t="n">
-        <v>967</v>
-      </c>
-      <c r="K30" s="74" t="n">
-        <v>1</v>
-      </c>
-      <c r="L30" s="79" t="n">
-        <v>1</v>
-      </c>
-      <c r="M30" s="79" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N30" s="80">
-        <f>IF(OR(K30="",L30="",M30=""),"",IF(AND(K30=1,L30&gt;=0.9,L30&lt;=1.1,M30&gt;=0.70),"pass","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="O30" s="83" t="n">
-        <v>0.0206</v>
-      </c>
-      <c r="P30" s="83" t="n">
-        <v>0.0245</v>
-      </c>
-      <c r="Q30" s="84">
-        <f>IF(OR(O30="",P30=""),"",SQRT(0.5*(O30^2+P30^2)))</f>
-        <v/>
-      </c>
-      <c r="R30" s="75">
-        <f>IF(OR(G30="",$G$29="",$G$29=0),"",G30/$G$29)</f>
-        <v/>
-      </c>
-      <c r="S30" s="111">
-        <f>IF(OR(M30="",$M$29=""),"",M30-$M$29)</f>
-        <v/>
-      </c>
-      <c r="T30" s="81" t="inlineStr">
-        <is>
-          <t>cap 1. First attempt gave sigma 0.1856 (sv/su 3.4) while area/fill/lobe were identical - a rig disturbance mid-run, rejected and re-measured. Thickness adds nothing at 25 mm: same fill, same lobe, 5% more exposure.  flux 24</t>
-        </is>
-      </c>
-      <c r="U30" s="126" t="n">
-        <v>0.062</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="80" t="inlineStr">
-        <is>
-          <t>drop</t>
-        </is>
-      </c>
-      <c r="B31" s="133" t="inlineStr">
-        <is>
-          <t>XL</t>
-        </is>
-      </c>
-      <c r="C31" s="85" t="n">
-        <v>25</v>
-      </c>
-      <c r="D31" s="86" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E31" s="86">
-        <f>IF($B$5="inward",C31-2*D31,C31)</f>
-        <v/>
-      </c>
-      <c r="F31" s="86">
-        <f>IF(OR(E31="",$B$4=""),"",E31/2-$B$4)</f>
-        <v/>
-      </c>
-      <c r="G31" s="74" t="n"/>
-      <c r="H31" s="74" t="n"/>
-      <c r="I31" s="72" t="n"/>
-      <c r="J31" s="74" t="n"/>
-      <c r="K31" s="74" t="n"/>
-      <c r="L31" s="79" t="n"/>
-      <c r="M31" s="79" t="n"/>
-      <c r="N31" s="80">
-        <f>IF(OR(K31="",L31="",M31=""),"",IF(AND(K31=1,L31&gt;=0.9,L31&lt;=1.1,M31&gt;=0.70),"pass","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="O31" s="83" t="n"/>
-      <c r="P31" s="83" t="n"/>
-      <c r="Q31" s="84">
-        <f>IF(OR(O31="",P31=""),"",SQRT(0.5*(O31^2+P31^2)))</f>
-        <v/>
-      </c>
-      <c r="R31" s="75">
-        <f>IF(OR(G31="",$G$29="",$G$29=0),"",G31/$G$29)</f>
-        <v/>
-      </c>
-      <c r="S31" s="111">
-        <f>IF(OR(M31="",$M$29=""),"",M31-$M$29)</f>
-        <v/>
-      </c>
-      <c r="T31" s="123" t="inlineStr">
-        <is>
-          <t>DROPPED 2026-09-04. 0.5 mm measured worse than 0.4 mm at identical transmitted flux, i.e. cap variation not thickness. Ladder reduced to 0.2 / 0.4 mm with REPLICATE caps instead.</t>
-        </is>
-      </c>
-      <c r="U31" s="126" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="76" t="inlineStr">
-        <is>
-          <t>HOW TO READ THIS</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="91" t="inlineStr">
-        <is>
-          <t>Priority 1 is Kingbright and Vishay. They are the parts that RING (fill 0.77-0.82 and 0.67-0.69 at 0.2 mm) and the only ones with the light budget to pay for a thicker wall - 251-1186 us against XL's 6057. Kingbright first: it needs the smallest lift (0.82 -&gt; 0.85) and already has the study's best sigma.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="91" t="inlineStr">
-        <is>
-          <t>Priority 3 is XL, and only as a control. It already reads fill 0.99-1.08, so a thicker wall can only cost it light, and it has the least to spare. Its value is that it is already uniform, so its exposure-vs-wall curve is the cleanest measurement of the MATERIAL's attenuation per mm - which then predicts the cost for the others.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="91" t="inlineStr">
-        <is>
-          <t>Standoff is NOT a confound at these thicknesses. Going 0.2 -&gt; 0.5 mm on a 20 mm shell moves the wall 0.3 mm closer to the LEDs - against a cavity radius of ~10 mm, that is negligible. This is a clean test of scattering versus transmission: a thicker wall scatters more (better fill) and transmits less (more exposure). Exposure vs 0.2 mm is the price, Fill vs 0.2 mm is what you bought.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="91" t="inlineStr">
-        <is>
-          <t>Diameter and thickness interact differently per part. On the 2 mm caps, diameter helped Kingbright (fill 0.77 -&gt; 0.82, sigma 0.0230 -&gt; 0.0162), barely moved Vishay (0.67 -&gt; 0.69) and was irrelevant to XL (already ~1.0). Expect wall thickness to follow the same ordering: most useful where the beam is narrowest.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="91" t="inlineStr">
-        <is>
-          <t>Exposure vs 2 mm is the price. Fill vs 2 mm is what you bought. A row is only interesting if it buys enough fill to pass the gate without pricing itself out on smear - at ~1300 px/s per m/s, every 1000 us of exposure is 1.3 px of smear at 1 m/s.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="91" t="inlineStr">
-        <is>
-          <t>Do NOT re-measure the 0.2 mm rows here - they are pulled live from A_Bench and shown in grey. They will be blank until Test A run 3 is done, since the rig was torn down after run 2.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/LED_characterisation.xlsx
+++ b/LED_characterisation.xlsx
@@ -1878,7 +1878,6 @@
         </is>
       </c>
     </row>
-    <row r="102"/>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
@@ -1914,7 +1913,6 @@
         </is>
       </c>
     </row>
-    <row r="108"/>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
@@ -1957,7 +1955,6 @@
         </is>
       </c>
     </row>
-    <row r="115"/>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
@@ -9487,6 +9484,13 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>RUN 3 - 10 Sep, CORRIDOR (not the arena). Camera 1, filter fitted, focus as locked 9 Sep - NOT re-touched. INSTRUMENT CHANGE: blob selection is now PEAK-based, not area-based. A corridor wall reflection is dimmer but more SPREAD OUT, so the old max-by-pixels pick locks onto the reflection at the long exposures this sweep uses (at 120 ms: reflection 463 px/peak 157 vs marker 325 px/peak 204). Run-2 rows were arena, single source, so they are unaffected. VENUE CAVEAT: reflections are in frame (blobs=3 at 8 m) and the marker is not isolated from its surround, so ABSOLUTE exposures do not transfer to the arena. Build-to-build RANKING is the intended use and is robust to a common-mode surround term. MARKER SIZE UNEXPLAINED: resolved as a ~68 px disc at 8 m vs ~7 px geometric for a 25 mm cap. Not defocus (blur circle &lt;2.5 px for any plausible focus - would need focus at 52 mm), not saturation (clean at peak 211), not the sideways lobe (0 deg and 90 deg give rms_r 26.2 vs 24.8, i.e. unchanged). Most likely the LED plus an illuminated surround. OPEN.</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" s="66" t="inlineStr">
         <is>
@@ -9621,43 +9625,47 @@
         <v>1</v>
       </c>
       <c r="D7" s="129" t="n">
-        <v>6035</v>
+        <v>7140</v>
       </c>
       <c r="E7" s="129" t="n">
-        <v>208.7</v>
+        <v>211.6</v>
       </c>
       <c r="F7" s="134" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="129" t="n">
-        <v>2458</v>
+        <v>5535</v>
       </c>
       <c r="H7" s="129" t="n">
-        <v>3065</v>
+        <v>6690</v>
       </c>
       <c r="I7" s="129" t="n">
         <v>1</v>
       </c>
       <c r="J7" s="130" t="n">
-        <v>0.9</v>
+        <v>0.97</v>
       </c>
       <c r="K7" s="130" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="L7" s="131" t="n">
-        <v>0.121</v>
+        <v>0.029</v>
       </c>
       <c r="M7" s="132" t="n">
-        <v>0.0108</v>
+        <v>0.0344</v>
       </c>
       <c r="N7" s="132" t="n">
-        <v>0.0137</v>
+        <v>0.0408</v>
       </c>
       <c r="O7" s="107">
         <f>IF(OR(M7="",N7=""),"",SQRT(0.5*(M7^2+N7^2)))</f>
         <v/>
       </c>
-      <c r="P7" s="135" t="n"/>
+      <c r="P7" s="135" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="Q7" s="100">
         <f>IF(OR(C7="",G7=""),"",G7*C7^2)</f>
         <v/>
@@ -9679,19 +9687,19 @@
         <v>2</v>
       </c>
       <c r="D8" s="74" t="n">
-        <v>20617</v>
+        <v>17998</v>
       </c>
       <c r="E8" s="74" t="n">
-        <v>212.6</v>
+        <v>209.2</v>
       </c>
       <c r="F8" s="72" t="n">
         <v>0</v>
       </c>
       <c r="G8" s="74" t="n">
-        <v>1546</v>
+        <v>4812</v>
       </c>
       <c r="H8" s="74" t="n">
-        <v>1793</v>
+        <v>5705</v>
       </c>
       <c r="I8" s="74" t="n">
         <v>1</v>
@@ -9700,22 +9708,26 @@
         <v>0.98</v>
       </c>
       <c r="K8" s="79" t="n">
-        <v>1.2</v>
+        <v>1.51</v>
       </c>
       <c r="L8" s="126" t="n">
-        <v>0.081</v>
+        <v>0.037</v>
       </c>
       <c r="M8" s="83" t="n">
-        <v>0.0129</v>
+        <v>0.0216</v>
       </c>
       <c r="N8" s="83" t="n">
-        <v>0.0269</v>
+        <v>0.0378</v>
       </c>
       <c r="O8" s="84">
         <f>IF(OR(M8="",N8=""),"",SQRT(0.5*(M8^2+N8^2)))</f>
         <v/>
       </c>
-      <c r="P8" s="78" t="n"/>
+      <c r="P8" s="78" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="Q8" s="85">
         <f>IF(OR(C8="",G8=""),"",G8*C8^2)</f>
         <v/>
@@ -9737,43 +9749,47 @@
         <v>3</v>
       </c>
       <c r="D9" s="74" t="n">
-        <v>32215</v>
+        <v>38887</v>
       </c>
       <c r="E9" s="74" t="n">
-        <v>207.3</v>
+        <v>211.9</v>
       </c>
       <c r="F9" s="72" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="74" t="n">
-        <v>1186</v>
+        <v>4741</v>
       </c>
       <c r="H9" s="74" t="n">
-        <v>1350</v>
+        <v>5485</v>
       </c>
       <c r="I9" s="74" t="n">
         <v>1</v>
       </c>
       <c r="J9" s="79" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="K9" s="79" t="n">
-        <v>1.24</v>
+        <v>1.48</v>
       </c>
       <c r="L9" s="126" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.029</v>
       </c>
       <c r="M9" s="83" t="n">
-        <v>0.0113</v>
+        <v>0.0292</v>
       </c>
       <c r="N9" s="83" t="n">
-        <v>0.0183</v>
+        <v>0.0466</v>
       </c>
       <c r="O9" s="84">
         <f>IF(OR(M9="",N9=""),"",SQRT(0.5*(M9^2+N9^2)))</f>
         <v/>
       </c>
-      <c r="P9" s="78" t="n"/>
+      <c r="P9" s="78" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="Q9" s="85">
         <f>IF(OR(C9="",G9=""),"",G9*C9^2)</f>
         <v/>
@@ -9795,43 +9811,47 @@
         <v>4</v>
       </c>
       <c r="D10" s="74" t="n">
-        <v>50320</v>
+        <v>68488</v>
       </c>
       <c r="E10" s="74" t="n">
-        <v>213.5</v>
+        <v>212.9</v>
       </c>
       <c r="F10" s="72" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="74" t="n">
-        <v>1008</v>
+        <v>4663</v>
       </c>
       <c r="H10" s="74" t="n">
-        <v>1124</v>
+        <v>5375</v>
       </c>
       <c r="I10" s="74" t="n">
         <v>1</v>
       </c>
       <c r="J10" s="79" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="K10" s="79" t="n">
-        <v>1.02</v>
+        <v>1.47</v>
       </c>
       <c r="L10" s="126" t="n">
-        <v>0.064</v>
+        <v>0.025</v>
       </c>
       <c r="M10" s="83" t="n">
-        <v>0.0117</v>
+        <v>0.0257</v>
       </c>
       <c r="N10" s="83" t="n">
-        <v>0.0224</v>
+        <v>0.022</v>
       </c>
       <c r="O10" s="84">
         <f>IF(OR(M10="",N10=""),"",SQRT(0.5*(M10^2+N10^2)))</f>
         <v/>
       </c>
-      <c r="P10" s="78" t="n"/>
+      <c r="P10" s="78" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="Q10" s="85">
         <f>IF(OR(C10="",G10=""),"",G10*C10^2)</f>
         <v/>
@@ -9853,43 +9873,47 @@
         <v>5</v>
       </c>
       <c r="D11" s="74" t="n">
-        <v>63558</v>
+        <v>104018</v>
       </c>
       <c r="E11" s="74" t="n">
-        <v>212.2</v>
+        <v>212.5</v>
       </c>
       <c r="F11" s="72" t="n">
         <v>0</v>
       </c>
       <c r="G11" s="74" t="n">
-        <v>894</v>
+        <v>4639</v>
       </c>
       <c r="H11" s="74" t="n">
-        <v>991</v>
+        <v>5342</v>
       </c>
       <c r="I11" s="74" t="n">
         <v>1</v>
       </c>
       <c r="J11" s="79" t="n">
-        <v>0.97</v>
+        <v>1</v>
       </c>
       <c r="K11" s="79" t="n">
-        <v>0.86</v>
+        <v>1.47</v>
       </c>
       <c r="L11" s="126" t="n">
-        <v>0.052</v>
+        <v>0.026</v>
       </c>
       <c r="M11" s="83" t="n">
-        <v>0.0145</v>
+        <v>0.0108</v>
       </c>
       <c r="N11" s="83" t="n">
-        <v>0.024</v>
+        <v>0.0292</v>
       </c>
       <c r="O11" s="84">
         <f>IF(OR(M11="",N11=""),"",SQRT(0.5*(M11^2+N11^2)))</f>
         <v/>
       </c>
-      <c r="P11" s="78" t="n"/>
+      <c r="P11" s="78" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="Q11" s="85">
         <f>IF(OR(C11="",G11=""),"",G11*C11^2)</f>
         <v/>
@@ -9910,22 +9934,48 @@
       <c r="C12" s="137" t="n">
         <v>6</v>
       </c>
-      <c r="D12" s="74" t="n"/>
-      <c r="E12" s="74" t="n"/>
-      <c r="F12" s="72" t="n"/>
-      <c r="G12" s="74" t="n"/>
-      <c r="H12" s="74" t="n"/>
-      <c r="I12" s="74" t="n"/>
-      <c r="J12" s="79" t="n"/>
-      <c r="K12" s="79" t="n"/>
-      <c r="L12" s="126" t="n"/>
-      <c r="M12" s="83" t="n"/>
-      <c r="N12" s="83" t="n"/>
+      <c r="D12" s="74" t="n">
+        <v>148983</v>
+      </c>
+      <c r="E12" s="74" t="n">
+        <v>214.8</v>
+      </c>
+      <c r="F12" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="74" t="n">
+        <v>4625</v>
+      </c>
+      <c r="H12" s="74" t="n">
+        <v>5323</v>
+      </c>
+      <c r="I12" s="74" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" s="79" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" s="79" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="L12" s="126" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="M12" s="83" t="n">
+        <v>0.0254</v>
+      </c>
+      <c r="N12" s="83" t="n">
+        <v>0.0354</v>
+      </c>
       <c r="O12" s="84">
         <f>IF(OR(M12="",N12=""),"",SQRT(0.5*(M12^2+N12^2)))</f>
         <v/>
       </c>
-      <c r="P12" s="78" t="n"/>
+      <c r="P12" s="78" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="Q12" s="85">
         <f>IF(OR(C12="",G12=""),"",G12*C12^2)</f>
         <v/>
@@ -9942,22 +9992,48 @@
       <c r="C13" s="137" t="n">
         <v>7</v>
       </c>
-      <c r="D13" s="74" t="n"/>
-      <c r="E13" s="74" t="n"/>
-      <c r="F13" s="72" t="n"/>
-      <c r="G13" s="74" t="n"/>
-      <c r="H13" s="74" t="n"/>
-      <c r="I13" s="74" t="n"/>
-      <c r="J13" s="79" t="n"/>
-      <c r="K13" s="79" t="n"/>
-      <c r="L13" s="126" t="n"/>
-      <c r="M13" s="83" t="n"/>
-      <c r="N13" s="83" t="n"/>
+      <c r="D13" s="74" t="n">
+        <v>196562</v>
+      </c>
+      <c r="E13" s="74" t="n">
+        <v>214.6</v>
+      </c>
+      <c r="F13" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="74" t="n">
+        <v>4620</v>
+      </c>
+      <c r="H13" s="74" t="n">
+        <v>5313</v>
+      </c>
+      <c r="I13" s="74" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" s="79" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="K13" s="79" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="L13" s="126" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="M13" s="83" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="N13" s="83" t="n">
+        <v>0.0568</v>
+      </c>
       <c r="O13" s="84">
         <f>IF(OR(M13="",N13=""),"",SQRT(0.5*(M13^2+N13^2)))</f>
         <v/>
       </c>
-      <c r="P13" s="78" t="n"/>
+      <c r="P13" s="78" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="Q13" s="85">
         <f>IF(OR(C13="",G13=""),"",G13*C13^2)</f>
         <v/>
@@ -9974,22 +10050,48 @@
       <c r="C14" s="137" t="n">
         <v>8</v>
       </c>
-      <c r="D14" s="74" t="n"/>
-      <c r="E14" s="74" t="n"/>
-      <c r="F14" s="72" t="n"/>
-      <c r="G14" s="74" t="n"/>
-      <c r="H14" s="74" t="n"/>
-      <c r="I14" s="74" t="n"/>
-      <c r="J14" s="79" t="n"/>
-      <c r="K14" s="79" t="n"/>
-      <c r="L14" s="126" t="n"/>
-      <c r="M14" s="83" t="n"/>
-      <c r="N14" s="83" t="n"/>
+      <c r="D14" s="74" t="n">
+        <v>249985</v>
+      </c>
+      <c r="E14" s="74" t="n">
+        <v>211.1</v>
+      </c>
+      <c r="F14" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="74" t="n">
+        <v>4575</v>
+      </c>
+      <c r="H14" s="74" t="n">
+        <v>5282</v>
+      </c>
+      <c r="I14" s="74" t="n">
+        <v>2</v>
+      </c>
+      <c r="J14" s="79" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="K14" s="79" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="L14" s="126" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="M14" s="83" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="N14" s="83" t="n">
+        <v>0.0225</v>
+      </c>
       <c r="O14" s="84">
         <f>IF(OR(M14="",N14=""),"",SQRT(0.5*(M14^2+N14^2)))</f>
         <v/>
       </c>
-      <c r="P14" s="78" t="n"/>
+      <c r="P14" s="78" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="Q14" s="85">
         <f>IF(OR(C14="",G14=""),"",G14*C14^2)</f>
         <v/>
@@ -10001,7 +10103,11 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="133" t="n"/>
+      <c r="A15" s="133" t="inlineStr">
+        <is>
+          <t>RUN 3 RESULT. Power law over 2-8 m: n=1.906 (90 deg, rms resid 1.0%) and n=1.854 (0 deg, 2.2%). Anisotropy 90/0 = 1.95 +/- 0.08, NO distance trend. Exposure span 1-8 m = 35x (not 64x). n&lt;2 IS INSTRUMENTAL, NOT THE LED: inverse square 16.00 -&gt; 15.22 (partial resolution, PSF 76 px) -&gt; 14.58 (vignetting) vs 13.89 measured, 5% residual. The marker slid from r=430 px to r=658 px off-axis as it came in, so RADIAL POSITION WAS CONFOUNDED WITH RANGE. Do NOT rank builds on the exponent - rank on col S at matched distance. 1 m departs the power law (n=1.33/1.38): the marker becomes RESOLVED, surface brightness is conserved, so peak grows slower than flux. Fit gives PSF 76.0 px, effective emitter 17.8 mm behind a 25 mm cap.</t>
+        </is>
+      </c>
       <c r="B15" s="85" t="n"/>
       <c r="C15" s="137" t="n"/>
       <c r="D15" s="74" t="n"/>
@@ -10072,22 +10178,48 @@
       <c r="C17" s="137" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="74" t="n"/>
-      <c r="E17" s="74" t="n"/>
-      <c r="F17" s="72" t="n"/>
-      <c r="G17" s="74" t="n"/>
-      <c r="H17" s="74" t="n"/>
-      <c r="I17" s="74" t="n"/>
-      <c r="J17" s="79" t="n"/>
-      <c r="K17" s="79" t="n"/>
-      <c r="L17" s="126" t="n"/>
-      <c r="M17" s="83" t="n"/>
-      <c r="N17" s="83" t="n"/>
+      <c r="D17" s="74" t="n">
+        <v>3782</v>
+      </c>
+      <c r="E17" s="74" t="n">
+        <v>213.2</v>
+      </c>
+      <c r="F17" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="74" t="n">
+        <v>5635</v>
+      </c>
+      <c r="H17" s="74" t="n">
+        <v>6815</v>
+      </c>
+      <c r="I17" s="74" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" s="79" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="K17" s="79" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="L17" s="126" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="M17" s="83" t="n">
+        <v>0.0296</v>
+      </c>
+      <c r="N17" s="83" t="n">
+        <v>0.036</v>
+      </c>
       <c r="O17" s="84">
         <f>IF(OR(M17="",N17=""),"",SQRT(0.5*(M17^2+N17^2)))</f>
         <v/>
       </c>
-      <c r="P17" s="78" t="n"/>
+      <c r="P17" s="78" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="Q17" s="85">
         <f>IF(OR(C17="",G17=""),"",G17*C17^2)</f>
         <v/>
@@ -10104,22 +10236,48 @@
       <c r="C18" s="137" t="n">
         <v>2</v>
       </c>
-      <c r="D18" s="74" t="n"/>
-      <c r="E18" s="74" t="n"/>
-      <c r="F18" s="72" t="n"/>
-      <c r="G18" s="74" t="n"/>
-      <c r="H18" s="74" t="n"/>
-      <c r="I18" s="74" t="n"/>
-      <c r="J18" s="79" t="n"/>
-      <c r="K18" s="79" t="n"/>
-      <c r="L18" s="126" t="n"/>
-      <c r="M18" s="83" t="n"/>
-      <c r="N18" s="83" t="n"/>
+      <c r="D18" s="74" t="n">
+        <v>9860</v>
+      </c>
+      <c r="E18" s="74" t="n">
+        <v>205.5</v>
+      </c>
+      <c r="F18" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="74" t="n">
+        <v>4811</v>
+      </c>
+      <c r="H18" s="74" t="n">
+        <v>5697</v>
+      </c>
+      <c r="I18" s="74" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" s="79" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="K18" s="79" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="L18" s="126" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="M18" s="83" t="n">
+        <v>0.0237</v>
+      </c>
+      <c r="N18" s="83" t="n">
+        <v>0.0286</v>
+      </c>
       <c r="O18" s="84">
         <f>IF(OR(M18="",N18=""),"",SQRT(0.5*(M18^2+N18^2)))</f>
         <v/>
       </c>
-      <c r="P18" s="78" t="n"/>
+      <c r="P18" s="78" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="Q18" s="85">
         <f>IF(OR(C18="",G18=""),"",G18*C18^2)</f>
         <v/>
@@ -10136,22 +10294,48 @@
       <c r="C19" s="137" t="n">
         <v>3</v>
       </c>
-      <c r="D19" s="74" t="n"/>
-      <c r="E19" s="74" t="n"/>
-      <c r="F19" s="72" t="n"/>
-      <c r="G19" s="74" t="n"/>
-      <c r="H19" s="74" t="n"/>
-      <c r="I19" s="74" t="n"/>
-      <c r="J19" s="79" t="n"/>
-      <c r="K19" s="79" t="n"/>
-      <c r="L19" s="126" t="n"/>
-      <c r="M19" s="83" t="n"/>
-      <c r="N19" s="83" t="n"/>
+      <c r="D19" s="74" t="n">
+        <v>20400</v>
+      </c>
+      <c r="E19" s="74" t="n">
+        <v>212.1</v>
+      </c>
+      <c r="F19" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="74" t="n">
+        <v>4747</v>
+      </c>
+      <c r="H19" s="74" t="n">
+        <v>5524</v>
+      </c>
+      <c r="I19" s="74" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" s="79" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="K19" s="79" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="L19" s="126" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="M19" s="83" t="n">
+        <v>0.0144</v>
+      </c>
+      <c r="N19" s="83" t="n">
+        <v>0.0192</v>
+      </c>
       <c r="O19" s="84">
         <f>IF(OR(M19="",N19=""),"",SQRT(0.5*(M19^2+N19^2)))</f>
         <v/>
       </c>
-      <c r="P19" s="78" t="n"/>
+      <c r="P19" s="78" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="Q19" s="85">
         <f>IF(OR(C19="",G19=""),"",G19*C19^2)</f>
         <v/>
@@ -10168,22 +10352,48 @@
       <c r="C20" s="137" t="n">
         <v>4</v>
       </c>
-      <c r="D20" s="74" t="n"/>
-      <c r="E20" s="74" t="n"/>
-      <c r="F20" s="72" t="n"/>
-      <c r="G20" s="74" t="n"/>
-      <c r="H20" s="74" t="n"/>
-      <c r="I20" s="74" t="n"/>
-      <c r="J20" s="79" t="n"/>
-      <c r="K20" s="79" t="n"/>
-      <c r="L20" s="126" t="n"/>
-      <c r="M20" s="83" t="n"/>
-      <c r="N20" s="83" t="n"/>
+      <c r="D20" s="74" t="n">
+        <v>34998</v>
+      </c>
+      <c r="E20" s="74" t="n">
+        <v>209.3</v>
+      </c>
+      <c r="F20" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="74" t="n">
+        <v>4624</v>
+      </c>
+      <c r="H20" s="74" t="n">
+        <v>5346</v>
+      </c>
+      <c r="I20" s="74" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" s="79" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" s="79" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="L20" s="126" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="M20" s="83" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="N20" s="83" t="n">
+        <v>0.0237</v>
+      </c>
       <c r="O20" s="84">
         <f>IF(OR(M20="",N20=""),"",SQRT(0.5*(M20^2+N20^2)))</f>
         <v/>
       </c>
-      <c r="P20" s="78" t="n"/>
+      <c r="P20" s="78" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="Q20" s="85">
         <f>IF(OR(C20="",G20=""),"",G20*C20^2)</f>
         <v/>
@@ -10200,22 +10410,48 @@
       <c r="C21" s="137" t="n">
         <v>5</v>
       </c>
-      <c r="D21" s="74" t="n"/>
-      <c r="E21" s="74" t="n"/>
-      <c r="F21" s="72" t="n"/>
-      <c r="G21" s="74" t="n"/>
-      <c r="H21" s="74" t="n"/>
-      <c r="I21" s="74" t="n"/>
-      <c r="J21" s="79" t="n"/>
-      <c r="K21" s="79" t="n"/>
-      <c r="L21" s="126" t="n"/>
-      <c r="M21" s="83" t="n"/>
-      <c r="N21" s="83" t="n"/>
+      <c r="D21" s="74" t="n">
+        <v>51446</v>
+      </c>
+      <c r="E21" s="74" t="n">
+        <v>207.2</v>
+      </c>
+      <c r="F21" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="74" t="n">
+        <v>4529</v>
+      </c>
+      <c r="H21" s="74" t="n">
+        <v>5229</v>
+      </c>
+      <c r="I21" s="74" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" s="79" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="K21" s="79" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="L21" s="126" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="M21" s="83" t="n">
+        <v>0.0248</v>
+      </c>
+      <c r="N21" s="83" t="n">
+        <v>0.039</v>
+      </c>
       <c r="O21" s="84">
         <f>IF(OR(M21="",N21=""),"",SQRT(0.5*(M21^2+N21^2)))</f>
         <v/>
       </c>
-      <c r="P21" s="78" t="n"/>
+      <c r="P21" s="78" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="Q21" s="85">
         <f>IF(OR(C21="",G21=""),"",G21*C21^2)</f>
         <v/>
@@ -10232,22 +10468,48 @@
       <c r="C22" s="137" t="n">
         <v>6</v>
       </c>
-      <c r="D22" s="74" t="n"/>
-      <c r="E22" s="74" t="n"/>
-      <c r="F22" s="72" t="n"/>
-      <c r="G22" s="74" t="n"/>
-      <c r="H22" s="74" t="n"/>
-      <c r="I22" s="74" t="n"/>
-      <c r="J22" s="79" t="n"/>
-      <c r="K22" s="79" t="n"/>
-      <c r="L22" s="126" t="n"/>
-      <c r="M22" s="83" t="n"/>
-      <c r="N22" s="83" t="n"/>
+      <c r="D22" s="74" t="n">
+        <v>71995</v>
+      </c>
+      <c r="E22" s="74" t="n">
+        <v>209.9</v>
+      </c>
+      <c r="F22" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="74" t="n">
+        <v>4523</v>
+      </c>
+      <c r="H22" s="74" t="n">
+        <v>5208</v>
+      </c>
+      <c r="I22" s="74" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" s="79" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="K22" s="79" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="L22" s="126" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="M22" s="83" t="n">
+        <v>0.0333</v>
+      </c>
+      <c r="N22" s="83" t="n">
+        <v>0.0345</v>
+      </c>
       <c r="O22" s="84">
         <f>IF(OR(M22="",N22=""),"",SQRT(0.5*(M22^2+N22^2)))</f>
         <v/>
       </c>
-      <c r="P22" s="78" t="n"/>
+      <c r="P22" s="78" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="Q22" s="85">
         <f>IF(OR(C22="",G22=""),"",G22*C22^2)</f>
         <v/>
@@ -10264,22 +10526,48 @@
       <c r="C23" s="137" t="n">
         <v>7</v>
       </c>
-      <c r="D23" s="74" t="n"/>
-      <c r="E23" s="74" t="n"/>
-      <c r="F23" s="72" t="n"/>
-      <c r="G23" s="74" t="n"/>
-      <c r="H23" s="74" t="n"/>
-      <c r="I23" s="74" t="n"/>
-      <c r="J23" s="79" t="n"/>
-      <c r="K23" s="79" t="n"/>
-      <c r="L23" s="126" t="n"/>
-      <c r="M23" s="83" t="n"/>
-      <c r="N23" s="83" t="n"/>
+      <c r="D23" s="74" t="n">
+        <v>99216</v>
+      </c>
+      <c r="E23" s="74" t="n">
+        <v>213.1</v>
+      </c>
+      <c r="F23" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="74" t="n">
+        <v>4555</v>
+      </c>
+      <c r="H23" s="74" t="n">
+        <v>5235</v>
+      </c>
+      <c r="I23" s="74" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" s="79" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="K23" s="79" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="L23" s="126" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="M23" s="83" t="n">
+        <v>0.0134</v>
+      </c>
+      <c r="N23" s="83" t="n">
+        <v>0.0203</v>
+      </c>
       <c r="O23" s="84">
         <f>IF(OR(M23="",N23=""),"",SQRT(0.5*(M23^2+N23^2)))</f>
         <v/>
       </c>
-      <c r="P23" s="78" t="n"/>
+      <c r="P23" s="78" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="Q23" s="85">
         <f>IF(OR(C23="",G23=""),"",G23*C23^2)</f>
         <v/>
@@ -10296,27 +10584,57 @@
       <c r="C24" s="137" t="n">
         <v>8</v>
       </c>
-      <c r="D24" s="74" t="n"/>
-      <c r="E24" s="74" t="n"/>
-      <c r="F24" s="72" t="n"/>
-      <c r="G24" s="74" t="n"/>
-      <c r="H24" s="74" t="n"/>
-      <c r="I24" s="74" t="n"/>
-      <c r="J24" s="79" t="n"/>
-      <c r="K24" s="79" t="n"/>
-      <c r="L24" s="126" t="n"/>
-      <c r="M24" s="83" t="n"/>
-      <c r="N24" s="83" t="n"/>
+      <c r="D24" s="74" t="n">
+        <v>131282</v>
+      </c>
+      <c r="E24" s="74" t="n">
+        <v>213.6</v>
+      </c>
+      <c r="F24" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="74" t="n">
+        <v>4530</v>
+      </c>
+      <c r="H24" s="74" t="n">
+        <v>5193</v>
+      </c>
+      <c r="I24" s="74" t="n">
+        <v>3</v>
+      </c>
+      <c r="J24" s="79" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" s="79" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="L24" s="126" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="M24" s="83" t="n">
+        <v>0.0321</v>
+      </c>
+      <c r="N24" s="83" t="n">
+        <v>0.0352</v>
+      </c>
       <c r="O24" s="84">
         <f>IF(OR(M24="",N24=""),"",SQRT(0.5*(M24^2+N24^2)))</f>
         <v/>
       </c>
-      <c r="P24" s="78" t="n"/>
+      <c r="P24" s="78" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="Q24" s="85">
         <f>IF(OR(C24="",G24=""),"",G24*C24^2)</f>
         <v/>
       </c>
-      <c r="R24" s="81" t="n"/>
+      <c r="R24" s="81" t="inlineStr">
+        <is>
+          <t>RUN 3 corridor. blobs=3. DRIFT CHECK: repeated at end of session -&gt; 126458 us vs 131282 us (-3.7%, within the 3.2% placement repeatability). NO battery droop; the fitted exponent is real.</t>
+        </is>
+      </c>
       <c r="S24" s="140">
         <f>IF(OR(D24="",D17=""),"",D24/D17)</f>
         <v/>

--- a/LED_characterisation.xlsx
+++ b/LED_characterisation.xlsx
@@ -9446,7 +9446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S66"/>
+  <dimension ref="A1:U66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -9609,6 +9609,18 @@
         <is>
           <t>Exp / exp(1 m)
 (battery-independent)</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Exp for marginal
+detection (us)</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>E_min / E_210
+(measured)</t>
         </is>
       </c>
     </row>
